--- a/tracker.xlsx
+++ b/tracker.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Tracker" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Tracker'!$A$1:$L$234</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Tracker'!$A$1:$M$234</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L234"/>
+  <dimension ref="A1:M234"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -440,6 +440,7 @@
     <col width="22" customWidth="1" min="10" max="10"/>
     <col width="13" customWidth="1" min="11" max="11"/>
     <col width="50" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -503,6 +504,11 @@
           <t>Notes</t>
         </is>
       </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Cover Letter Needed</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -540,6 +546,11 @@
           <t>Consider for Brett Kollman referral if applying here instead of Data Engineer post; Source: Direct / referral</t>
         </is>
       </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -572,6 +583,11 @@
           <t>Source: Greenhouse</t>
         </is>
       </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -609,6 +625,11 @@
           <t>Source: Greenhouse</t>
         </is>
       </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -641,6 +662,11 @@
           <t>Source: Greenhouse</t>
         </is>
       </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -673,6 +699,11 @@
           <t>Source: Greenhouse</t>
         </is>
       </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -705,6 +736,11 @@
           <t>Source: Greenhouse</t>
         </is>
       </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -737,6 +773,11 @@
           <t>Source: Greenhouse</t>
         </is>
       </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -769,6 +810,11 @@
           <t>Source: Greenhouse</t>
         </is>
       </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -801,6 +847,11 @@
           <t>Source: Greenhouse</t>
         </is>
       </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -833,6 +884,11 @@
           <t>Source: Greenhouse</t>
         </is>
       </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -865,6 +921,11 @@
           <t>Source: Greenhouse</t>
         </is>
       </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -897,6 +958,11 @@
           <t>Source: Greenhouse</t>
         </is>
       </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>No field</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -929,6 +995,11 @@
           <t>Source: Greenhouse</t>
         </is>
       </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>No field</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -961,6 +1032,11 @@
           <t>Source: Greenhouse</t>
         </is>
       </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>No field</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -993,6 +1069,11 @@
           <t>Source: Greenhouse</t>
         </is>
       </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>No field</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1025,6 +1106,11 @@
           <t>Source: Greenhouse</t>
         </is>
       </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1057,6 +1143,11 @@
           <t>Source: Greenhouse</t>
         </is>
       </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1089,6 +1180,11 @@
           <t>Source: Greenhouse</t>
         </is>
       </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1121,6 +1217,11 @@
           <t>Source: Greenhouse</t>
         </is>
       </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1153,6 +1254,11 @@
           <t>Source: Greenhouse</t>
         </is>
       </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1185,6 +1291,11 @@
           <t>Source: Greenhouse</t>
         </is>
       </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>No field</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1217,6 +1328,11 @@
           <t>Source: Greenhouse</t>
         </is>
       </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1249,6 +1365,11 @@
           <t>Source: Greenhouse</t>
         </is>
       </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1281,6 +1402,11 @@
           <t>Source: Greenhouse</t>
         </is>
       </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1313,6 +1439,11 @@
           <t>Source: Greenhouse</t>
         </is>
       </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>No field</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1345,6 +1476,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1377,6 +1513,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1409,6 +1550,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1441,6 +1587,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1473,6 +1624,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1505,6 +1661,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1537,6 +1698,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1569,6 +1735,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1601,6 +1772,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1633,6 +1809,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1665,6 +1846,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1697,6 +1883,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1729,6 +1920,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1761,6 +1957,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1793,6 +1994,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1825,6 +2031,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1857,6 +2068,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1889,6 +2105,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1921,6 +2142,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1953,6 +2179,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1985,6 +2216,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2017,6 +2253,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2049,6 +2290,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2081,6 +2327,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2113,6 +2364,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2145,6 +2401,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2177,6 +2438,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2209,6 +2475,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2241,6 +2512,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2273,6 +2549,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2305,6 +2586,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2337,6 +2623,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2369,6 +2660,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2401,6 +2697,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2433,6 +2734,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2465,6 +2771,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2497,6 +2808,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2529,6 +2845,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2561,6 +2882,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2593,6 +2919,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2625,6 +2956,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2657,6 +2993,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2689,6 +3030,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2721,6 +3067,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2753,6 +3104,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2785,6 +3141,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2817,6 +3178,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2849,6 +3215,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2881,6 +3252,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2913,6 +3289,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2945,6 +3326,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2977,6 +3363,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3009,6 +3400,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3041,6 +3437,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3073,6 +3474,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3105,6 +3511,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3137,6 +3548,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3169,6 +3585,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3201,6 +3622,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3233,6 +3659,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3265,6 +3696,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3297,6 +3733,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3329,6 +3770,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3361,6 +3807,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3393,6 +3844,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3425,6 +3881,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3457,6 +3918,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3489,6 +3955,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3521,6 +3992,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3553,6 +4029,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3585,6 +4066,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3617,6 +4103,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3649,6 +4140,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3681,6 +4177,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3713,6 +4214,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -3745,6 +4251,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -3777,6 +4288,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -3809,6 +4325,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -3841,6 +4362,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -3873,6 +4399,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -3905,6 +4436,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -3937,6 +4473,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -3969,6 +4510,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -4001,6 +4547,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -4033,6 +4584,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -4065,6 +4621,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -4097,6 +4658,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -4129,6 +4695,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -4161,6 +4732,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -4193,6 +4769,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -4225,6 +4806,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -4257,6 +4843,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -4289,6 +4880,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -4321,6 +4917,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -4353,6 +4954,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -4385,6 +4991,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -4417,6 +5028,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4449,6 +5065,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -4481,6 +5102,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -4513,6 +5139,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -4545,6 +5176,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>No field</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -4577,6 +5213,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -4609,6 +5250,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -4641,6 +5287,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -4673,6 +5324,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -4705,6 +5361,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -4737,6 +5398,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -4769,6 +5435,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -4801,6 +5472,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -4833,6 +5509,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -4865,6 +5546,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -4897,6 +5583,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -4929,6 +5620,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -4961,6 +5657,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -4993,6 +5694,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -5025,6 +5731,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -5057,6 +5768,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -5089,6 +5805,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -5121,6 +5842,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -5153,6 +5879,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -5185,6 +5916,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -5217,6 +5953,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -5249,6 +5990,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -5281,6 +6027,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -5313,6 +6064,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -5345,6 +6101,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -5377,6 +6138,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -5409,6 +6175,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -5441,6 +6212,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -5473,6 +6249,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -5505,6 +6286,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -5537,6 +6323,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -5569,6 +6360,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -5601,6 +6397,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -5633,6 +6434,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -5665,6 +6471,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -5697,6 +6508,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>No field</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -5729,6 +6545,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>No field</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -5761,6 +6582,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -5793,6 +6619,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -5825,6 +6656,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -5857,6 +6693,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -5889,6 +6730,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -5921,6 +6767,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -5953,6 +6804,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -5985,6 +6841,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -6017,6 +6878,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>No field</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -6049,6 +6915,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>No field</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -6081,6 +6952,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -6113,6 +6989,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -6145,6 +7026,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -6177,6 +7063,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -6209,6 +7100,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>No field</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -6241,6 +7137,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>No field</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -6273,6 +7174,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>No field</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -6305,6 +7211,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>No field</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -6337,6 +7248,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>No field</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -6369,6 +7285,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>No field</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -6401,6 +7322,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>No field</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -6433,6 +7359,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>No field</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -6465,6 +7396,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>No field</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -6497,6 +7433,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -6529,6 +7470,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M189" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -6561,6 +7507,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -6593,6 +7544,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -6625,6 +7581,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M192" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -6657,6 +7618,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M193" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -6689,6 +7655,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -6721,6 +7692,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -6753,6 +7729,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -6785,6 +7766,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -6817,6 +7803,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -6849,6 +7840,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -6881,6 +7877,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -6913,6 +7914,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -6945,6 +7951,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -6977,6 +7988,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -7009,6 +8025,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -7041,6 +8062,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -7073,6 +8099,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -7105,6 +8136,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -7137,6 +8173,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -7169,6 +8210,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -7201,6 +8247,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -7233,6 +8284,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -7265,6 +8321,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -7297,6 +8358,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>No field</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -7329,6 +8395,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -7361,6 +8432,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -7393,6 +8469,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M216" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -7425,6 +8506,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -7457,6 +8543,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -7489,6 +8580,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -7521,6 +8617,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>No field</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -7553,6 +8654,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -7585,6 +8691,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -7617,6 +8728,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -7649,6 +8765,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -7681,6 +8802,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -7713,6 +8839,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -7745,6 +8876,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>No field</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -7777,6 +8913,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>No field</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -7809,6 +8950,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>No field</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -7841,6 +8987,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>No field</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -7873,6 +9024,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M231" t="inlineStr">
+        <is>
+          <t>No field</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -7905,6 +9061,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M232" t="inlineStr">
+        <is>
+          <t>No field</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -7937,6 +9098,11 @@
           <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t>No field</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -7984,9 +9150,14 @@
           <t>Source: Gem; resume tailored, cover letter not started</t>
         </is>
       </c>
+      <c r="M234" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L234"/>
+  <autoFilter ref="A1:M234"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/tracker.xlsx
+++ b/tracker.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Tracker" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Tracker'!$A$1:$M$234</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Tracker'!$A$1:$O$234</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M234"/>
+  <dimension ref="A1:O234"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -441,6 +441,8 @@
     <col width="13" customWidth="1" min="11" max="11"/>
     <col width="50" customWidth="1" min="12" max="12"/>
     <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -509,6 +511,16 @@
           <t>Cover Letter Needed</t>
         </is>
       </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Has Extra Questions</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Effort</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -551,6 +563,16 @@
           <t>Unknown</t>
         </is>
       </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -588,6 +610,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -630,6 +662,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Short</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -667,6 +709,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -704,6 +756,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Short</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -741,6 +803,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -778,6 +850,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -815,6 +897,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -852,6 +944,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -889,6 +991,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -926,6 +1038,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Short</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -963,6 +1085,16 @@
           <t>No field</t>
         </is>
       </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1000,6 +1132,16 @@
           <t>No field</t>
         </is>
       </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Short</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1037,6 +1179,16 @@
           <t>No field</t>
         </is>
       </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1074,6 +1226,16 @@
           <t>No field</t>
         </is>
       </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1111,6 +1273,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1148,6 +1320,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1185,6 +1367,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1222,6 +1414,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1259,6 +1461,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1296,6 +1508,16 @@
           <t>No field</t>
         </is>
       </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1333,6 +1555,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1370,6 +1602,16 @@
           <t>Unknown</t>
         </is>
       </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1407,6 +1649,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1444,6 +1696,16 @@
           <t>No field</t>
         </is>
       </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1481,6 +1743,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1518,6 +1790,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1555,6 +1837,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1592,6 +1884,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Short</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1629,6 +1931,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1666,6 +1978,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1703,6 +2025,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1740,6 +2072,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1777,6 +2119,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1814,6 +2166,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1851,6 +2213,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Short</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1888,6 +2260,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1925,6 +2307,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1962,6 +2354,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1999,6 +2401,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2036,6 +2448,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2073,6 +2495,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2110,6 +2542,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2147,6 +2589,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2184,6 +2636,16 @@
           <t>Unknown</t>
         </is>
       </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2221,6 +2683,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2258,6 +2730,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2295,6 +2777,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2332,6 +2824,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2369,6 +2871,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2406,6 +2918,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2443,6 +2965,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2480,6 +3012,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2517,6 +3059,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2554,6 +3106,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2591,6 +3153,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2628,6 +3200,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2665,6 +3247,16 @@
           <t>Unknown</t>
         </is>
       </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2702,6 +3294,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2739,6 +3341,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2776,6 +3388,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2813,6 +3435,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2850,6 +3482,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2887,6 +3529,16 @@
           <t>Unknown</t>
         </is>
       </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2924,6 +3576,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2961,6 +3623,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2998,6 +3670,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3035,6 +3717,16 @@
           <t>Unknown</t>
         </is>
       </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3072,6 +3764,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3109,6 +3811,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3146,6 +3858,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3183,6 +3905,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3220,6 +3952,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3257,6 +3999,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3294,6 +4046,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3331,6 +4093,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3368,6 +4140,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3405,6 +4187,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3442,6 +4234,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3479,6 +4281,16 @@
           <t>Unknown</t>
         </is>
       </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3516,6 +4328,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3553,6 +4375,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3590,6 +4422,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3627,6 +4469,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3664,6 +4516,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3701,6 +4563,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3738,6 +4610,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3775,6 +4657,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3812,6 +4704,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3849,6 +4751,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3886,6 +4798,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3923,6 +4845,16 @@
           <t>Unknown</t>
         </is>
       </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3960,6 +4892,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3997,6 +4939,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -4034,6 +4986,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -4071,6 +5033,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -4108,6 +5080,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -4145,6 +5127,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -4182,6 +5174,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -4219,6 +5221,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -4256,6 +5268,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -4293,6 +5315,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -4330,6 +5362,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -4367,6 +5409,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -4404,6 +5456,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -4441,6 +5503,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -4478,6 +5550,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -4515,6 +5597,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -4552,6 +5644,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -4589,6 +5691,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -4626,6 +5738,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -4663,6 +5785,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -4700,6 +5832,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -4737,6 +5879,16 @@
           <t>Unknown</t>
         </is>
       </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -4774,6 +5926,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -4811,6 +5973,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -4848,6 +6020,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -4885,6 +6067,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -4922,6 +6114,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -4959,6 +6161,16 @@
           <t>Unknown</t>
         </is>
       </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -4996,6 +6208,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -5033,6 +6255,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -5070,6 +6302,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -5107,6 +6349,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -5144,6 +6396,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -5181,6 +6443,16 @@
           <t>No field</t>
         </is>
       </c>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -5218,6 +6490,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -5255,6 +6537,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -5292,6 +6584,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -5329,6 +6631,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -5366,6 +6678,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -5403,6 +6725,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -5440,6 +6772,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -5477,6 +6819,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -5514,6 +6866,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -5551,6 +6913,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -5588,6 +6960,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -5625,6 +7007,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -5662,6 +7054,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -5699,6 +7101,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -5736,6 +7148,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -5773,6 +7195,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -5810,6 +7242,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -5847,6 +7289,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -5884,6 +7336,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -5921,6 +7383,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -5958,6 +7430,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -5995,6 +7477,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -6032,6 +7524,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -6069,6 +7571,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -6106,6 +7618,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -6143,6 +7665,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -6180,6 +7712,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -6217,6 +7759,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -6254,6 +7806,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -6291,6 +7853,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O157" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -6328,6 +7900,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N158" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O158" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -6365,6 +7947,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N159" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O159" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -6402,6 +7994,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N160" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O160" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -6439,6 +8041,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N161" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O161" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -6476,6 +8088,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N162" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O162" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -6513,6 +8135,16 @@
           <t>No field</t>
         </is>
       </c>
+      <c r="N163" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O163" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -6550,6 +8182,16 @@
           <t>No field</t>
         </is>
       </c>
+      <c r="N164" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O164" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -6587,6 +8229,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N165" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O165" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -6624,6 +8276,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N166" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O166" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -6661,6 +8323,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N167" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O167" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -6698,6 +8370,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N168" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O168" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -6735,6 +8417,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N169" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O169" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -6772,6 +8464,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N170" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O170" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -6809,6 +8511,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N171" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O171" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -6846,6 +8558,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N172" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O172" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -6883,6 +8605,16 @@
           <t>No field</t>
         </is>
       </c>
+      <c r="N173" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="O173" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -6920,6 +8652,16 @@
           <t>No field</t>
         </is>
       </c>
+      <c r="N174" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="O174" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -6957,6 +8699,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N175" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O175" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -6994,6 +8746,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N176" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O176" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -7031,6 +8793,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N177" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O177" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -7068,6 +8840,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N178" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O178" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -7105,6 +8887,16 @@
           <t>No field</t>
         </is>
       </c>
+      <c r="N179" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O179" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -7142,6 +8934,16 @@
           <t>No field</t>
         </is>
       </c>
+      <c r="N180" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O180" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -7179,6 +8981,16 @@
           <t>No field</t>
         </is>
       </c>
+      <c r="N181" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O181" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -7216,6 +9028,16 @@
           <t>No field</t>
         </is>
       </c>
+      <c r="N182" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O182" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -7253,6 +9075,16 @@
           <t>No field</t>
         </is>
       </c>
+      <c r="N183" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O183" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -7290,6 +9122,16 @@
           <t>No field</t>
         </is>
       </c>
+      <c r="N184" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O184" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -7327,6 +9169,16 @@
           <t>No field</t>
         </is>
       </c>
+      <c r="N185" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O185" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -7364,6 +9216,16 @@
           <t>No field</t>
         </is>
       </c>
+      <c r="N186" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O186" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -7401,6 +9263,16 @@
           <t>No field</t>
         </is>
       </c>
+      <c r="N187" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O187" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -7438,6 +9310,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N188" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O188" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -7475,6 +9357,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N189" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O189" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -7512,6 +9404,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N190" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O190" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -7549,6 +9451,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N191" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O191" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -7586,6 +9498,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N192" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O192" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -7623,6 +9545,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N193" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O193" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -7660,6 +9592,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N194" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O194" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -7697,6 +9639,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N195" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O195" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -7734,6 +9686,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N196" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O196" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -7771,6 +9733,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N197" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O197" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -7808,6 +9780,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N198" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O198" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -7845,6 +9827,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N199" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O199" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -7882,6 +9874,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N200" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O200" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -7919,6 +9921,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N201" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O201" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -7956,6 +9968,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N202" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O202" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -7993,6 +10015,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N203" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O203" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -8030,6 +10062,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N204" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="O204" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -8067,6 +10109,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N205" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="O205" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -8104,6 +10156,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N206" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O206" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -8141,6 +10203,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N207" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O207" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -8178,6 +10250,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N208" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O208" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -8215,6 +10297,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N209" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O209" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -8252,6 +10344,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N210" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O210" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -8289,6 +10391,16 @@
           <t>Required</t>
         </is>
       </c>
+      <c r="N211" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O211" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -8326,6 +10438,16 @@
           <t>Required</t>
         </is>
       </c>
+      <c r="N212" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O212" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -8363,6 +10485,16 @@
           <t>No field</t>
         </is>
       </c>
+      <c r="N213" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O213" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -8400,6 +10532,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N214" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O214" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -8437,6 +10579,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N215" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O215" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -8474,6 +10626,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N216" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O216" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -8511,6 +10673,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N217" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O217" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -8548,6 +10720,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N218" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O218" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -8585,6 +10767,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N219" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O219" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -8622,6 +10814,16 @@
           <t>No field</t>
         </is>
       </c>
+      <c r="N220" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O220" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -8659,6 +10861,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N221" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O221" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -8696,6 +10908,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N222" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O222" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -8733,6 +10955,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N223" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O223" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -8770,6 +11002,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N224" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O224" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -8807,6 +11049,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N225" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O225" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -8844,6 +11096,16 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N226" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O226" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -8881,6 +11143,16 @@
           <t>No field</t>
         </is>
       </c>
+      <c r="N227" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="O227" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -8918,6 +11190,16 @@
           <t>No field</t>
         </is>
       </c>
+      <c r="N228" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="O228" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -8955,6 +11237,16 @@
           <t>No field</t>
         </is>
       </c>
+      <c r="N229" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="O229" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -8992,6 +11284,16 @@
           <t>No field</t>
         </is>
       </c>
+      <c r="N230" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="O230" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -9029,6 +11331,16 @@
           <t>No field</t>
         </is>
       </c>
+      <c r="N231" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="O231" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -9066,6 +11378,16 @@
           <t>No field</t>
         </is>
       </c>
+      <c r="N232" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="O232" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -9103,6 +11425,16 @@
           <t>No field</t>
         </is>
       </c>
+      <c r="N233" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="O233" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -9155,9 +11487,19 @@
           <t>Unknown</t>
         </is>
       </c>
+      <c r="N234" t="inlineStr">
+        <is>
+          <t>Short</t>
+        </is>
+      </c>
+      <c r="O234" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M234"/>
+  <autoFilter ref="A1:O234"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/tracker.xlsx
+++ b/tracker.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Tracker" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Tracker'!$A$1:$O$234</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Tracker'!$A$1:$O$232</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O234"/>
+  <dimension ref="A1:O232"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -550,7 +550,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>applied</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -597,7 +597,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>applied</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -608,11 +608,6 @@
       <c r="M3" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -624,32 +619,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PrizePicks</t>
+          <t>Catapult Sports</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Staff Machine Learning Engineer</t>
+          <t>Agentic AI Engineer</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://prizepicks.com/position?gh_jid=7618741003</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>$220k-$280k</t>
+          <t>https://job-boards.greenhouse.io/catapultsports/jobs/8083093</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>[C] Staff/P5 — stretch role, highest comp found.</t>
+          <t>[B] Athlete wearable/tracking data — strong domain fit. Listed as New York only, remote status unconfirmed — verify before applying.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>applied</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -662,14 +652,9 @@
           <t>Optional</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Short</t>
-        </is>
-      </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -681,22 +666,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Agentic AI Engineer</t>
+          <t>Senior ML/Data Engineer</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/catapultsports/jobs/8083093</t>
+          <t>https://job-boards.greenhouse.io/catapultsports/jobs/8083099</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>[B] Athlete wearable/tracking data — strong domain fit. Listed as New York only, remote status unconfirmed — verify before applying.</t>
+          <t>[B] Same caveat: New York location, remote status unconfirmed — verify before applying.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>applied</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -711,7 +696,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Short</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -723,27 +708,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Catapult Sports</t>
+          <t>GitLab</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Senior ML/Data Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/catapultsports/jobs/8083099</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8565469002</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>[B] Same caveat: New York location, remote status unconfirmed — verify before applying.</t>
+          <t>[B] Remote, US. Fully-remote company, strong AI/infra fit.</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>applied</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -754,11 +739,6 @@
       <c r="M6" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Short</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -775,22 +755,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Staff Backend Engineer, Database Automation (Go)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8565469002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8770702002</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>[B] Remote, US. Fully-remote company, strong AI/infra fit.</t>
+          <t>[B] Remote, US. Database/infra automation.</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>applied</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -801,11 +781,6 @@
       <c r="M7" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -822,22 +797,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Staff Backend Engineer (Ruby), AI Engineering: DAP Repository Flows</t>
+          <t>Senior Platform Engineer, GitLab Orbit</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8646573002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8771527002</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>[B] Remote, US.</t>
+          <t>[B] Remote, US. Platform engineering.</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>applied</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -848,11 +823,6 @@
       <c r="M8" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -869,22 +839,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Staff Backend Engineer, Database Automation (Go)</t>
+          <t>Backend Engineer, AI Engineering: Duo Chat</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8770702002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8698314002</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>[B] Remote, US. Database/infra automation.</t>
+          <t>[B] Remote, US.</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>applied</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -895,11 +865,6 @@
       <c r="M9" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -916,22 +881,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer, GitLab Orbit</t>
+          <t>Fullstack Engineer (TypeScript), AI Engineering: Duo Client SDK</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8771527002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8698330002</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>[B] Remote, US. Platform engineering.</t>
+          <t>[C] Remote, US. More frontend-leaning than your other targets.</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>applied</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -946,7 +911,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Short</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -958,27 +923,27 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GitLab</t>
+          <t>Grafana Labs</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Backend Engineer, AI Engineering: Duo Chat</t>
+          <t>Staff AI Engineer</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8698314002</t>
+          <t>https://job-boards.greenhouse.io/grafanalabs/jobs/6092955004</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>[B] Remote, US.</t>
+          <t>[B] United States (Remote).</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>applied</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -988,12 +953,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Optional</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>No field</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1005,27 +965,27 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>GitLab</t>
+          <t>Grafana Labs</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Fullstack Engineer (TypeScript), AI Engineering: Duo Client SDK</t>
+          <t>Staff Backend Engineer - Databases Tempo</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8698330002</t>
+          <t>https://job-boards.greenhouse.io/grafanalabs/jobs/5982444004</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>[C] Remote, US. More frontend-leaning than your other targets.</t>
+          <t>[B] United States (Remote). Observability/telemetry data infra.</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>applied</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1035,7 +995,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>No field</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1057,22 +1017,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Staff AI Engineer</t>
+          <t>Staff Backend Engineer - Mimir Query, Databases</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/grafanalabs/jobs/6092955004</t>
+          <t>https://job-boards.greenhouse.io/grafanalabs/jobs/6146604004</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>[B] United States (Remote).</t>
+          <t>[B] United States (Remote). Observability/telemetry data infra.</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>applied</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1083,11 +1043,6 @@
       <c r="M13" t="inlineStr">
         <is>
           <t>No field</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1104,22 +1059,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Staff Backend Engineer - Databases Tempo</t>
+          <t>Staff Software Engineer - Adaptive Telemetry, Databases</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/grafanalabs/jobs/5982444004</t>
+          <t>https://job-boards.greenhouse.io/grafanalabs/jobs/6108384004</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>[B] United States (Remote). Observability/telemetry data infra.</t>
+          <t>[B] United States (Remote).</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>applied</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1130,11 +1085,6 @@
       <c r="M14" t="inlineStr">
         <is>
           <t>No field</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>Short</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1146,22 +1096,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Grafana Labs</t>
+          <t>Elastic</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Staff Backend Engineer - Mimir Query, Databases</t>
+          <t>Platform Engineer - Kubernetes</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/grafanalabs/jobs/6146604004</t>
+          <t>https://jobs.elastic.co/jobs?gh_jid=8047349</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>[B] United States (Remote). Observability/telemetry data infra.</t>
+          <t>[B] United States. Elastic is a distributed-first company — K8s platform role builds directly on your Trustless Engineering experience.</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1176,12 +1126,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>No field</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>Optional</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1193,22 +1138,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Grafana Labs</t>
+          <t>Elastic</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Staff Software Engineer - Adaptive Telemetry, Databases</t>
+          <t>Agentic AI Engineer</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/grafanalabs/jobs/6108384004</t>
+          <t>https://jobs.elastic.co/jobs?gh_jid=8079636</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>[B] United States (Remote).</t>
+          <t>[B] United States. Distributed-first company.</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1223,39 +1168,39 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>No field</t>
+          <t>Optional</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Elastic</t>
+          <t>Vercel</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Platform Engineer - Kubernetes</t>
+          <t>Software Engineer - Data Platform</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://jobs.elastic.co/jobs?gh_jid=8047349</t>
+          <t>https://job-boards.greenhouse.io/vercel/jobs/6188400004</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>[B] United States. Elastic is a distributed-first company — K8s platform role builds directly on your Trustless Engineering experience.</t>
+          <t>[B] Remote - United States. Direct title match.</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1271,11 +1216,6 @@
       <c r="M17" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -1287,22 +1227,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Elastic</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Agentic AI Engineer</t>
+          <t>Staff Software Engineer (L4) Data Platform</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://jobs.elastic.co/jobs?gh_jid=8079636</t>
+          <t>https://job-boards.greenhouse.io/twilio/jobs/7782805</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>[B] United States. Distributed-first company.</t>
+          <t>[B] Remote - US. Direct title match.</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1320,36 +1260,31 @@
           <t>Optional</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>Long</t>
-        </is>
-      </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Vercel</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Software Engineer - Data Platform</t>
+          <t>Software Engineer, Platform Engineering (L2)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/vercel/jobs/6188400004</t>
+          <t>https://job-boards.greenhouse.io/twilio/jobs/8026207</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>[B] Remote - United States. Direct title match.</t>
+          <t>[C] Remote - US.</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1365,11 +1300,6 @@
       <c r="M19" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -1381,22 +1311,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Figma</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Staff Software Engineer (L4) Data Platform</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/twilio/jobs/7782805</t>
+          <t>https://boards.greenhouse.io/figma/jobs/6201407004</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>[B] Remote - US. Direct title match.</t>
+          <t>[B] SF / NYC / United States — remote option listed alongside hub cities, verify before applying.</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1411,39 +1341,39 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>No field</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Software Engineer, Platform Engineering (L2)</t>
+          <t>AI Engineer – Forward Deployed Engineering (AI FDE)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/twilio/jobs/8026207</t>
+          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8546367002</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>[C] Remote - US.</t>
+          <t>[C] United States (broad, likely remote-eligible w/ travel). Forward-deployed = customer-facing, different flavor than pure IC infra work.</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1459,11 +1389,6 @@
       <c r="M21" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -1475,22 +1400,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Figma</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Specialist Solutions Architect - Data Engineering &amp; Warehousing (Digital Native Business)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/figma/jobs/6201407004</t>
+          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8761732002</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>[B] SF / NYC / United States — remote option listed alongside hub cities, verify before applying.</t>
+          <t>[C] United States (broad). Customer-facing solutions architecture, not pure IC.</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1505,17 +1430,17 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>No field</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
@@ -1527,17 +1452,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>AI Engineer – Forward Deployed Engineering (AI FDE)</t>
+          <t>Specialist Solutions Architect - Data Engineering &amp; Warehousing (Financial Services)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8546367002</t>
+          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8692962002</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>[C] United States (broad, likely remote-eligible w/ travel). Forward-deployed = customer-facing, different flavor than pure IC infra work.</t>
+          <t>[C] United States (broad). Customer-facing solutions architecture, not pure IC.</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1553,11 +1478,6 @@
       <c r="M23" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -1569,22 +1489,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Data Engineering &amp; Warehousing (Digital Native Business)</t>
+          <t>Staff+ Software Engineer, Data Infrastructure</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8761732002</t>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5114768008</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>[C] United States (broad). Customer-facing solutions architecture, not pure IC.</t>
+          <t>[C] Remote-friendly but travel-required. Staff+ is a seniority stretch; every other Anthropic data/ML role requires a hub city (SF/NYC/Seattle) — skipped those as not remote.</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1599,39 +1519,39 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>No field</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Affirm</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Data Engineering &amp; Warehousing (Financial Services)</t>
+          <t>Machine Learning Engineer II (Underwriting ML)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8692962002</t>
+          <t>https://job-boards.greenhouse.io/affirm/jobs/7822387003</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>[C] United States (broad). Customer-facing solutions architecture, not pure IC.</t>
+          <t>[B] Remote US.</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1641,17 +1561,12 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Source: Greenhouse</t>
+          <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -1663,22 +1578,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Affirm</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Staff+ Software Engineer, Data Infrastructure</t>
+          <t>Model Risk Management Lead, Machine Learning</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/anthropic/jobs/5114768008</t>
+          <t>https://job-boards.greenhouse.io/affirm/jobs/7775353003</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>[C] Remote-friendly but travel-required. Staff+ is a seniority stretch; every other Anthropic data/ML role requires a hub city (SF/NYC/Seattle) — skipped those as not remote.</t>
+          <t>[B] Remote US.</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1688,44 +1603,39 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Source: Greenhouse</t>
+          <t>Source: Greenhouse/Lever</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>No field</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>Long</t>
+          <t>Optional</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Affirm</t>
+          <t>Airbnb</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II (Underwriting ML)</t>
+          <t>Principal Machine Learning Engineer- LLM Fine-tuning and Optimization</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/affirm/jobs/7822387003</t>
+          <t>https://careers.airbnb.com/positions/7955579?gh_jid=7955579</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>[B] Remote US.</t>
+          <t>[C] United States.</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1741,11 +1651,6 @@
       <c r="M27" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -1757,22 +1662,22 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Affirm</t>
+          <t>Airbnb</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Model Risk Management Lead, Machine Learning</t>
+          <t>Senior Data Scientist - Payments (Inference)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/affirm/jobs/7775353003</t>
+          <t>https://careers.airbnb.com/positions/8123037?gh_jid=8123037</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>[B] Remote US.</t>
+          <t>[C] Remote - USA.</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1792,7 +1697,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Short</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -1809,17 +1714,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Principal Machine Learning Engineer- LLM Fine-tuning and Optimization</t>
+          <t>Senior Machine Learning Engineer, Assistance Engineering</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://careers.airbnb.com/positions/7955579?gh_jid=7955579</t>
+          <t>https://careers.airbnb.com/positions/8014904?gh_jid=8014904</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>[C] United States.</t>
+          <t>[B] Remote-USA.</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1835,11 +1740,6 @@
       <c r="M29" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -1856,17 +1756,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - Payments (Inference)</t>
+          <t>Senior Machine Learning Engineer, Query Intelligence</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://careers.airbnb.com/positions/8123037?gh_jid=8123037</t>
+          <t>https://careers.airbnb.com/positions/8065789?gh_jid=8065789</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>[C] Remote - USA.</t>
+          <t>[B] United States.</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1882,11 +1782,6 @@
       <c r="M30" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>Short</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -1903,17 +1798,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Assistance Engineering</t>
+          <t>Senior Staff Data Engineer - Data Stewardship</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://careers.airbnb.com/positions/8014904?gh_jid=8014904</t>
+          <t>https://careers.airbnb.com/positions/7998356?gh_jid=7998356</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>[B] Remote-USA.</t>
+          <t>[B] United States.</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1929,11 +1824,6 @@
       <c r="M31" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -1950,12 +1840,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Query Intelligence</t>
+          <t>Senior Staff Data Engineer, Foundational Data</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://careers.airbnb.com/positions/8065789?gh_jid=8065789</t>
+          <t>https://careers.airbnb.com/positions/8224032?gh_jid=8224032</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1976,11 +1866,6 @@
       <c r="M32" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -1997,12 +1882,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Senior Staff Data Engineer - Data Stewardship</t>
+          <t>Senior Staff Machine Learning Engineer, Data &amp; Eval</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://careers.airbnb.com/positions/7998356?gh_jid=7998356</t>
+          <t>https://careers.airbnb.com/positions/6757302?gh_jid=6757302</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2023,11 +1908,6 @@
       <c r="M33" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -2044,17 +1924,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Senior Staff Data Engineer, Foundational Data</t>
+          <t>Senior Staff Machine Learning Engineer, Growth Platform Engineering</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://careers.airbnb.com/positions/8224032?gh_jid=8224032</t>
+          <t>https://careers.airbnb.com/positions/7747259?gh_jid=7747259</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>[B] United States.</t>
+          <t>[B] Remote - USA.</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2070,11 +1950,6 @@
       <c r="M34" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -2091,17 +1966,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Senior Staff Machine Learning Engineer, Data &amp; Eval</t>
+          <t>Senior Staff Machine Learning Engineer, Guest &amp; Host</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://careers.airbnb.com/positions/6757302?gh_jid=6757302</t>
+          <t>https://careers.airbnb.com/positions/7005605?gh_jid=7005605</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>[B] United States.</t>
+          <t>[B] Remote - USA.</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2121,7 +1996,7 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Short</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -2138,12 +2013,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Senior Staff Machine Learning Engineer, Growth Platform Engineering</t>
+          <t>Senior Staff Machine Learning Engineer, Post Training</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://careers.airbnb.com/positions/7747259?gh_jid=7747259</t>
+          <t>https://careers.airbnb.com/positions/7858738?gh_jid=7858738</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2164,11 +2039,6 @@
       <c r="M36" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -2185,12 +2055,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Senior Staff Machine Learning Engineer, Guest &amp; Host</t>
+          <t>Senior Staff Machine Learning Engineer, Trust</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://careers.airbnb.com/positions/7005605?gh_jid=7005605</t>
+          <t>https://careers.airbnb.com/positions/7592146?gh_jid=7592146</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2211,11 +2081,6 @@
       <c r="M37" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>Short</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -2232,12 +2097,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Senior Staff Machine Learning Engineer, Post Training</t>
+          <t>Staff Backend Engineer - Ads Platform</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://careers.airbnb.com/positions/7858738?gh_jid=7858738</t>
+          <t>https://careers.airbnb.com/positions/8074897?gh_jid=8074897</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2258,11 +2123,6 @@
       <c r="M38" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -2279,17 +2139,17 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Senior Staff Machine Learning Engineer, Trust</t>
+          <t>Staff Machine Learning Engineer, Traffic Intelligence</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://careers.airbnb.com/positions/7592146?gh_jid=7592146</t>
+          <t>https://careers.airbnb.com/positions/8129371?gh_jid=8129371</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>[B] Remote - USA.</t>
+          <t>[B] United States.</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2305,11 +2165,6 @@
       <c r="M39" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -2321,22 +2176,22 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Airbnb</t>
+          <t>Block</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Staff Backend Engineer - Ads Platform</t>
+          <t>Data Scientist, Payments</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://careers.airbnb.com/positions/8074897?gh_jid=8074897</t>
+          <t>http://block.xyz/careers/jobs/5214784008?gh_jid=5214784008</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>[B] Remote - USA.</t>
+          <t>[C] Bay Area, CA.</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2356,34 +2211,34 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Airbnb</t>
+          <t>Block</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Staff Machine Learning Engineer, Traffic Intelligence</t>
+          <t>Enterprise People Platform Engineer</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://careers.airbnb.com/positions/8129371?gh_jid=8129371</t>
+          <t>http://block.xyz/careers/jobs/5381210008?gh_jid=5381210008</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>[B] United States.</t>
+          <t>[B] Bay Area, CA.</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2403,12 +2258,12 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -2420,17 +2275,17 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Data Scientist, Payments</t>
+          <t>Senior Analytics Engineer, AI &amp; DX Analytics</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>http://block.xyz/careers/jobs/5214784008?gh_jid=5214784008</t>
+          <t>http://block.xyz/careers/jobs/5424561008?gh_jid=5424561008</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>[C] Bay Area, CA.</t>
+          <t>[B] Bay Area, CA.</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2467,17 +2322,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Enterprise People Platform Engineer</t>
+          <t>Senior Analytics Engineer, AI &amp; DX Analytics</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>http://block.xyz/careers/jobs/5381210008?gh_jid=5381210008</t>
+          <t>http://block.xyz/careers/jobs/5434325008?gh_jid=5434325008</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>[B] Bay Area, CA.</t>
+          <t>[B] New York, NY.</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2514,12 +2369,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer, AI &amp; DX Analytics</t>
+          <t>Senior Data Engineer, Risk</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>http://block.xyz/careers/jobs/5424561008?gh_jid=5424561008</t>
+          <t>http://block.xyz/careers/jobs/5281312008?gh_jid=5281312008</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2539,17 +2394,17 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
@@ -2561,17 +2416,17 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer, AI &amp; DX Analytics</t>
+          <t>Senior Data Scientist, Risk and Support</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>http://block.xyz/careers/jobs/5434325008?gh_jid=5434325008</t>
+          <t>http://block.xyz/careers/jobs/5418716008?gh_jid=5418716008</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>[B] New York, NY.</t>
+          <t>[C] Seattle, WA.</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2608,17 +2463,17 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Risk</t>
+          <t>Senior Data Scientist, Risk and Support</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>http://block.xyz/careers/jobs/5281312008?gh_jid=5281312008</t>
+          <t>http://block.xyz/careers/jobs/5412922008?gh_jid=5412922008</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>[B] Bay Area, CA.</t>
+          <t>[C] Bay Area, CA.</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2633,17 +2488,17 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Optional</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -2655,17 +2510,17 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Senior Data Scientist, Risk and Support</t>
+          <t>Senior ML/AI Modeler, Risk Automation Machine Learning</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>http://block.xyz/careers/jobs/5418716008?gh_jid=5418716008</t>
+          <t>http://block.xyz/careers/jobs/5394441008?gh_jid=5394441008</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>[C] Seattle, WA.</t>
+          <t>[B] Bay Area, CA.</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2702,17 +2557,17 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Senior Data Scientist, Risk and Support</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>http://block.xyz/careers/jobs/5412922008?gh_jid=5412922008</t>
+          <t>http://block.xyz/careers/jobs/5182994008?gh_jid=5182994008</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>[C] Bay Area, CA.</t>
+          <t>[B] New York, NY.</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2749,12 +2604,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Senior ML/AI Modeler, Risk Automation Machine Learning</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>http://block.xyz/careers/jobs/5394441008?gh_jid=5394441008</t>
+          <t>http://block.xyz/careers/jobs/5181749008?gh_jid=5181749008</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -2796,17 +2651,17 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Software Engineer, Data Platform</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>http://block.xyz/careers/jobs/5182994008?gh_jid=5182994008</t>
+          <t>http://block.xyz/careers/jobs/5381381008?gh_jid=5381381008</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>[B] New York, NY.</t>
+          <t>[B] Bay Area, CA.</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2843,12 +2698,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Staff Applied Machine Learning Engineer - Intelligent Data, Signals &amp; Systems</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>http://block.xyz/careers/jobs/5181749008?gh_jid=5181749008</t>
+          <t>http://block.xyz/careers/jobs/4959469008?gh_jid=4959469008</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -2890,17 +2745,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Platform</t>
+          <t>Staff Data Scientist, Pricing</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>http://block.xyz/careers/jobs/5381381008?gh_jid=5381381008</t>
+          <t>http://block.xyz/careers/jobs/5364922008?gh_jid=5364922008</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>[B] Bay Area, CA.</t>
+          <t>[C] Bay Area, CA.</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2937,17 +2792,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Staff Applied Machine Learning Engineer - Intelligent Data, Signals &amp; Systems</t>
+          <t>Staff Machine Learning Engineer (Modeling), Support</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>http://block.xyz/careers/jobs/4959469008?gh_jid=4959469008</t>
+          <t>http://block.xyz/careers/jobs/5431987008?gh_jid=5431987008</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>[B] Bay Area, CA.</t>
+          <t>[B] Seattle, WA.</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2984,17 +2839,17 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Staff Data Scientist, Pricing</t>
+          <t>Staff Product Data Scientist, Lending</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>http://block.xyz/careers/jobs/5364922008?gh_jid=5364922008</t>
+          <t>http://block.xyz/careers/jobs/5366281008?gh_jid=5366281008</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>[C] Bay Area, CA.</t>
+          <t>[B] New York, NY.</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3031,12 +2886,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Staff Machine Learning Engineer (Modeling), Support</t>
+          <t>Staff Product Data Scientist, Lending</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>http://block.xyz/careers/jobs/5431987008?gh_jid=5431987008</t>
+          <t>http://block.xyz/careers/jobs/5192640008?gh_jid=5192640008</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -3083,12 +2938,12 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>http://block.xyz/careers/jobs/5366281008?gh_jid=5366281008</t>
+          <t>http://block.xyz/careers/jobs/5366284008?gh_jid=5366284008</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>[B] New York, NY.</t>
+          <t>[B] San Francisco, CA.</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3120,22 +2975,22 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Block</t>
+          <t>Chime</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Staff Product Data Scientist, Lending</t>
+          <t>Data Scientist, Growth Product</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>http://block.xyz/careers/jobs/5192640008?gh_jid=5192640008</t>
+          <t>https://boards.greenhouse.io/chime/jobs/8586430002?gh_jid=8586430002</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>[B] Seattle, WA.</t>
+          <t>[C] San Francisco, CA.</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3150,39 +3005,39 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Block</t>
+          <t>Chime</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Staff Product Data Scientist, Lending</t>
+          <t>Senior AI/ML Engineer</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>http://block.xyz/careers/jobs/5366284008?gh_jid=5366284008</t>
+          <t>https://boards.greenhouse.io/chime/jobs/8569366002?gh_jid=8569366002</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>[B] San Francisco, CA.</t>
+          <t>[B] Chicago, IL; New York, NY; San Francisco, CA.</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3200,14 +3055,9 @@
           <t>Optional</t>
         </is>
       </c>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t>Long</t>
-        </is>
-      </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -3219,12 +3069,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Data Scientist, Growth Product</t>
+          <t>Senior Data Scientist, Organic Growth</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/chime/jobs/8586430002?gh_jid=8586430002</t>
+          <t>https://boards.greenhouse.io/chime/jobs/8790231002?gh_jid=8790231002</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -3244,17 +3094,12 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t>Unknown</t>
+          <t>Optional</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -3266,17 +3111,17 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer</t>
+          <t>Senior Mobile Cross Platform Engineer</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/chime/jobs/8569366002?gh_jid=8569366002</t>
+          <t>https://boards.greenhouse.io/chime/jobs/8604565002?gh_jid=8604565002</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>[B] Chicago, IL; New York, NY; San Francisco, CA.</t>
+          <t>[B] New York, NY; San Francisco, CA.</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -3292,11 +3137,6 @@
       <c r="M60" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
@@ -3313,17 +3153,17 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Senior Data Scientist, Organic Growth</t>
+          <t>Senior Software Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/chime/jobs/8790231002?gh_jid=8790231002</t>
+          <t>https://boards.greenhouse.io/chime/jobs/8505462002?gh_jid=8505462002</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>[C] San Francisco, CA.</t>
+          <t>[B] San Francisco, CA.</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -3339,11 +3179,6 @@
       <c r="M61" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
@@ -3360,17 +3195,17 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Senior Mobile Cross Platform Engineer</t>
+          <t>Senior Software Engineer, Machine Learning Platform</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/chime/jobs/8604565002?gh_jid=8604565002</t>
+          <t>https://boards.greenhouse.io/chime/jobs/8765684002?gh_jid=8765684002</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>[B] New York, NY; San Francisco, CA.</t>
+          <t>[B] San Francisco, CA.</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -3386,11 +3221,6 @@
       <c r="M62" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
@@ -3402,22 +3232,22 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Chime</t>
+          <t>Dropbox</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Engineering</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/chime/jobs/8505462002?gh_jid=8505462002</t>
+          <t>https://jobs.dropbox.com/listing/8211529?gh_jid=8211529</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>[B] San Francisco, CA.</t>
+          <t>[B] Remote - US: Select locations.</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -3432,39 +3262,39 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Chime</t>
+          <t>Epic Games</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Machine Learning Platform</t>
+          <t>Machine Learning Engineer, Memory</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/chime/jobs/8765684002?gh_jid=8765684002</t>
+          <t>https://epicgames.com/careers/jobs/6134271004?gh_jid=6134271004</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>[B] San Francisco, CA.</t>
+          <t>[B] Cary, NC.</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -3480,11 +3310,6 @@
       <c r="M64" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
@@ -3496,22 +3321,22 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Dropbox</t>
+          <t>Epic Games</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Principal AI Engineer, Unreal Assistant</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/8211529?gh_jid=8211529</t>
+          <t>https://epicgames.com/careers/jobs/6200780004?gh_jid=6200780004</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>[B] Remote - US: Select locations.</t>
+          <t>[C] Cary, NC.</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -3526,17 +3351,12 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr">
-        <is>
-          <t>Unknown</t>
+          <t>Optional</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -3548,17 +3368,17 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Memory</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://epicgames.com/careers/jobs/6134271004?gh_jid=6134271004</t>
+          <t>https://epicgames.com/careers/jobs/6117889004?gh_jid=6117889004</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>[B] Cary, NC.</t>
+          <t>[C] Cary, NC.</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -3574,11 +3394,6 @@
       <c r="M66" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
@@ -3595,17 +3410,17 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Principal AI Engineer, Unreal Assistant</t>
+          <t>Senior Machine Learning Engineer, Discovery Recommendations</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://epicgames.com/careers/jobs/6200780004?gh_jid=6200780004</t>
+          <t>https://epicgames.com/careers/jobs/5972880004?gh_jid=5972880004</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>[C] Cary, NC.</t>
+          <t>[B] Cary, NC.</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -3620,39 +3435,39 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Epic Games</t>
+          <t>Instacart</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Senior Machine Learning Engineer, Digital Twin Platform</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>https://epicgames.com/careers/jobs/6117889004?gh_jid=6117889004</t>
+          <t>https://instacart.careers/job/?gh_jid=8143145</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>[C] Cary, NC.</t>
+          <t>[B] US - Remote.</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3668,11 +3483,6 @@
       <c r="M68" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
@@ -3684,22 +3494,22 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Epic Games</t>
+          <t>Instacart</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Discovery Recommendations</t>
+          <t>Senior Machine Learning Engineer, Economist</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>https://epicgames.com/careers/jobs/5972880004?gh_jid=5972880004</t>
+          <t>https://instacart.careers/job/?gh_jid=8157736</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>[B] Cary, NC.</t>
+          <t>[B] US - Remote.</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3714,17 +3524,12 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr">
-        <is>
-          <t>Unknown</t>
+          <t>Optional</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -3736,12 +3541,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Digital Twin Platform</t>
+          <t>Senior Machine Learning Engineer II, Ads Response Prediction</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>https://instacart.careers/job/?gh_jid=8143145</t>
+          <t>https://instacart.careers/job/?gh_jid=7963838</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -3762,11 +3567,6 @@
       <c r="M70" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
@@ -3783,12 +3583,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Economist</t>
+          <t>Senior Machine Learning Engineer II, Search &amp; Recommendations Ranking</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>https://instacart.careers/job/?gh_jid=8157736</t>
+          <t>https://instacart.careers/job/?gh_jid=7565508</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -3809,11 +3609,6 @@
       <c r="M71" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
@@ -3830,12 +3625,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer II, Ads Response Prediction</t>
+          <t>Senior Machine Learning Engineer, Operations Research</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>https://instacart.careers/job/?gh_jid=7963838</t>
+          <t>https://instacart.careers/job/?gh_jid=7793089</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -3856,11 +3651,6 @@
       <c r="M72" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
@@ -3872,22 +3662,22 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Instacart</t>
+          <t>MongoDB</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer II, Search &amp; Recommendations Ranking</t>
+          <t>Senior Site Reliability Engineer, Fabric</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>https://instacart.careers/job/?gh_jid=7565508</t>
+          <t>https://www.mongodb.com/careers/job/?gh_jid=7727920</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>[B] US - Remote.</t>
+          <t>[B] Austin/NYC/SF.</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -3903,11 +3693,6 @@
       <c r="M73" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N73" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
@@ -3919,22 +3704,22 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Instacart</t>
+          <t>MongoDB</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Operations Research</t>
+          <t>Senior Site Reliability Engineer, Fleet Management</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>https://instacart.careers/job/?gh_jid=7793089</t>
+          <t>https://www.mongodb.com/careers/job/?gh_jid=7727873</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>[B] US - Remote.</t>
+          <t>[B] multiple US cities.</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -3950,11 +3735,6 @@
       <c r="M74" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
@@ -3971,17 +3751,17 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer, Fabric</t>
+          <t>Site Reliability Engineer, Infrastructure Security</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>https://www.mongodb.com/careers/job/?gh_jid=7727920</t>
+          <t>https://www.mongodb.com/careers/job/?gh_jid=7758610</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>[B] Austin/NYC/SF.</t>
+          <t>[B] Austin/NYC.</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -3997,11 +3777,6 @@
       <c r="M75" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
@@ -4018,12 +3793,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer, Fleet Management</t>
+          <t>Site Reliability Engineer, Atlas</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>https://www.mongodb.com/careers/job/?gh_jid=7727873</t>
+          <t>https://www.mongodb.com/careers/job/?gh_jid=7727964</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -4044,11 +3819,6 @@
       <c r="M76" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
@@ -4065,17 +3835,17 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer, Infrastructure Security</t>
+          <t>Site Reliability Engineer, Storage Layer Services</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>https://www.mongodb.com/careers/job/?gh_jid=7758610</t>
+          <t>https://www.mongodb.com/careers/job/?gh_jid=7743366</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>[B] Austin/NYC.</t>
+          <t>[B] multiple US cities.</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -4091,11 +3861,6 @@
       <c r="M77" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
@@ -4107,22 +3872,22 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>MongoDB</t>
+          <t>Pinterest</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer, Atlas</t>
+          <t>Data Scientist II, Infrastructure</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>https://www.mongodb.com/careers/job/?gh_jid=7727964</t>
+          <t>https://www.pinterestcareers.com/jobs/?gh_jid=7816424</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>[B] multiple US cities.</t>
+          <t>[C] SF/Remote US.</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -4138,11 +3903,6 @@
       <c r="M78" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N78" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
@@ -4154,22 +3914,22 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>MongoDB</t>
+          <t>Pinterest</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer, Storage Layer Services</t>
+          <t>Data Scientist II, ML Infrastructure</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>https://www.mongodb.com/careers/job/?gh_jid=7743366</t>
+          <t>https://www.pinterestcareers.com/jobs/?gh_jid=8071670</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>[B] multiple US cities.</t>
+          <t>[C] Palo Alto/Remote US.</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -4184,17 +3944,17 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
@@ -4206,17 +3966,17 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Data Scientist II, Infrastructure</t>
+          <t>Machine Learning Engineer, Core Engineering</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>https://www.pinterestcareers.com/jobs/?gh_jid=7816424</t>
+          <t>https://www.pinterestcareers.com/jobs/?gh_jid=6121450</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>[C] SF/Remote US.</t>
+          <t>[B] SF/Palo Alto/Seattle/Remote US.</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -4232,11 +3992,6 @@
       <c r="M80" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
@@ -4253,17 +4008,17 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Data Scientist II, ML Infrastructure</t>
+          <t>Machine Learning Engineer II, Responsible AI</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>https://www.pinterestcareers.com/jobs/?gh_jid=8071670</t>
+          <t>https://www.pinterestcareers.com/jobs/?gh_jid=8162046</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>[C] Palo Alto/Remote US.</t>
+          <t>[B] SF/Remote US.</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -4278,17 +4033,12 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr">
-        <is>
-          <t>Unknown</t>
+          <t>Optional</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -4300,17 +4050,17 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Core Engineering</t>
+          <t>Machine Learning Engineer II, Visual AI</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>https://www.pinterestcareers.com/jobs/?gh_jid=6121450</t>
+          <t>https://www.pinterestcareers.com/jobs/?gh_jid=7697137</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>[B] SF/Palo Alto/Seattle/Remote US.</t>
+          <t>[B] SF/Remote US.</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -4326,11 +4076,6 @@
       <c r="M82" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
@@ -4347,17 +4092,17 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II, Responsible AI</t>
+          <t>Machine Learning Engineer, Monetization Engineering</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>https://www.pinterestcareers.com/jobs/?gh_jid=8162046</t>
+          <t>https://www.pinterestcareers.com/jobs/?gh_jid=6121543</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>[B] SF/Remote US.</t>
+          <t>[B] SF/Palo Alto/Seattle.</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -4373,11 +4118,6 @@
       <c r="M83" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
@@ -4394,17 +4134,17 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II, Visual AI</t>
+          <t>Principal Engineer, Big Data Platform</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>https://www.pinterestcareers.com/jobs/?gh_jid=7697137</t>
+          <t>https://www.pinterestcareers.com/jobs/?gh_jid=7683981</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>[B] SF/Remote US.</t>
+          <t>[C] SF/Remote US.</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -4420,11 +4160,6 @@
       <c r="M84" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
@@ -4441,17 +4176,17 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Monetization Engineering</t>
+          <t>Principal Machine Learning Engineer, Ads Delivery</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>https://www.pinterestcareers.com/jobs/?gh_jid=6121543</t>
+          <t>https://www.pinterestcareers.com/jobs/?gh_jid=6963868</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>[B] SF/Palo Alto/Seattle.</t>
+          <t>[C] SF/Palo Alto/Seattle.</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -4467,11 +4202,6 @@
       <c r="M85" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
@@ -4488,17 +4218,17 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Principal Engineer, Big Data Platform</t>
+          <t>Site Reliability Engineer II, tvScientific</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>https://www.pinterestcareers.com/jobs/?gh_jid=7683981</t>
+          <t>https://www.pinterestcareers.com/jobs/?gh_jid=7782538</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>[C] SF/Remote US.</t>
+          <t>[B] SF/Remote US.</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -4514,11 +4244,6 @@
       <c r="M86" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
@@ -4535,17 +4260,17 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Principal Machine Learning Engineer, Ads Delivery</t>
+          <t>Sr. Data Scientist, Core</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>https://www.pinterestcareers.com/jobs/?gh_jid=6963868</t>
+          <t>https://www.pinterestcareers.com/jobs/?gh_jid=6087213</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>[C] SF/Palo Alto/Seattle.</t>
+          <t>[C] SF/Remote US.</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -4561,11 +4286,6 @@
       <c r="M87" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N87" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
@@ -4582,17 +4302,17 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer II, tvScientific</t>
+          <t>Sr. Data Scientist, Infrastructure</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>https://www.pinterestcareers.com/jobs/?gh_jid=7782538</t>
+          <t>https://www.pinterestcareers.com/jobs/?gh_jid=8024966</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>[B] SF/Remote US.</t>
+          <t>[C] SF/Remote US.</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -4608,11 +4328,6 @@
       <c r="M88" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N88" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
@@ -4629,12 +4344,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Sr. Data Scientist, Core</t>
+          <t>Sr. Data Scientist, Marketing</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>https://www.pinterestcareers.com/jobs/?gh_jid=6087213</t>
+          <t>https://www.pinterestcareers.com/jobs/?gh_jid=8011376</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -4655,11 +4370,6 @@
       <c r="M89" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N89" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
@@ -4676,17 +4386,17 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Sr. Data Scientist, Infrastructure</t>
+          <t>Sr. Data Scientist, Monetization</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>https://www.pinterestcareers.com/jobs/?gh_jid=8024966</t>
+          <t>https://www.pinterestcareers.com/jobs/?gh_jid=5740948</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>[C] SF/Remote US.</t>
+          <t>[C] SF/Seattle.</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -4702,11 +4412,6 @@
       <c r="M90" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N90" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O90" t="inlineStr">
@@ -4723,12 +4428,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Sr. Data Scientist, Marketing</t>
+          <t>Sr. Data Scientist, tvScientific</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>https://www.pinterestcareers.com/jobs/?gh_jid=8011376</t>
+          <t>https://www.pinterestcareers.com/jobs/?gh_jid=7642251</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -4748,17 +4453,17 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
@@ -4770,17 +4475,17 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Sr. Data Scientist, Monetization</t>
+          <t>Sr. Machine Learning Engineer, Applied Science</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>https://www.pinterestcareers.com/jobs/?gh_jid=5740948</t>
+          <t>https://www.pinterestcareers.com/jobs/?gh_jid=6894747</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>[C] SF/Seattle.</t>
+          <t>[B] SF/Remote US.</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -4796,11 +4501,6 @@
       <c r="M92" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N92" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O92" t="inlineStr">
@@ -4817,17 +4517,17 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Sr. Data Scientist, tvScientific</t>
+          <t>Sr. Machine Learning Engineer, Core Engineering</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>https://www.pinterestcareers.com/jobs/?gh_jid=7642251</t>
+          <t>https://www.pinterestcareers.com/jobs/?gh_jid=6121464</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>[C] SF/Remote US.</t>
+          <t>[B] SF/Palo Alto/Seattle.</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -4842,17 +4542,12 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="N93" t="inlineStr">
-        <is>
-          <t>Unknown</t>
+          <t>Optional</t>
         </is>
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -4864,17 +4559,17 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Sr. Machine Learning Engineer, Applied Science</t>
+          <t>Sr. Machine Learning Engineer, Monetization Engineering</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>https://www.pinterestcareers.com/jobs/?gh_jid=6894747</t>
+          <t>https://www.pinterestcareers.com/jobs/?gh_jid=6121551</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>[B] SF/Remote US.</t>
+          <t>[B] SF/Palo Alto/Seattle.</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -4890,11 +4585,6 @@
       <c r="M94" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N94" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O94" t="inlineStr">
@@ -4911,17 +4601,17 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Sr. Machine Learning Engineer, Core Engineering</t>
+          <t>Sr. Site Reliability Engineer, tvScientific</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>https://www.pinterestcareers.com/jobs/?gh_jid=6121464</t>
+          <t>https://www.pinterestcareers.com/jobs/?gh_jid=7782550</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>[B] SF/Palo Alto/Seattle.</t>
+          <t>[B] SF/Remote US.</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -4937,11 +4627,6 @@
       <c r="M95" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N95" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O95" t="inlineStr">
@@ -4958,17 +4643,17 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Sr. Machine Learning Engineer, Monetization Engineering</t>
+          <t>Staff Data Scientist, Ads Delivery</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>https://www.pinterestcareers.com/jobs/?gh_jid=6121551</t>
+          <t>https://www.pinterestcareers.com/jobs/?gh_jid=8026607</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>[B] SF/Palo Alto/Seattle.</t>
+          <t>[C] SF/Remote US.</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -4984,11 +4669,6 @@
       <c r="M96" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N96" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O96" t="inlineStr">
@@ -5005,17 +4685,17 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer, tvScientific</t>
+          <t>Staff Data Scientist, Ads Product</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>https://www.pinterestcareers.com/jobs/?gh_jid=7782550</t>
+          <t>https://www.pinterestcareers.com/jobs/?gh_jid=7963755</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>[B] SF/Remote US.</t>
+          <t>[C] SF/Seattle.</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -5031,11 +4711,6 @@
       <c r="M97" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O97" t="inlineStr">
@@ -5052,12 +4727,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Staff Data Scientist, Ads Delivery</t>
+          <t>Staff Data Scientist, Forecasting</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>https://www.pinterestcareers.com/jobs/?gh_jid=8026607</t>
+          <t>https://www.pinterestcareers.com/jobs/?gh_jid=8001932</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -5078,11 +4753,6 @@
       <c r="M98" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N98" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O98" t="inlineStr">
@@ -5099,17 +4769,17 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Staff Data Scientist, Ads Product</t>
+          <t>Staff Data Scientist, Notifications</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>https://www.pinterestcareers.com/jobs/?gh_jid=7963755</t>
+          <t>https://www.pinterestcareers.com/jobs/?gh_jid=8095343</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>[C] SF/Seattle.</t>
+          <t>[C] SF/Remote US.</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -5125,11 +4795,6 @@
       <c r="M99" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N99" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O99" t="inlineStr">
@@ -5146,17 +4811,17 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Staff Data Scientist, Forecasting</t>
+          <t>Staff Machine Learning Engineer, Ads Conversion Core Modeling</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>https://www.pinterestcareers.com/jobs/?gh_jid=8001932</t>
+          <t>https://www.pinterestcareers.com/jobs/?gh_jid=8011452</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>[C] SF/Remote US.</t>
+          <t>[B] SF/Palo Alto/Seattle.</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -5172,11 +4837,6 @@
       <c r="M100" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N100" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O100" t="inlineStr">
@@ -5193,17 +4853,17 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Staff Data Scientist, Notifications</t>
+          <t>Staff Machine Learning Engineer, Shopping Ads</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>https://www.pinterestcareers.com/jobs/?gh_jid=8095343</t>
+          <t>https://www.pinterestcareers.com/jobs/?gh_jid=8049465</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>[C] SF/Remote US.</t>
+          <t>[B] SF/Palo Alto/Seattle.</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -5219,11 +4879,6 @@
       <c r="M101" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N101" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O101" t="inlineStr">
@@ -5235,22 +4890,22 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Pinterest</t>
+          <t>Reddit</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Staff Machine Learning Engineer, Ads Conversion Core Modeling</t>
+          <t>Backend Engineer, IAM</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>https://www.pinterestcareers.com/jobs/?gh_jid=8011452</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/8189317</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>[B] SF/Palo Alto/Seattle.</t>
+          <t>[B] Remote - US.</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -5266,11 +4921,6 @@
       <c r="M102" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N102" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O102" t="inlineStr">
@@ -5282,22 +4932,22 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Pinterest</t>
+          <t>Reddit</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Staff Machine Learning Engineer, Shopping Ads</t>
+          <t>Principal Data Scientist, Ads</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>https://www.pinterestcareers.com/jobs/?gh_jid=8049465</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7330347</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>[B] SF/Palo Alto/Seattle.</t>
+          <t>[C] Remote - US.</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -5313,11 +4963,6 @@
       <c r="M103" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N103" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O103" t="inlineStr">
@@ -5334,12 +4979,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Backend Engineer, IAM</t>
+          <t>Senior Backend Engineer, Compliance Engineering</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/8189317</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/8128860</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -5360,11 +5005,6 @@
       <c r="M104" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N104" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O104" t="inlineStr">
@@ -5381,17 +5021,17 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Principal Data Scientist, Ads</t>
+          <t>Senior Backend Engineer, IAM</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7330347</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/8044767</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>[C] Remote - US.</t>
+          <t>[B] Remote - US.</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -5407,11 +5047,6 @@
       <c r="M105" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N105" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O105" t="inlineStr">
@@ -5428,12 +5063,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer, Compliance Engineering</t>
+          <t>Senior Backend Engineer, Safety</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/8128860</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/8093006</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -5454,11 +5089,6 @@
       <c r="M106" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N106" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O106" t="inlineStr">
@@ -5475,17 +5105,17 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer, IAM</t>
+          <t>Senior Data Scientist, Ads</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/8044767</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/8104403</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>[B] Remote - US.</t>
+          <t>[C] Remote - US.</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -5501,11 +5131,6 @@
       <c r="M107" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N107" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O107" t="inlineStr">
@@ -5522,17 +5147,17 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer, Safety</t>
+          <t>Senior Data Scientist, Ads Integrity</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/8093006</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/8157580</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>[B] Remote - US.</t>
+          <t>[C] Remote - US.</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -5548,11 +5173,6 @@
       <c r="M108" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N108" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O108" t="inlineStr">
@@ -5569,12 +5189,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Senior Data Scientist, Ads</t>
+          <t>Senior Data Scientist - Consumer</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/8104403</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/8126946</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -5595,11 +5215,6 @@
       <c r="M109" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N109" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O109" t="inlineStr">
@@ -5616,17 +5231,17 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Senior Data Scientist, Ads Integrity</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/8157580</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/6960831</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>[C] Remote - US.</t>
+          <t>[B] Remote - US.</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -5642,11 +5257,6 @@
       <c r="M110" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N110" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O110" t="inlineStr">
@@ -5663,17 +5273,17 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - Consumer</t>
+          <t>Senior Machine Learning Engineer, Ads Optimization</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/8126946</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/8029120</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>[C] Remote - US.</t>
+          <t>[B] Remote - US.</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -5689,11 +5299,6 @@
       <c r="M111" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N111" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O111" t="inlineStr">
@@ -5710,12 +5315,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Senior Machine Learning Systems Engineer</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/6960831</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7731772</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -5736,11 +5341,6 @@
       <c r="M112" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N112" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O112" t="inlineStr">
@@ -5757,12 +5357,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Ads Optimization</t>
+          <t>Senior Machine Learning Systems Engineer, Ads ML Experience Platform</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/8029120</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/8112967</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -5782,17 +5382,17 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
@@ -5804,12 +5404,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Systems Engineer</t>
+          <t>Senior Staff Data Scientist - Consumer Experimentation</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7731772</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7974504</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -5830,11 +5430,6 @@
       <c r="M114" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N114" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O114" t="inlineStr">
@@ -5851,12 +5446,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Systems Engineer, Ads ML Experience Platform</t>
+          <t>Senior Staff Machine Learning Engineer, Ads Ranking</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/8112967</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/8201359</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -5876,17 +5471,12 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="N115" t="inlineStr">
-        <is>
-          <t>Unknown</t>
+          <t>Optional</t>
         </is>
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -5898,12 +5488,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Senior Staff Data Scientist - Consumer Experimentation</t>
+          <t>Senior Staff Machine Learning Engineer, Feed Relevance</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7974504</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/8122606</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -5924,11 +5514,6 @@
       <c r="M116" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N116" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O116" t="inlineStr">
@@ -5945,12 +5530,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Senior Staff Machine Learning Engineer, Ads Ranking</t>
+          <t>Senior Staff Machine Learning Engineer, GenAI Platform</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/8201359</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7772274</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -5971,11 +5556,6 @@
       <c r="M117" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N117" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O117" t="inlineStr">
@@ -5992,12 +5572,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Senior Staff Machine Learning Engineer, Feed Relevance</t>
+          <t>Senior Staff Machine Learning Systems Engineer, Ads ML Platform</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/8122606</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/8157275</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -6018,11 +5598,6 @@
       <c r="M118" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N118" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O118" t="inlineStr">
@@ -6039,12 +5614,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Senior Staff Machine Learning Engineer, GenAI Platform</t>
+          <t>Sr. Staff Data Scientist - Ads Measurement, Signals, Privacy</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7772274</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/8072046</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -6064,17 +5639,17 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
@@ -6086,17 +5661,17 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Senior Staff Machine Learning Systems Engineer, Ads ML Platform</t>
+          <t>Staff Data Scientist, Ads</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/8157275</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7721787</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>[B] Remote - US.</t>
+          <t>[C] Remote - US.</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -6112,11 +5687,6 @@
       <c r="M120" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N120" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O120" t="inlineStr">
@@ -6133,17 +5703,17 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Sr. Staff Data Scientist - Ads Measurement, Signals, Privacy</t>
+          <t>Staff Data Scientist - Ads Measurement, Signals, Privacy</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/8072046</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/8072076</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>[B] Remote - US.</t>
+          <t>[C] Remote - US.</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -6158,17 +5728,12 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="N121" t="inlineStr">
-        <is>
-          <t>Unknown</t>
+          <t>Optional</t>
         </is>
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -6180,12 +5745,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Staff Data Scientist, Ads</t>
+          <t>Staff Data Scientist, Marketing</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7721787</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7445240</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -6206,11 +5771,6 @@
       <c r="M122" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N122" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O122" t="inlineStr">
@@ -6227,17 +5787,17 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Staff Data Scientist - Ads Measurement, Signals, Privacy</t>
+          <t>Staff Machine Learning Engineer, AI Security</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/8072076</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/8203478</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>[C] Remote - US.</t>
+          <t>[B] Remote - US.</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -6253,11 +5813,6 @@
       <c r="M123" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N123" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O123" t="inlineStr">
@@ -6274,17 +5829,17 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Staff Data Scientist, Marketing</t>
+          <t>Staff Machine Learning Engineer, App Ads Modeling</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7445240</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/8187652</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>[C] Remote - US.</t>
+          <t>[B] Remote - US.</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -6300,11 +5855,6 @@
       <c r="M124" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N124" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O124" t="inlineStr">
@@ -6321,12 +5871,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Staff Machine Learning Engineer, AI Security</t>
+          <t>Staff Machine Learning Engineer, Consumer</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/8203478</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7747244</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -6346,12 +5896,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>Optional</t>
-        </is>
-      </c>
-      <c r="N125" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>No field</t>
         </is>
       </c>
       <c r="O125" t="inlineStr">
@@ -6368,12 +5913,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Staff Machine Learning Engineer, App Ads Modeling</t>
+          <t>Staff Machine Learning Engineer, Retrieval</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/8187652</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/8178085</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -6394,11 +5939,6 @@
       <c r="M126" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N126" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O126" t="inlineStr">
@@ -6415,12 +5955,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Staff Machine Learning Engineer, Consumer</t>
+          <t>Staff Machine Learning Systems Engineer</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7747244</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7731788</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -6440,12 +5980,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>No field</t>
-        </is>
-      </c>
-      <c r="N127" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>Optional</t>
         </is>
       </c>
       <c r="O127" t="inlineStr">
@@ -6457,22 +5992,22 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Reddit</t>
+          <t>Riot Games</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Staff Machine Learning Engineer, Retrieval</t>
+          <t>Principal Data Engineer, Personalization</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/8178085</t>
+          <t>https://www.riotgames.com/en/work-with-us/job/8049834?gh_jid=8049834</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>[B] Remote - US.</t>
+          <t>[C] Los Angeles.</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -6488,11 +6023,6 @@
       <c r="M128" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N128" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O128" t="inlineStr">
@@ -6504,22 +6034,22 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Reddit</t>
+          <t>Riot Games</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Staff Machine Learning Systems Engineer</t>
+          <t>Principal Data Engineer - Teamfight Tactics</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7731788</t>
+          <t>https://www.riotgames.com/en/work-with-us/job/8187622?gh_jid=8187622</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>[B] Remote - US.</t>
+          <t>[C] Los Angeles.</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -6535,11 +6065,6 @@
       <c r="M129" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N129" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O129" t="inlineStr">
@@ -6556,12 +6081,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Principal Data Engineer, Personalization</t>
+          <t>Principal Machine Learning Engineer (Platform &amp; Integrations) - League of Legends</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>https://www.riotgames.com/en/work-with-us/job/8049834?gh_jid=8049834</t>
+          <t>https://www.riotgames.com/en/work-with-us/job/7944656?gh_jid=7944656</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -6582,11 +6107,6 @@
       <c r="M130" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N130" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O130" t="inlineStr">
@@ -6603,12 +6123,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Principal Data Engineer - Teamfight Tactics</t>
+          <t>Principal Software Engineer, Services/DevOps - Wild Rift</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>https://www.riotgames.com/en/work-with-us/job/8187622?gh_jid=8187622</t>
+          <t>https://www.riotgames.com/en/work-with-us/job/8104538?gh_jid=8104538</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -6629,11 +6149,6 @@
       <c r="M131" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N131" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O131" t="inlineStr">
@@ -6650,17 +6165,17 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Principal Machine Learning Engineer (Platform &amp; Integrations) - League of Legends</t>
+          <t>Staff Data and AI Engineer - Enterprise</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>https://www.riotgames.com/en/work-with-us/job/7944656?gh_jid=7944656</t>
+          <t>https://www.riotgames.com/en/work-with-us/job/8014875?gh_jid=8014875</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>[C] Los Angeles.</t>
+          <t>[B] Los Angeles.</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -6676,11 +6191,6 @@
       <c r="M132" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N132" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O132" t="inlineStr">
@@ -6697,17 +6207,17 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Principal Software Engineer, Services/DevOps - Wild Rift</t>
+          <t>Staff Machine Learning Engineer (Applied Modeling) - League of Legends</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>https://www.riotgames.com/en/work-with-us/job/8104538?gh_jid=8104538</t>
+          <t>https://www.riotgames.com/en/work-with-us/job/7981132?gh_jid=7981132</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>[C] Los Angeles.</t>
+          <t>[B] Los Angeles.</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -6723,11 +6233,6 @@
       <c r="M133" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N133" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O133" t="inlineStr">
@@ -6744,12 +6249,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Staff Data and AI Engineer - Enterprise</t>
+          <t>Staff Machine Learning Engineer - Game Tech Group, ML Platform</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>https://www.riotgames.com/en/work-with-us/job/8014875?gh_jid=8014875</t>
+          <t>https://www.riotgames.com/en/work-with-us/job/7977840?gh_jid=7977840</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -6770,11 +6275,6 @@
       <c r="M134" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N134" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O134" t="inlineStr">
@@ -6786,22 +6286,22 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Riot Games</t>
+          <t>Roblox</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Staff Machine Learning Engineer (Applied Modeling) - League of Legends</t>
+          <t>Distinguished Engineer, Machine Learning Systems - Economy</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>https://www.riotgames.com/en/work-with-us/job/7981132?gh_jid=7981132</t>
+          <t>https://careers.roblox.com/jobs/7332473?gh_jid=7332473</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>[B] Los Angeles.</t>
+          <t>[C] San Mateo, CA.</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -6817,11 +6317,6 @@
       <c r="M135" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N135" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O135" t="inlineStr">
@@ -6833,22 +6328,22 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Riot Games</t>
+          <t>Roblox</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Staff Machine Learning Engineer - Game Tech Group, ML Platform</t>
+          <t>Principal Client Platform Engineer</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>https://www.riotgames.com/en/work-with-us/job/7977840?gh_jid=7977840</t>
+          <t>https://careers.roblox.com/jobs/8212529?gh_jid=8212529</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>[B] Los Angeles.</t>
+          <t>[C] San Mateo, CA.</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -6864,11 +6359,6 @@
       <c r="M136" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N136" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O136" t="inlineStr">
@@ -6885,12 +6375,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Distinguished Engineer, Machine Learning Systems - Economy</t>
+          <t>Principal Data Engineer - Economy</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>https://careers.roblox.com/jobs/7332473?gh_jid=7332473</t>
+          <t>https://careers.roblox.com/jobs/7629489?gh_jid=7629489</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -6911,11 +6401,6 @@
       <c r="M137" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N137" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O137" t="inlineStr">
@@ -6932,12 +6417,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Principal Client Platform Engineer</t>
+          <t>Principal Machine Learning Engineer, Alt Defense</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>https://careers.roblox.com/jobs/8212529?gh_jid=8212529</t>
+          <t>https://careers.roblox.com/jobs/8187377?gh_jid=8187377</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -6958,11 +6443,6 @@
       <c r="M138" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N138" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O138" t="inlineStr">
@@ -6979,12 +6459,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Principal Data Engineer - Economy</t>
+          <t>Principal Machine Learning Engineer, Asset Safety</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>https://careers.roblox.com/jobs/7629489?gh_jid=7629489</t>
+          <t>https://careers.roblox.com/jobs/8073283?gh_jid=8073283</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -7005,11 +6485,6 @@
       <c r="M139" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N139" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O139" t="inlineStr">
@@ -7026,12 +6501,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Principal Machine Learning Engineer, Alt Defense</t>
+          <t>Principal Machine Learning Engineer, Embodied AI and Smart NPCs</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>https://careers.roblox.com/jobs/8187377?gh_jid=8187377</t>
+          <t>https://careers.roblox.com/jobs/7629843?gh_jid=7629843</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -7052,11 +6527,6 @@
       <c r="M140" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N140" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O140" t="inlineStr">
@@ -7073,12 +6543,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Principal Machine Learning Engineer, Asset Safety</t>
+          <t>Principal Machine Learning Infrastructure Engineer, Ads &amp; Discovery</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>https://careers.roblox.com/jobs/8073283?gh_jid=8073283</t>
+          <t>https://careers.roblox.com/jobs/7351202?gh_jid=7351202</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -7099,11 +6569,6 @@
       <c r="M141" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N141" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O141" t="inlineStr">
@@ -7120,12 +6585,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Principal Machine Learning Engineer, Embodied AI and Smart NPCs</t>
+          <t>Principal/Senior Machine Learning Scientist - Search and Discovery</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>https://careers.roblox.com/jobs/7629843?gh_jid=7629843</t>
+          <t>https://careers.roblox.com/jobs/7655346?gh_jid=7655346</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -7146,11 +6611,6 @@
       <c r="M142" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N142" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O142" t="inlineStr">
@@ -7167,12 +6627,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Principal Machine Learning Infrastructure Engineer, Ads &amp; Discovery</t>
+          <t>Principal Software Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>https://careers.roblox.com/jobs/7351202?gh_jid=7351202</t>
+          <t>https://careers.roblox.com/jobs/7678832?gh_jid=7678832</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -7193,11 +6653,6 @@
       <c r="M143" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N143" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O143" t="inlineStr">
@@ -7214,12 +6669,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Principal/Senior Machine Learning Scientist - Search and Discovery</t>
+          <t>Principal Software Engineer, Data Infrastructure</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>https://careers.roblox.com/jobs/7655346?gh_jid=7655346</t>
+          <t>https://careers.roblox.com/jobs/8029695?gh_jid=8029695</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -7240,11 +6695,6 @@
       <c r="M144" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N144" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O144" t="inlineStr">
@@ -7261,17 +6711,17 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Principal Software Engineer, Data Engineering</t>
+          <t>Senior Data Engineer, Economy</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>https://careers.roblox.com/jobs/7678832?gh_jid=7678832</t>
+          <t>https://careers.roblox.com/jobs/8172297?gh_jid=8172297</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>[C] San Mateo, CA.</t>
+          <t>[B] San Mateo, CA.</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -7287,11 +6737,6 @@
       <c r="M145" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N145" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O145" t="inlineStr">
@@ -7308,12 +6753,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Principal Software Engineer, Data Infrastructure</t>
+          <t>Senior Data Scientist, Consumer Apps</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>https://careers.roblox.com/jobs/8029695?gh_jid=8029695</t>
+          <t>https://careers.roblox.com/jobs/8127054?gh_jid=8127054</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -7334,11 +6779,6 @@
       <c r="M146" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N146" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O146" t="inlineStr">
@@ -7355,17 +6795,17 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Economy</t>
+          <t>Senior Data Scientist - Consumer Frontend</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>https://careers.roblox.com/jobs/8172297?gh_jid=8172297</t>
+          <t>https://careers.roblox.com/jobs/7977682?gh_jid=7977682</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>[B] San Mateo, CA.</t>
+          <t>[C] San Mateo, CA.</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -7381,11 +6821,6 @@
       <c r="M147" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N147" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O147" t="inlineStr">
@@ -7402,12 +6837,12 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Senior Data Scientist, Consumer Apps</t>
+          <t>Senior Data Scientist - Discovery</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>https://careers.roblox.com/jobs/8127054?gh_jid=8127054</t>
+          <t>https://careers.roblox.com/jobs/8037082?gh_jid=8037082</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -7428,11 +6863,6 @@
       <c r="M148" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N148" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O148" t="inlineStr">
@@ -7449,12 +6879,12 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - Consumer Frontend</t>
+          <t>Senior Data Scientist, Engine Infra</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>https://careers.roblox.com/jobs/7977682?gh_jid=7977682</t>
+          <t>https://careers.roblox.com/jobs/8193712?gh_jid=8193712</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
@@ -7475,11 +6905,6 @@
       <c r="M149" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N149" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O149" t="inlineStr">
@@ -7496,17 +6921,17 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - Discovery</t>
+          <t>Senior Growth Data Engineer</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>https://careers.roblox.com/jobs/8037082?gh_jid=8037082</t>
+          <t>https://careers.roblox.com/jobs/8055450?gh_jid=8055450</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>[C] San Mateo, CA.</t>
+          <t>[B] San Mateo, CA.</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -7522,11 +6947,6 @@
       <c r="M150" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N150" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O150" t="inlineStr">
@@ -7543,17 +6963,17 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Senior Data Scientist, Engine Infra</t>
+          <t>Senior Machine Learning Engineer, Ads</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>https://careers.roblox.com/jobs/8193712?gh_jid=8193712</t>
+          <t>https://careers.roblox.com/jobs/7351220?gh_jid=7351220</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>[C] San Mateo, CA.</t>
+          <t>[B] San Mateo, CA.</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -7569,11 +6989,6 @@
       <c r="M151" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N151" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O151" t="inlineStr">
@@ -7590,17 +7005,17 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Senior Growth Data Engineer</t>
+          <t>Senior/Principal Infrastructure Engineer - ML Platform</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>https://careers.roblox.com/jobs/8055450?gh_jid=8055450</t>
+          <t>https://careers.roblox.com/jobs/8027755?gh_jid=8027755</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>[B] San Mateo, CA.</t>
+          <t>[C] San Mateo, CA.</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -7616,11 +7031,6 @@
       <c r="M152" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N152" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O152" t="inlineStr">
@@ -7637,17 +7047,17 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Ads</t>
+          <t>Senior/Principal Machine Learning Engineer, 3D Data</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>https://careers.roblox.com/jobs/7351220?gh_jid=7351220</t>
+          <t>https://careers.roblox.com/jobs/7943933?gh_jid=7943933</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>[B] San Mateo, CA.</t>
+          <t>[C] San Mateo, CA.</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -7663,11 +7073,6 @@
       <c r="M153" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N153" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O153" t="inlineStr">
@@ -7684,12 +7089,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Senior/Principal Infrastructure Engineer - ML Platform</t>
+          <t>Senior/Principal Platform Engineer, ML Platform</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>https://careers.roblox.com/jobs/8027755?gh_jid=8027755</t>
+          <t>https://careers.roblox.com/jobs/8047833?gh_jid=8047833</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
@@ -7710,11 +7115,6 @@
       <c r="M154" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N154" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O154" t="inlineStr">
@@ -7731,17 +7131,17 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Senior/Principal Machine Learning Engineer, 3D Data</t>
+          <t>Senior Site Reliability Engineer, Compute</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>https://careers.roblox.com/jobs/7943933?gh_jid=7943933</t>
+          <t>https://careers.roblox.com/jobs/8042554?gh_jid=8042554</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>[C] San Mateo, CA.</t>
+          <t>[B] San Mateo, CA.</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -7757,11 +7157,6 @@
       <c r="M155" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N155" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O155" t="inlineStr">
@@ -7778,17 +7173,17 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Senior/Principal Platform Engineer, ML Platform</t>
+          <t>Senior Software Engineer, Data Infrastructure</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>https://careers.roblox.com/jobs/8047833?gh_jid=8047833</t>
+          <t>https://careers.roblox.com/jobs/8014486?gh_jid=8014486</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>[C] San Mateo, CA.</t>
+          <t>[B] San Mateo, CA.</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -7804,11 +7199,6 @@
       <c r="M156" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N156" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O156" t="inlineStr">
@@ -7825,12 +7215,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer, Compute</t>
+          <t>Senior Software Engineer - Data Infrastructure, Safety</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>https://careers.roblox.com/jobs/8042554?gh_jid=8042554</t>
+          <t>https://careers.roblox.com/jobs/7852258?gh_jid=7852258</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
@@ -7851,11 +7241,6 @@
       <c r="M157" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N157" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O157" t="inlineStr">
@@ -7872,12 +7257,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Infrastructure</t>
+          <t>Senior Software Engineer, ML Infra - Asset Safety</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>https://careers.roblox.com/jobs/8014486?gh_jid=8014486</t>
+          <t>https://careers.roblox.com/jobs/8224452?gh_jid=8224452</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
@@ -7898,11 +7283,6 @@
       <c r="M158" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N158" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O158" t="inlineStr">
@@ -7914,22 +7294,22 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Roblox</t>
+          <t>SoFi</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Data Infrastructure, Safety</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>https://careers.roblox.com/jobs/7852258?gh_jid=7852258</t>
+          <t>https://sofi.com/careers/job/7805247003?gh_jid=7805247003</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>[B] San Mateo, CA.</t>
+          <t>[C] United States.</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -7945,11 +7325,6 @@
       <c r="M159" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N159" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O159" t="inlineStr">
@@ -7961,22 +7336,22 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Roblox</t>
+          <t>Take-Two</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, ML Infra - Asset Safety</t>
+          <t>Lead DevOps Engineer</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>https://careers.roblox.com/jobs/8224452?gh_jid=8224452</t>
+          <t>https://job-boards.greenhouse.io/taketwo/jobs/8075024</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>[B] San Mateo, CA.</t>
+          <t>[B] Austin, TX.</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -7992,11 +7367,6 @@
       <c r="M160" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N160" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O160" t="inlineStr">
@@ -8008,22 +7378,22 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>SoFi</t>
+          <t>Toast</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Data Scientist II</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>https://sofi.com/careers/job/7805247003?gh_jid=7805247003</t>
+          <t>https://careers.toasttab.com/jobs?gh_jid=7984730</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>[C] United States.</t>
+          <t>[C] Remote, USA.</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -8038,12 +7408,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>Optional</t>
-        </is>
-      </c>
-      <c r="N161" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>No field</t>
         </is>
       </c>
       <c r="O161" t="inlineStr">
@@ -8055,22 +7420,22 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Take-Two</t>
+          <t>Toast</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Lead DevOps Engineer</t>
+          <t>Staff Data Scientist</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/taketwo/jobs/8075024</t>
+          <t>https://careers.toasttab.com/jobs?gh_jid=8029049</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>[B] Austin, TX.</t>
+          <t>[C] Remote, USA.</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -8085,12 +7450,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>Optional</t>
-        </is>
-      </c>
-      <c r="N162" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>No field</t>
         </is>
       </c>
       <c r="O162" t="inlineStr">
@@ -8102,22 +7462,22 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Toast</t>
+          <t>Zscaler</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Data Scientist II</t>
+          <t>AI DevOps Engineer</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>https://careers.toasttab.com/jobs?gh_jid=7984730</t>
+          <t>https://job-boards.greenhouse.io/zscaler/jobs/5208829007</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>[C] Remote, USA.</t>
+          <t>[B] Remote - USA / San Jose, CA.</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -8132,12 +7492,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>No field</t>
-        </is>
-      </c>
-      <c r="N163" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>Optional</t>
         </is>
       </c>
       <c r="O163" t="inlineStr">
@@ -8149,22 +7504,22 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Toast</t>
+          <t>Zscaler</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Staff Data Scientist</t>
+          <t>Senior Software Architect, Platform Engineering</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>https://careers.toasttab.com/jobs?gh_jid=8029049</t>
+          <t>https://job-boards.greenhouse.io/zscaler/jobs/5082275007</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>[C] Remote, USA.</t>
+          <t>[B] San Jose, CA.</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -8179,12 +7534,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>No field</t>
-        </is>
-      </c>
-      <c r="N164" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>Optional</t>
         </is>
       </c>
       <c r="O164" t="inlineStr">
@@ -8201,17 +7551,17 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>AI DevOps Engineer</t>
+          <t>Staff Machine Learning Engineer - Data Lake, Anomaly Detection</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/zscaler/jobs/5208829007</t>
+          <t>https://job-boards.greenhouse.io/zscaler/jobs/5114450007</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>[B] Remote - USA / San Jose, CA.</t>
+          <t>[B] San Jose, CA.</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -8227,11 +7577,6 @@
       <c r="M165" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N165" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O165" t="inlineStr">
@@ -8248,12 +7593,12 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Senior Software Architect, Platform Engineering</t>
+          <t>Staff Site Reliability Engineer</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/zscaler/jobs/5082275007</t>
+          <t>https://job-boards.greenhouse.io/zscaler/jobs/5130009007</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
@@ -8274,11 +7619,6 @@
       <c r="M166" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N166" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O166" t="inlineStr">
@@ -8295,17 +7635,17 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Staff Machine Learning Engineer - Data Lake, Anomaly Detection</t>
+          <t>Staff Site Reliability Engineer (Production Engineer)-Federal</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/zscaler/jobs/5114450007</t>
+          <t>https://job-boards.greenhouse.io/zscaler/jobs/5029669007</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>[B] San Jose, CA.</t>
+          <t>[B] multiple US cities.</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -8321,11 +7661,6 @@
       <c r="M167" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N167" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O167" t="inlineStr">
@@ -8337,22 +7672,22 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Zscaler</t>
+          <t>Clover Health</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Staff Site Reliability Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/zscaler/jobs/5130009007</t>
+          <t>https://job-boards.greenhouse.io/cloverhealth/jobs/7848974</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>[B] San Jose, CA.</t>
+          <t>[C] Remote - USA.</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -8368,11 +7703,6 @@
       <c r="M168" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N168" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O168" t="inlineStr">
@@ -8384,22 +7714,22 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Zscaler</t>
+          <t>Clover Health</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Staff Site Reliability Engineer (Production Engineer)-Federal</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/zscaler/jobs/5029669007</t>
+          <t>https://job-boards.greenhouse.io/cloverhealth/jobs/8074957</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>[B] multiple US cities.</t>
+          <t>[B] Remote - USA.</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -8415,11 +7745,6 @@
       <c r="M169" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N169" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O169" t="inlineStr">
@@ -8431,22 +7756,22 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Clover Health</t>
+          <t>Flatiron Health</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Senior Software Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/cloverhealth/jobs/7848974</t>
+          <t>https://flatiron.com/careers/open-positions/job?gh_jid=8079733</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>[C] Remote - USA.</t>
+          <t>[B] NY office.</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -8462,11 +7787,6 @@
       <c r="M170" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N170" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O170" t="inlineStr">
@@ -8478,22 +7798,22 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Clover Health</t>
+          <t>Ro</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Analytics Engineer, Conversational Analytics</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/cloverhealth/jobs/8074957</t>
+          <t>https://jobs.lever.co/ro/3910baa9-f961-4380-ad0a-01deec07f7a2</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>[B] Remote - USA.</t>
+          <t>[B] New York, NY.</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -8508,39 +7828,39 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>No field</t>
         </is>
       </c>
       <c r="N171" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="O171" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Flatiron Health</t>
+          <t>Ro</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Engineering</t>
+          <t>Senior Backend Engineer, Product</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>https://flatiron.com/careers/open-positions/job?gh_jid=8079733</t>
+          <t>https://jobs.lever.co/ro/efbeeea0-5007-4d21-9bbd-e889a5148138</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>[B] NY office.</t>
+          <t>[B] New York, NY.</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -8555,39 +7875,39 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>No field</t>
         </is>
       </c>
       <c r="N172" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="O172" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Ro</t>
+          <t>Airbnb</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Analytics Engineer, Conversational Analytics</t>
+          <t>Senior Machine Learning Engineer, Trust</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/ro/3910baa9-f961-4380-ad0a-01deec07f7a2</t>
+          <t>https://careers.airbnb.com/positions/8130355?gh_jid=8130355</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>[B] New York, NY.</t>
+          <t>[B] San Francisco, CA.</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -8602,39 +7922,34 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>No field</t>
-        </is>
-      </c>
-      <c r="N173" t="inlineStr">
-        <is>
-          <t>Unknown</t>
+          <t>Optional</t>
         </is>
       </c>
       <c r="O173" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Ro</t>
+          <t>Airbnb</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer, Product</t>
+          <t>Senior Machine Learning Engineer, Trust</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/ro/efbeeea0-5007-4d21-9bbd-e889a5148138</t>
+          <t>https://careers.airbnb.com/positions/8232153?gh_jid=8232153</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>[B] New York, NY.</t>
+          <t>[B] San Francisco, CA.</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -8649,17 +7964,12 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>No field</t>
-        </is>
-      </c>
-      <c r="N174" t="inlineStr">
-        <is>
-          <t>Unknown</t>
+          <t>Optional</t>
         </is>
       </c>
       <c r="O174" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -8671,17 +7981,17 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Trust</t>
+          <t>Senior Staff Data Scientist, Guest &amp; Host Marketplace AI</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>https://careers.airbnb.com/positions/8130355?gh_jid=8130355</t>
+          <t>https://careers.airbnb.com/positions/7107054?gh_jid=7107054</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>[B] San Francisco, CA.</t>
+          <t>[B] Remote.</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -8697,11 +8007,6 @@
       <c r="M175" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N175" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O175" t="inlineStr">
@@ -8718,12 +8023,12 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Trust</t>
+          <t>Staff Machine Learning Engineer, Assistance Engineering</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>https://careers.airbnb.com/positions/8232153?gh_jid=8232153</t>
+          <t>https://careers.airbnb.com/positions/8024316?gh_jid=8024316</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
@@ -8744,11 +8049,6 @@
       <c r="M176" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N176" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O176" t="inlineStr">
@@ -8760,22 +8060,22 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Airbnb</t>
+          <t>Lyft</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Senior Staff Data Scientist, Guest &amp; Host Marketplace AI</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>https://careers.airbnb.com/positions/7107054?gh_jid=7107054</t>
+          <t>https://app.careerpuck.com/job-board/lyft/job/8772592002?gh_jid=8772592002</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>[B] Remote.</t>
+          <t>[C] Seattle, WA.</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -8790,12 +8090,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>Optional</t>
-        </is>
-      </c>
-      <c r="N177" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>No field</t>
         </is>
       </c>
       <c r="O177" t="inlineStr">
@@ -8807,22 +8102,22 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Airbnb</t>
+          <t>Lyft</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Staff Machine Learning Engineer, Assistance Engineering</t>
+          <t>Data Scientist, Decisions - Central Market Management</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>https://careers.airbnb.com/positions/8024316?gh_jid=8024316</t>
+          <t>https://app.careerpuck.com/job-board/lyft/job/8376875002?gh_jid=8376875002</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>[B] San Francisco, CA.</t>
+          <t>[C] San Francisco, CA.</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -8837,12 +8132,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>Optional</t>
-        </is>
-      </c>
-      <c r="N178" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>No field</t>
         </is>
       </c>
       <c r="O178" t="inlineStr">
@@ -8859,17 +8149,17 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Data Scientist, Decisions - Central Market Management</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>https://app.careerpuck.com/job-board/lyft/job/8772592002?gh_jid=8772592002</t>
+          <t>https://app.careerpuck.com/job-board/lyft/job/8378473002?gh_jid=8378473002</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>[C] Seattle, WA.</t>
+          <t>[C] New York, NY.</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -8885,11 +8175,6 @@
       <c r="M179" t="inlineStr">
         <is>
           <t>No field</t>
-        </is>
-      </c>
-      <c r="N179" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O179" t="inlineStr">
@@ -8906,17 +8191,17 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Data Scientist, Decisions - Central Market Management</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>https://app.careerpuck.com/job-board/lyft/job/8376875002?gh_jid=8376875002</t>
+          <t>https://app.careerpuck.com/job-board/lyft/job/8689127002?gh_jid=8689127002</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>[C] San Francisco, CA.</t>
+          <t>[B] New York, NY.</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -8932,11 +8217,6 @@
       <c r="M180" t="inlineStr">
         <is>
           <t>No field</t>
-        </is>
-      </c>
-      <c r="N180" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O180" t="inlineStr">
@@ -8953,17 +8233,17 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Data Scientist, Decisions - Central Market Management</t>
+          <t>Machine Learning Engineer, Fulfillment</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>https://app.careerpuck.com/job-board/lyft/job/8378473002?gh_jid=8378473002</t>
+          <t>https://app.careerpuck.com/job-board/lyft/job/8688633002?gh_jid=8688633002</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>[C] New York, NY.</t>
+          <t>[B] San Francisco, CA.</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -8979,11 +8259,6 @@
       <c r="M181" t="inlineStr">
         <is>
           <t>No field</t>
-        </is>
-      </c>
-      <c r="N181" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O181" t="inlineStr">
@@ -9000,17 +8275,17 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Data Scientist, Causal Inference</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>https://app.careerpuck.com/job-board/lyft/job/8689127002?gh_jid=8689127002</t>
+          <t>https://app.careerpuck.com/job-board/lyft/job/8584595002?gh_jid=8584595002</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>[B] New York, NY.</t>
+          <t>[C] San Francisco, CA.</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -9026,11 +8301,6 @@
       <c r="M182" t="inlineStr">
         <is>
           <t>No field</t>
-        </is>
-      </c>
-      <c r="N182" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O182" t="inlineStr">
@@ -9047,17 +8317,17 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Fulfillment</t>
+          <t>Senior Data Scientist, Causal Inference</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>https://app.careerpuck.com/job-board/lyft/job/8688633002?gh_jid=8688633002</t>
+          <t>https://app.careerpuck.com/job-board/lyft/job/8584688002?gh_jid=8584688002</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>[B] San Francisco, CA.</t>
+          <t>[C] New York, NY.</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -9073,11 +8343,6 @@
       <c r="M183" t="inlineStr">
         <is>
           <t>No field</t>
-        </is>
-      </c>
-      <c r="N183" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O183" t="inlineStr">
@@ -9099,12 +8364,12 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>https://app.careerpuck.com/job-board/lyft/job/8584595002?gh_jid=8584595002</t>
+          <t>https://app.careerpuck.com/job-board/lyft/job/8584695002?gh_jid=8584695002</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>[C] San Francisco, CA.</t>
+          <t>[C] Seattle, WA.</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -9120,11 +8385,6 @@
       <c r="M184" t="inlineStr">
         <is>
           <t>No field</t>
-        </is>
-      </c>
-      <c r="N184" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O184" t="inlineStr">
@@ -9141,17 +8401,17 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Senior Data Scientist, Causal Inference</t>
+          <t>Senior Machine Learning Engineer, Recommendations</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>https://app.careerpuck.com/job-board/lyft/job/8584688002?gh_jid=8584688002</t>
+          <t>https://app.careerpuck.com/job-board/lyft/job/8430552002?gh_jid=8430552002</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>[C] New York, NY.</t>
+          <t>[B] San Francisco, CA.</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -9167,11 +8427,6 @@
       <c r="M185" t="inlineStr">
         <is>
           <t>No field</t>
-        </is>
-      </c>
-      <c r="N185" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O185" t="inlineStr">
@@ -9183,22 +8438,22 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Lyft</t>
+          <t>Samsara</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Senior Data Scientist, Causal Inference</t>
+          <t>AI Engineer, Customer Success</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>https://app.careerpuck.com/job-board/lyft/job/8584695002?gh_jid=8584695002</t>
+          <t>https://www.samsara.com/company/careers/roles/8024110?gh_jid=8024110</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>[C] Seattle, WA.</t>
+          <t>[B] Remote - US.</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -9213,12 +8468,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>No field</t>
-        </is>
-      </c>
-      <c r="N186" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>Optional</t>
         </is>
       </c>
       <c r="O186" t="inlineStr">
@@ -9230,22 +8480,22 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Lyft</t>
+          <t>Samsara</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Recommendations</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>https://app.careerpuck.com/job-board/lyft/job/8430552002?gh_jid=8430552002</t>
+          <t>https://www.samsara.com/company/careers/roles/7859702?gh_jid=7859702</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>[B] San Francisco, CA.</t>
+          <t>[B] Remote - US.</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -9260,12 +8510,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>No field</t>
-        </is>
-      </c>
-      <c r="N187" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>Optional</t>
         </is>
       </c>
       <c r="O187" t="inlineStr">
@@ -9282,17 +8527,17 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>AI Engineer, Customer Success</t>
+          <t>Finance &amp; Strategy AI Engineer</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>https://www.samsara.com/company/careers/roles/8024110?gh_jid=8024110</t>
+          <t>https://www.samsara.com/company/careers/roles/8113356?gh_jid=8113356</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>[B] Remote - US.</t>
+          <t>[B] San Francisco - SF9.</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -9308,11 +8553,6 @@
       <c r="M188" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N188" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O188" t="inlineStr">
@@ -9329,12 +8569,12 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Lead Machine Learning Engineer - ML Infrastructure</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>https://www.samsara.com/company/careers/roles/7859702?gh_jid=7859702</t>
+          <t>https://www.samsara.com/company/careers/roles/7721193?gh_jid=7721193</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
@@ -9355,11 +8595,6 @@
       <c r="M189" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N189" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O189" t="inlineStr">
@@ -9376,17 +8611,17 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Finance &amp; Strategy AI Engineer</t>
+          <t>People Analytics AI Engineer</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>https://www.samsara.com/company/careers/roles/8113356?gh_jid=8113356</t>
+          <t>https://www.samsara.com/company/careers/roles/7858719?gh_jid=7858719</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>[B] San Francisco - SF9.</t>
+          <t>[B] Remote - Seattle.</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -9402,11 +8637,6 @@
       <c r="M190" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N190" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O190" t="inlineStr">
@@ -9423,12 +8653,12 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Lead Machine Learning Engineer - ML Infrastructure</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>https://www.samsara.com/company/careers/roles/7721193?gh_jid=7721193</t>
+          <t>https://www.samsara.com/company/careers/roles/7964565?gh_jid=7964565</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
@@ -9449,11 +8679,6 @@
       <c r="M191" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N191" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O191" t="inlineStr">
@@ -9470,17 +8695,17 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>People Analytics AI Engineer</t>
+          <t>Senior Data Engineer II</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>https://www.samsara.com/company/careers/roles/7858719?gh_jid=7858719</t>
+          <t>https://www.samsara.com/company/careers/roles/8039914?gh_jid=8039914</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>[B] Remote - Seattle.</t>
+          <t>[B] Remote - US.</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -9496,11 +8721,6 @@
       <c r="M192" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N192" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O192" t="inlineStr">
@@ -9517,12 +8737,12 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>https://www.samsara.com/company/careers/roles/7964565?gh_jid=7964565</t>
+          <t>https://www.samsara.com/company/careers/roles/8055245?gh_jid=8055245</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
@@ -9543,11 +8763,6 @@
       <c r="M193" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N193" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O193" t="inlineStr">
@@ -9564,12 +8779,12 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Senior Data Engineer II</t>
+          <t>Software Engineer - Data Platform</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>https://www.samsara.com/company/careers/roles/8039914?gh_jid=8039914</t>
+          <t>https://www.samsara.com/company/careers/roles/7922530?gh_jid=7922530</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
@@ -9590,11 +8805,6 @@
       <c r="M194" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N194" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O194" t="inlineStr">
@@ -9611,12 +8821,12 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Staff Machine Learning Engineer - Edge AI</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>https://www.samsara.com/company/careers/roles/8055245?gh_jid=8055245</t>
+          <t>https://www.samsara.com/company/careers/roles/7266357?gh_jid=7266357</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
@@ -9637,11 +8847,6 @@
       <c r="M195" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N195" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O195" t="inlineStr">
@@ -9653,22 +8858,22 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Samsara</t>
+          <t>Faire</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Software Engineer - Data Platform</t>
+          <t>Senior Client Platform Engineer</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>https://www.samsara.com/company/careers/roles/7922530?gh_jid=7922530</t>
+          <t>https://boards.greenhouse.io/faire/jobs/8758597002</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>[B] Remote - US.</t>
+          <t>[B] San Francisco, CA.</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -9684,11 +8889,6 @@
       <c r="M196" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N196" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O196" t="inlineStr">
@@ -9700,22 +8900,22 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Samsara</t>
+          <t>Faire</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Staff Machine Learning Engineer - Edge AI</t>
+          <t>Senior Data Scientist / Machine Learning Engineer - Listing Quality</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>https://www.samsara.com/company/careers/roles/7266357?gh_jid=7266357</t>
+          <t>https://boards.greenhouse.io/faire/jobs/8831888002</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>[B] Remote - US.</t>
+          <t>[C] San Francisco, CA.</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -9731,11 +8931,6 @@
       <c r="M197" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N197" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O197" t="inlineStr">
@@ -9752,17 +8947,17 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Senior Client Platform Engineer</t>
+          <t>Senior Finance Analytics Engineer</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/faire/jobs/8758597002</t>
+          <t>https://boards.greenhouse.io/faire/jobs/8828560002</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>[B] San Francisco, CA.</t>
+          <t>[B] NYC, NY; San Francisco, CA.</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -9778,11 +8973,6 @@
       <c r="M198" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N198" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O198" t="inlineStr">
@@ -9799,17 +8989,17 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Senior Data Scientist / Machine Learning Engineer - Listing Quality</t>
+          <t>Senior Staff Machine Learning Platform Engineer</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/faire/jobs/8831888002</t>
+          <t>https://boards.greenhouse.io/faire/jobs/8731172002</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>[C] San Francisco, CA.</t>
+          <t>[B] Remote - US; San Francisco, CA.</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -9825,11 +9015,6 @@
       <c r="M199" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N199" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O199" t="inlineStr">
@@ -9846,17 +9031,17 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Senior Finance Analytics Engineer</t>
+          <t>Staff Machine Learning Platform Engineer</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/faire/jobs/8828560002</t>
+          <t>https://boards.greenhouse.io/faire/jobs/8426107002</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>[B] NYC, NY; San Francisco, CA.</t>
+          <t>[B] San Francisco, CA.</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -9872,11 +9057,6 @@
       <c r="M200" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N200" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O200" t="inlineStr">
@@ -9888,22 +9068,22 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Faire</t>
+          <t>Gusto</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Senior Staff Machine Learning Platform Engineer</t>
+          <t>Data Scientist, Risk</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/faire/jobs/8731172002</t>
+          <t>https://job-boards.greenhouse.io/gusto/jobs/7656216</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>[B] Remote - US; San Francisco, CA.</t>
+          <t>[C] San Francisco, CA - Hybrid.</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -9919,11 +9099,6 @@
       <c r="M201" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N201" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O201" t="inlineStr">
@@ -9935,22 +9110,22 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Faire</t>
+          <t>Gusto</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Staff Machine Learning Platform Engineer</t>
+          <t>Enterprise Application AI Engineer</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/faire/jobs/8426107002</t>
+          <t>https://job-boards.greenhouse.io/gusto/jobs/7369003</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>[B] San Francisco, CA.</t>
+          <t>[B] San Francisco, CA - Hybrid.</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -9970,12 +9145,12 @@
       </c>
       <c r="N202" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="O202" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -9987,17 +9162,17 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Data Scientist, Risk</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gusto/jobs/7656216</t>
+          <t>https://job-boards.greenhouse.io/gusto/jobs/8099751</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>[C] San Francisco, CA - Hybrid.</t>
+          <t>[B] Denver, CO/NYC/SF - Hybrid.</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -10017,12 +9192,12 @@
       </c>
       <c r="N203" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="O203" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -10034,17 +9209,17 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Enterprise Application AI Engineer</t>
+          <t>Senior Staff Engineer - Tax Platform Engineering</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gusto/jobs/7369003</t>
+          <t>https://job-boards.greenhouse.io/gusto/jobs/8013480</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>[B] San Francisco, CA - Hybrid.</t>
+          <t>[B] Chicago-Remote; Denver/NYC/SF-Hybrid.</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -10062,14 +9237,9 @@
           <t>Optional</t>
         </is>
       </c>
-      <c r="N204" t="inlineStr">
-        <is>
-          <t>Long</t>
-        </is>
-      </c>
       <c r="O204" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -10081,17 +9251,17 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer, ML Platform</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gusto/jobs/8099751</t>
+          <t>https://job-boards.greenhouse.io/gusto/jobs/8073232</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>[B] Denver, CO/NYC/SF - Hybrid.</t>
+          <t>[B] Denver/NYC/SF - Hybrid.</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -10109,36 +9279,31 @@
           <t>Optional</t>
         </is>
       </c>
-      <c r="N205" t="inlineStr">
-        <is>
-          <t>Long</t>
-        </is>
-      </c>
       <c r="O205" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Gusto</t>
+          <t>Justworks</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Senior Staff Engineer - Tax Platform Engineering</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gusto/jobs/8013480</t>
+          <t>https://boards.greenhouse.io/justworks/jobs/7960800</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>[B] Chicago-Remote; Denver/NYC/SF-Hybrid.</t>
+          <t>[C] New York, New York.</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -10154,11 +9319,6 @@
       <c r="M206" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N206" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O206" t="inlineStr">
@@ -10170,22 +9330,22 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Gusto</t>
+          <t>Brex</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Software Engineer, ML Platform</t>
+          <t>AI Engineer, Product</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gusto/jobs/8073232</t>
+          <t>https://www.brex.com/careers/8606845002</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>[B] Denver/NYC/SF - Hybrid.</t>
+          <t>[B] San Francisco, CA.</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -10201,11 +9361,6 @@
       <c r="M207" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N207" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O207" t="inlineStr">
@@ -10217,22 +9372,22 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Justworks</t>
+          <t>Brex</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/justworks/jobs/7960800</t>
+          <t>https://www.brex.com/careers/8366850002</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>[C] New York, New York.</t>
+          <t>[B] San Francisco, CA.</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -10248,11 +9403,6 @@
       <c r="M208" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N208" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O208" t="inlineStr">
@@ -10269,12 +9419,12 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>AI Engineer, Product</t>
+          <t>Staff Software Engineer, Product Data Platform</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>https://www.brex.com/careers/8606845002</t>
+          <t>https://www.brex.com/careers/8430182002</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
@@ -10294,17 +9444,12 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>Optional</t>
-        </is>
-      </c>
-      <c r="N209" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>Required</t>
         </is>
       </c>
       <c r="O209" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -10316,17 +9461,17 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Staff Software Engineer, Product Data Platform</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>https://www.brex.com/careers/8366850002</t>
+          <t>https://www.brex.com/careers/8430197002</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>[B] San Francisco, CA.</t>
+          <t>[B] Seattle, WA.</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -10341,39 +9486,34 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>Optional</t>
-        </is>
-      </c>
-      <c r="N210" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>Required</t>
         </is>
       </c>
       <c r="O210" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Brex</t>
+          <t>Verkada</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Staff Software Engineer, Product Data Platform</t>
+          <t>Backend Engineer - Connectivity</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>https://www.brex.com/careers/8430182002</t>
+          <t>https://job-boards.greenhouse.io/verkada/jobs/5194598007</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>[B] San Francisco, CA.</t>
+          <t>[B] San Mateo, CA.</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -10388,39 +9528,34 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>Required</t>
-        </is>
-      </c>
-      <c r="N211" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>No field</t>
         </is>
       </c>
       <c r="O211" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Brex</t>
+          <t>Verkada</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Staff Software Engineer, Product Data Platform</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>https://www.brex.com/careers/8430197002</t>
+          <t>https://job-boards.greenhouse.io/verkada/jobs/5233096007</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>[B] Seattle, WA.</t>
+          <t>[B] San Mateo, CA.</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -10435,17 +9570,12 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>Required</t>
-        </is>
-      </c>
-      <c r="N212" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>Optional</t>
         </is>
       </c>
       <c r="O212" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -10457,12 +9587,12 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Backend Engineer - Connectivity</t>
+          <t>Senior Backend Engineer - Access Control</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/verkada/jobs/5194598007</t>
+          <t>https://job-boards.greenhouse.io/verkada/jobs/5233103007</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
@@ -10482,12 +9612,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>No field</t>
-        </is>
-      </c>
-      <c r="N213" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>Optional</t>
         </is>
       </c>
       <c r="O213" t="inlineStr">
@@ -10504,12 +9629,12 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Senior Backend Engineer - Device Platform</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/verkada/jobs/5233096007</t>
+          <t>https://job-boards.greenhouse.io/verkada/jobs/5233095007</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
@@ -10530,11 +9655,6 @@
       <c r="M214" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N214" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O214" t="inlineStr">
@@ -10551,12 +9671,12 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer - Access Control</t>
+          <t>Senior Software Engineer, Data Platform</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/verkada/jobs/5233103007</t>
+          <t>https://job-boards.greenhouse.io/verkada/jobs/5215882007</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
@@ -10577,11 +9697,6 @@
       <c r="M215" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N215" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O215" t="inlineStr">
@@ -10598,12 +9713,12 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer - Device Platform</t>
+          <t>Software Engineer - Data Platform</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/verkada/jobs/5233095007</t>
+          <t>https://job-boards.greenhouse.io/verkada/jobs/4129304007</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
@@ -10624,11 +9739,6 @@
       <c r="M216" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N216" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O216" t="inlineStr">
@@ -10645,12 +9755,12 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Platform</t>
+          <t>Staff Backend Engineer - Device Security</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/verkada/jobs/5215882007</t>
+          <t>https://job-boards.greenhouse.io/verkada/jobs/5154370007</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
@@ -10671,11 +9781,6 @@
       <c r="M217" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N217" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O217" t="inlineStr">
@@ -10692,12 +9797,12 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Software Engineer - Data Platform</t>
+          <t>Staff Backend Engineer - Licensing &amp; Revenue Platform</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/verkada/jobs/4129304007</t>
+          <t>https://job-boards.greenhouse.io/verkada/jobs/5221363007</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
@@ -10717,12 +9822,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>Optional</t>
-        </is>
-      </c>
-      <c r="N218" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>No field</t>
         </is>
       </c>
       <c r="O218" t="inlineStr">
@@ -10739,12 +9839,12 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Staff Backend Engineer - Device Security</t>
+          <t>Staff Backend Engineer - Streaming</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/verkada/jobs/5154370007</t>
+          <t>https://job-boards.greenhouse.io/verkada/jobs/4128603007</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
@@ -10765,11 +9865,6 @@
       <c r="M219" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N219" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O219" t="inlineStr">
@@ -10781,22 +9876,22 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Verkada</t>
+          <t>Scale AI</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Staff Backend Engineer - Licensing &amp; Revenue Platform</t>
+          <t>DevOps Engineer, Infrastructure &amp; Security</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/verkada/jobs/5221363007</t>
+          <t>https://job-boards.greenhouse.io/scaleai/jobs/4674863005</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>[B] San Mateo, CA.</t>
+          <t>[B] Washington, DC.</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -10811,12 +9906,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>No field</t>
-        </is>
-      </c>
-      <c r="N220" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>Optional</t>
         </is>
       </c>
       <c r="O220" t="inlineStr">
@@ -10828,22 +9918,22 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Verkada</t>
+          <t>Scale AI</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Staff Backend Engineer - Streaming</t>
+          <t>Machine Learning Engineer, Public Sector</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/verkada/jobs/4128603007</t>
+          <t>https://job-boards.greenhouse.io/scaleai/jobs/4631848005</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>[B] San Mateo, CA.</t>
+          <t>[B] Denver, CO; Honolulu, HI; Washington, DC.</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -10859,11 +9949,6 @@
       <c r="M221" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N221" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O221" t="inlineStr">
@@ -10880,17 +9965,17 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>DevOps Engineer, Infrastructure &amp; Security</t>
+          <t>Senior Machine Learning Engineer, Public Sector</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/scaleai/jobs/4674863005</t>
+          <t>https://job-boards.greenhouse.io/scaleai/jobs/4732798005</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>[B] Washington, DC.</t>
+          <t>[B] Denver, CO; Honolulu, HI; Washington, DC.</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -10906,11 +9991,6 @@
       <c r="M222" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N222" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O222" t="inlineStr">
@@ -10927,17 +10007,17 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Public Sector</t>
+          <t>Staff Machine Learning Engineer, Public Sector</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/scaleai/jobs/4631848005</t>
+          <t>https://job-boards.greenhouse.io/scaleai/jobs/4654382005</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>[B] Denver, CO; Honolulu, HI; Washington, DC.</t>
+          <t>[B] Denver, CO; Washington, DC.</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -10953,11 +10033,6 @@
       <c r="M223" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N223" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O223" t="inlineStr">
@@ -10974,17 +10049,17 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Public Sector</t>
+          <t>Staff Software Engineer, Data Platform</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/scaleai/jobs/4732798005</t>
+          <t>https://job-boards.greenhouse.io/scaleai/jobs/4649903005</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>[B] Denver, CO; Honolulu, HI; Washington, DC.</t>
+          <t>[B] San Francisco, CA; New York, NY.</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -11000,11 +10075,6 @@
       <c r="M224" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N224" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="O224" t="inlineStr">
@@ -11016,22 +10086,22 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Scale AI</t>
+          <t>Spotify</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Staff Machine Learning Engineer, Public Sector</t>
+          <t>Data Scientist - Music Mission</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/scaleai/jobs/4654382005</t>
+          <t>https://jobs.lever.co/spotify/1bbaf909-5ff3-4ed6-87ca-f7ff007a169c</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>[B] Denver, CO; Washington, DC.</t>
+          <t>[C] New York, NY.</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -11046,39 +10116,39 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>No field</t>
         </is>
       </c>
       <c r="N225" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="O225" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Scale AI</t>
+          <t>Spotify</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Staff Software Engineer, Data Platform</t>
+          <t>Data Scientist - Music Promotion</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/scaleai/jobs/4649903005</t>
+          <t>https://jobs.lever.co/spotify/56ea6f2e-f20b-4e46-ab94-d3eb0a89482d</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>[B] San Francisco, CA; New York, NY.</t>
+          <t>[C] New York, NY.</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -11093,17 +10163,17 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>No field</t>
         </is>
       </c>
       <c r="N226" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="O226" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
@@ -11115,17 +10185,17 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Data Scientist - Music Mission</t>
+          <t>Senior Machine Learning Engineer - Policy &amp; Safety</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/spotify/1bbaf909-5ff3-4ed6-87ca-f7ff007a169c</t>
+          <t>https://jobs.lever.co/spotify/9eca14d3-8e0b-46de-8161-704e07f3d9d0</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>[C] New York, NY.</t>
+          <t>[B] New York, NY.</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -11162,17 +10232,17 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Data Scientist - Music Promotion</t>
+          <t>Senior Machine Learning Engineer, Personalization, Muse</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/spotify/56ea6f2e-f20b-4e46-ab94-d3eb0a89482d</t>
+          <t>https://jobs.lever.co/spotify/d7c43743-2240-45b6-bc31-33e50cbaba4a</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>[C] New York, NY.</t>
+          <t>[B] New York, NY.</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -11209,12 +10279,12 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - Policy &amp; Safety</t>
+          <t>Senior Staff Machine Learning Engineer - Content Platform</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/spotify/9eca14d3-8e0b-46de-8161-704e07f3d9d0</t>
+          <t>https://jobs.lever.co/spotify/47d4eabf-8d5a-4dab-ac72-de7b5b56841c</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
@@ -11256,12 +10326,12 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Personalization, Muse</t>
+          <t>Staff Machine Learning Engineer, Home Surfaces</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/spotify/d7c43743-2240-45b6-bc31-33e50cbaba4a</t>
+          <t>https://jobs.lever.co/spotify/281e7db9-86ba-4a1c-8773-c23b96ed32dc</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
@@ -11303,12 +10373,12 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Senior Staff Machine Learning Engineer - Content Platform</t>
+          <t>Staff Machine Learning Engineer, Personalization</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/spotify/47d4eabf-8d5a-4dab-ac72-de7b5b56841c</t>
+          <t>https://jobs.lever.co/spotify/9761af44-be41-43ca-8c01-79cdbb2aef93</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
@@ -11345,161 +10415,67 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Spotify</t>
+          <t>Narmi</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Staff Machine Learning Engineer, Home Surfaces</t>
+          <t>Software Engineer - Forward Deployed</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>New York, NY (in-person ~3 days/wk; friend says full remote OK)</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/spotify/281e7db9-86ba-4a1c-8773-c23b96ed32dc</t>
+          <t>https://jobs.gem.com/narmi/am9icG9zdDrAJaEbCOTTdxbRZOF7nP2T</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>$91k-$110k</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>[B] New York, NY.</t>
+          <t>Forward-deployed role: customer-facing builds, Python/Node/React, LLM/agent nice-to-have, AWS nice-to-have. Referral via friend.</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>tailoring</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>resume/narmi branch (jack-resume-narmi.pdf)</t>
         </is>
       </c>
       <c r="L232" t="inlineStr">
         <is>
-          <t>Source: Greenhouse/Lever</t>
+          <t>Source: Gem; resume tailored, cover letter not started</t>
         </is>
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>No field</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="N232" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Short</t>
         </is>
       </c>
       <c r="O232" t="inlineStr">
         <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" t="inlineStr">
-        <is>
-          <t>Spotify</t>
-        </is>
-      </c>
-      <c r="B233" t="inlineStr">
-        <is>
-          <t>Staff Machine Learning Engineer, Personalization</t>
-        </is>
-      </c>
-      <c r="D233" t="inlineStr">
-        <is>
-          <t>https://jobs.lever.co/spotify/9761af44-be41-43ca-8c01-79cdbb2aef93</t>
-        </is>
-      </c>
-      <c r="G233" t="inlineStr">
-        <is>
-          <t>[B] New York, NY.</t>
-        </is>
-      </c>
-      <c r="H233" t="inlineStr">
-        <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="L233" t="inlineStr">
-        <is>
-          <t>Source: Greenhouse/Lever</t>
-        </is>
-      </c>
-      <c r="M233" t="inlineStr">
-        <is>
-          <t>No field</t>
-        </is>
-      </c>
-      <c r="N233" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="O233" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" t="inlineStr">
-        <is>
-          <t>Narmi</t>
-        </is>
-      </c>
-      <c r="B234" t="inlineStr">
-        <is>
-          <t>Software Engineer - Forward Deployed</t>
-        </is>
-      </c>
-      <c r="C234" t="inlineStr">
-        <is>
-          <t>New York, NY (in-person ~3 days/wk; friend says full remote OK)</t>
-        </is>
-      </c>
-      <c r="D234" t="inlineStr">
-        <is>
-          <t>https://jobs.gem.com/narmi/am9icG9zdDrAJaEbCOTTdxbRZOF7nP2T</t>
-        </is>
-      </c>
-      <c r="F234" t="inlineStr">
-        <is>
-          <t>$91k-$110k</t>
-        </is>
-      </c>
-      <c r="G234" t="inlineStr">
-        <is>
-          <t>Forward-deployed role: customer-facing builds, Python/Node/React, LLM/agent nice-to-have, AWS nice-to-have. Referral via friend.</t>
-        </is>
-      </c>
-      <c r="H234" t="inlineStr">
-        <is>
-          <t>tailoring</t>
-        </is>
-      </c>
-      <c r="I234" t="inlineStr">
-        <is>
-          <t>resume/narmi branch (jack-resume-narmi.pdf)</t>
-        </is>
-      </c>
-      <c r="L234" t="inlineStr">
-        <is>
-          <t>Source: Gem; resume tailored, cover letter not started</t>
-        </is>
-      </c>
-      <c r="M234" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="N234" t="inlineStr">
-        <is>
-          <t>Short</t>
-        </is>
-      </c>
-      <c r="O234" t="inlineStr">
-        <is>
           <t>Low</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O234"/>
+  <autoFilter ref="A1:O232"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/tracker.xlsx
+++ b/tracker.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Tracker" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Tracker'!$A$1:$O$232</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Tracker'!$A$1:$O$234</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O232"/>
+  <dimension ref="A1:O234"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -619,32 +619,37 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Catapult Sports</t>
+          <t>PrizePicks</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Agentic AI Engineer</t>
+          <t>Staff Machine Learning Engineer</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/catapultsports/jobs/8083093</t>
+          <t>https://prizepicks.com/position?gh_jid=7618741003</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>$220k-$280k</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>[B] Athlete wearable/tracking data — strong domain fit. Listed as New York only, remote status unconfirmed — verify before applying.</t>
+          <t>[C] Staff/P5 — stretch role, highest comp found.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>applied</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Source: Greenhouse</t>
+          <t>Not qualified. Source: Greenhouse</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -652,9 +657,14 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Short</t>
+        </is>
+      </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -666,17 +676,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Senior ML/Data Engineer</t>
+          <t>Agentic AI Engineer</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/catapultsports/jobs/8083099</t>
+          <t>https://job-boards.greenhouse.io/catapultsports/jobs/8083093</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>[B] Same caveat: New York location, remote status unconfirmed — verify before applying.</t>
+          <t>[B] Athlete wearable/tracking data — strong domain fit. Listed as New York only, remote status unconfirmed — verify before applying.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -692,11 +702,6 @@
       <c r="M5" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>Short</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -708,22 +713,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>GitLab</t>
+          <t>Catapult Sports</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Senior ML/Data Engineer</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8565469002</t>
+          <t>https://job-boards.greenhouse.io/catapultsports/jobs/8083099</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>[B] Remote, US. Fully-remote company, strong AI/infra fit.</t>
+          <t>[B] Same caveat: New York location, remote status unconfirmed — verify before applying.</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -739,6 +744,11 @@
       <c r="M6" t="inlineStr">
         <is>
           <t>Optional</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Short</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -755,17 +765,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Staff Backend Engineer, Database Automation (Go)</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8770702002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8565469002</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>[B] Remote, US. Database/infra automation.</t>
+          <t>[B] Remote, US. Fully-remote company, strong AI/infra fit.</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -797,27 +807,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer, GitLab Orbit</t>
+          <t>Staff Backend Engineer (Ruby), AI Engineering: DAP Repository Flows</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8771527002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8646573002</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>[B] Remote, US. Platform engineering.</t>
+          <t>[B] Remote, US.</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>applied</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Source: Greenhouse</t>
+          <t>Not qualified. Source: Greenhouse</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -839,17 +849,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Backend Engineer, AI Engineering: Duo Chat</t>
+          <t>Staff Backend Engineer, Database Automation (Go)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8698314002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8770702002</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>[B] Remote, US.</t>
+          <t>[B] Remote, US. Database/infra automation.</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -881,17 +891,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Fullstack Engineer (TypeScript), AI Engineering: Duo Client SDK</t>
+          <t>Senior Platform Engineer, GitLab Orbit</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8698330002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8771527002</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>[C] Remote, US. More frontend-leaning than your other targets.</t>
+          <t>[B] Remote, US. Platform engineering.</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -907,11 +917,6 @@
       <c r="M10" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>Short</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -923,22 +928,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Grafana Labs</t>
+          <t>GitLab</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Staff AI Engineer</t>
+          <t>Backend Engineer, AI Engineering: Duo Chat</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/grafanalabs/jobs/6092955004</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8698314002</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>[B] United States (Remote).</t>
+          <t>[B] Remote, US.</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -953,7 +958,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>No field</t>
+          <t>Optional</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -965,22 +970,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Grafana Labs</t>
+          <t>GitLab</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Staff Backend Engineer - Databases Tempo</t>
+          <t>Fullstack Engineer (TypeScript), AI Engineering: Duo Client SDK</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/grafanalabs/jobs/5982444004</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8698330002</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>[B] United States (Remote). Observability/telemetry data infra.</t>
+          <t>[C] Remote, US. More frontend-leaning than your other targets.</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -995,7 +1000,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>No field</t>
+          <t>Optional</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1017,17 +1022,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Staff Backend Engineer - Mimir Query, Databases</t>
+          <t>Staff AI Engineer</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/grafanalabs/jobs/6146604004</t>
+          <t>https://job-boards.greenhouse.io/grafanalabs/jobs/6092955004</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>[B] United States (Remote). Observability/telemetry data infra.</t>
+          <t>[B] United States (Remote).</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1059,17 +1064,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Staff Software Engineer - Adaptive Telemetry, Databases</t>
+          <t>Staff Backend Engineer - Databases Tempo</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/grafanalabs/jobs/6108384004</t>
+          <t>https://job-boards.greenhouse.io/grafanalabs/jobs/5982444004</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>[B] United States (Remote).</t>
+          <t>[B] United States (Remote). Observability/telemetry data infra.</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1085,6 +1090,11 @@
       <c r="M14" t="inlineStr">
         <is>
           <t>No field</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Short</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1096,27 +1106,27 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Elastic</t>
+          <t>Grafana Labs</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Platform Engineer - Kubernetes</t>
+          <t>Staff Backend Engineer - Mimir Query, Databases</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://jobs.elastic.co/jobs?gh_jid=8047349</t>
+          <t>https://job-boards.greenhouse.io/grafanalabs/jobs/6146604004</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>[B] United States. Elastic is a distributed-first company — K8s platform role builds directly on your Trustless Engineering experience.</t>
+          <t>[B] United States (Remote). Observability/telemetry data infra.</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>applied</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1126,7 +1136,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>No field</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1138,27 +1148,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Elastic</t>
+          <t>Grafana Labs</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Agentic AI Engineer</t>
+          <t>Staff Software Engineer - Adaptive Telemetry, Databases</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://jobs.elastic.co/jobs?gh_jid=8079636</t>
+          <t>https://job-boards.greenhouse.io/grafanalabs/jobs/6108384004</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>[B] United States. Distributed-first company.</t>
+          <t>[B] United States (Remote).</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>applied</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1168,39 +1178,34 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Optional</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>Long</t>
+          <t>No field</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Vercel</t>
+          <t>Elastic</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Software Engineer - Data Platform</t>
+          <t>Platform Engineer - Kubernetes</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/vercel/jobs/6188400004</t>
+          <t>https://jobs.elastic.co/jobs?gh_jid=8047349</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>[B] Remote - United States. Direct title match.</t>
+          <t>[B] United States. Elastic is a distributed-first company — K8s platform role builds directly on your Trustless Engineering experience.</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1227,22 +1232,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Elastic</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Staff Software Engineer (L4) Data Platform</t>
+          <t>Agentic AI Engineer</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/twilio/jobs/7782805</t>
+          <t>https://jobs.elastic.co/jobs?gh_jid=8079636</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>[B] Remote - US. Direct title match.</t>
+          <t>[B] United States. Distributed-first company.</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1260,31 +1265,36 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Vercel</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Software Engineer, Platform Engineering (L2)</t>
+          <t>Software Engineer - Data Platform</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/twilio/jobs/8026207</t>
+          <t>https://job-boards.greenhouse.io/vercel/jobs/6188400004</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>[C] Remote - US.</t>
+          <t>[B] Remote - United States. Direct title match.</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1311,22 +1321,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Figma</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Staff Software Engineer (L4) Data Platform</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/figma/jobs/6201407004</t>
+          <t>https://job-boards.greenhouse.io/twilio/jobs/7782805</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>[B] SF / NYC / United States — remote option listed alongside hub cities, verify before applying.</t>
+          <t>[B] Remote - US. Direct title match.</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1341,39 +1351,34 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>No field</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>Long</t>
+          <t>Optional</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>AI Engineer – Forward Deployed Engineering (AI FDE)</t>
+          <t>Software Engineer, Platform Engineering (L2)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8546367002</t>
+          <t>https://job-boards.greenhouse.io/twilio/jobs/8026207</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>[C] United States (broad, likely remote-eligible w/ travel). Forward-deployed = customer-facing, different flavor than pure IC infra work.</t>
+          <t>[C] Remote - US.</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1400,22 +1405,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Figma</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Data Engineering &amp; Warehousing (Digital Native Business)</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8761732002</t>
+          <t>https://boards.greenhouse.io/figma/jobs/6201407004</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>[C] United States (broad). Customer-facing solutions architecture, not pure IC.</t>
+          <t>[B] SF / NYC / United States — remote option listed alongside hub cities, verify before applying.</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1430,17 +1435,17 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>No field</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1452,17 +1457,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Data Engineering &amp; Warehousing (Financial Services)</t>
+          <t>AI Engineer – Forward Deployed Engineering (AI FDE)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8692962002</t>
+          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8546367002</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>[C] United States (broad). Customer-facing solutions architecture, not pure IC.</t>
+          <t>[C] United States (broad, likely remote-eligible w/ travel). Forward-deployed = customer-facing, different flavor than pure IC infra work.</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1489,22 +1494,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Staff+ Software Engineer, Data Infrastructure</t>
+          <t>Specialist Solutions Architect - Data Engineering &amp; Warehousing (Digital Native Business)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/anthropic/jobs/5114768008</t>
+          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8761732002</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>[C] Remote-friendly but travel-required. Staff+ is a seniority stretch; every other Anthropic data/ML role requires a hub city (SF/NYC/Seattle) — skipped those as not remote.</t>
+          <t>[C] United States (broad). Customer-facing solutions architecture, not pure IC.</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1519,39 +1524,39 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>No field</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Affirm</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II (Underwriting ML)</t>
+          <t>Specialist Solutions Architect - Data Engineering &amp; Warehousing (Financial Services)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/affirm/jobs/7822387003</t>
+          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8692962002</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>[B] Remote US.</t>
+          <t>[C] United States (broad). Customer-facing solutions architecture, not pure IC.</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1561,7 +1566,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Source: Greenhouse/Lever</t>
+          <t>Source: Greenhouse</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1578,22 +1583,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Affirm</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Model Risk Management Lead, Machine Learning</t>
+          <t>Staff+ Software Engineer, Data Infrastructure</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/affirm/jobs/7775353003</t>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5114768008</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>[B] Remote US.</t>
+          <t>[C] Remote-friendly but travel-required. Staff+ is a seniority stretch; every other Anthropic data/ML role requires a hub city (SF/NYC/Seattle) — skipped those as not remote.</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1603,39 +1608,44 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Source: Greenhouse/Lever</t>
+          <t>Source: Greenhouse</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>No field</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Long</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Airbnb</t>
+          <t>Affirm</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Principal Machine Learning Engineer- LLM Fine-tuning and Optimization</t>
+          <t>Machine Learning Engineer II (Underwriting ML)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://careers.airbnb.com/positions/7955579?gh_jid=7955579</t>
+          <t>https://job-boards.greenhouse.io/affirm/jobs/7822387003</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>[C] United States.</t>
+          <t>[B] Remote US.</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1662,22 +1672,22 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Airbnb</t>
+          <t>Affirm</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - Payments (Inference)</t>
+          <t>Model Risk Management Lead, Machine Learning</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://careers.airbnb.com/positions/8123037?gh_jid=8123037</t>
+          <t>https://job-boards.greenhouse.io/affirm/jobs/7775353003</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>[C] Remote - USA.</t>
+          <t>[B] Remote US.</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1693,11 +1703,6 @@
       <c r="M28" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>Short</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -1714,17 +1719,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Assistance Engineering</t>
+          <t>Principal Machine Learning Engineer- LLM Fine-tuning and Optimization</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://careers.airbnb.com/positions/8014904?gh_jid=8014904</t>
+          <t>https://careers.airbnb.com/positions/7955579?gh_jid=7955579</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>[B] Remote-USA.</t>
+          <t>[C] United States.</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1756,17 +1761,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Query Intelligence</t>
+          <t>Senior Data Scientist - Payments (Inference)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://careers.airbnb.com/positions/8065789?gh_jid=8065789</t>
+          <t>https://careers.airbnb.com/positions/8123037?gh_jid=8123037</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>[B] United States.</t>
+          <t>[C] Remote - USA.</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1782,6 +1787,11 @@
       <c r="M30" t="inlineStr">
         <is>
           <t>Optional</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Short</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -1798,17 +1808,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Senior Staff Data Engineer - Data Stewardship</t>
+          <t>Senior Machine Learning Engineer, Assistance Engineering</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://careers.airbnb.com/positions/7998356?gh_jid=7998356</t>
+          <t>https://careers.airbnb.com/positions/8014904?gh_jid=8014904</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>[B] United States.</t>
+          <t>[B] Remote-USA.</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1840,12 +1850,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Senior Staff Data Engineer, Foundational Data</t>
+          <t>Senior Machine Learning Engineer, Query Intelligence</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://careers.airbnb.com/positions/8224032?gh_jid=8224032</t>
+          <t>https://careers.airbnb.com/positions/8065789?gh_jid=8065789</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1882,12 +1892,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Senior Staff Machine Learning Engineer, Data &amp; Eval</t>
+          <t>Senior Staff Data Engineer - Data Stewardship</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://careers.airbnb.com/positions/6757302?gh_jid=6757302</t>
+          <t>https://careers.airbnb.com/positions/7998356?gh_jid=7998356</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1924,17 +1934,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Senior Staff Machine Learning Engineer, Growth Platform Engineering</t>
+          <t>Senior Staff Data Engineer, Foundational Data</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://careers.airbnb.com/positions/7747259?gh_jid=7747259</t>
+          <t>https://careers.airbnb.com/positions/8224032?gh_jid=8224032</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>[B] Remote - USA.</t>
+          <t>[B] United States.</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -1966,17 +1976,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Senior Staff Machine Learning Engineer, Guest &amp; Host</t>
+          <t>Senior Staff Machine Learning Engineer, Data &amp; Eval</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://careers.airbnb.com/positions/7005605?gh_jid=7005605</t>
+          <t>https://careers.airbnb.com/positions/6757302?gh_jid=6757302</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>[B] Remote - USA.</t>
+          <t>[B] United States.</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -1992,11 +2002,6 @@
       <c r="M35" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>Short</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -2013,12 +2018,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Senior Staff Machine Learning Engineer, Post Training</t>
+          <t>Senior Staff Machine Learning Engineer, Growth Platform Engineering</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://careers.airbnb.com/positions/7858738?gh_jid=7858738</t>
+          <t>https://careers.airbnb.com/positions/7747259?gh_jid=7747259</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2055,12 +2060,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Senior Staff Machine Learning Engineer, Trust</t>
+          <t>Senior Staff Machine Learning Engineer, Guest &amp; Host</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://careers.airbnb.com/positions/7592146?gh_jid=7592146</t>
+          <t>https://careers.airbnb.com/positions/7005605?gh_jid=7005605</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2081,6 +2086,11 @@
       <c r="M37" t="inlineStr">
         <is>
           <t>Optional</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Short</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -2097,12 +2107,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Staff Backend Engineer - Ads Platform</t>
+          <t>Senior Staff Machine Learning Engineer, Post Training</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://careers.airbnb.com/positions/8074897?gh_jid=8074897</t>
+          <t>https://careers.airbnb.com/positions/7858738?gh_jid=7858738</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2139,17 +2149,17 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Staff Machine Learning Engineer, Traffic Intelligence</t>
+          <t>Senior Staff Machine Learning Engineer, Trust</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://careers.airbnb.com/positions/8129371?gh_jid=8129371</t>
+          <t>https://careers.airbnb.com/positions/7592146?gh_jid=7592146</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>[B] United States.</t>
+          <t>[B] Remote - USA.</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2176,22 +2186,22 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Block</t>
+          <t>Airbnb</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Data Scientist, Payments</t>
+          <t>Staff Backend Engineer - Ads Platform</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>http://block.xyz/careers/jobs/5214784008?gh_jid=5214784008</t>
+          <t>https://careers.airbnb.com/positions/8074897?gh_jid=8074897</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>[C] Bay Area, CA.</t>
+          <t>[B] Remote - USA.</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2209,36 +2219,31 @@
           <t>Optional</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>Long</t>
-        </is>
-      </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Block</t>
+          <t>Airbnb</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Enterprise People Platform Engineer</t>
+          <t>Staff Machine Learning Engineer, Traffic Intelligence</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>http://block.xyz/careers/jobs/5381210008?gh_jid=5381210008</t>
+          <t>https://careers.airbnb.com/positions/8129371?gh_jid=8129371</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>[B] Bay Area, CA.</t>
+          <t>[B] United States.</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2256,14 +2261,9 @@
           <t>Optional</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>Long</t>
-        </is>
-      </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -2275,17 +2275,17 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer, AI &amp; DX Analytics</t>
+          <t>Data Scientist, Payments</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>http://block.xyz/careers/jobs/5424561008?gh_jid=5424561008</t>
+          <t>http://block.xyz/careers/jobs/5214784008?gh_jid=5214784008</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>[B] Bay Area, CA.</t>
+          <t>[C] Bay Area, CA.</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2322,17 +2322,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer, AI &amp; DX Analytics</t>
+          <t>Enterprise People Platform Engineer</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>http://block.xyz/careers/jobs/5434325008?gh_jid=5434325008</t>
+          <t>http://block.xyz/careers/jobs/5381210008?gh_jid=5381210008</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>[B] New York, NY.</t>
+          <t>[B] Bay Area, CA.</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2369,12 +2369,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Risk</t>
+          <t>Senior Analytics Engineer, AI &amp; DX Analytics</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>http://block.xyz/careers/jobs/5281312008?gh_jid=5281312008</t>
+          <t>http://block.xyz/careers/jobs/5424561008?gh_jid=5424561008</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2394,17 +2394,17 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Optional</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -2416,17 +2416,17 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Senior Data Scientist, Risk and Support</t>
+          <t>Senior Analytics Engineer, AI &amp; DX Analytics</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>http://block.xyz/careers/jobs/5418716008?gh_jid=5418716008</t>
+          <t>http://block.xyz/careers/jobs/5434325008?gh_jid=5434325008</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>[C] Seattle, WA.</t>
+          <t>[B] New York, NY.</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2463,17 +2463,17 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Senior Data Scientist, Risk and Support</t>
+          <t>Senior Data Engineer, Risk</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>http://block.xyz/careers/jobs/5412922008?gh_jid=5412922008</t>
+          <t>http://block.xyz/careers/jobs/5281312008?gh_jid=5281312008</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>[C] Bay Area, CA.</t>
+          <t>[B] Bay Area, CA.</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2488,17 +2488,17 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
@@ -2510,17 +2510,17 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Senior ML/AI Modeler, Risk Automation Machine Learning</t>
+          <t>Senior Data Scientist, Risk and Support</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>http://block.xyz/careers/jobs/5394441008?gh_jid=5394441008</t>
+          <t>http://block.xyz/careers/jobs/5418716008?gh_jid=5418716008</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>[B] Bay Area, CA.</t>
+          <t>[C] Seattle, WA.</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2557,17 +2557,17 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Senior Data Scientist, Risk and Support</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>http://block.xyz/careers/jobs/5182994008?gh_jid=5182994008</t>
+          <t>http://block.xyz/careers/jobs/5412922008?gh_jid=5412922008</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>[B] New York, NY.</t>
+          <t>[C] Bay Area, CA.</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2604,12 +2604,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Senior ML/AI Modeler, Risk Automation Machine Learning</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>http://block.xyz/careers/jobs/5181749008?gh_jid=5181749008</t>
+          <t>http://block.xyz/careers/jobs/5394441008?gh_jid=5394441008</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -2651,17 +2651,17 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Platform</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>http://block.xyz/careers/jobs/5381381008?gh_jid=5381381008</t>
+          <t>http://block.xyz/careers/jobs/5182994008?gh_jid=5182994008</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>[B] Bay Area, CA.</t>
+          <t>[B] New York, NY.</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Staff Applied Machine Learning Engineer - Intelligent Data, Signals &amp; Systems</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>http://block.xyz/careers/jobs/4959469008?gh_jid=4959469008</t>
+          <t>http://block.xyz/careers/jobs/5181749008?gh_jid=5181749008</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -2745,17 +2745,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Staff Data Scientist, Pricing</t>
+          <t>Software Engineer, Data Platform</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>http://block.xyz/careers/jobs/5364922008?gh_jid=5364922008</t>
+          <t>http://block.xyz/careers/jobs/5381381008?gh_jid=5381381008</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>[C] Bay Area, CA.</t>
+          <t>[B] Bay Area, CA.</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2792,17 +2792,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Staff Machine Learning Engineer (Modeling), Support</t>
+          <t>Staff Applied Machine Learning Engineer - Intelligent Data, Signals &amp; Systems</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>http://block.xyz/careers/jobs/5431987008?gh_jid=5431987008</t>
+          <t>http://block.xyz/careers/jobs/4959469008?gh_jid=4959469008</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>[B] Seattle, WA.</t>
+          <t>[B] Bay Area, CA.</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2839,17 +2839,17 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Staff Product Data Scientist, Lending</t>
+          <t>Staff Data Scientist, Pricing</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>http://block.xyz/careers/jobs/5366281008?gh_jid=5366281008</t>
+          <t>http://block.xyz/careers/jobs/5364922008?gh_jid=5364922008</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>[B] New York, NY.</t>
+          <t>[C] Bay Area, CA.</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2886,12 +2886,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Staff Product Data Scientist, Lending</t>
+          <t>Staff Machine Learning Engineer (Modeling), Support</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>http://block.xyz/careers/jobs/5192640008?gh_jid=5192640008</t>
+          <t>http://block.xyz/careers/jobs/5431987008?gh_jid=5431987008</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>http://block.xyz/careers/jobs/5366284008?gh_jid=5366284008</t>
+          <t>http://block.xyz/careers/jobs/5366281008?gh_jid=5366281008</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>[B] San Francisco, CA.</t>
+          <t>[B] New York, NY.</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -2975,22 +2975,22 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Chime</t>
+          <t>Block</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Data Scientist, Growth Product</t>
+          <t>Staff Product Data Scientist, Lending</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/chime/jobs/8586430002?gh_jid=8586430002</t>
+          <t>http://block.xyz/careers/jobs/5192640008?gh_jid=5192640008</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>[C] San Francisco, CA.</t>
+          <t>[B] Seattle, WA.</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3005,39 +3005,39 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Optional</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Chime</t>
+          <t>Block</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer</t>
+          <t>Staff Product Data Scientist, Lending</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/chime/jobs/8569366002?gh_jid=8569366002</t>
+          <t>http://block.xyz/careers/jobs/5366284008?gh_jid=5366284008</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>[B] Chicago, IL; New York, NY; San Francisco, CA.</t>
+          <t>[B] San Francisco, CA.</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3055,9 +3055,14 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -3069,12 +3074,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Senior Data Scientist, Organic Growth</t>
+          <t>Data Scientist, Growth Product</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/chime/jobs/8790231002?gh_jid=8790231002</t>
+          <t>https://boards.greenhouse.io/chime/jobs/8586430002?gh_jid=8586430002</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -3094,12 +3099,17 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
@@ -3111,17 +3121,17 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Senior Mobile Cross Platform Engineer</t>
+          <t>Senior AI/ML Engineer</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/chime/jobs/8604565002?gh_jid=8604565002</t>
+          <t>https://boards.greenhouse.io/chime/jobs/8569366002?gh_jid=8569366002</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>[B] New York, NY; San Francisco, CA.</t>
+          <t>[B] Chicago, IL; New York, NY; San Francisco, CA.</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -3153,17 +3163,17 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Engineering</t>
+          <t>Senior Data Scientist, Organic Growth</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/chime/jobs/8505462002?gh_jid=8505462002</t>
+          <t>https://boards.greenhouse.io/chime/jobs/8790231002?gh_jid=8790231002</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>[B] San Francisco, CA.</t>
+          <t>[C] San Francisco, CA.</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -3195,17 +3205,17 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Machine Learning Platform</t>
+          <t>Senior Mobile Cross Platform Engineer</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/chime/jobs/8765684002?gh_jid=8765684002</t>
+          <t>https://boards.greenhouse.io/chime/jobs/8604565002?gh_jid=8604565002</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>[B] San Francisco, CA.</t>
+          <t>[B] New York, NY; San Francisco, CA.</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -3232,22 +3242,22 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Dropbox</t>
+          <t>Chime</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/8211529?gh_jid=8211529</t>
+          <t>https://boards.greenhouse.io/chime/jobs/8505462002?gh_jid=8505462002</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>[B] Remote - US: Select locations.</t>
+          <t>[B] San Francisco, CA.</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -3262,39 +3272,34 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr">
-        <is>
-          <t>Unknown</t>
+          <t>Optional</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Epic Games</t>
+          <t>Chime</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Memory</t>
+          <t>Senior Software Engineer, Machine Learning Platform</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://epicgames.com/careers/jobs/6134271004?gh_jid=6134271004</t>
+          <t>https://boards.greenhouse.io/chime/jobs/8765684002?gh_jid=8765684002</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>[B] Cary, NC.</t>
+          <t>[B] San Francisco, CA.</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -3321,22 +3326,22 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Epic Games</t>
+          <t>Dropbox</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Principal AI Engineer, Unreal Assistant</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://epicgames.com/careers/jobs/6200780004?gh_jid=6200780004</t>
+          <t>https://jobs.dropbox.com/listing/8211529?gh_jid=8211529</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>[C] Cary, NC.</t>
+          <t>[B] Remote - US: Select locations.</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -3351,12 +3356,17 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
@@ -3368,17 +3378,17 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Machine Learning Engineer, Memory</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://epicgames.com/careers/jobs/6117889004?gh_jid=6117889004</t>
+          <t>https://epicgames.com/careers/jobs/6134271004?gh_jid=6134271004</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>[C] Cary, NC.</t>
+          <t>[B] Cary, NC.</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -3410,17 +3420,17 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Discovery Recommendations</t>
+          <t>Principal AI Engineer, Unreal Assistant</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://epicgames.com/careers/jobs/5972880004?gh_jid=5972880004</t>
+          <t>https://epicgames.com/careers/jobs/6200780004?gh_jid=6200780004</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>[B] Cary, NC.</t>
+          <t>[C] Cary, NC.</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -3435,39 +3445,34 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr">
-        <is>
-          <t>Unknown</t>
+          <t>Optional</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Instacart</t>
+          <t>Epic Games</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Digital Twin Platform</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>https://instacart.careers/job/?gh_jid=8143145</t>
+          <t>https://epicgames.com/careers/jobs/6117889004?gh_jid=6117889004</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>[B] US - Remote.</t>
+          <t>[C] Cary, NC.</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3494,22 +3499,22 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Instacart</t>
+          <t>Epic Games</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Economist</t>
+          <t>Senior Machine Learning Engineer, Discovery Recommendations</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>https://instacart.careers/job/?gh_jid=8157736</t>
+          <t>https://epicgames.com/careers/jobs/5972880004?gh_jid=5972880004</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>[B] US - Remote.</t>
+          <t>[B] Cary, NC.</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3524,12 +3529,17 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
@@ -3541,12 +3551,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer II, Ads Response Prediction</t>
+          <t>Senior Machine Learning Engineer, Digital Twin Platform</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>https://instacart.careers/job/?gh_jid=7963838</t>
+          <t>https://instacart.careers/job/?gh_jid=8143145</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -3583,12 +3593,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer II, Search &amp; Recommendations Ranking</t>
+          <t>Senior Machine Learning Engineer, Economist</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>https://instacart.careers/job/?gh_jid=7565508</t>
+          <t>https://instacart.careers/job/?gh_jid=8157736</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -3625,12 +3635,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Operations Research</t>
+          <t>Senior Machine Learning Engineer II, Ads Response Prediction</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>https://instacart.careers/job/?gh_jid=7793089</t>
+          <t>https://instacart.careers/job/?gh_jid=7963838</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -3662,22 +3672,22 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>MongoDB</t>
+          <t>Instacart</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer, Fabric</t>
+          <t>Senior Machine Learning Engineer II, Search &amp; Recommendations Ranking</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>https://www.mongodb.com/careers/job/?gh_jid=7727920</t>
+          <t>https://instacart.careers/job/?gh_jid=7565508</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>[B] Austin/NYC/SF.</t>
+          <t>[B] US - Remote.</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -3704,22 +3714,22 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>MongoDB</t>
+          <t>Instacart</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer, Fleet Management</t>
+          <t>Senior Machine Learning Engineer, Operations Research</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>https://www.mongodb.com/careers/job/?gh_jid=7727873</t>
+          <t>https://instacart.careers/job/?gh_jid=7793089</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>[B] multiple US cities.</t>
+          <t>[B] US - Remote.</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -3751,17 +3761,17 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer, Infrastructure Security</t>
+          <t>Senior Site Reliability Engineer, Fabric</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>https://www.mongodb.com/careers/job/?gh_jid=7758610</t>
+          <t>https://www.mongodb.com/careers/job/?gh_jid=7727920</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>[B] Austin/NYC.</t>
+          <t>[B] Austin/NYC/SF.</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -3793,12 +3803,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer, Atlas</t>
+          <t>Senior Site Reliability Engineer, Fleet Management</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>https://www.mongodb.com/careers/job/?gh_jid=7727964</t>
+          <t>https://www.mongodb.com/careers/job/?gh_jid=7727873</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -3835,17 +3845,17 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer, Storage Layer Services</t>
+          <t>Site Reliability Engineer, Infrastructure Security</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>https://www.mongodb.com/careers/job/?gh_jid=7743366</t>
+          <t>https://www.mongodb.com/careers/job/?gh_jid=7758610</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>[B] multiple US cities.</t>
+          <t>[B] Austin/NYC.</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -3872,22 +3882,22 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Pinterest</t>
+          <t>MongoDB</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Data Scientist II, Infrastructure</t>
+          <t>Site Reliability Engineer, Atlas</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>https://www.pinterestcareers.com/jobs/?gh_jid=7816424</t>
+          <t>https://www.mongodb.com/careers/job/?gh_jid=7727964</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>[C] SF/Remote US.</t>
+          <t>[B] multiple US cities.</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -3914,22 +3924,22 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Pinterest</t>
+          <t>MongoDB</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Data Scientist II, ML Infrastructure</t>
+          <t>Site Reliability Engineer, Storage Layer Services</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>https://www.pinterestcareers.com/jobs/?gh_jid=8071670</t>
+          <t>https://www.mongodb.com/careers/job/?gh_jid=7743366</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>[C] Palo Alto/Remote US.</t>
+          <t>[B] multiple US cities.</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -3944,17 +3954,12 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="N79" t="inlineStr">
-        <is>
-          <t>Unknown</t>
+          <t>Optional</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -3966,17 +3971,17 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Core Engineering</t>
+          <t>Data Scientist II, Infrastructure</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>https://www.pinterestcareers.com/jobs/?gh_jid=6121450</t>
+          <t>https://www.pinterestcareers.com/jobs/?gh_jid=7816424</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>[B] SF/Palo Alto/Seattle/Remote US.</t>
+          <t>[C] SF/Remote US.</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -4008,17 +4013,17 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II, Responsible AI</t>
+          <t>Data Scientist II, ML Infrastructure</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>https://www.pinterestcareers.com/jobs/?gh_jid=8162046</t>
+          <t>https://www.pinterestcareers.com/jobs/?gh_jid=8071670</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>[B] SF/Remote US.</t>
+          <t>[C] Palo Alto/Remote US.</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -4033,12 +4038,17 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
@@ -4050,17 +4060,17 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II, Visual AI</t>
+          <t>Machine Learning Engineer, Core Engineering</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>https://www.pinterestcareers.com/jobs/?gh_jid=7697137</t>
+          <t>https://www.pinterestcareers.com/jobs/?gh_jid=6121450</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>[B] SF/Remote US.</t>
+          <t>[B] SF/Palo Alto/Seattle/Remote US.</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -4092,17 +4102,17 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Monetization Engineering</t>
+          <t>Machine Learning Engineer II, Responsible AI</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>https://www.pinterestcareers.com/jobs/?gh_jid=6121543</t>
+          <t>https://www.pinterestcareers.com/jobs/?gh_jid=8162046</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>[B] SF/Palo Alto/Seattle.</t>
+          <t>[B] SF/Remote US.</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -4134,17 +4144,17 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Principal Engineer, Big Data Platform</t>
+          <t>Machine Learning Engineer II, Visual AI</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>https://www.pinterestcareers.com/jobs/?gh_jid=7683981</t>
+          <t>https://www.pinterestcareers.com/jobs/?gh_jid=7697137</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>[C] SF/Remote US.</t>
+          <t>[B] SF/Remote US.</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -4176,17 +4186,17 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Principal Machine Learning Engineer, Ads Delivery</t>
+          <t>Machine Learning Engineer, Monetization Engineering</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>https://www.pinterestcareers.com/jobs/?gh_jid=6963868</t>
+          <t>https://www.pinterestcareers.com/jobs/?gh_jid=6121543</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>[C] SF/Palo Alto/Seattle.</t>
+          <t>[B] SF/Palo Alto/Seattle.</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -4218,17 +4228,17 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer II, tvScientific</t>
+          <t>Principal Engineer, Big Data Platform</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>https://www.pinterestcareers.com/jobs/?gh_jid=7782538</t>
+          <t>https://www.pinterestcareers.com/jobs/?gh_jid=7683981</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>[B] SF/Remote US.</t>
+          <t>[C] SF/Remote US.</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -4260,17 +4270,17 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Sr. Data Scientist, Core</t>
+          <t>Principal Machine Learning Engineer, Ads Delivery</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>https://www.pinterestcareers.com/jobs/?gh_jid=6087213</t>
+          <t>https://www.pinterestcareers.com/jobs/?gh_jid=6963868</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>[C] SF/Remote US.</t>
+          <t>[C] SF/Palo Alto/Seattle.</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -4302,17 +4312,17 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Sr. Data Scientist, Infrastructure</t>
+          <t>Site Reliability Engineer II, tvScientific</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>https://www.pinterestcareers.com/jobs/?gh_jid=8024966</t>
+          <t>https://www.pinterestcareers.com/jobs/?gh_jid=7782538</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>[C] SF/Remote US.</t>
+          <t>[B] SF/Remote US.</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -4344,12 +4354,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Sr. Data Scientist, Marketing</t>
+          <t>Sr. Data Scientist, Core</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>https://www.pinterestcareers.com/jobs/?gh_jid=8011376</t>
+          <t>https://www.pinterestcareers.com/jobs/?gh_jid=6087213</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -4386,17 +4396,17 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Sr. Data Scientist, Monetization</t>
+          <t>Sr. Data Scientist, Infrastructure</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>https://www.pinterestcareers.com/jobs/?gh_jid=5740948</t>
+          <t>https://www.pinterestcareers.com/jobs/?gh_jid=8024966</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>[C] SF/Seattle.</t>
+          <t>[C] SF/Remote US.</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -4428,12 +4438,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Sr. Data Scientist, tvScientific</t>
+          <t>Sr. Data Scientist, Marketing</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>https://www.pinterestcareers.com/jobs/?gh_jid=7642251</t>
+          <t>https://www.pinterestcareers.com/jobs/?gh_jid=8011376</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -4453,17 +4463,12 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="N91" t="inlineStr">
-        <is>
-          <t>Unknown</t>
+          <t>Optional</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -4475,17 +4480,17 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Sr. Machine Learning Engineer, Applied Science</t>
+          <t>Sr. Data Scientist, Monetization</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>https://www.pinterestcareers.com/jobs/?gh_jid=6894747</t>
+          <t>https://www.pinterestcareers.com/jobs/?gh_jid=5740948</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>[B] SF/Remote US.</t>
+          <t>[C] SF/Seattle.</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -4517,17 +4522,17 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Sr. Machine Learning Engineer, Core Engineering</t>
+          <t>Sr. Data Scientist, tvScientific</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>https://www.pinterestcareers.com/jobs/?gh_jid=6121464</t>
+          <t>https://www.pinterestcareers.com/jobs/?gh_jid=7642251</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>[B] SF/Palo Alto/Seattle.</t>
+          <t>[C] SF/Remote US.</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -4542,12 +4547,17 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
@@ -4559,17 +4569,17 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Sr. Machine Learning Engineer, Monetization Engineering</t>
+          <t>Sr. Machine Learning Engineer, Applied Science</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>https://www.pinterestcareers.com/jobs/?gh_jid=6121551</t>
+          <t>https://www.pinterestcareers.com/jobs/?gh_jid=6894747</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>[B] SF/Palo Alto/Seattle.</t>
+          <t>[B] SF/Remote US.</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -4601,17 +4611,17 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer, tvScientific</t>
+          <t>Sr. Machine Learning Engineer, Core Engineering</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>https://www.pinterestcareers.com/jobs/?gh_jid=7782550</t>
+          <t>https://www.pinterestcareers.com/jobs/?gh_jid=6121464</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>[B] SF/Remote US.</t>
+          <t>[B] SF/Palo Alto/Seattle.</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -4643,17 +4653,17 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Staff Data Scientist, Ads Delivery</t>
+          <t>Sr. Machine Learning Engineer, Monetization Engineering</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>https://www.pinterestcareers.com/jobs/?gh_jid=8026607</t>
+          <t>https://www.pinterestcareers.com/jobs/?gh_jid=6121551</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>[C] SF/Remote US.</t>
+          <t>[B] SF/Palo Alto/Seattle.</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -4685,17 +4695,17 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Staff Data Scientist, Ads Product</t>
+          <t>Sr. Site Reliability Engineer, tvScientific</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>https://www.pinterestcareers.com/jobs/?gh_jid=7963755</t>
+          <t>https://www.pinterestcareers.com/jobs/?gh_jid=7782550</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>[C] SF/Seattle.</t>
+          <t>[B] SF/Remote US.</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -4727,12 +4737,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Staff Data Scientist, Forecasting</t>
+          <t>Staff Data Scientist, Ads Delivery</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>https://www.pinterestcareers.com/jobs/?gh_jid=8001932</t>
+          <t>https://www.pinterestcareers.com/jobs/?gh_jid=8026607</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -4769,17 +4779,17 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Staff Data Scientist, Notifications</t>
+          <t>Staff Data Scientist, Ads Product</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>https://www.pinterestcareers.com/jobs/?gh_jid=8095343</t>
+          <t>https://www.pinterestcareers.com/jobs/?gh_jid=7963755</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>[C] SF/Remote US.</t>
+          <t>[C] SF/Seattle.</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -4811,17 +4821,17 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Staff Machine Learning Engineer, Ads Conversion Core Modeling</t>
+          <t>Staff Data Scientist, Forecasting</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>https://www.pinterestcareers.com/jobs/?gh_jid=8011452</t>
+          <t>https://www.pinterestcareers.com/jobs/?gh_jid=8001932</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>[B] SF/Palo Alto/Seattle.</t>
+          <t>[C] SF/Remote US.</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -4853,17 +4863,17 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Staff Machine Learning Engineer, Shopping Ads</t>
+          <t>Staff Data Scientist, Notifications</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>https://www.pinterestcareers.com/jobs/?gh_jid=8049465</t>
+          <t>https://www.pinterestcareers.com/jobs/?gh_jid=8095343</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>[B] SF/Palo Alto/Seattle.</t>
+          <t>[C] SF/Remote US.</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -4890,22 +4900,22 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Reddit</t>
+          <t>Pinterest</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Backend Engineer, IAM</t>
+          <t>Staff Machine Learning Engineer, Ads Conversion Core Modeling</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/8189317</t>
+          <t>https://www.pinterestcareers.com/jobs/?gh_jid=8011452</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>[B] Remote - US.</t>
+          <t>[B] SF/Palo Alto/Seattle.</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -4932,22 +4942,22 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Reddit</t>
+          <t>Pinterest</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Principal Data Scientist, Ads</t>
+          <t>Staff Machine Learning Engineer, Shopping Ads</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7330347</t>
+          <t>https://www.pinterestcareers.com/jobs/?gh_jid=8049465</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>[C] Remote - US.</t>
+          <t>[B] SF/Palo Alto/Seattle.</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -4979,12 +4989,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer, Compliance Engineering</t>
+          <t>Backend Engineer, IAM</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/8128860</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/8189317</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -5021,17 +5031,17 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer, IAM</t>
+          <t>Principal Data Scientist, Ads</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/8044767</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7330347</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>[B] Remote - US.</t>
+          <t>[C] Remote - US.</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -5063,12 +5073,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer, Safety</t>
+          <t>Senior Backend Engineer, Compliance Engineering</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/8093006</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/8128860</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -5105,17 +5115,17 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Senior Data Scientist, Ads</t>
+          <t>Senior Backend Engineer, IAM</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/8104403</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/8044767</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>[C] Remote - US.</t>
+          <t>[B] Remote - US.</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -5147,17 +5157,17 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Senior Data Scientist, Ads Integrity</t>
+          <t>Senior Backend Engineer, Safety</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/8157580</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/8093006</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>[C] Remote - US.</t>
+          <t>[B] Remote - US.</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -5189,12 +5199,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - Consumer</t>
+          <t>Senior Data Scientist, Ads</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/8126946</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/8104403</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -5231,17 +5241,17 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Senior Data Scientist, Ads Integrity</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/6960831</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/8157580</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>[B] Remote - US.</t>
+          <t>[C] Remote - US.</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -5273,17 +5283,17 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Ads Optimization</t>
+          <t>Senior Data Scientist - Consumer</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/8029120</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/8126946</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>[B] Remote - US.</t>
+          <t>[C] Remote - US.</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -5315,12 +5325,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Systems Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7731772</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/6960831</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -5357,12 +5367,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Systems Engineer, Ads ML Experience Platform</t>
+          <t>Senior Machine Learning Engineer, Ads Optimization</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/8112967</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/8029120</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -5382,17 +5392,12 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="N113" t="inlineStr">
-        <is>
-          <t>Unknown</t>
+          <t>Optional</t>
         </is>
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -5404,12 +5409,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Senior Staff Data Scientist - Consumer Experimentation</t>
+          <t>Senior Machine Learning Systems Engineer</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7974504</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7731772</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -5446,12 +5451,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Senior Staff Machine Learning Engineer, Ads Ranking</t>
+          <t>Senior Machine Learning Systems Engineer, Ads ML Experience Platform</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/8201359</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/8112967</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -5471,12 +5476,17 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
@@ -5488,12 +5498,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Senior Staff Machine Learning Engineer, Feed Relevance</t>
+          <t>Senior Staff Data Scientist - Consumer Experimentation</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/8122606</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7974504</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -5530,12 +5540,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Senior Staff Machine Learning Engineer, GenAI Platform</t>
+          <t>Senior Staff Machine Learning Engineer, Ads Ranking</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7772274</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/8201359</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -5572,12 +5582,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Senior Staff Machine Learning Systems Engineer, Ads ML Platform</t>
+          <t>Senior Staff Machine Learning Engineer, Feed Relevance</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/8157275</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/8122606</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -5614,12 +5624,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Sr. Staff Data Scientist - Ads Measurement, Signals, Privacy</t>
+          <t>Senior Staff Machine Learning Engineer, GenAI Platform</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/8072046</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7772274</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -5639,17 +5649,12 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="N119" t="inlineStr">
-        <is>
-          <t>Unknown</t>
+          <t>Optional</t>
         </is>
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -5661,17 +5666,17 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Staff Data Scientist, Ads</t>
+          <t>Senior Staff Machine Learning Systems Engineer, Ads ML Platform</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7721787</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/8157275</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>[C] Remote - US.</t>
+          <t>[B] Remote - US.</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -5703,17 +5708,17 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Staff Data Scientist - Ads Measurement, Signals, Privacy</t>
+          <t>Sr. Staff Data Scientist - Ads Measurement, Signals, Privacy</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/8072076</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/8072046</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>[C] Remote - US.</t>
+          <t>[B] Remote - US.</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -5728,12 +5733,17 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
@@ -5745,12 +5755,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Staff Data Scientist, Marketing</t>
+          <t>Staff Data Scientist, Ads</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7445240</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7721787</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -5787,17 +5797,17 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Staff Machine Learning Engineer, AI Security</t>
+          <t>Staff Data Scientist - Ads Measurement, Signals, Privacy</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/8203478</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/8072076</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>[B] Remote - US.</t>
+          <t>[C] Remote - US.</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -5829,17 +5839,17 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Staff Machine Learning Engineer, App Ads Modeling</t>
+          <t>Staff Data Scientist, Marketing</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/8187652</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7445240</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>[B] Remote - US.</t>
+          <t>[C] Remote - US.</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -5871,12 +5881,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Staff Machine Learning Engineer, Consumer</t>
+          <t>Staff Machine Learning Engineer, AI Security</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7747244</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/8203478</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -5896,7 +5906,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>No field</t>
+          <t>Optional</t>
         </is>
       </c>
       <c r="O125" t="inlineStr">
@@ -5913,12 +5923,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Staff Machine Learning Engineer, Retrieval</t>
+          <t>Staff Machine Learning Engineer, App Ads Modeling</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/8178085</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/8187652</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -5955,12 +5965,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Staff Machine Learning Systems Engineer</t>
+          <t>Staff Machine Learning Engineer, Consumer</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7731788</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7747244</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -5980,7 +5990,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>No field</t>
         </is>
       </c>
       <c r="O127" t="inlineStr">
@@ -5992,22 +6002,22 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Riot Games</t>
+          <t>Reddit</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Principal Data Engineer, Personalization</t>
+          <t>Staff Machine Learning Engineer, Retrieval</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>https://www.riotgames.com/en/work-with-us/job/8049834?gh_jid=8049834</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/8178085</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>[C] Los Angeles.</t>
+          <t>[B] Remote - US.</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -6034,22 +6044,22 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Riot Games</t>
+          <t>Reddit</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Principal Data Engineer - Teamfight Tactics</t>
+          <t>Staff Machine Learning Systems Engineer</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>https://www.riotgames.com/en/work-with-us/job/8187622?gh_jid=8187622</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7731788</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>[C] Los Angeles.</t>
+          <t>[B] Remote - US.</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -6081,12 +6091,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Principal Machine Learning Engineer (Platform &amp; Integrations) - League of Legends</t>
+          <t>Principal Data Engineer, Personalization</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>https://www.riotgames.com/en/work-with-us/job/7944656?gh_jid=7944656</t>
+          <t>https://www.riotgames.com/en/work-with-us/job/8049834?gh_jid=8049834</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -6123,12 +6133,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Principal Software Engineer, Services/DevOps - Wild Rift</t>
+          <t>Principal Data Engineer - Teamfight Tactics</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>https://www.riotgames.com/en/work-with-us/job/8104538?gh_jid=8104538</t>
+          <t>https://www.riotgames.com/en/work-with-us/job/8187622?gh_jid=8187622</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -6165,17 +6175,17 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Staff Data and AI Engineer - Enterprise</t>
+          <t>Principal Machine Learning Engineer (Platform &amp; Integrations) - League of Legends</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>https://www.riotgames.com/en/work-with-us/job/8014875?gh_jid=8014875</t>
+          <t>https://www.riotgames.com/en/work-with-us/job/7944656?gh_jid=7944656</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>[B] Los Angeles.</t>
+          <t>[C] Los Angeles.</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -6207,17 +6217,17 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Staff Machine Learning Engineer (Applied Modeling) - League of Legends</t>
+          <t>Principal Software Engineer, Services/DevOps - Wild Rift</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>https://www.riotgames.com/en/work-with-us/job/7981132?gh_jid=7981132</t>
+          <t>https://www.riotgames.com/en/work-with-us/job/8104538?gh_jid=8104538</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>[B] Los Angeles.</t>
+          <t>[C] Los Angeles.</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -6249,12 +6259,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Staff Machine Learning Engineer - Game Tech Group, ML Platform</t>
+          <t>Staff Data and AI Engineer - Enterprise</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>https://www.riotgames.com/en/work-with-us/job/7977840?gh_jid=7977840</t>
+          <t>https://www.riotgames.com/en/work-with-us/job/8014875?gh_jid=8014875</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -6286,22 +6296,22 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Roblox</t>
+          <t>Riot Games</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Distinguished Engineer, Machine Learning Systems - Economy</t>
+          <t>Staff Machine Learning Engineer (Applied Modeling) - League of Legends</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>https://careers.roblox.com/jobs/7332473?gh_jid=7332473</t>
+          <t>https://www.riotgames.com/en/work-with-us/job/7981132?gh_jid=7981132</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>[C] San Mateo, CA.</t>
+          <t>[B] Los Angeles.</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -6328,22 +6338,22 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Roblox</t>
+          <t>Riot Games</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Principal Client Platform Engineer</t>
+          <t>Staff Machine Learning Engineer - Game Tech Group, ML Platform</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>https://careers.roblox.com/jobs/8212529?gh_jid=8212529</t>
+          <t>https://www.riotgames.com/en/work-with-us/job/7977840?gh_jid=7977840</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>[C] San Mateo, CA.</t>
+          <t>[B] Los Angeles.</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -6375,12 +6385,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Principal Data Engineer - Economy</t>
+          <t>Distinguished Engineer, Machine Learning Systems - Economy</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>https://careers.roblox.com/jobs/7629489?gh_jid=7629489</t>
+          <t>https://careers.roblox.com/jobs/7332473?gh_jid=7332473</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -6417,12 +6427,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Principal Machine Learning Engineer, Alt Defense</t>
+          <t>Principal Client Platform Engineer</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>https://careers.roblox.com/jobs/8187377?gh_jid=8187377</t>
+          <t>https://careers.roblox.com/jobs/8212529?gh_jid=8212529</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -6459,12 +6469,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Principal Machine Learning Engineer, Asset Safety</t>
+          <t>Principal Data Engineer - Economy</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>https://careers.roblox.com/jobs/8073283?gh_jid=8073283</t>
+          <t>https://careers.roblox.com/jobs/7629489?gh_jid=7629489</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -6501,12 +6511,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Principal Machine Learning Engineer, Embodied AI and Smart NPCs</t>
+          <t>Principal Machine Learning Engineer, Alt Defense</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>https://careers.roblox.com/jobs/7629843?gh_jid=7629843</t>
+          <t>https://careers.roblox.com/jobs/8187377?gh_jid=8187377</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -6543,12 +6553,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Principal Machine Learning Infrastructure Engineer, Ads &amp; Discovery</t>
+          <t>Principal Machine Learning Engineer, Asset Safety</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>https://careers.roblox.com/jobs/7351202?gh_jid=7351202</t>
+          <t>https://careers.roblox.com/jobs/8073283?gh_jid=8073283</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -6585,12 +6595,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Principal/Senior Machine Learning Scientist - Search and Discovery</t>
+          <t>Principal Machine Learning Engineer, Embodied AI and Smart NPCs</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>https://careers.roblox.com/jobs/7655346?gh_jid=7655346</t>
+          <t>https://careers.roblox.com/jobs/7629843?gh_jid=7629843</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -6627,12 +6637,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Principal Software Engineer, Data Engineering</t>
+          <t>Principal Machine Learning Infrastructure Engineer, Ads &amp; Discovery</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>https://careers.roblox.com/jobs/7678832?gh_jid=7678832</t>
+          <t>https://careers.roblox.com/jobs/7351202?gh_jid=7351202</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -6669,12 +6679,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Principal Software Engineer, Data Infrastructure</t>
+          <t>Principal/Senior Machine Learning Scientist - Search and Discovery</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>https://careers.roblox.com/jobs/8029695?gh_jid=8029695</t>
+          <t>https://careers.roblox.com/jobs/7655346?gh_jid=7655346</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -6711,17 +6721,17 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Economy</t>
+          <t>Principal Software Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>https://careers.roblox.com/jobs/8172297?gh_jid=8172297</t>
+          <t>https://careers.roblox.com/jobs/7678832?gh_jid=7678832</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>[B] San Mateo, CA.</t>
+          <t>[C] San Mateo, CA.</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -6753,12 +6763,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Senior Data Scientist, Consumer Apps</t>
+          <t>Principal Software Engineer, Data Infrastructure</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>https://careers.roblox.com/jobs/8127054?gh_jid=8127054</t>
+          <t>https://careers.roblox.com/jobs/8029695?gh_jid=8029695</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -6795,17 +6805,17 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - Consumer Frontend</t>
+          <t>Senior Data Engineer, Economy</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>https://careers.roblox.com/jobs/7977682?gh_jid=7977682</t>
+          <t>https://careers.roblox.com/jobs/8172297?gh_jid=8172297</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>[C] San Mateo, CA.</t>
+          <t>[B] San Mateo, CA.</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -6837,12 +6847,12 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - Discovery</t>
+          <t>Senior Data Scientist, Consumer Apps</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>https://careers.roblox.com/jobs/8037082?gh_jid=8037082</t>
+          <t>https://careers.roblox.com/jobs/8127054?gh_jid=8127054</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -6879,12 +6889,12 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Senior Data Scientist, Engine Infra</t>
+          <t>Senior Data Scientist - Consumer Frontend</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>https://careers.roblox.com/jobs/8193712?gh_jid=8193712</t>
+          <t>https://careers.roblox.com/jobs/7977682?gh_jid=7977682</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
@@ -6921,17 +6931,17 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Senior Growth Data Engineer</t>
+          <t>Senior Data Scientist - Discovery</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>https://careers.roblox.com/jobs/8055450?gh_jid=8055450</t>
+          <t>https://careers.roblox.com/jobs/8037082?gh_jid=8037082</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>[B] San Mateo, CA.</t>
+          <t>[C] San Mateo, CA.</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -6963,17 +6973,17 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Ads</t>
+          <t>Senior Data Scientist, Engine Infra</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>https://careers.roblox.com/jobs/7351220?gh_jid=7351220</t>
+          <t>https://careers.roblox.com/jobs/8193712?gh_jid=8193712</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>[B] San Mateo, CA.</t>
+          <t>[C] San Mateo, CA.</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -7005,17 +7015,17 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Senior/Principal Infrastructure Engineer - ML Platform</t>
+          <t>Senior Growth Data Engineer</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>https://careers.roblox.com/jobs/8027755?gh_jid=8027755</t>
+          <t>https://careers.roblox.com/jobs/8055450?gh_jid=8055450</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>[C] San Mateo, CA.</t>
+          <t>[B] San Mateo, CA.</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -7047,17 +7057,17 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Senior/Principal Machine Learning Engineer, 3D Data</t>
+          <t>Senior Machine Learning Engineer, Ads</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>https://careers.roblox.com/jobs/7943933?gh_jid=7943933</t>
+          <t>https://careers.roblox.com/jobs/7351220?gh_jid=7351220</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>[C] San Mateo, CA.</t>
+          <t>[B] San Mateo, CA.</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -7089,12 +7099,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Senior/Principal Platform Engineer, ML Platform</t>
+          <t>Senior/Principal Infrastructure Engineer - ML Platform</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>https://careers.roblox.com/jobs/8047833?gh_jid=8047833</t>
+          <t>https://careers.roblox.com/jobs/8027755?gh_jid=8027755</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
@@ -7131,17 +7141,17 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer, Compute</t>
+          <t>Senior/Principal Machine Learning Engineer, 3D Data</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>https://careers.roblox.com/jobs/8042554?gh_jid=8042554</t>
+          <t>https://careers.roblox.com/jobs/7943933?gh_jid=7943933</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>[B] San Mateo, CA.</t>
+          <t>[C] San Mateo, CA.</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -7173,17 +7183,17 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Infrastructure</t>
+          <t>Senior/Principal Platform Engineer, ML Platform</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>https://careers.roblox.com/jobs/8014486?gh_jid=8014486</t>
+          <t>https://careers.roblox.com/jobs/8047833?gh_jid=8047833</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>[B] San Mateo, CA.</t>
+          <t>[C] San Mateo, CA.</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -7215,12 +7225,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Data Infrastructure, Safety</t>
+          <t>Senior Site Reliability Engineer, Compute</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>https://careers.roblox.com/jobs/7852258?gh_jid=7852258</t>
+          <t>https://careers.roblox.com/jobs/8042554?gh_jid=8042554</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
@@ -7257,12 +7267,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, ML Infra - Asset Safety</t>
+          <t>Senior Software Engineer, Data Infrastructure</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>https://careers.roblox.com/jobs/8224452?gh_jid=8224452</t>
+          <t>https://careers.roblox.com/jobs/8014486?gh_jid=8014486</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
@@ -7294,22 +7304,22 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>SoFi</t>
+          <t>Roblox</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Senior Software Engineer - Data Infrastructure, Safety</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>https://sofi.com/careers/job/7805247003?gh_jid=7805247003</t>
+          <t>https://careers.roblox.com/jobs/7852258?gh_jid=7852258</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>[C] United States.</t>
+          <t>[B] San Mateo, CA.</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -7336,22 +7346,22 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Take-Two</t>
+          <t>Roblox</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Lead DevOps Engineer</t>
+          <t>Senior Software Engineer, ML Infra - Asset Safety</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/taketwo/jobs/8075024</t>
+          <t>https://careers.roblox.com/jobs/8224452?gh_jid=8224452</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>[B] Austin, TX.</t>
+          <t>[B] San Mateo, CA.</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -7378,22 +7388,22 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Toast</t>
+          <t>SoFi</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Data Scientist II</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>https://careers.toasttab.com/jobs?gh_jid=7984730</t>
+          <t>https://sofi.com/careers/job/7805247003?gh_jid=7805247003</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>[C] Remote, USA.</t>
+          <t>[C] United States.</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -7408,7 +7418,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>No field</t>
+          <t>Optional</t>
         </is>
       </c>
       <c r="O161" t="inlineStr">
@@ -7420,22 +7430,22 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Toast</t>
+          <t>Take-Two</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Staff Data Scientist</t>
+          <t>Lead DevOps Engineer</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>https://careers.toasttab.com/jobs?gh_jid=8029049</t>
+          <t>https://job-boards.greenhouse.io/taketwo/jobs/8075024</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>[C] Remote, USA.</t>
+          <t>[B] Austin, TX.</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -7450,7 +7460,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>No field</t>
+          <t>Optional</t>
         </is>
       </c>
       <c r="O162" t="inlineStr">
@@ -7462,22 +7472,22 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Zscaler</t>
+          <t>Toast</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>AI DevOps Engineer</t>
+          <t>Data Scientist II</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/zscaler/jobs/5208829007</t>
+          <t>https://careers.toasttab.com/jobs?gh_jid=7984730</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>[B] Remote - USA / San Jose, CA.</t>
+          <t>[C] Remote, USA.</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -7492,7 +7502,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>No field</t>
         </is>
       </c>
       <c r="O163" t="inlineStr">
@@ -7504,22 +7514,22 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Zscaler</t>
+          <t>Toast</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Senior Software Architect, Platform Engineering</t>
+          <t>Staff Data Scientist</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/zscaler/jobs/5082275007</t>
+          <t>https://careers.toasttab.com/jobs?gh_jid=8029049</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>[B] San Jose, CA.</t>
+          <t>[C] Remote, USA.</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -7534,7 +7544,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>No field</t>
         </is>
       </c>
       <c r="O164" t="inlineStr">
@@ -7551,17 +7561,17 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Staff Machine Learning Engineer - Data Lake, Anomaly Detection</t>
+          <t>AI DevOps Engineer</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/zscaler/jobs/5114450007</t>
+          <t>https://job-boards.greenhouse.io/zscaler/jobs/5208829007</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>[B] San Jose, CA.</t>
+          <t>[B] Remote - USA / San Jose, CA.</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -7593,12 +7603,12 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Staff Site Reliability Engineer</t>
+          <t>Senior Software Architect, Platform Engineering</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/zscaler/jobs/5130009007</t>
+          <t>https://job-boards.greenhouse.io/zscaler/jobs/5082275007</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
@@ -7635,17 +7645,17 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Staff Site Reliability Engineer (Production Engineer)-Federal</t>
+          <t>Staff Machine Learning Engineer - Data Lake, Anomaly Detection</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/zscaler/jobs/5029669007</t>
+          <t>https://job-boards.greenhouse.io/zscaler/jobs/5114450007</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>[B] multiple US cities.</t>
+          <t>[B] San Jose, CA.</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -7672,22 +7682,22 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Clover Health</t>
+          <t>Zscaler</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Staff Site Reliability Engineer</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/cloverhealth/jobs/7848974</t>
+          <t>https://job-boards.greenhouse.io/zscaler/jobs/5130009007</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>[C] Remote - USA.</t>
+          <t>[B] San Jose, CA.</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -7714,22 +7724,22 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Clover Health</t>
+          <t>Zscaler</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Staff Site Reliability Engineer (Production Engineer)-Federal</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/cloverhealth/jobs/8074957</t>
+          <t>https://job-boards.greenhouse.io/zscaler/jobs/5029669007</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>[B] Remote - USA.</t>
+          <t>[B] multiple US cities.</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -7756,22 +7766,22 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Flatiron Health</t>
+          <t>Clover Health</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Engineering</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>https://flatiron.com/careers/open-positions/job?gh_jid=8079733</t>
+          <t>https://job-boards.greenhouse.io/cloverhealth/jobs/7848974</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>[B] NY office.</t>
+          <t>[C] Remote - USA.</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -7798,22 +7808,22 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Ro</t>
+          <t>Clover Health</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Analytics Engineer, Conversational Analytics</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/ro/3910baa9-f961-4380-ad0a-01deec07f7a2</t>
+          <t>https://job-boards.greenhouse.io/cloverhealth/jobs/8074957</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>[B] New York, NY.</t>
+          <t>[B] Remote - USA.</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -7828,39 +7838,34 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>No field</t>
-        </is>
-      </c>
-      <c r="N171" t="inlineStr">
-        <is>
-          <t>Unknown</t>
+          <t>Optional</t>
         </is>
       </c>
       <c r="O171" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Ro</t>
+          <t>Flatiron Health</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer, Product</t>
+          <t>Senior Software Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/ro/efbeeea0-5007-4d21-9bbd-e889a5148138</t>
+          <t>https://flatiron.com/careers/open-positions/job?gh_jid=8079733</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>[B] New York, NY.</t>
+          <t>[B] NY office.</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -7875,39 +7880,34 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>No field</t>
-        </is>
-      </c>
-      <c r="N172" t="inlineStr">
-        <is>
-          <t>Unknown</t>
+          <t>Optional</t>
         </is>
       </c>
       <c r="O172" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Airbnb</t>
+          <t>Ro</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Trust</t>
+          <t>Analytics Engineer, Conversational Analytics</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>https://careers.airbnb.com/positions/8130355?gh_jid=8130355</t>
+          <t>https://jobs.lever.co/ro/3910baa9-f961-4380-ad0a-01deec07f7a2</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>[B] San Francisco, CA.</t>
+          <t>[B] New York, NY.</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -7922,34 +7922,39 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>No field</t>
+        </is>
+      </c>
+      <c r="N173" t="inlineStr">
+        <is>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="O173" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Airbnb</t>
+          <t>Ro</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Trust</t>
+          <t>Senior Backend Engineer, Product</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>https://careers.airbnb.com/positions/8232153?gh_jid=8232153</t>
+          <t>https://jobs.lever.co/ro/efbeeea0-5007-4d21-9bbd-e889a5148138</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>[B] San Francisco, CA.</t>
+          <t>[B] New York, NY.</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -7964,12 +7969,17 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>No field</t>
+        </is>
+      </c>
+      <c r="N174" t="inlineStr">
+        <is>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="O174" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
@@ -7981,17 +7991,17 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Senior Staff Data Scientist, Guest &amp; Host Marketplace AI</t>
+          <t>Senior Machine Learning Engineer, Trust</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>https://careers.airbnb.com/positions/7107054?gh_jid=7107054</t>
+          <t>https://careers.airbnb.com/positions/8130355?gh_jid=8130355</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>[B] Remote.</t>
+          <t>[B] San Francisco, CA.</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -8023,12 +8033,12 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Staff Machine Learning Engineer, Assistance Engineering</t>
+          <t>Senior Machine Learning Engineer, Trust</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>https://careers.airbnb.com/positions/8024316?gh_jid=8024316</t>
+          <t>https://careers.airbnb.com/positions/8232153?gh_jid=8232153</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
@@ -8060,22 +8070,22 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Lyft</t>
+          <t>Airbnb</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Staff Data Scientist, Guest &amp; Host Marketplace AI</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>https://app.careerpuck.com/job-board/lyft/job/8772592002?gh_jid=8772592002</t>
+          <t>https://careers.airbnb.com/positions/7107054?gh_jid=7107054</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>[C] Seattle, WA.</t>
+          <t>[B] Remote.</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -8090,7 +8100,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>No field</t>
+          <t>Optional</t>
         </is>
       </c>
       <c r="O177" t="inlineStr">
@@ -8102,22 +8112,22 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Lyft</t>
+          <t>Airbnb</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Data Scientist, Decisions - Central Market Management</t>
+          <t>Staff Machine Learning Engineer, Assistance Engineering</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>https://app.careerpuck.com/job-board/lyft/job/8376875002?gh_jid=8376875002</t>
+          <t>https://careers.airbnb.com/positions/8024316?gh_jid=8024316</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>[C] San Francisco, CA.</t>
+          <t>[B] San Francisco, CA.</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -8132,7 +8142,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>No field</t>
+          <t>Optional</t>
         </is>
       </c>
       <c r="O178" t="inlineStr">
@@ -8149,17 +8159,17 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Data Scientist, Decisions - Central Market Management</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>https://app.careerpuck.com/job-board/lyft/job/8378473002?gh_jid=8378473002</t>
+          <t>https://app.careerpuck.com/job-board/lyft/job/8772592002?gh_jid=8772592002</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>[C] New York, NY.</t>
+          <t>[C] Seattle, WA.</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -8191,17 +8201,17 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Data Scientist, Decisions - Central Market Management</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>https://app.careerpuck.com/job-board/lyft/job/8689127002?gh_jid=8689127002</t>
+          <t>https://app.careerpuck.com/job-board/lyft/job/8376875002?gh_jid=8376875002</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>[B] New York, NY.</t>
+          <t>[C] San Francisco, CA.</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -8233,17 +8243,17 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Fulfillment</t>
+          <t>Data Scientist, Decisions - Central Market Management</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>https://app.careerpuck.com/job-board/lyft/job/8688633002?gh_jid=8688633002</t>
+          <t>https://app.careerpuck.com/job-board/lyft/job/8378473002?gh_jid=8378473002</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>[B] San Francisco, CA.</t>
+          <t>[C] New York, NY.</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -8275,17 +8285,17 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Senior Data Scientist, Causal Inference</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>https://app.careerpuck.com/job-board/lyft/job/8584595002?gh_jid=8584595002</t>
+          <t>https://app.careerpuck.com/job-board/lyft/job/8689127002?gh_jid=8689127002</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>[C] San Francisco, CA.</t>
+          <t>[B] New York, NY.</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -8317,17 +8327,17 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Senior Data Scientist, Causal Inference</t>
+          <t>Machine Learning Engineer, Fulfillment</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>https://app.careerpuck.com/job-board/lyft/job/8584688002?gh_jid=8584688002</t>
+          <t>https://app.careerpuck.com/job-board/lyft/job/8688633002?gh_jid=8688633002</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>[C] New York, NY.</t>
+          <t>[B] San Francisco, CA.</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -8364,12 +8374,12 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>https://app.careerpuck.com/job-board/lyft/job/8584695002?gh_jid=8584695002</t>
+          <t>https://app.careerpuck.com/job-board/lyft/job/8584595002?gh_jid=8584595002</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>[C] Seattle, WA.</t>
+          <t>[C] San Francisco, CA.</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -8401,17 +8411,17 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Recommendations</t>
+          <t>Senior Data Scientist, Causal Inference</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>https://app.careerpuck.com/job-board/lyft/job/8430552002?gh_jid=8430552002</t>
+          <t>https://app.careerpuck.com/job-board/lyft/job/8584688002?gh_jid=8584688002</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>[B] San Francisco, CA.</t>
+          <t>[C] New York, NY.</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -8438,22 +8448,22 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Samsara</t>
+          <t>Lyft</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>AI Engineer, Customer Success</t>
+          <t>Senior Data Scientist, Causal Inference</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>https://www.samsara.com/company/careers/roles/8024110?gh_jid=8024110</t>
+          <t>https://app.careerpuck.com/job-board/lyft/job/8584695002?gh_jid=8584695002</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>[B] Remote - US.</t>
+          <t>[C] Seattle, WA.</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -8468,7 +8478,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>No field</t>
         </is>
       </c>
       <c r="O186" t="inlineStr">
@@ -8480,22 +8490,22 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Samsara</t>
+          <t>Lyft</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Machine Learning Engineer, Recommendations</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>https://www.samsara.com/company/careers/roles/7859702?gh_jid=7859702</t>
+          <t>https://app.careerpuck.com/job-board/lyft/job/8430552002?gh_jid=8430552002</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>[B] Remote - US.</t>
+          <t>[B] San Francisco, CA.</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -8510,7 +8520,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>No field</t>
         </is>
       </c>
       <c r="O187" t="inlineStr">
@@ -8527,17 +8537,17 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Finance &amp; Strategy AI Engineer</t>
+          <t>AI Engineer, Customer Success</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>https://www.samsara.com/company/careers/roles/8113356?gh_jid=8113356</t>
+          <t>https://www.samsara.com/company/careers/roles/8024110?gh_jid=8024110</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>[B] San Francisco - SF9.</t>
+          <t>[B] Remote - US.</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -8569,12 +8579,12 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Lead Machine Learning Engineer - ML Infrastructure</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>https://www.samsara.com/company/careers/roles/7721193?gh_jid=7721193</t>
+          <t>https://www.samsara.com/company/careers/roles/7859702?gh_jid=7859702</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
@@ -8611,17 +8621,17 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>People Analytics AI Engineer</t>
+          <t>Finance &amp; Strategy AI Engineer</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>https://www.samsara.com/company/careers/roles/7858719?gh_jid=7858719</t>
+          <t>https://www.samsara.com/company/careers/roles/8113356?gh_jid=8113356</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>[B] Remote - Seattle.</t>
+          <t>[B] San Francisco - SF9.</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -8653,12 +8663,12 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Lead Machine Learning Engineer - ML Infrastructure</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>https://www.samsara.com/company/careers/roles/7964565?gh_jid=7964565</t>
+          <t>https://www.samsara.com/company/careers/roles/7721193?gh_jid=7721193</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
@@ -8695,17 +8705,17 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Senior Data Engineer II</t>
+          <t>People Analytics AI Engineer</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>https://www.samsara.com/company/careers/roles/8039914?gh_jid=8039914</t>
+          <t>https://www.samsara.com/company/careers/roles/7858719?gh_jid=7858719</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>[B] Remote - US.</t>
+          <t>[B] Remote - Seattle.</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -8737,12 +8747,12 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>https://www.samsara.com/company/careers/roles/8055245?gh_jid=8055245</t>
+          <t>https://www.samsara.com/company/careers/roles/7964565?gh_jid=7964565</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
@@ -8779,12 +8789,12 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Software Engineer - Data Platform</t>
+          <t>Senior Data Engineer II</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>https://www.samsara.com/company/careers/roles/7922530?gh_jid=7922530</t>
+          <t>https://www.samsara.com/company/careers/roles/8039914?gh_jid=8039914</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
@@ -8821,12 +8831,12 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Staff Machine Learning Engineer - Edge AI</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>https://www.samsara.com/company/careers/roles/7266357?gh_jid=7266357</t>
+          <t>https://www.samsara.com/company/careers/roles/8055245?gh_jid=8055245</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
@@ -8858,22 +8868,22 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Faire</t>
+          <t>Samsara</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Senior Client Platform Engineer</t>
+          <t>Software Engineer - Data Platform</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/faire/jobs/8758597002</t>
+          <t>https://www.samsara.com/company/careers/roles/7922530?gh_jid=7922530</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>[B] San Francisco, CA.</t>
+          <t>[B] Remote - US.</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -8900,22 +8910,22 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Faire</t>
+          <t>Samsara</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Senior Data Scientist / Machine Learning Engineer - Listing Quality</t>
+          <t>Staff Machine Learning Engineer - Edge AI</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/faire/jobs/8831888002</t>
+          <t>https://www.samsara.com/company/careers/roles/7266357?gh_jid=7266357</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>[C] San Francisco, CA.</t>
+          <t>[B] Remote - US.</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -8947,17 +8957,17 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Senior Finance Analytics Engineer</t>
+          <t>Senior Client Platform Engineer</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/faire/jobs/8828560002</t>
+          <t>https://boards.greenhouse.io/faire/jobs/8758597002</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>[B] NYC, NY; San Francisco, CA.</t>
+          <t>[B] San Francisco, CA.</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -8989,17 +8999,17 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Senior Staff Machine Learning Platform Engineer</t>
+          <t>Senior Data Scientist / Machine Learning Engineer - Listing Quality</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/faire/jobs/8731172002</t>
+          <t>https://boards.greenhouse.io/faire/jobs/8831888002</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>[B] Remote - US; San Francisco, CA.</t>
+          <t>[C] San Francisco, CA.</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -9031,17 +9041,17 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Staff Machine Learning Platform Engineer</t>
+          <t>Senior Finance Analytics Engineer</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/faire/jobs/8426107002</t>
+          <t>https://boards.greenhouse.io/faire/jobs/8828560002</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>[B] San Francisco, CA.</t>
+          <t>[B] NYC, NY; San Francisco, CA.</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -9068,22 +9078,22 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Gusto</t>
+          <t>Faire</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Data Scientist, Risk</t>
+          <t>Senior Staff Machine Learning Platform Engineer</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gusto/jobs/7656216</t>
+          <t>https://boards.greenhouse.io/faire/jobs/8731172002</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>[C] San Francisco, CA - Hybrid.</t>
+          <t>[B] Remote - US; San Francisco, CA.</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -9110,22 +9120,22 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Gusto</t>
+          <t>Faire</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Enterprise Application AI Engineer</t>
+          <t>Staff Machine Learning Platform Engineer</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gusto/jobs/7369003</t>
+          <t>https://boards.greenhouse.io/faire/jobs/8426107002</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>[B] San Francisco, CA - Hybrid.</t>
+          <t>[B] San Francisco, CA.</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -9143,14 +9153,9 @@
           <t>Optional</t>
         </is>
       </c>
-      <c r="N202" t="inlineStr">
-        <is>
-          <t>Long</t>
-        </is>
-      </c>
       <c r="O202" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -9162,17 +9167,17 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Scientist, Risk</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gusto/jobs/8099751</t>
+          <t>https://job-boards.greenhouse.io/gusto/jobs/7656216</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>[B] Denver, CO/NYC/SF - Hybrid.</t>
+          <t>[C] San Francisco, CA - Hybrid.</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -9190,14 +9195,9 @@
           <t>Optional</t>
         </is>
       </c>
-      <c r="N203" t="inlineStr">
-        <is>
-          <t>Long</t>
-        </is>
-      </c>
       <c r="O203" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -9209,17 +9209,17 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Senior Staff Engineer - Tax Platform Engineering</t>
+          <t>Enterprise Application AI Engineer</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gusto/jobs/8013480</t>
+          <t>https://job-boards.greenhouse.io/gusto/jobs/7369003</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>[B] Chicago-Remote; Denver/NYC/SF-Hybrid.</t>
+          <t>[B] San Francisco, CA - Hybrid.</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -9237,9 +9237,14 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N204" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
       <c r="O204" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -9251,17 +9256,17 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Software Engineer, ML Platform</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gusto/jobs/8073232</t>
+          <t>https://job-boards.greenhouse.io/gusto/jobs/8099751</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>[B] Denver/NYC/SF - Hybrid.</t>
+          <t>[B] Denver, CO/NYC/SF - Hybrid.</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -9279,31 +9284,36 @@
           <t>Optional</t>
         </is>
       </c>
+      <c r="N205" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
       <c r="O205" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Justworks</t>
+          <t>Gusto</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Senior Staff Engineer - Tax Platform Engineering</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/justworks/jobs/7960800</t>
+          <t>https://job-boards.greenhouse.io/gusto/jobs/8013480</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>[C] New York, New York.</t>
+          <t>[B] Chicago-Remote; Denver/NYC/SF-Hybrid.</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -9330,22 +9340,22 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Brex</t>
+          <t>Gusto</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>AI Engineer, Product</t>
+          <t>Software Engineer, ML Platform</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>https://www.brex.com/careers/8606845002</t>
+          <t>https://job-boards.greenhouse.io/gusto/jobs/8073232</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>[B] San Francisco, CA.</t>
+          <t>[B] Denver/NYC/SF - Hybrid.</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -9372,22 +9382,22 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Brex</t>
+          <t>Justworks</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>https://www.brex.com/careers/8366850002</t>
+          <t>https://boards.greenhouse.io/justworks/jobs/7960800</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>[B] San Francisco, CA.</t>
+          <t>[C] New York, New York.</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -9419,12 +9429,12 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Staff Software Engineer, Product Data Platform</t>
+          <t>AI Engineer, Product</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>https://www.brex.com/careers/8430182002</t>
+          <t>https://www.brex.com/careers/8606845002</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
@@ -9444,12 +9454,12 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>Required</t>
+          <t>Optional</t>
         </is>
       </c>
       <c r="O209" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -9461,17 +9471,17 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Staff Software Engineer, Product Data Platform</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>https://www.brex.com/careers/8430197002</t>
+          <t>https://www.brex.com/careers/8366850002</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>[B] Seattle, WA.</t>
+          <t>[B] San Francisco, CA.</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -9486,34 +9496,34 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>Required</t>
+          <t>Optional</t>
         </is>
       </c>
       <c r="O210" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Verkada</t>
+          <t>Brex</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Backend Engineer - Connectivity</t>
+          <t>Staff Software Engineer, Product Data Platform</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/verkada/jobs/5194598007</t>
+          <t>https://www.brex.com/careers/8430182002</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>[B] San Mateo, CA.</t>
+          <t>[B] San Francisco, CA.</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -9528,34 +9538,34 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>No field</t>
+          <t>Required</t>
         </is>
       </c>
       <c r="O211" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Verkada</t>
+          <t>Brex</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Staff Software Engineer, Product Data Platform</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/verkada/jobs/5233096007</t>
+          <t>https://www.brex.com/careers/8430197002</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>[B] San Mateo, CA.</t>
+          <t>[B] Seattle, WA.</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -9570,12 +9580,12 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>Required</t>
         </is>
       </c>
       <c r="O212" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -9587,12 +9597,12 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer - Access Control</t>
+          <t>Backend Engineer - Connectivity</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/verkada/jobs/5233103007</t>
+          <t>https://job-boards.greenhouse.io/verkada/jobs/5194598007</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
@@ -9612,7 +9622,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>No field</t>
         </is>
       </c>
       <c r="O213" t="inlineStr">
@@ -9629,12 +9639,12 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer - Device Platform</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/verkada/jobs/5233095007</t>
+          <t>https://job-boards.greenhouse.io/verkada/jobs/5233096007</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
@@ -9671,12 +9681,12 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Platform</t>
+          <t>Senior Backend Engineer - Access Control</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/verkada/jobs/5215882007</t>
+          <t>https://job-boards.greenhouse.io/verkada/jobs/5233103007</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
@@ -9713,12 +9723,12 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Software Engineer - Data Platform</t>
+          <t>Senior Backend Engineer - Device Platform</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/verkada/jobs/4129304007</t>
+          <t>https://job-boards.greenhouse.io/verkada/jobs/5233095007</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
@@ -9755,12 +9765,12 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Staff Backend Engineer - Device Security</t>
+          <t>Senior Software Engineer, Data Platform</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/verkada/jobs/5154370007</t>
+          <t>https://job-boards.greenhouse.io/verkada/jobs/5215882007</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
@@ -9797,12 +9807,12 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Staff Backend Engineer - Licensing &amp; Revenue Platform</t>
+          <t>Software Engineer - Data Platform</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/verkada/jobs/5221363007</t>
+          <t>https://job-boards.greenhouse.io/verkada/jobs/4129304007</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
@@ -9822,7 +9832,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>No field</t>
+          <t>Optional</t>
         </is>
       </c>
       <c r="O218" t="inlineStr">
@@ -9839,12 +9849,12 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Staff Backend Engineer - Streaming</t>
+          <t>Staff Backend Engineer - Device Security</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/verkada/jobs/4128603007</t>
+          <t>https://job-boards.greenhouse.io/verkada/jobs/5154370007</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
@@ -9876,22 +9886,22 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Scale AI</t>
+          <t>Verkada</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>DevOps Engineer, Infrastructure &amp; Security</t>
+          <t>Staff Backend Engineer - Licensing &amp; Revenue Platform</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/scaleai/jobs/4674863005</t>
+          <t>https://job-boards.greenhouse.io/verkada/jobs/5221363007</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>[B] Washington, DC.</t>
+          <t>[B] San Mateo, CA.</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -9906,7 +9916,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>No field</t>
         </is>
       </c>
       <c r="O220" t="inlineStr">
@@ -9918,22 +9928,22 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Scale AI</t>
+          <t>Verkada</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Public Sector</t>
+          <t>Staff Backend Engineer - Streaming</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/scaleai/jobs/4631848005</t>
+          <t>https://job-boards.greenhouse.io/verkada/jobs/4128603007</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>[B] Denver, CO; Honolulu, HI; Washington, DC.</t>
+          <t>[B] San Mateo, CA.</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -9965,17 +9975,17 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Public Sector</t>
+          <t>DevOps Engineer, Infrastructure &amp; Security</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/scaleai/jobs/4732798005</t>
+          <t>https://job-boards.greenhouse.io/scaleai/jobs/4674863005</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>[B] Denver, CO; Honolulu, HI; Washington, DC.</t>
+          <t>[B] Washington, DC.</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -10007,17 +10017,17 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Staff Machine Learning Engineer, Public Sector</t>
+          <t>Machine Learning Engineer, Public Sector</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/scaleai/jobs/4654382005</t>
+          <t>https://job-boards.greenhouse.io/scaleai/jobs/4631848005</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>[B] Denver, CO; Washington, DC.</t>
+          <t>[B] Denver, CO; Honolulu, HI; Washington, DC.</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -10049,17 +10059,17 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Staff Software Engineer, Data Platform</t>
+          <t>Senior Machine Learning Engineer, Public Sector</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/scaleai/jobs/4649903005</t>
+          <t>https://job-boards.greenhouse.io/scaleai/jobs/4732798005</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>[B] San Francisco, CA; New York, NY.</t>
+          <t>[B] Denver, CO; Honolulu, HI; Washington, DC.</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -10086,22 +10096,22 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Spotify</t>
+          <t>Scale AI</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Data Scientist - Music Mission</t>
+          <t>Staff Machine Learning Engineer, Public Sector</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/spotify/1bbaf909-5ff3-4ed6-87ca-f7ff007a169c</t>
+          <t>https://job-boards.greenhouse.io/scaleai/jobs/4654382005</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>[C] New York, NY.</t>
+          <t>[B] Denver, CO; Washington, DC.</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -10116,39 +10126,34 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>No field</t>
-        </is>
-      </c>
-      <c r="N225" t="inlineStr">
-        <is>
-          <t>Unknown</t>
+          <t>Optional</t>
         </is>
       </c>
       <c r="O225" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Spotify</t>
+          <t>Scale AI</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Data Scientist - Music Promotion</t>
+          <t>Staff Software Engineer, Data Platform</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/spotify/56ea6f2e-f20b-4e46-ab94-d3eb0a89482d</t>
+          <t>https://job-boards.greenhouse.io/scaleai/jobs/4649903005</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>[C] New York, NY.</t>
+          <t>[B] San Francisco, CA; New York, NY.</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -10163,17 +10168,12 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>No field</t>
-        </is>
-      </c>
-      <c r="N226" t="inlineStr">
-        <is>
-          <t>Unknown</t>
+          <t>Optional</t>
         </is>
       </c>
       <c r="O226" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -10185,17 +10185,17 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - Policy &amp; Safety</t>
+          <t>Data Scientist - Music Mission</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/spotify/9eca14d3-8e0b-46de-8161-704e07f3d9d0</t>
+          <t>https://jobs.lever.co/spotify/1bbaf909-5ff3-4ed6-87ca-f7ff007a169c</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>[B] New York, NY.</t>
+          <t>[C] New York, NY.</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -10232,17 +10232,17 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Personalization, Muse</t>
+          <t>Data Scientist - Music Promotion</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/spotify/d7c43743-2240-45b6-bc31-33e50cbaba4a</t>
+          <t>https://jobs.lever.co/spotify/56ea6f2e-f20b-4e46-ab94-d3eb0a89482d</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>[B] New York, NY.</t>
+          <t>[C] New York, NY.</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -10279,12 +10279,12 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Senior Staff Machine Learning Engineer - Content Platform</t>
+          <t>Senior Machine Learning Engineer - Policy &amp; Safety</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/spotify/47d4eabf-8d5a-4dab-ac72-de7b5b56841c</t>
+          <t>https://jobs.lever.co/spotify/9eca14d3-8e0b-46de-8161-704e07f3d9d0</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
@@ -10326,12 +10326,12 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Staff Machine Learning Engineer, Home Surfaces</t>
+          <t>Senior Machine Learning Engineer, Personalization, Muse</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/spotify/281e7db9-86ba-4a1c-8773-c23b96ed32dc</t>
+          <t>https://jobs.lever.co/spotify/d7c43743-2240-45b6-bc31-33e50cbaba4a</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Staff Machine Learning Engineer, Personalization</t>
+          <t>Senior Staff Machine Learning Engineer - Content Platform</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/spotify/9761af44-be41-43ca-8c01-79cdbb2aef93</t>
+          <t>https://jobs.lever.co/spotify/47d4eabf-8d5a-4dab-ac72-de7b5b56841c</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
@@ -10415,67 +10415,161 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
+          <t>Spotify</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Staff Machine Learning Engineer, Home Surfaces</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/spotify/281e7db9-86ba-4a1c-8773-c23b96ed32dc</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>[B] New York, NY.</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L232" t="inlineStr">
+        <is>
+          <t>Source: Greenhouse/Lever</t>
+        </is>
+      </c>
+      <c r="M232" t="inlineStr">
+        <is>
+          <t>No field</t>
+        </is>
+      </c>
+      <c r="N232" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="O232" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>Spotify</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Staff Machine Learning Engineer, Personalization</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/spotify/9761af44-be41-43ca-8c01-79cdbb2aef93</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>[B] New York, NY.</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>Source: Greenhouse/Lever</t>
+        </is>
+      </c>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t>No field</t>
+        </is>
+      </c>
+      <c r="N233" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="O233" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
           <t>Narmi</t>
         </is>
       </c>
-      <c r="B232" t="inlineStr">
+      <c r="B234" t="inlineStr">
         <is>
           <t>Software Engineer - Forward Deployed</t>
         </is>
       </c>
-      <c r="C232" t="inlineStr">
+      <c r="C234" t="inlineStr">
         <is>
           <t>New York, NY (in-person ~3 days/wk; friend says full remote OK)</t>
         </is>
       </c>
-      <c r="D232" t="inlineStr">
+      <c r="D234" t="inlineStr">
         <is>
           <t>https://jobs.gem.com/narmi/am9icG9zdDrAJaEbCOTTdxbRZOF7nP2T</t>
         </is>
       </c>
-      <c r="F232" t="inlineStr">
+      <c r="F234" t="inlineStr">
         <is>
           <t>$91k-$110k</t>
         </is>
       </c>
-      <c r="G232" t="inlineStr">
+      <c r="G234" t="inlineStr">
         <is>
           <t>Forward-deployed role: customer-facing builds, Python/Node/React, LLM/agent nice-to-have, AWS nice-to-have. Referral via friend.</t>
         </is>
       </c>
-      <c r="H232" t="inlineStr">
+      <c r="H234" t="inlineStr">
         <is>
           <t>tailoring</t>
         </is>
       </c>
-      <c r="I232" t="inlineStr">
+      <c r="I234" t="inlineStr">
         <is>
           <t>resume/narmi branch (jack-resume-narmi.pdf)</t>
         </is>
       </c>
-      <c r="L232" t="inlineStr">
+      <c r="L234" t="inlineStr">
         <is>
           <t>Source: Gem; resume tailored, cover letter not started</t>
         </is>
       </c>
-      <c r="M232" t="inlineStr">
+      <c r="M234" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="N232" t="inlineStr">
+      <c r="N234" t="inlineStr">
         <is>
           <t>Short</t>
         </is>
       </c>
-      <c r="O232" t="inlineStr">
+      <c r="O234" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O232"/>
+  <autoFilter ref="A1:O234"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/tracker.xlsx
+++ b/tracker.xlsx
@@ -1210,7 +1210,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>tailoring</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>resume-elastic-platform-engineer-kubernetes.pdf</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>cover-letter-elastic-platform-engineer-kubernetes.pdf</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1252,12 +1262,22 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>tailoring</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>resume-elastic-agentic-ai-engineer.pdf</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>cover-letter-elastic-agentic-ai-engineer.pdf</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Source: Greenhouse</t>
+          <t>Stretch: wants multi-agent A2A in production; Source: Greenhouse</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1299,12 +1319,22 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>tailoring</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>resume-vercel-software-engineer-data-platform.pdf</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>cover-letter-vercel-software-engineer-data-platform.pdf</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Source: Greenhouse</t>
+          <t>Stretch: Staff level, Kafka/ClickHouse; Source: Greenhouse</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1341,12 +1371,22 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>tailoring</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>resume-twilio-staff-software-engineer-data-platform.pdf</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>cover-letter-twilio-staff-software-engineer-data-platform.pdf</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Source: Greenhouse</t>
+          <t>Long shot: Staff distributed data systems; Source: Greenhouse</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1383,12 +1423,22 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>tailoring</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>resume-twilio-software-engineer-platform-engineering.pdf</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>cover-letter-twilio-software-engineer-platform-engineering.pdf</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Source: Greenhouse</t>
+          <t>Underleveled (L2) but tasks match; Source: Greenhouse</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1425,12 +1475,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>tailoring</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>resume-figma-data-platform-engineer.pdf</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Source: Greenhouse</t>
+          <t>No cover letter field; wants 5+ yrs data platform; Source: Greenhouse</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1472,12 +1527,22 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>tailoring</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>resume-databricks-ai-engineer-forward-deployed-engineering.pdf</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>cover-letter-databricks-ai-engineer-forward-deployed-engineering.pdf</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Source: Greenhouse</t>
+          <t>Good fit; Source: Greenhouse</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1519,7 +1584,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Source: Greenhouse</t>
+          <t>Posting appears closed (API 404). Source: Greenhouse</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1566,7 +1631,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Source: Greenhouse</t>
+          <t>Likely not qualified (wants deep Spark/Databricks). No resume made. Source: Greenhouse</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1603,12 +1668,17 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>tailoring</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>resume-anthropic-staff-software-engineer-data-infrastructure.pdf</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Source: Greenhouse</t>
+          <t>No cover letter field; long shot (Staff+, petabyte scale, BigQuery/Airflow/dbt); Source: Greenhouse</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -1650,12 +1720,22 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>tailoring</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>resume-affirm-machine-learning-engineer-ii-underwriting-ml.pdf</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>cover-letter-affirm-machine-learning-engineer-ii-underwriting-ml.pdf</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Source: Greenhouse/Lever</t>
+          <t>Stretch: no credit/GBDT modeling experience; Source: Greenhouse/Lever</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -1697,7 +1777,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Source: Greenhouse/Lever</t>
+          <t>Likely not qualified (credit model validation). No resume made. Source: Greenhouse/Lever</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">

--- a/tracker.xlsx
+++ b/tracker.xlsx
@@ -1891,6 +1891,11 @@
           <t>Senior Machine Learning Engineer, Assistance Engineering</t>
         </is>
       </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Remote-USA</t>
+        </is>
+      </c>
       <c r="D31" t="inlineStr">
         <is>
           <t>https://careers.airbnb.com/positions/8014904?gh_jid=8014904</t>
@@ -1903,12 +1908,22 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>tailoring</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>resume-airbnb-senior-machine-learning-engineer-assistance-engineering.pdf</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>cover-letter-airbnb-senior-machine-learning-engineer-assistance-engineering.pdf</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Source: Greenhouse/Lever</t>
+          <t>Good fit (voice/agentic assistants); Source: Greenhouse/Lever</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2828,6 +2843,11 @@
           <t>Software Engineer, Data Platform</t>
         </is>
       </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Bay Area, CA, United States of America</t>
+        </is>
+      </c>
       <c r="D52" t="inlineStr">
         <is>
           <t>http://block.xyz/careers/jobs/5381381008?gh_jid=5381381008</t>
@@ -2840,7 +2860,17 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>tailoring</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>resume-block-software-engineer-data-platform.pdf</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>cover-letter-block-software-engineer-data-platform.pdf</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -3204,6 +3234,11 @@
           <t>Senior AI/ML Engineer</t>
         </is>
       </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Chicago, IL, USA; New York, NY, USA; San Francisco, CA, USA</t>
+        </is>
+      </c>
       <c r="D60" t="inlineStr">
         <is>
           <t>https://boards.greenhouse.io/chime/jobs/8569366002?gh_jid=8569366002</t>
@@ -3216,12 +3251,22 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>tailoring</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>resume-chime-senior-ai-ml-engineer.pdf</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>cover-letter-chime-senior-ai-ml-engineer.pdf</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>Source: Greenhouse/Lever</t>
+          <t>Stretch: no fraud/credit modeling; Source: Greenhouse/Lever</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -3372,6 +3417,11 @@
           <t>Senior Software Engineer, Machine Learning Platform</t>
         </is>
       </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, USA</t>
+        </is>
+      </c>
       <c r="D64" t="inlineStr">
         <is>
           <t>https://boards.greenhouse.io/chime/jobs/8765684002?gh_jid=8765684002</t>
@@ -3384,7 +3434,17 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>tailoring</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>resume-chime-senior-software-engineer-machine-learning-platform.pdf</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>cover-letter-chime-senior-software-engineer-machine-learning-platform.pdf</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -3461,6 +3521,11 @@
           <t>Machine Learning Engineer, Memory</t>
         </is>
       </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Cary,North Carolina,United States</t>
+        </is>
+      </c>
       <c r="D66" t="inlineStr">
         <is>
           <t>https://epicgames.com/careers/jobs/6134271004?gh_jid=6134271004</t>
@@ -3473,12 +3538,22 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>tailoring</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>resume-epic-games-machine-learning-engineer-memory.pdf</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>cover-letter-epic-games-machine-learning-engineer-memory.pdf</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>Source: Greenhouse/Lever</t>
+          <t>Stretch: wants long-horizon memory research; Source: Greenhouse/Lever</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -4143,6 +4218,11 @@
           <t>Machine Learning Engineer, Core Engineering</t>
         </is>
       </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US; Palo Alto, CA, US; Seattle, WA, US; Remote, US</t>
+        </is>
+      </c>
       <c r="D82" t="inlineStr">
         <is>
           <t>https://www.pinterestcareers.com/jobs/?gh_jid=6121450</t>
@@ -4155,7 +4235,17 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>tailoring</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>resume-pinterest-machine-learning-engineer-core-engineering.pdf</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>cover-letter-pinterest-machine-learning-engineer-core-engineering.pdf</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -4227,6 +4317,11 @@
           <t>Machine Learning Engineer II, Visual AI</t>
         </is>
       </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US; Remote, US</t>
+        </is>
+      </c>
       <c r="D84" t="inlineStr">
         <is>
           <t>https://www.pinterestcareers.com/jobs/?gh_jid=7697137</t>
@@ -4239,7 +4334,17 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>tailoring</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>resume-pinterest-machine-learning-engineer-ii-visual-ai.pdf</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>cover-letter-pinterest-machine-learning-engineer-ii-visual-ai.pdf</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -4694,6 +4799,11 @@
           <t>Sr. Machine Learning Engineer, Core Engineering</t>
         </is>
       </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US; Palo Alto, CA, US; Seattle, WA, US</t>
+        </is>
+      </c>
       <c r="D95" t="inlineStr">
         <is>
           <t>https://www.pinterestcareers.com/jobs/?gh_jid=6121464</t>
@@ -4706,7 +4816,17 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>tailoring</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>resume-pinterest-sr-machine-learning-engineer-core-engineering.pdf</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>cover-letter-pinterest-sr-machine-learning-engineer-core-engineering.pdf</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -5240,6 +5360,11 @@
           <t>Senior Backend Engineer, Safety</t>
         </is>
       </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Remote - United States</t>
+        </is>
+      </c>
       <c r="D108" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/reddit/jobs/8093006</t>
@@ -5252,7 +5377,17 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>tailoring</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>resume-reddit-senior-backend-engineer-safety.pdf</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>cover-letter-reddit-senior-backend-engineer-safety.pdf</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -5408,6 +5543,11 @@
           <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Remote - United States</t>
+        </is>
+      </c>
       <c r="D112" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/reddit/jobs/6960831</t>
@@ -5420,7 +5560,17 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>tailoring</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>resume-reddit-senior-machine-learning-engineer.pdf</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>cover-letter-reddit-senior-machine-learning-engineer.pdf</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -5492,6 +5642,11 @@
           <t>Senior Machine Learning Systems Engineer</t>
         </is>
       </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Remote - United States</t>
+        </is>
+      </c>
       <c r="D114" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/reddit/jobs/7731772</t>
@@ -5504,7 +5659,17 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>tailoring</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>resume-reddit-senior-machine-learning-systems-engineer.pdf</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>cover-letter-reddit-senior-machine-learning-systems-engineer.pdf</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -6426,6 +6591,11 @@
           <t>Staff Machine Learning Engineer - Game Tech Group, ML Platform</t>
         </is>
       </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Los Angeles, USA</t>
+        </is>
+      </c>
       <c r="D136" t="inlineStr">
         <is>
           <t>https://www.riotgames.com/en/work-with-us/job/7977840?gh_jid=7977840</t>
@@ -6438,12 +6608,22 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>tailoring</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>resume-riot-games-staff-machine-learning-engineer-game-tech-group-ml-platform.pdf</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>cover-letter-riot-games-staff-machine-learning-engineer-game-tech-group-ml-platform.pdf</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>Source: Greenhouse/Lever</t>
+          <t>Stretch: Staff level; Riot fan; Los Angeles; Source: Greenhouse/Lever</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
@@ -7182,6 +7362,11 @@
           <t>Senior/Principal Infrastructure Engineer - ML Platform</t>
         </is>
       </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>San Mateo, CA, United States</t>
+        </is>
+      </c>
       <c r="D154" t="inlineStr">
         <is>
           <t>https://careers.roblox.com/jobs/8027755?gh_jid=8027755</t>
@@ -7194,7 +7379,17 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>tailoring</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>resume-roblox-senior-principal-infrastructure-engineer-ml-platform.pdf</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>cover-letter-roblox-senior-principal-infrastructure-engineer-ml-platform.pdf</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
@@ -7266,6 +7461,11 @@
           <t>Senior/Principal Platform Engineer, ML Platform</t>
         </is>
       </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>San Mateo, CA, United States</t>
+        </is>
+      </c>
       <c r="D156" t="inlineStr">
         <is>
           <t>https://careers.roblox.com/jobs/8047833?gh_jid=8047833</t>
@@ -7278,7 +7478,17 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>tailoring</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>resume-roblox-senior-principal-platform-engineer-ml-platform.pdf</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>cover-letter-roblox-senior-principal-platform-engineer-ml-platform.pdf</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
@@ -7350,6 +7560,11 @@
           <t>Senior Software Engineer, Data Infrastructure</t>
         </is>
       </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>San Mateo, CA, United States</t>
+        </is>
+      </c>
       <c r="D158" t="inlineStr">
         <is>
           <t>https://careers.roblox.com/jobs/8014486?gh_jid=8014486</t>
@@ -7362,7 +7577,17 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>tailoring</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>resume-roblox-senior-software-engineer-data-infrastructure.pdf</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>cover-letter-roblox-senior-software-engineer-data-infrastructure.pdf</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
@@ -7434,6 +7659,11 @@
           <t>Senior Software Engineer, ML Infra - Asset Safety</t>
         </is>
       </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>San Mateo, CA, United States</t>
+        </is>
+      </c>
       <c r="D160" t="inlineStr">
         <is>
           <t>https://careers.roblox.com/jobs/8224452?gh_jid=8224452</t>
@@ -7446,7 +7676,17 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>tailoring</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>resume-roblox-senior-software-engineer-ml-infra-asset-safety.pdf</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>cover-letter-roblox-senior-software-engineer-ml-infra-asset-safety.pdf</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
@@ -7644,6 +7884,11 @@
           <t>AI DevOps Engineer</t>
         </is>
       </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Remote - USA; San Jose, California, USA</t>
+        </is>
+      </c>
       <c r="D165" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/zscaler/jobs/5208829007</t>
@@ -7656,12 +7901,22 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>tailoring</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>resume-zscaler-ai-devops-engineer.pdf</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>cover-letter-zscaler-ai-devops-engineer.pdf</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>Source: Greenhouse/Lever</t>
+          <t>Stretch: 5+ yrs multi-cloud infra; Source: Greenhouse/Lever</t>
         </is>
       </c>
       <c r="M165" t="inlineStr">
@@ -8620,6 +8875,11 @@
           <t>AI Engineer, Customer Success</t>
         </is>
       </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Remote - US</t>
+        </is>
+      </c>
       <c r="D188" t="inlineStr">
         <is>
           <t>https://www.samsara.com/company/careers/roles/8024110?gh_jid=8024110</t>
@@ -8632,7 +8892,17 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>tailoring</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>resume-samsara-ai-engineer-customer-success.pdf</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>cover-letter-samsara-ai-engineer-customer-success.pdf</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
@@ -8914,6 +9184,11 @@
           <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Remote - US</t>
+        </is>
+      </c>
       <c r="D195" t="inlineStr">
         <is>
           <t>https://www.samsara.com/company/careers/roles/8055245?gh_jid=8055245</t>
@@ -8926,12 +9201,22 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>tailoring</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>resume-samsara-senior-machine-learning-engineer.pdf</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>cover-letter-samsara-senior-machine-learning-engineer.pdf</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>Source: Greenhouse/Lever</t>
+          <t>Stretch: wants 6+ yrs ML; Source: Greenhouse/Lever</t>
         </is>
       </c>
       <c r="M195" t="inlineStr">
@@ -8956,6 +9241,11 @@
           <t>Software Engineer - Data Platform</t>
         </is>
       </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Remote - US</t>
+        </is>
+      </c>
       <c r="D196" t="inlineStr">
         <is>
           <t>https://www.samsara.com/company/careers/roles/7922530?gh_jid=7922530</t>
@@ -8968,7 +9258,17 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>tailoring</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>resume-samsara-software-engineer-data-platform.pdf</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>cover-letter-samsara-software-engineer-data-platform.pdf</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
@@ -9512,6 +9812,11 @@
           <t>AI Engineer, Product</t>
         </is>
       </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>San Francisco, California, United States</t>
+        </is>
+      </c>
       <c r="D209" t="inlineStr">
         <is>
           <t>https://www.brex.com/careers/8606845002</t>
@@ -9524,7 +9829,17 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>tailoring</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>resume-brex-ai-engineer-product.pdf</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>cover-letter-brex-ai-engineer-product.pdf</t>
         </is>
       </c>
       <c r="L209" t="inlineStr">
@@ -9554,6 +9869,11 @@
           <t>Data Engineer</t>
         </is>
       </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>San Francisco, California, United States</t>
+        </is>
+      </c>
       <c r="D210" t="inlineStr">
         <is>
           <t>https://www.brex.com/careers/8366850002</t>
@@ -9566,7 +9886,17 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>tailoring</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>resume-brex-data-engineer.pdf</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>cover-letter-brex-data-engineer.pdf</t>
         </is>
       </c>
       <c r="L210" t="inlineStr">
@@ -9722,6 +10052,11 @@
           <t>Senior Backend Engineer</t>
         </is>
       </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>San Mateo, CA United States</t>
+        </is>
+      </c>
       <c r="D214" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/verkada/jobs/5233096007</t>
@@ -9734,7 +10069,17 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>tailoring</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>resume-verkada-senior-backend-engineer.pdf</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>cover-letter-verkada-senior-backend-engineer.pdf</t>
         </is>
       </c>
       <c r="L214" t="inlineStr">
@@ -9890,6 +10235,11 @@
           <t>Software Engineer - Data Platform</t>
         </is>
       </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>San Mateo, CA United States</t>
+        </is>
+      </c>
       <c r="D218" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/verkada/jobs/4129304007</t>
@@ -9902,12 +10252,22 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>tailoring</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>resume-verkada-software-engineer-data-platform.pdf</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>cover-letter-verkada-software-engineer-data-platform.pdf</t>
         </is>
       </c>
       <c r="L218" t="inlineStr">
         <is>
-          <t>Source: Greenhouse/Lever</t>
+          <t>Underleveled (1-3 yrs) but tasks match; Source: Greenhouse/Lever</t>
         </is>
       </c>
       <c r="M218" t="inlineStr">

--- a/tracker.xlsx
+++ b/tracker.xlsx
@@ -1802,6 +1802,11 @@
           <t>Principal Machine Learning Engineer- LLM Fine-tuning and Optimization</t>
         </is>
       </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>United States (Remote eligible)</t>
+        </is>
+      </c>
       <c r="D29" t="inlineStr">
         <is>
           <t>https://careers.airbnb.com/positions/7955579?gh_jid=7955579</t>
@@ -1814,12 +1819,22 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>tailoring</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>resume-airbnb-principal-machine-learning-engineer-llm-fine-tuning-and-optimization.pdf</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>cover-letter-airbnb-principal-machine-learning-engineer-llm-fine-tuning-and-optimization.pdf</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Source: Greenhouse/Lever</t>
+          <t>Long shot: min quals PhD + 10+ yrs; remote-eligible only in Airbnb-registered states; Source: Greenhouse/Lever</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">

--- a/tracker.xlsx
+++ b/tracker.xlsx
@@ -1859,6 +1859,11 @@
           <t>Senior Data Scientist - Payments (Inference)</t>
         </is>
       </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Remote - USA</t>
+        </is>
+      </c>
       <c r="D30" t="inlineStr">
         <is>
           <t>https://careers.airbnb.com/positions/8123037?gh_jid=8123037</t>
@@ -1871,12 +1876,22 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>tailoring</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>resume-airbnb-senior-data-scientist-payments-inference.pdf</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>cover-letter-airbnb-senior-data-scientist-payments-inference.pdf</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Source: Greenhouse/Lever</t>
+          <t>Long shot: causal inference/experimentation DS role; min 5+ yrs quant analysis + Master's; remote-eligible only in Airbnb-registered states. Source: Greenhouse/Lever</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">

--- a/tracker.xlsx
+++ b/tracker.xlsx
@@ -1614,6 +1614,11 @@
           <t>Specialist Solutions Architect - Data Engineering &amp; Warehousing (Financial Services)</t>
         </is>
       </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>United States (Remote)</t>
+        </is>
+      </c>
       <c r="D25" t="inlineStr">
         <is>
           <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8692962002</t>
@@ -1626,12 +1631,22 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>tailoring</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>resume-databricks-specialist-solutions-architect-data-engineering-warehousing-financial-services.pdf</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>cover-letter-databricks-specialist-solutions-architect-data-engineering-warehousing-financial-services.pdf</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Likely not qualified (wants deep Spark/Databricks). No resume made. Source: Greenhouse</t>
+          <t>Long shot: wants 6+ yrs solutions architecture/pre-sales, deep Spark/Kafka; travel up to 30%. Source: Greenhouse</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">

--- a/tracker.xlsx
+++ b/tracker.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Tracker" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tracker" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Tracker'!$A$1:$O$234</definedName>
@@ -18,7 +18,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -57,9 +59,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1210,7 +1213,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>tailoring</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1262,7 +1265,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>tailoring</t>
+          <t>applied</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1274,6 +1277,9 @@
         <is>
           <t>cover-letter-elastic-agentic-ai-engineer.pdf</t>
         </is>
+      </c>
+      <c r="K18" s="2" t="n">
+        <v>46295</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1319,7 +1325,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>tailoring</t>
+          <t>applied</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1331,6 +1337,9 @@
         <is>
           <t>cover-letter-vercel-software-engineer-data-platform.pdf</t>
         </is>
+      </c>
+      <c r="K19" s="2" t="n">
+        <v>46294</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1371,7 +1380,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>tailoring</t>
+          <t>applied</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1383,6 +1392,9 @@
         <is>
           <t>cover-letter-twilio-staff-software-engineer-data-platform.pdf</t>
         </is>
+      </c>
+      <c r="K20" s="2" t="n">
+        <v>46295</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1423,7 +1435,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>tailoring</t>
+          <t>applied</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1435,6 +1447,9 @@
         <is>
           <t>cover-letter-twilio-software-engineer-platform-engineering.pdf</t>
         </is>
+      </c>
+      <c r="K21" s="2" t="n">
+        <v>46295</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1475,13 +1490,16 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>tailoring</t>
+          <t>applied</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
           <t>resume-figma-data-platform-engineer.pdf</t>
         </is>
+      </c>
+      <c r="K22" s="2" t="n">
+        <v>46295</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -1527,7 +1545,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>tailoring</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1579,7 +1597,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -1631,7 +1649,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>tailoring</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1683,13 +1701,16 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>tailoring</t>
+          <t>applied</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
           <t>resume-anthropic-staff-software-engineer-data-infrastructure.pdf</t>
         </is>
+      </c>
+      <c r="K26" s="2" t="n">
+        <v>46295</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -1735,7 +1756,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>tailoring</t>
+          <t>applied</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1747,6 +1768,9 @@
         <is>
           <t>cover-letter-affirm-machine-learning-engineer-ii-underwriting-ml.pdf</t>
         </is>
+      </c>
+      <c r="K27" s="2" t="n">
+        <v>46294</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -1787,8 +1811,11 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>new</t>
-        </is>
+          <t>applied</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="n">
+        <v>46295</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -1834,7 +1861,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>tailoring</t>
+          <t>applied</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1846,6 +1873,9 @@
         <is>
           <t>cover-letter-airbnb-principal-machine-learning-engineer-llm-fine-tuning-and-optimization.pdf</t>
         </is>
+      </c>
+      <c r="K29" s="2" t="n">
+        <v>46295</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -1891,7 +1921,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>tailoring</t>
+          <t>applied</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1903,6 +1933,9 @@
         <is>
           <t>cover-letter-airbnb-senior-data-scientist-payments-inference.pdf</t>
         </is>
+      </c>
+      <c r="K30" s="2" t="n">
+        <v>46295</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -1953,7 +1986,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>tailoring</t>
+          <t>applied</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -1965,6 +1998,9 @@
         <is>
           <t>cover-letter-airbnb-senior-machine-learning-engineer-assistance-engineering.pdf</t>
         </is>
+      </c>
+      <c r="K31" s="2" t="n">
+        <v>46294</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -2905,7 +2941,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>tailoring</t>
+          <t>applied</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -2917,6 +2953,9 @@
         <is>
           <t>cover-letter-block-software-engineer-data-platform.pdf</t>
         </is>
+      </c>
+      <c r="K52" s="2" t="n">
+        <v>46295</v>
       </c>
       <c r="L52" t="inlineStr">
         <is>

--- a/tracker.xlsx
+++ b/tracker.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tracker" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Tracker" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Tracker'!$A$1:$O$234</definedName>
@@ -4359,6 +4359,11 @@
           <t>Machine Learning Engineer II, Responsible AI</t>
         </is>
       </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US; Remote, US</t>
+        </is>
+      </c>
       <c r="D83" t="inlineStr">
         <is>
           <t>https://www.pinterestcareers.com/jobs/?gh_jid=8162046</t>
@@ -4371,12 +4376,22 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>tailoring</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>resume-pinterest-machine-learning-engineer-ii-responsible-ai.pdf</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>cover-letter-pinterest-machine-learning-engineer-ii-responsible-ai.pdf</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>Source: Greenhouse/Lever</t>
+          <t>Stretch: no responsible-AI team experience; Source: Greenhouse/Lever</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -5276,6 +5291,11 @@
           <t>Backend Engineer, IAM</t>
         </is>
       </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Remote - United States</t>
+        </is>
+      </c>
       <c r="D104" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/reddit/jobs/8189317</t>
@@ -5288,12 +5308,22 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>tailoring</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>resume-reddit-backend-engineer-iam.pdf</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>cover-letter-reddit-backend-engineer-iam.pdf</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>Source: Greenhouse/Lever</t>
+          <t>Good-ish: scoped-token gateway; no IAM-at-scale; Source: Greenhouse/Lever</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
@@ -8277,6 +8307,11 @@
           <t>Senior Software Engineer, Data Engineering</t>
         </is>
       </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>NY office</t>
+        </is>
+      </c>
       <c r="D172" t="inlineStr">
         <is>
           <t>https://flatiron.com/careers/open-positions/job?gh_jid=8079733</t>
@@ -8289,12 +8324,22 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>tailoring</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>resume-flatiron-health-senior-software-engineer-data-engineering.pdf</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>cover-letter-flatiron-health-senior-software-engineer-data-engineering.pdf</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>Source: Greenhouse/Lever</t>
+          <t>Stretch: healthcare data; NY office; Source: Greenhouse/Lever</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
@@ -8366,6 +8411,11 @@
           <t>Senior Backend Engineer, Product</t>
         </is>
       </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>New York, NY</t>
+        </is>
+      </c>
       <c r="D174" t="inlineStr">
         <is>
           <t>https://jobs.lever.co/ro/efbeeea0-5007-4d21-9bbd-e889a5148138</t>
@@ -8378,12 +8428,17 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>tailoring</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>resume-ro-senior-backend-engineer-product.pdf</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>Source: Greenhouse/Lever</t>
+          <t>Resume only (no cover letter field); wants 5+ yrs backend; NYC; Source: Greenhouse/Lever</t>
         </is>
       </c>
       <c r="M174" t="inlineStr">
@@ -8413,6 +8468,11 @@
           <t>Senior Machine Learning Engineer, Trust</t>
         </is>
       </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>San Francisco, CA</t>
+        </is>
+      </c>
       <c r="D175" t="inlineStr">
         <is>
           <t>https://careers.airbnb.com/positions/8130355?gh_jid=8130355</t>
@@ -8425,12 +8485,22 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>tailoring</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>resume-airbnb-senior-machine-learning-engineer-trust-genai.pdf</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>cover-letter-airbnb-senior-machine-learning-engineer-trust-genai.pdf</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>Source: Greenhouse/Lever</t>
+          <t>Stretch: wants 5-10 yrs applied ML; SF; Source: Greenhouse/Lever</t>
         </is>
       </c>
       <c r="M175" t="inlineStr">
@@ -8707,6 +8777,11 @@
           <t>Machine Learning Engineer</t>
         </is>
       </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>New York, NY</t>
+        </is>
+      </c>
       <c r="D182" t="inlineStr">
         <is>
           <t>https://app.careerpuck.com/job-board/lyft/job/8689127002?gh_jid=8689127002</t>
@@ -8719,12 +8794,17 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>tailoring</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>resume-lyft-machine-learning-engineer.pdf</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>Source: Greenhouse/Lever</t>
+          <t>Resume only (no cover letter field); wants 2+ yrs ML modeling; NYC; Source: Greenhouse/Lever</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
@@ -8749,6 +8829,11 @@
           <t>Machine Learning Engineer, Fulfillment</t>
         </is>
       </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>San Francisco, CA</t>
+        </is>
+      </c>
       <c r="D183" t="inlineStr">
         <is>
           <t>https://app.careerpuck.com/job-board/lyft/job/8688633002?gh_jid=8688633002</t>
@@ -8761,12 +8846,17 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>tailoring</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>resume-lyft-machine-learning-engineer-fulfillment.pdf</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>Source: Greenhouse/Lever</t>
+          <t>Resume only (no cover letter field); marketplace ML; SF; Source: Greenhouse/Lever</t>
         </is>
       </c>
       <c r="M183" t="inlineStr">
@@ -9016,6 +9106,11 @@
           <t>Data Engineer</t>
         </is>
       </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Remote - US</t>
+        </is>
+      </c>
       <c r="D189" t="inlineStr">
         <is>
           <t>https://www.samsara.com/company/careers/roles/7859702?gh_jid=7859702</t>
@@ -9028,12 +9123,22 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>tailoring</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>resume-samsara-data-engineer.pdf</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>cover-letter-samsara-data-engineer.pdf</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>Source: Greenhouse/Lever</t>
+          <t>Stretch: wants 4+ yrs data engineering; Source: Greenhouse/Lever</t>
         </is>
       </c>
       <c r="M189" t="inlineStr">

--- a/tracker.xlsx
+++ b/tracker.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Tracker" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tracker" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Tracker'!$A$1:$O$234</definedName>
@@ -3695,7 +3695,7 @@
       </c>
       <c r="H60" s="7" t="inlineStr">
         <is>
-          <t>tailoring</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="I60" s="7" t="inlineStr">
@@ -3711,7 +3711,7 @@
       <c r="K60" s="7" t="n"/>
       <c r="L60" s="7" t="inlineStr">
         <is>
-          <t>Stretch: no fraud/credit modeling; Source: Greenhouse/Lever</t>
+          <t>Skipped 2026-10-01: in-office requirement outside SLC (standing rule)</t>
         </is>
       </c>
       <c r="M60" s="7" t="inlineStr">
@@ -3903,7 +3903,7 @@
       </c>
       <c r="H64" s="7" t="inlineStr">
         <is>
-          <t>tailoring</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="I64" s="7" t="inlineStr">
@@ -3919,7 +3919,7 @@
       <c r="K64" s="7" t="n"/>
       <c r="L64" s="7" t="inlineStr">
         <is>
-          <t>Source: Greenhouse/Lever</t>
+          <t>Skipped 2026-10-01: in-office requirement outside SLC (standing rule)</t>
         </is>
       </c>
       <c r="M64" s="7" t="inlineStr">
@@ -11384,7 +11384,7 @@
       </c>
       <c r="H209" s="7" t="inlineStr">
         <is>
-          <t>tailoring</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="I209" s="7" t="inlineStr">
@@ -11400,7 +11400,7 @@
       <c r="K209" s="7" t="n"/>
       <c r="L209" s="7" t="inlineStr">
         <is>
-          <t>Source: Greenhouse/Lever</t>
+          <t>Skipped 2026-10-01: in-office requirement outside SLC (standing rule)</t>
         </is>
       </c>
       <c r="M209" s="7" t="inlineStr">
@@ -11445,7 +11445,7 @@
       </c>
       <c r="H210" s="7" t="inlineStr">
         <is>
-          <t>tailoring</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="I210" s="7" t="inlineStr">
@@ -11461,7 +11461,7 @@
       <c r="K210" s="7" t="n"/>
       <c r="L210" s="7" t="inlineStr">
         <is>
-          <t>Source: Greenhouse/Lever</t>
+          <t>Skipped 2026-10-01: in-office requirement outside SLC (standing rule)</t>
         </is>
       </c>
       <c r="M210" s="7" t="inlineStr">

--- a/tracker.xlsx
+++ b/tracker.xlsx
@@ -4017,7 +4017,7 @@
       </c>
       <c r="H66" s="7" t="inlineStr">
         <is>
-          <t>tailoring</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="I66" s="7" t="inlineStr">
@@ -4033,7 +4033,7 @@
       <c r="K66" s="7" t="n"/>
       <c r="L66" s="7" t="inlineStr">
         <is>
-          <t>Stretch: wants long-horizon memory research; Source: Greenhouse/Lever</t>
+          <t>Skipped 2026-10-01: in-office requirement outside SLC (standing rule)</t>
         </is>
       </c>
       <c r="M66" s="7" t="inlineStr">
@@ -5498,7 +5498,7 @@
       </c>
       <c r="H95" s="7" t="inlineStr">
         <is>
-          <t>tailoring</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="I95" s="7" t="inlineStr">
@@ -5514,7 +5514,7 @@
       <c r="K95" s="7" t="n"/>
       <c r="L95" s="7" t="inlineStr">
         <is>
-          <t>Source: Greenhouse/Lever</t>
+          <t>Skipped 2026-10-01: in-office requirement outside SLC (standing rule)</t>
         </is>
       </c>
       <c r="M95" s="7" t="inlineStr">
@@ -7599,7 +7599,7 @@
       </c>
       <c r="H136" s="7" t="inlineStr">
         <is>
-          <t>tailoring</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="I136" s="7" t="inlineStr">
@@ -7615,7 +7615,7 @@
       <c r="K136" s="7" t="n"/>
       <c r="L136" s="7" t="inlineStr">
         <is>
-          <t>Stretch: Staff level; Riot fan; Los Angeles; Source: Greenhouse/Lever</t>
+          <t>Skipped 2026-10-01: in-office requirement outside SLC (standing rule)</t>
         </is>
       </c>
       <c r="M136" s="7" t="inlineStr">
@@ -8493,7 +8493,7 @@
       </c>
       <c r="H154" s="7" t="inlineStr">
         <is>
-          <t>tailoring</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="I154" s="7" t="inlineStr">
@@ -8509,7 +8509,7 @@
       <c r="K154" s="7" t="n"/>
       <c r="L154" s="7" t="inlineStr">
         <is>
-          <t>Source: Greenhouse/Lever</t>
+          <t>Skipped 2026-10-01: in-office requirement outside SLC (standing rule)</t>
         </is>
       </c>
       <c r="M154" s="7" t="inlineStr">
@@ -8603,7 +8603,7 @@
       </c>
       <c r="H156" s="7" t="inlineStr">
         <is>
-          <t>tailoring</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="I156" s="7" t="inlineStr">
@@ -8619,7 +8619,7 @@
       <c r="K156" s="7" t="n"/>
       <c r="L156" s="7" t="inlineStr">
         <is>
-          <t>Source: Greenhouse/Lever</t>
+          <t>Skipped 2026-10-01: in-office requirement outside SLC (standing rule)</t>
         </is>
       </c>
       <c r="M156" s="7" t="inlineStr">
@@ -8713,7 +8713,7 @@
       </c>
       <c r="H158" s="7" t="inlineStr">
         <is>
-          <t>tailoring</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="I158" s="7" t="inlineStr">
@@ -8729,7 +8729,7 @@
       <c r="K158" s="7" t="n"/>
       <c r="L158" s="7" t="inlineStr">
         <is>
-          <t>Source: Greenhouse/Lever</t>
+          <t>Skipped 2026-10-01: in-office requirement outside SLC (standing rule)</t>
         </is>
       </c>
       <c r="M158" s="7" t="inlineStr">
@@ -8774,7 +8774,7 @@
       </c>
       <c r="H159" s="7" t="inlineStr">
         <is>
-          <t>tailoring</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="I159" s="7" t="inlineStr">
@@ -8790,7 +8790,7 @@
       <c r="K159" s="7" t="n"/>
       <c r="L159" s="7" t="inlineStr">
         <is>
-          <t>In-person/hybrid: San Mateo, CA, United States; Stretch: short of years listed; Source: Greenhouse/Lever</t>
+          <t>Skipped 2026-10-01: in-office requirement outside SLC (standing rule)</t>
         </is>
       </c>
       <c r="M159" s="7" t="inlineStr">
@@ -8835,7 +8835,7 @@
       </c>
       <c r="H160" s="7" t="inlineStr">
         <is>
-          <t>tailoring</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="I160" s="7" t="inlineStr">
@@ -8851,7 +8851,7 @@
       <c r="K160" s="7" t="n"/>
       <c r="L160" s="7" t="inlineStr">
         <is>
-          <t>Source: Greenhouse/Lever</t>
+          <t>Skipped 2026-10-01: in-office requirement outside SLC (standing rule)</t>
         </is>
       </c>
       <c r="M160" s="7" t="inlineStr">
@@ -9447,7 +9447,7 @@
       </c>
       <c r="H172" s="7" t="inlineStr">
         <is>
-          <t>tailoring</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="I172" s="7" t="inlineStr">
@@ -9463,7 +9463,7 @@
       <c r="K172" s="7" t="n"/>
       <c r="L172" s="7" t="inlineStr">
         <is>
-          <t>Stretch: healthcare data; NY office; Source: Greenhouse/Lever</t>
+          <t>Skipped 2026-10-01: in-office requirement outside SLC (standing rule)</t>
         </is>
       </c>
       <c r="M172" s="7" t="inlineStr">
@@ -9561,7 +9561,7 @@
       </c>
       <c r="H174" s="7" t="inlineStr">
         <is>
-          <t>tailoring</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="I174" s="7" t="inlineStr">
@@ -9573,7 +9573,7 @@
       <c r="K174" s="7" t="n"/>
       <c r="L174" s="7" t="inlineStr">
         <is>
-          <t>Resume only (no cover letter field); wants 5+ yrs backend; NYC; Source: Greenhouse/Lever</t>
+          <t>Skipped 2026-10-01: in-office requirement outside SLC (standing rule)</t>
         </is>
       </c>
       <c r="M174" s="7" t="inlineStr">
@@ -9977,7 +9977,7 @@
       </c>
       <c r="H182" s="7" t="inlineStr">
         <is>
-          <t>tailoring</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="I182" s="7" t="inlineStr">
@@ -9989,7 +9989,7 @@
       <c r="K182" s="7" t="n"/>
       <c r="L182" s="7" t="inlineStr">
         <is>
-          <t>Resume only (no cover letter field); wants 2+ yrs ML modeling; NYC; Source: Greenhouse/Lever</t>
+          <t>Skipped 2026-10-01: in-office requirement outside SLC (standing rule)</t>
         </is>
       </c>
       <c r="M182" s="7" t="inlineStr">
@@ -10034,7 +10034,7 @@
       </c>
       <c r="H183" s="7" t="inlineStr">
         <is>
-          <t>tailoring</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="I183" s="7" t="inlineStr">
@@ -10046,7 +10046,7 @@
       <c r="K183" s="7" t="n"/>
       <c r="L183" s="7" t="inlineStr">
         <is>
-          <t>Resume only (no cover letter field); marketplace ML; SF; Source: Greenhouse/Lever</t>
+          <t>Skipped 2026-10-01: in-office requirement outside SLC (standing rule)</t>
         </is>
       </c>
       <c r="M183" s="7" t="inlineStr">
@@ -11274,7 +11274,7 @@
       </c>
       <c r="H207" s="7" t="inlineStr">
         <is>
-          <t>tailoring</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="I207" s="7" t="inlineStr">
@@ -11290,7 +11290,7 @@
       <c r="K207" s="7" t="n"/>
       <c r="L207" s="7" t="inlineStr">
         <is>
-          <t>In-person/hybrid: Denver, CO - Hybrid; New York, NY - Hybrid; San Francisco, C; Hybrid Denver/NY; no Ruby/Java; Source: Greenhouse/Lever</t>
+          <t>Skipped 2026-10-01: in-office requirement outside SLC (standing rule)</t>
         </is>
       </c>
       <c r="M207" s="7" t="inlineStr">
@@ -11604,7 +11604,7 @@
       </c>
       <c r="H213" s="7" t="inlineStr">
         <is>
-          <t>tailoring</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="I213" s="7" t="inlineStr">
@@ -11616,7 +11616,7 @@
       <c r="K213" s="7" t="n"/>
       <c r="L213" s="7" t="inlineStr">
         <is>
-          <t>In-person/hybrid: San Mateo, CA United States; Resume only (no letter field); Source: Greenhouse/Lever</t>
+          <t>Skipped 2026-10-01: in-office requirement outside SLC (standing rule)</t>
         </is>
       </c>
       <c r="M213" s="7" t="inlineStr">
@@ -11661,7 +11661,7 @@
       </c>
       <c r="H214" s="7" t="inlineStr">
         <is>
-          <t>tailoring</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="I214" s="7" t="inlineStr">
@@ -11677,7 +11677,7 @@
       <c r="K214" s="7" t="n"/>
       <c r="L214" s="7" t="inlineStr">
         <is>
-          <t>Source: Greenhouse/Lever</t>
+          <t>Skipped 2026-10-01: in-office requirement outside SLC (standing rule)</t>
         </is>
       </c>
       <c r="M214" s="7" t="inlineStr">
@@ -11722,7 +11722,7 @@
       </c>
       <c r="H215" s="7" t="inlineStr">
         <is>
-          <t>tailoring</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="I215" s="7" t="inlineStr">
@@ -11738,7 +11738,7 @@
       <c r="K215" s="7" t="n"/>
       <c r="L215" s="7" t="inlineStr">
         <is>
-          <t>In-person/hybrid: San Mateo, CA United States; Stretch: short of years listed; Source: Greenhouse/Lever</t>
+          <t>Skipped 2026-10-01: in-office requirement outside SLC (standing rule)</t>
         </is>
       </c>
       <c r="M215" s="7" t="inlineStr">
@@ -11783,7 +11783,7 @@
       </c>
       <c r="H216" s="7" t="inlineStr">
         <is>
-          <t>tailoring</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="I216" s="7" t="inlineStr">
@@ -11799,7 +11799,7 @@
       <c r="K216" s="7" t="n"/>
       <c r="L216" s="7" t="inlineStr">
         <is>
-          <t>In-person/hybrid: San Mateo, CA United States; Stretch: short of years listed; Source: Greenhouse/Lever</t>
+          <t>Skipped 2026-10-01: in-office requirement outside SLC (standing rule)</t>
         </is>
       </c>
       <c r="M216" s="7" t="inlineStr">
@@ -11844,7 +11844,7 @@
       </c>
       <c r="H217" s="7" t="inlineStr">
         <is>
-          <t>tailoring</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="I217" s="7" t="inlineStr">
@@ -11860,7 +11860,7 @@
       <c r="K217" s="7" t="n"/>
       <c r="L217" s="7" t="inlineStr">
         <is>
-          <t>In-person/hybrid: San Mateo, CA United States; Stretch: short of years listed; Source: Greenhouse/Lever</t>
+          <t>Skipped 2026-10-01: in-office requirement outside SLC (standing rule)</t>
         </is>
       </c>
       <c r="M217" s="7" t="inlineStr">
@@ -11905,7 +11905,7 @@
       </c>
       <c r="H218" s="7" t="inlineStr">
         <is>
-          <t>tailoring</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="I218" s="7" t="inlineStr">
@@ -11921,7 +11921,7 @@
       <c r="K218" s="7" t="n"/>
       <c r="L218" s="7" t="inlineStr">
         <is>
-          <t>Underleveled (1-3 yrs) but tasks match; Source: Greenhouse/Lever</t>
+          <t>Skipped 2026-10-01: in-office requirement outside SLC (standing rule)</t>
         </is>
       </c>
       <c r="M218" s="7" t="inlineStr">
@@ -12464,7 +12464,7 @@
       </c>
       <c r="H229" s="7" t="inlineStr">
         <is>
-          <t>tailoring</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="I229" s="7" t="inlineStr">
@@ -12476,7 +12476,7 @@
       <c r="K229" s="7" t="n"/>
       <c r="L229" s="7" t="inlineStr">
         <is>
-          <t>In-person/hybrid: New York, NY; Resume only (no letter field); Source: Greenhouse/Lever</t>
+          <t>Skipped 2026-10-01: in-office requirement outside SLC (standing rule)</t>
         </is>
       </c>
       <c r="M229" s="7" t="inlineStr">

--- a/tracker.xlsx
+++ b/tracker.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:O234"/>
+  <dimension ref="A1:O243"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.453125" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="22" customWidth="1" style="4" min="1" max="1"/>
@@ -12772,6 +12772,369 @@
         </is>
       </c>
     </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>SRS Acquiom</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Remote (Continental US) or Denver, CO hybrid</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/srsacquiom/jobs/5167579007</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>$145k-$160k</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>Internal data platform on Platform Engineering team: AWS data infra, Postgres/MySQL, Python. Fully remote within Continental US (Denver hybrid option); HQ visits ~3x/yr.</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="O235" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>SERHANT.</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Remote (US)</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/serhant/jobs/4121489009</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>$170,000</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>Lakehouse architecture, ClickHouse/Postgres, ETL/ELT; LLM use for data transformation. Remote, must live in US.</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="O236" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>ParetoHealth</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/paretocaptiveservicesllc/jobs/4705491006</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>Serverless AWS pipelines (Lambda/Glue/Athena/S3) and data models for AI/Analytics teams; supports MLOps, feature stores, model training/scoring.</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="O237" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>Hopscotch Primary Care</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/hopscotchprimarycare/jobs/6112800004</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>$140,000-$170,000</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>Own and evolve the data platform; Python/PySpark, data models/warehouses/lakehouses.</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="O238" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>Cresta</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Senior Infrastructure Engineer/SRE</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>United States (Remote)</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/cresta/jobs/5137153008</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>OTE $205,000-$270,000 + equity</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>Core infrastructure team; builds ML infrastructure so AI teams can train/test/deploy on large-scale datasets; multi-cloud Kubernetes. Salary band shown is OTE.</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="O239" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>Render</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Senior/Staff Data Engineer</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>SF or Remote (US/Canada)</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/render/f846e1fc-0099-4456-9232-9abe83dff272</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>Data Platform Engineering: pipelines, BigQuery warehouse, orchestration platform; model-ready datasets and AI/LLM workflow integration. Requires 7+ yrs.</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="O240" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>Cortex</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Remote (US)</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/cortex/jobs/5380208008</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>Own internal data systems/pipelines (Segment/Hevo/BigQuery/Omni) with AI-driven automation on top. Fully remote US; all-company offsites a few times/yr.</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="O241" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>Webflow</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Staff Data Engineer</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Remote-first (United States)</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/webflow/jobs/8165290</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>Zone A $212,500-$255,000; Zone B $200,000-$240,000; Zone C $186,500-$224,000</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>Data lake, event instrumentation, data quality/governance; Spark/Kafka/Iceberg/Airflow. 5+ yrs data engineering. Utah salary zone unconfirmed.</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="O242" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>Fora Financial</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Staff Data Engineer</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Remote (US)</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/forafinancial/jobs/4298234009</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>$175,000-$200,000</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>Staff IC on Data &amp; AI team: data platform architecture, Snowflake, data contracts, AI/agent-ready data products. Eastern/Central time zones preferred, not required.</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="O243" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:O234"/>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>

--- a/tracker.xlsx
+++ b/tracker.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tracker" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Tracker" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Tracker'!$A$1:$O$234</definedName>
@@ -12773,363 +12773,438 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" t="inlineStr">
+      <c r="A235" s="4" t="inlineStr">
         <is>
           <t>SRS Acquiom</t>
         </is>
       </c>
-      <c r="B235" t="inlineStr">
+      <c r="B235" s="4" t="inlineStr">
         <is>
           <t>Senior Data Engineer</t>
         </is>
       </c>
-      <c r="C235" t="inlineStr">
+      <c r="C235" s="4" t="inlineStr">
         <is>
           <t>Remote (Continental US) or Denver, CO hybrid</t>
         </is>
       </c>
-      <c r="D235" t="inlineStr">
+      <c r="D235" s="4" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/srsacquiom/jobs/5167579007</t>
         </is>
       </c>
-      <c r="F235" t="inlineStr">
+      <c r="F235" s="4" t="inlineStr">
         <is>
           <t>$145k-$160k</t>
         </is>
       </c>
-      <c r="G235" t="inlineStr">
+      <c r="G235" s="4" t="inlineStr">
         <is>
           <t>Internal data platform on Platform Engineering team: AWS data infra, Postgres/MySQL, Python. Fully remote within Continental US (Denver hybrid option); HQ visits ~3x/yr.</t>
         </is>
       </c>
-      <c r="H235" t="inlineStr">
-        <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="O235" t="inlineStr">
+      <c r="H235" s="4" t="inlineStr">
+        <is>
+          <t>tailoring</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>resume-srs-acquiom-senior-data-engineer.pdf</t>
+        </is>
+      </c>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>cover-letter-srs-acquiom-senior-data-engineer.pdf</t>
+        </is>
+      </c>
+      <c r="L235" t="inlineStr">
+        <is>
+          <t>Stretch: 6+ yrs SQL/Postgres; no Kafka/Glue/Terraform. Form has a "which core value resonates" question</t>
+        </is>
+      </c>
+      <c r="O235" s="4" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
     <row r="236">
-      <c r="A236" t="inlineStr">
+      <c r="A236" s="4" t="inlineStr">
         <is>
           <t>SERHANT.</t>
         </is>
       </c>
-      <c r="B236" t="inlineStr">
+      <c r="B236" s="4" t="inlineStr">
         <is>
           <t>Senior Data Engineer</t>
         </is>
       </c>
-      <c r="C236" t="inlineStr">
+      <c r="C236" s="4" t="inlineStr">
         <is>
           <t>Remote (US)</t>
         </is>
       </c>
-      <c r="D236" t="inlineStr">
+      <c r="D236" s="4" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/serhant/jobs/4121489009</t>
         </is>
       </c>
-      <c r="F236" t="inlineStr">
+      <c r="F236" s="4" t="inlineStr">
         <is>
           <t>$170,000</t>
         </is>
       </c>
-      <c r="G236" t="inlineStr">
+      <c r="G236" s="4" t="inlineStr">
         <is>
           <t>Lakehouse architecture, ClickHouse/Postgres, ETL/ELT; LLM use for data transformation. Remote, must live in US.</t>
         </is>
       </c>
-      <c r="H236" t="inlineStr">
-        <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="O236" t="inlineStr">
+      <c r="H236" s="4" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L236" t="inlineStr">
+        <is>
+          <t>Skipped: Spark/Airflow/Kafka/dbt/Iceberg stack; 5+ yrs</t>
+        </is>
+      </c>
+      <c r="O236" s="4" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
     <row r="237">
-      <c r="A237" t="inlineStr">
+      <c r="A237" s="4" t="inlineStr">
         <is>
           <t>ParetoHealth</t>
         </is>
       </c>
-      <c r="B237" t="inlineStr">
+      <c r="B237" s="4" t="inlineStr">
         <is>
           <t>Senior Data Engineer</t>
         </is>
       </c>
-      <c r="C237" t="inlineStr">
+      <c r="C237" s="4" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="D237" t="inlineStr">
+      <c r="D237" s="4" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/paretocaptiveservicesllc/jobs/4705491006</t>
         </is>
       </c>
-      <c r="G237" t="inlineStr">
+      <c r="G237" s="4" t="inlineStr">
         <is>
           <t>Serverless AWS pipelines (Lambda/Glue/Athena/S3) and data models for AI/Analytics teams; supports MLOps, feature stores, model training/scoring.</t>
         </is>
       </c>
-      <c r="H237" t="inlineStr">
-        <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="O237" t="inlineStr">
+      <c r="H237" s="4" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L237" t="inlineStr">
+        <is>
+          <t>Skipped: AWS Glue/Spark/Kafka pipelines; 5+ yrs</t>
+        </is>
+      </c>
+      <c r="O237" s="4" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
     <row r="238">
-      <c r="A238" t="inlineStr">
+      <c r="A238" s="4" t="inlineStr">
         <is>
           <t>Hopscotch Primary Care</t>
         </is>
       </c>
-      <c r="B238" t="inlineStr">
+      <c r="B238" s="4" t="inlineStr">
         <is>
           <t>Senior Data Engineer</t>
         </is>
       </c>
-      <c r="C238" t="inlineStr">
+      <c r="C238" s="4" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="D238" t="inlineStr">
+      <c r="D238" s="4" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/hopscotchprimarycare/jobs/6112800004</t>
         </is>
       </c>
-      <c r="F238" t="inlineStr">
+      <c r="F238" s="4" t="inlineStr">
         <is>
           <t>$140,000-$170,000</t>
         </is>
       </c>
-      <c r="G238" t="inlineStr">
+      <c r="G238" s="4" t="inlineStr">
         <is>
           <t>Own and evolve the data platform; Python/PySpark, data models/warehouses/lakehouses.</t>
         </is>
       </c>
-      <c r="H238" t="inlineStr">
-        <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="O238" t="inlineStr">
+      <c r="H238" s="4" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L238" t="inlineStr">
+        <is>
+          <t>Skipped: PySpark/Snowflake/Databricks; 4+ yrs</t>
+        </is>
+      </c>
+      <c r="O238" s="4" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
     <row r="239">
-      <c r="A239" t="inlineStr">
+      <c r="A239" s="4" t="inlineStr">
         <is>
           <t>Cresta</t>
         </is>
       </c>
-      <c r="B239" t="inlineStr">
+      <c r="B239" s="4" t="inlineStr">
         <is>
           <t>Senior Infrastructure Engineer/SRE</t>
         </is>
       </c>
-      <c r="C239" t="inlineStr">
+      <c r="C239" s="4" t="inlineStr">
         <is>
           <t>United States (Remote)</t>
         </is>
       </c>
-      <c r="D239" t="inlineStr">
+      <c r="D239" s="4" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/cresta/jobs/5137153008</t>
         </is>
       </c>
-      <c r="F239" t="inlineStr">
+      <c r="F239" s="4" t="inlineStr">
         <is>
           <t>OTE $205,000-$270,000 + equity</t>
         </is>
       </c>
-      <c r="G239" t="inlineStr">
+      <c r="G239" s="4" t="inlineStr">
         <is>
           <t>Core infrastructure team; builds ML infrastructure so AI teams can train/test/deploy on large-scale datasets; multi-cloud Kubernetes. Salary band shown is OTE.</t>
         </is>
       </c>
-      <c r="H239" t="inlineStr">
-        <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="O239" t="inlineStr">
+      <c r="H239" s="4" t="inlineStr">
+        <is>
+          <t>tailoring</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>resume-cresta-senior-infrastructure-engineer-sre.pdf</t>
+        </is>
+      </c>
+      <c r="J239" t="inlineStr">
+        <is>
+          <t>cover-letter-cresta-senior-infrastructure-engineer-sre.pdf</t>
+        </is>
+      </c>
+      <c r="L239" t="inlineStr">
+        <is>
+          <t>Stretch: 5+ yrs DevOps/SRE; multi-cloud Terraform</t>
+        </is>
+      </c>
+      <c r="O239" s="4" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="240">
-      <c r="A240" t="inlineStr">
+      <c r="A240" s="4" t="inlineStr">
         <is>
           <t>Render</t>
         </is>
       </c>
-      <c r="B240" t="inlineStr">
+      <c r="B240" s="4" t="inlineStr">
         <is>
           <t>Senior/Staff Data Engineer</t>
         </is>
       </c>
-      <c r="C240" t="inlineStr">
+      <c r="C240" s="4" t="inlineStr">
         <is>
           <t>SF or Remote (US/Canada)</t>
         </is>
       </c>
-      <c r="D240" t="inlineStr">
+      <c r="D240" s="4" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/render/f846e1fc-0099-4456-9232-9abe83dff272</t>
         </is>
       </c>
-      <c r="G240" t="inlineStr">
+      <c r="G240" s="4" t="inlineStr">
         <is>
           <t>Data Platform Engineering: pipelines, BigQuery warehouse, orchestration platform; model-ready datasets and AI/LLM workflow integration. Requires 7+ yrs.</t>
         </is>
       </c>
-      <c r="H240" t="inlineStr">
-        <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="O240" t="inlineStr">
+      <c r="H240" s="4" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L240" t="inlineStr">
+        <is>
+          <t>Skipped: 7+ yrs; Airflow/Snowflake/dbt</t>
+        </is>
+      </c>
+      <c r="O240" s="4" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="241">
-      <c r="A241" t="inlineStr">
+      <c r="A241" s="4" t="inlineStr">
         <is>
           <t>Cortex</t>
         </is>
       </c>
-      <c r="B241" t="inlineStr">
+      <c r="B241" s="4" t="inlineStr">
         <is>
           <t>Senior Data Engineer</t>
         </is>
       </c>
-      <c r="C241" t="inlineStr">
+      <c r="C241" s="4" t="inlineStr">
         <is>
           <t>Remote (US)</t>
         </is>
       </c>
-      <c r="D241" t="inlineStr">
+      <c r="D241" s="4" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/cortex/jobs/5380208008</t>
         </is>
       </c>
-      <c r="G241" t="inlineStr">
+      <c r="G241" s="4" t="inlineStr">
         <is>
           <t>Own internal data systems/pipelines (Segment/Hevo/BigQuery/Omni) with AI-driven automation on top. Fully remote US; all-company offsites a few times/yr.</t>
         </is>
       </c>
-      <c r="H241" t="inlineStr">
-        <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="O241" t="inlineStr">
+      <c r="H241" s="4" t="inlineStr">
+        <is>
+          <t>tailoring</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>resume-cortex-senior-data-engineer.pdf</t>
+        </is>
+      </c>
+      <c r="J241" t="inlineStr">
+        <is>
+          <t>cover-letter-cortex-senior-data-engineer.pdf</t>
+        </is>
+      </c>
+      <c r="L241" t="inlineStr">
+        <is>
+          <t>Stretch: no dbt/BigQuery. Form asks "tell us about a data pipeline you built" (Ralli ESPN ETL) and years as a DE</t>
+        </is>
+      </c>
+      <c r="O241" s="4" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
     <row r="242">
-      <c r="A242" t="inlineStr">
+      <c r="A242" s="4" t="inlineStr">
         <is>
           <t>Webflow</t>
         </is>
       </c>
-      <c r="B242" t="inlineStr">
+      <c r="B242" s="4" t="inlineStr">
         <is>
           <t>Staff Data Engineer</t>
         </is>
       </c>
-      <c r="C242" t="inlineStr">
+      <c r="C242" s="4" t="inlineStr">
         <is>
           <t>Remote-first (United States)</t>
         </is>
       </c>
-      <c r="D242" t="inlineStr">
+      <c r="D242" s="4" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/webflow/jobs/8165290</t>
         </is>
       </c>
-      <c r="F242" t="inlineStr">
+      <c r="F242" s="4" t="inlineStr">
         <is>
           <t>Zone A $212,500-$255,000; Zone B $200,000-$240,000; Zone C $186,500-$224,000</t>
         </is>
       </c>
-      <c r="G242" t="inlineStr">
+      <c r="G242" s="4" t="inlineStr">
         <is>
           <t>Data lake, event instrumentation, data quality/governance; Spark/Kafka/Iceberg/Airflow. 5+ yrs data engineering. Utah salary zone unconfirmed.</t>
         </is>
       </c>
-      <c r="H242" t="inlineStr">
-        <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="O242" t="inlineStr">
+      <c r="H242" s="4" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L242" t="inlineStr">
+        <is>
+          <t>Skipped: Staff; Spark/Kafka/Iceberg/Airflow; 5+ yrs</t>
+        </is>
+      </c>
+      <c r="O242" s="4" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="243">
-      <c r="A243" t="inlineStr">
+      <c r="A243" s="4" t="inlineStr">
         <is>
           <t>Fora Financial</t>
         </is>
       </c>
-      <c r="B243" t="inlineStr">
+      <c r="B243" s="4" t="inlineStr">
         <is>
           <t>Staff Data Engineer</t>
         </is>
       </c>
-      <c r="C243" t="inlineStr">
+      <c r="C243" s="4" t="inlineStr">
         <is>
           <t>Remote (US)</t>
         </is>
       </c>
-      <c r="D243" t="inlineStr">
+      <c r="D243" s="4" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/forafinancial/jobs/4298234009</t>
         </is>
       </c>
-      <c r="F243" t="inlineStr">
+      <c r="F243" s="4" t="inlineStr">
         <is>
           <t>$175,000-$200,000</t>
         </is>
       </c>
-      <c r="G243" t="inlineStr">
+      <c r="G243" s="4" t="inlineStr">
         <is>
           <t>Staff IC on Data &amp; AI team: data platform architecture, Snowflake, data contracts, AI/agent-ready data products. Eastern/Central time zones preferred, not required.</t>
         </is>
       </c>
-      <c r="H243" t="inlineStr">
-        <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="O243" t="inlineStr">
+      <c r="H243" s="4" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L243" t="inlineStr">
+        <is>
+          <t>Skipped: Staff; Snowflake/Airflow/Iceberg stack</t>
+        </is>
+      </c>
+      <c r="O243" s="4" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>

--- a/tracker.xlsx
+++ b/tracker.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:O243"/>
+  <dimension ref="A1:O244"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.453125" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="22" customWidth="1" style="4" min="1" max="1"/>
@@ -12808,17 +12808,17 @@
           <t>tailoring</t>
         </is>
       </c>
-      <c r="I235" t="inlineStr">
+      <c r="I235" s="4" t="inlineStr">
         <is>
           <t>resume-srs-acquiom-senior-data-engineer.pdf</t>
         </is>
       </c>
-      <c r="J235" t="inlineStr">
+      <c r="J235" s="4" t="inlineStr">
         <is>
           <t>cover-letter-srs-acquiom-senior-data-engineer.pdf</t>
         </is>
       </c>
-      <c r="L235" t="inlineStr">
+      <c r="L235" s="4" t="inlineStr">
         <is>
           <t>Stretch: 6+ yrs SQL/Postgres; no Kafka/Glue/Terraform. Form has a "which core value resonates" question</t>
         </is>
@@ -12865,7 +12865,7 @@
           <t>skipped</t>
         </is>
       </c>
-      <c r="L236" t="inlineStr">
+      <c r="L236" s="4" t="inlineStr">
         <is>
           <t>Skipped: Spark/Airflow/Kafka/dbt/Iceberg stack; 5+ yrs</t>
         </is>
@@ -12907,7 +12907,7 @@
           <t>skipped</t>
         </is>
       </c>
-      <c r="L237" t="inlineStr">
+      <c r="L237" s="4" t="inlineStr">
         <is>
           <t>Skipped: AWS Glue/Spark/Kafka pipelines; 5+ yrs</t>
         </is>
@@ -12954,7 +12954,7 @@
           <t>skipped</t>
         </is>
       </c>
-      <c r="L238" t="inlineStr">
+      <c r="L238" s="4" t="inlineStr">
         <is>
           <t>Skipped: PySpark/Snowflake/Databricks; 4+ yrs</t>
         </is>
@@ -13001,17 +13001,17 @@
           <t>tailoring</t>
         </is>
       </c>
-      <c r="I239" t="inlineStr">
+      <c r="I239" s="4" t="inlineStr">
         <is>
           <t>resume-cresta-senior-infrastructure-engineer-sre.pdf</t>
         </is>
       </c>
-      <c r="J239" t="inlineStr">
+      <c r="J239" s="4" t="inlineStr">
         <is>
           <t>cover-letter-cresta-senior-infrastructure-engineer-sre.pdf</t>
         </is>
       </c>
-      <c r="L239" t="inlineStr">
+      <c r="L239" s="4" t="inlineStr">
         <is>
           <t>Stretch: 5+ yrs DevOps/SRE; multi-cloud Terraform</t>
         </is>
@@ -13053,7 +13053,7 @@
           <t>skipped</t>
         </is>
       </c>
-      <c r="L240" t="inlineStr">
+      <c r="L240" s="4" t="inlineStr">
         <is>
           <t>Skipped: 7+ yrs; Airflow/Snowflake/dbt</t>
         </is>
@@ -13095,17 +13095,17 @@
           <t>tailoring</t>
         </is>
       </c>
-      <c r="I241" t="inlineStr">
+      <c r="I241" s="4" t="inlineStr">
         <is>
           <t>resume-cortex-senior-data-engineer.pdf</t>
         </is>
       </c>
-      <c r="J241" t="inlineStr">
+      <c r="J241" s="4" t="inlineStr">
         <is>
           <t>cover-letter-cortex-senior-data-engineer.pdf</t>
         </is>
       </c>
-      <c r="L241" t="inlineStr">
+      <c r="L241" s="4" t="inlineStr">
         <is>
           <t>Stretch: no dbt/BigQuery. Form asks "tell us about a data pipeline you built" (Ralli ESPN ETL) and years as a DE</t>
         </is>
@@ -13152,7 +13152,7 @@
           <t>skipped</t>
         </is>
       </c>
-      <c r="L242" t="inlineStr">
+      <c r="L242" s="4" t="inlineStr">
         <is>
           <t>Skipped: Staff; Spark/Kafka/Iceberg/Airflow; 5+ yrs</t>
         </is>
@@ -13199,7 +13199,7 @@
           <t>skipped</t>
         </is>
       </c>
-      <c r="L243" t="inlineStr">
+      <c r="L243" s="4" t="inlineStr">
         <is>
           <t>Skipped: Staff; Snowflake/Airflow/Iceberg stack</t>
         </is>
@@ -13207,6 +13207,69 @@
       <c r="O243" s="4" t="inlineStr">
         <is>
           <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="4" t="inlineStr">
+        <is>
+          <t>Cricut</t>
+        </is>
+      </c>
+      <c r="B244" s="4" t="inlineStr">
+        <is>
+          <t>AI Engineering Lead/Manager</t>
+        </is>
+      </c>
+      <c r="C244" s="4" t="inlineStr">
+        <is>
+          <t>South Jordan, UT</t>
+        </is>
+      </c>
+      <c r="D244" s="4" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4472943909/</t>
+        </is>
+      </c>
+      <c r="F244" s="4" t="n"/>
+      <c r="G244" s="4" t="inlineStr">
+        <is>
+          <t>Lead a team shipping AI features (image gen, agentic actions, MCP) into client apps; 5+ yrs Python/Kotlin/Swift/C#/Angular, 2+ yrs tech lead. In Utah (near SLC).</t>
+        </is>
+      </c>
+      <c r="H244" s="4" t="inlineStr">
+        <is>
+          <t>tailoring</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>resume-cricut-ai-engineering-lead-manager.pdf</t>
+        </is>
+      </c>
+      <c r="J244" t="inlineStr">
+        <is>
+          <t>cover-letter-cricut-ai-engineering-lead-manager.pdf</t>
+        </is>
+      </c>
+      <c r="L244" s="4" t="inlineStr">
+        <is>
+          <t>Added by Jack via LinkedIn. Stretch: no AI image generation or MCP in production; has led teams as CTO, not formal manager. Source: LinkedIn</t>
+        </is>
+      </c>
+      <c r="M244" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="N244" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="O244" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
         </is>
       </c>
     </row>

--- a/tracker.xlsx
+++ b/tracker.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Tracker" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tracker" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Tracker'!$A$1:$O$234</definedName>
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:O244"/>
+  <dimension ref="A1:O252"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.453125" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="22" customWidth="1" style="4" min="1" max="1"/>
@@ -13242,12 +13242,12 @@
           <t>tailoring</t>
         </is>
       </c>
-      <c r="I244" t="inlineStr">
+      <c r="I244" s="4" t="inlineStr">
         <is>
           <t>resume-cricut-ai-engineering-lead-manager.pdf</t>
         </is>
       </c>
-      <c r="J244" t="inlineStr">
+      <c r="J244" s="4" t="inlineStr">
         <is>
           <t>cover-letter-cricut-ai-engineering-lead-manager.pdf</t>
         </is>
@@ -13257,12 +13257,12 @@
           <t>Added by Jack via LinkedIn. Stretch: no AI image generation or MCP in production; has led teams as CTO, not formal manager. Source: LinkedIn</t>
         </is>
       </c>
-      <c r="M244" t="inlineStr">
+      <c r="M244" s="4" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="N244" t="inlineStr">
+      <c r="N244" s="4" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
@@ -13270,6 +13270,454 @@
       <c r="O244" s="4" t="inlineStr">
         <is>
           <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>Taulia</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>AI Data Engineer</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Remote (US)</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>https://www.obtainjob.com/2026/10/hiring-ai-data-engineer.html</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr"/>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>$165K-$185K (est.)</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>AI Data Engineer at fintech; LLM/data-tooling-adjacent title; remote US.</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr"/>
+      <c r="J245" t="inlineStr"/>
+      <c r="K245" t="inlineStr"/>
+      <c r="L245" t="inlineStr"/>
+      <c r="M245" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N245" t="inlineStr"/>
+      <c r="O245" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>Horizon3.ai</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer, Tech Lead</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Remote (US)</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>https://careers.nightdragon.com/companies/horizon3-ai-2/jobs/53692831-senior-data-engineer-tech-lead</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr"/>
+      <c r="F246" t="inlineStr"/>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>Senior DE tech lead; cybersecurity data platform; fully remote.</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr"/>
+      <c r="J246" t="inlineStr"/>
+      <c r="K246" t="inlineStr"/>
+      <c r="L246" t="inlineStr">
+        <is>
+          <t>TRAVEL: posting mentions ~5% travel - under veto threshold, fine.</t>
+        </is>
+      </c>
+      <c r="M246" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N246" t="inlineStr"/>
+      <c r="O246" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>iHerb</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Sr. Data Engineer I</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Remote (US)</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>https://builtin.com/job/sr-data-engineer-i/8204223</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>$116K-$170K</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>Ground-up cloud data platform + MLOps (feature stores, MLflow); remote US.</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr"/>
+      <c r="J247" t="inlineStr"/>
+      <c r="K247" t="inlineStr"/>
+      <c r="L247" t="inlineStr"/>
+      <c r="M247" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N247" t="inlineStr"/>
+      <c r="O247" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>Dragos</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Remote (US)</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>https://builtin.com/job/senior-data-engineer/10853364</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>$165,000</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>Cybersecurity/ICS data; streaming, K8s, data contracts; #LI-REMOTE.</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr"/>
+      <c r="J248" t="inlineStr"/>
+      <c r="K248" t="inlineStr"/>
+      <c r="L248" t="inlineStr"/>
+      <c r="M248" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N248" t="inlineStr"/>
+      <c r="O248" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>Healthie</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Remote (US)</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>https://farcoder.com/remote-data-and-analytics-job/senior-data-engineer-healthie</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>$185,000-$215,000</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>AI-accelerated health-tech data team; remote US.</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr"/>
+      <c r="J249" t="inlineStr"/>
+      <c r="K249" t="inlineStr"/>
+      <c r="L249" t="inlineStr"/>
+      <c r="M249" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N249" t="inlineStr"/>
+      <c r="O249" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>Truthset</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>https://jobs.gusto.com/boards/truthset-inc-8861de94-567d-4e85-8f64-fc9d6f7e1c3e</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>$120,000-$200,000</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>Data-intelligence/validation company; remote.</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr"/>
+      <c r="J250" t="inlineStr"/>
+      <c r="K250" t="inlineStr"/>
+      <c r="L250" t="inlineStr"/>
+      <c r="M250" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N250" t="inlineStr"/>
+      <c r="O250" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>Foley</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Remote (US)</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4358835419</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>$140,000-$180,000</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>Senior DE; remote US; apply via Ashby.</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr"/>
+      <c r="J251" t="inlineStr"/>
+      <c r="K251" t="inlineStr"/>
+      <c r="L251" t="inlineStr"/>
+      <c r="M251" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N251" t="inlineStr"/>
+      <c r="O251" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>Recharge</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Remote (US)</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4370238059</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>$108K-$185K (agg.)</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>Data pipelines + customer-facing data products; remote US.</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr"/>
+      <c r="J252" t="inlineStr"/>
+      <c r="K252" t="inlineStr"/>
+      <c r="L252" t="inlineStr"/>
+      <c r="M252" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N252" t="inlineStr"/>
+      <c r="O252" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
     </row>

--- a/tracker.xlsx
+++ b/tracker.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tracker" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Tracker" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Tracker'!$A$1:$O$234</definedName>
@@ -13274,448 +13274,492 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" t="inlineStr">
+      <c r="A245" s="4" t="inlineStr">
         <is>
           <t>Taulia</t>
         </is>
       </c>
-      <c r="B245" t="inlineStr">
+      <c r="B245" s="4" t="inlineStr">
         <is>
           <t>AI Data Engineer</t>
         </is>
       </c>
-      <c r="C245" t="inlineStr">
+      <c r="C245" s="4" t="inlineStr">
         <is>
           <t>Remote (US)</t>
         </is>
       </c>
-      <c r="D245" t="inlineStr">
+      <c r="D245" s="4" t="inlineStr">
         <is>
           <t>https://www.obtainjob.com/2026/10/hiring-ai-data-engineer.html</t>
         </is>
       </c>
-      <c r="E245" t="inlineStr"/>
-      <c r="F245" t="inlineStr">
+      <c r="E245" s="4" t="inlineStr"/>
+      <c r="F245" s="4" t="inlineStr">
         <is>
           <t>$165K-$185K (est.)</t>
         </is>
       </c>
-      <c r="G245" t="inlineStr">
+      <c r="G245" s="4" t="inlineStr">
         <is>
           <t>AI Data Engineer at fintech; LLM/data-tooling-adjacent title; remote US.</t>
         </is>
       </c>
-      <c r="H245" t="inlineStr">
+      <c r="H245" s="4" t="inlineStr">
+        <is>
+          <t>tailoring</t>
+        </is>
+      </c>
+      <c r="I245" s="4" t="inlineStr">
+        <is>
+          <t>resume-taulia-ai-data-engineer.pdf</t>
+        </is>
+      </c>
+      <c r="J245" s="4" t="inlineStr">
+        <is>
+          <t>cover-letter-taulia-ai-data-engineer.pdf</t>
+        </is>
+      </c>
+      <c r="K245" s="4" t="inlineStr"/>
+      <c r="L245" s="4" t="inlineStr">
+        <is>
+          <t>Strong-ish fit: RAG/vector/embeddings + ETL + REST. URL is an aggregator (obtainjob): find the real Taulia careers/apply page. No SAP/enterprise warehouse experience</t>
+        </is>
+      </c>
+      <c r="M245" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N245" s="4" t="inlineStr"/>
+      <c r="O245" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="4" t="inlineStr">
+        <is>
+          <t>Horizon3.ai</t>
+        </is>
+      </c>
+      <c r="B246" s="4" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer, Tech Lead</t>
+        </is>
+      </c>
+      <c r="C246" s="4" t="inlineStr">
+        <is>
+          <t>Remote (US)</t>
+        </is>
+      </c>
+      <c r="D246" s="4" t="inlineStr">
+        <is>
+          <t>https://careers.nightdragon.com/companies/horizon3-ai-2/jobs/53692831-senior-data-engineer-tech-lead</t>
+        </is>
+      </c>
+      <c r="E246" s="4" t="inlineStr"/>
+      <c r="F246" s="4" t="inlineStr"/>
+      <c r="G246" s="4" t="inlineStr">
+        <is>
+          <t>Senior DE tech lead; cybersecurity data platform; fully remote.</t>
+        </is>
+      </c>
+      <c r="H246" s="4" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="I246" s="4" t="inlineStr"/>
+      <c r="J246" s="4" t="inlineStr"/>
+      <c r="K246" s="4" t="inlineStr"/>
+      <c r="L246" s="4" t="inlineStr">
+        <is>
+          <t>Skipped: posting closed ("no longer accepting applications", posted 6+ months ago); TRAVEL: posting mentions ~5% travel - under veto threshold, fine.</t>
+        </is>
+      </c>
+      <c r="M246" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N246" s="4" t="inlineStr"/>
+      <c r="O246" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="4" t="inlineStr">
+        <is>
+          <t>iHerb</t>
+        </is>
+      </c>
+      <c r="B247" s="4" t="inlineStr">
+        <is>
+          <t>Sr. Data Engineer I</t>
+        </is>
+      </c>
+      <c r="C247" s="4" t="inlineStr">
+        <is>
+          <t>Remote (US)</t>
+        </is>
+      </c>
+      <c r="D247" s="4" t="inlineStr">
+        <is>
+          <t>https://builtin.com/job/sr-data-engineer-i/8204223</t>
+        </is>
+      </c>
+      <c r="E247" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="F247" s="4" t="inlineStr">
+        <is>
+          <t>$116K-$170K</t>
+        </is>
+      </c>
+      <c r="G247" s="4" t="inlineStr">
+        <is>
+          <t>Ground-up cloud data platform + MLOps (feature stores, MLflow); remote US.</t>
+        </is>
+      </c>
+      <c r="H247" s="4" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="I247" s="4" t="inlineStr"/>
+      <c r="J247" s="4" t="inlineStr"/>
+      <c r="K247" s="4" t="inlineStr"/>
+      <c r="L247" s="4" t="inlineStr">
+        <is>
+          <t>Skipped: needs Databricks/PySpark; 5+ yrs</t>
+        </is>
+      </c>
+      <c r="M247" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N247" s="4" t="inlineStr"/>
+      <c r="O247" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="4" t="inlineStr">
+        <is>
+          <t>Dragos</t>
+        </is>
+      </c>
+      <c r="B248" s="4" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="C248" s="4" t="inlineStr">
+        <is>
+          <t>Remote (US)</t>
+        </is>
+      </c>
+      <c r="D248" s="4" t="inlineStr">
+        <is>
+          <t>https://builtin.com/job/senior-data-engineer/10853364</t>
+        </is>
+      </c>
+      <c r="E248" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="F248" s="4" t="inlineStr">
+        <is>
+          <t>$165,000</t>
+        </is>
+      </c>
+      <c r="G248" s="4" t="inlineStr">
+        <is>
+          <t>Cybersecurity/ICS data; streaming, K8s, data contracts; #LI-REMOTE.</t>
+        </is>
+      </c>
+      <c r="H248" s="4" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="I248" s="4" t="inlineStr"/>
+      <c r="J248" s="4" t="inlineStr"/>
+      <c r="K248" s="4" t="inlineStr"/>
+      <c r="L248" s="4" t="inlineStr">
+        <is>
+          <t>Skipped: dimensional modeling/streaming/cybersecurity domain; 5+ yrs</t>
+        </is>
+      </c>
+      <c r="M248" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N248" s="4" t="inlineStr"/>
+      <c r="O248" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="4" t="inlineStr">
+        <is>
+          <t>Healthie</t>
+        </is>
+      </c>
+      <c r="B249" s="4" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="C249" s="4" t="inlineStr">
+        <is>
+          <t>Remote (US)</t>
+        </is>
+      </c>
+      <c r="D249" s="4" t="inlineStr">
+        <is>
+          <t>https://farcoder.com/remote-data-and-analytics-job/senior-data-engineer-healthie</t>
+        </is>
+      </c>
+      <c r="E249" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="F249" s="4" t="inlineStr">
+        <is>
+          <t>$185,000-$215,000</t>
+        </is>
+      </c>
+      <c r="G249" s="4" t="inlineStr">
+        <is>
+          <t>AI-accelerated health-tech data team; remote US.</t>
+        </is>
+      </c>
+      <c r="H249" s="4" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="I249" s="4" t="inlineStr"/>
+      <c r="J249" s="4" t="inlineStr"/>
+      <c r="K249" s="4" t="inlineStr"/>
+      <c r="L249" s="4" t="inlineStr">
+        <is>
+          <t>Skipped: Snowflake/dbt/Kafka/Scala stack; 6+ yrs</t>
+        </is>
+      </c>
+      <c r="M249" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N249" s="4" t="inlineStr"/>
+      <c r="O249" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="4" t="inlineStr">
+        <is>
+          <t>Truthset</t>
+        </is>
+      </c>
+      <c r="B250" s="4" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="C250" s="4" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="D250" s="4" t="inlineStr">
+        <is>
+          <t>https://jobs.gusto.com/boards/truthset-inc-8861de94-567d-4e85-8f64-fc9d6f7e1c3e</t>
+        </is>
+      </c>
+      <c r="E250" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="F250" s="4" t="inlineStr">
+        <is>
+          <t>$120,000-$200,000</t>
+        </is>
+      </c>
+      <c r="G250" s="4" t="inlineStr">
+        <is>
+          <t>Data-intelligence/validation company; remote.</t>
+        </is>
+      </c>
+      <c r="H250" s="4" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="I245" t="inlineStr"/>
-      <c r="J245" t="inlineStr"/>
-      <c r="K245" t="inlineStr"/>
-      <c r="L245" t="inlineStr"/>
-      <c r="M245" t="inlineStr">
+      <c r="I250" s="4" t="inlineStr"/>
+      <c r="J250" s="4" t="inlineStr"/>
+      <c r="K250" s="4" t="inlineStr"/>
+      <c r="L250" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Could not verify: posting page blocked (Cloudflare). Check by hand before applying; </t>
+        </is>
+      </c>
+      <c r="M250" s="4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="N245" t="inlineStr"/>
-      <c r="O245" t="inlineStr">
+      <c r="N250" s="4" t="inlineStr"/>
+      <c r="O250" s="4" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
-    <row r="246">
-      <c r="A246" t="inlineStr">
-        <is>
-          <t>Horizon3.ai</t>
-        </is>
-      </c>
-      <c r="B246" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer, Tech Lead</t>
-        </is>
-      </c>
-      <c r="C246" t="inlineStr">
+    <row r="251">
+      <c r="A251" s="4" t="inlineStr">
+        <is>
+          <t>Foley</t>
+        </is>
+      </c>
+      <c r="B251" s="4" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="C251" s="4" t="inlineStr">
         <is>
           <t>Remote (US)</t>
         </is>
       </c>
-      <c r="D246" t="inlineStr">
-        <is>
-          <t>https://careers.nightdragon.com/companies/horizon3-ai-2/jobs/53692831-senior-data-engineer-tech-lead</t>
-        </is>
-      </c>
-      <c r="E246" t="inlineStr"/>
-      <c r="F246" t="inlineStr"/>
-      <c r="G246" t="inlineStr">
-        <is>
-          <t>Senior DE tech lead; cybersecurity data platform; fully remote.</t>
-        </is>
-      </c>
-      <c r="H246" t="inlineStr">
-        <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="I246" t="inlineStr"/>
-      <c r="J246" t="inlineStr"/>
-      <c r="K246" t="inlineStr"/>
-      <c r="L246" t="inlineStr">
-        <is>
-          <t>TRAVEL: posting mentions ~5% travel - under veto threshold, fine.</t>
-        </is>
-      </c>
-      <c r="M246" t="inlineStr">
+      <c r="D251" s="4" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4358835419</t>
+        </is>
+      </c>
+      <c r="E251" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="F251" s="4" t="inlineStr">
+        <is>
+          <t>$140,000-$180,000</t>
+        </is>
+      </c>
+      <c r="G251" s="4" t="inlineStr">
+        <is>
+          <t>Senior DE; remote US; apply via Ashby.</t>
+        </is>
+      </c>
+      <c r="H251" s="4" t="inlineStr">
+        <is>
+          <t>tailoring</t>
+        </is>
+      </c>
+      <c r="I251" s="4" t="inlineStr">
+        <is>
+          <t>resume-foley-senior-data-engineer.pdf</t>
+        </is>
+      </c>
+      <c r="J251" s="4" t="inlineStr">
+        <is>
+          <t>cover-letter-foley-senior-data-engineer.pdf</t>
+        </is>
+      </c>
+      <c r="K251" s="4" t="inlineStr"/>
+      <c r="L251" s="4" t="inlineStr">
+        <is>
+          <t>Stretch: wants Redshift/Glue/EventBridge, CDC/streaming. Real posting is on Ashby: https://jobs.ashbyhq.com/foley/d292fa96-260a-4e03-9e39-853d085ff134 (remote US, EST hours, $140-180K)</t>
+        </is>
+      </c>
+      <c r="M251" s="4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="N246" t="inlineStr"/>
-      <c r="O246" t="inlineStr">
+      <c r="N251" s="4" t="inlineStr"/>
+      <c r="O251" s="4" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
-    <row r="247">
-      <c r="A247" t="inlineStr">
-        <is>
-          <t>iHerb</t>
-        </is>
-      </c>
-      <c r="B247" t="inlineStr">
-        <is>
-          <t>Sr. Data Engineer I</t>
-        </is>
-      </c>
-      <c r="C247" t="inlineStr">
+    <row r="252">
+      <c r="A252" s="4" t="inlineStr">
+        <is>
+          <t>Recharge</t>
+        </is>
+      </c>
+      <c r="B252" s="4" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="C252" s="4" t="inlineStr">
         <is>
           <t>Remote (US)</t>
         </is>
       </c>
-      <c r="D247" t="inlineStr">
-        <is>
-          <t>https://builtin.com/job/sr-data-engineer-i/8204223</t>
-        </is>
-      </c>
-      <c r="E247" t="inlineStr">
+      <c r="D252" s="4" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4370238059</t>
+        </is>
+      </c>
+      <c r="E252" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="F247" t="inlineStr">
-        <is>
-          <t>$116K-$170K</t>
-        </is>
-      </c>
-      <c r="G247" t="inlineStr">
-        <is>
-          <t>Ground-up cloud data platform + MLOps (feature stores, MLflow); remote US.</t>
-        </is>
-      </c>
-      <c r="H247" t="inlineStr">
-        <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="I247" t="inlineStr"/>
-      <c r="J247" t="inlineStr"/>
-      <c r="K247" t="inlineStr"/>
-      <c r="L247" t="inlineStr"/>
-      <c r="M247" t="inlineStr">
+      <c r="F252" s="4" t="inlineStr">
+        <is>
+          <t>$108K-$185K (agg.)</t>
+        </is>
+      </c>
+      <c r="G252" s="4" t="inlineStr">
+        <is>
+          <t>Data pipelines + customer-facing data products; remote US.</t>
+        </is>
+      </c>
+      <c r="H252" s="4" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="I252" s="4" t="inlineStr"/>
+      <c r="J252" s="4" t="inlineStr"/>
+      <c r="K252" s="4" t="inlineStr"/>
+      <c r="L252" s="4" t="inlineStr">
+        <is>
+          <t>Skipped: the LinkedIn link points to an unrelated job (a sales role in India), so this lead is not verified</t>
+        </is>
+      </c>
+      <c r="M252" s="4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="N247" t="inlineStr"/>
-      <c r="O247" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" t="inlineStr">
-        <is>
-          <t>Dragos</t>
-        </is>
-      </c>
-      <c r="B248" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="C248" t="inlineStr">
-        <is>
-          <t>Remote (US)</t>
-        </is>
-      </c>
-      <c r="D248" t="inlineStr">
-        <is>
-          <t>https://builtin.com/job/senior-data-engineer/10853364</t>
-        </is>
-      </c>
-      <c r="E248" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="F248" t="inlineStr">
-        <is>
-          <t>$165,000</t>
-        </is>
-      </c>
-      <c r="G248" t="inlineStr">
-        <is>
-          <t>Cybersecurity/ICS data; streaming, K8s, data contracts; #LI-REMOTE.</t>
-        </is>
-      </c>
-      <c r="H248" t="inlineStr">
-        <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="I248" t="inlineStr"/>
-      <c r="J248" t="inlineStr"/>
-      <c r="K248" t="inlineStr"/>
-      <c r="L248" t="inlineStr"/>
-      <c r="M248" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N248" t="inlineStr"/>
-      <c r="O248" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" t="inlineStr">
-        <is>
-          <t>Healthie</t>
-        </is>
-      </c>
-      <c r="B249" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="C249" t="inlineStr">
-        <is>
-          <t>Remote (US)</t>
-        </is>
-      </c>
-      <c r="D249" t="inlineStr">
-        <is>
-          <t>https://farcoder.com/remote-data-and-analytics-job/senior-data-engineer-healthie</t>
-        </is>
-      </c>
-      <c r="E249" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="F249" t="inlineStr">
-        <is>
-          <t>$185,000-$215,000</t>
-        </is>
-      </c>
-      <c r="G249" t="inlineStr">
-        <is>
-          <t>AI-accelerated health-tech data team; remote US.</t>
-        </is>
-      </c>
-      <c r="H249" t="inlineStr">
-        <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="I249" t="inlineStr"/>
-      <c r="J249" t="inlineStr"/>
-      <c r="K249" t="inlineStr"/>
-      <c r="L249" t="inlineStr"/>
-      <c r="M249" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N249" t="inlineStr"/>
-      <c r="O249" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" t="inlineStr">
-        <is>
-          <t>Truthset</t>
-        </is>
-      </c>
-      <c r="B250" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="C250" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
-      <c r="D250" t="inlineStr">
-        <is>
-          <t>https://jobs.gusto.com/boards/truthset-inc-8861de94-567d-4e85-8f64-fc9d6f7e1c3e</t>
-        </is>
-      </c>
-      <c r="E250" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="F250" t="inlineStr">
-        <is>
-          <t>$120,000-$200,000</t>
-        </is>
-      </c>
-      <c r="G250" t="inlineStr">
-        <is>
-          <t>Data-intelligence/validation company; remote.</t>
-        </is>
-      </c>
-      <c r="H250" t="inlineStr">
-        <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="I250" t="inlineStr"/>
-      <c r="J250" t="inlineStr"/>
-      <c r="K250" t="inlineStr"/>
-      <c r="L250" t="inlineStr"/>
-      <c r="M250" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N250" t="inlineStr"/>
-      <c r="O250" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" t="inlineStr">
-        <is>
-          <t>Foley</t>
-        </is>
-      </c>
-      <c r="B251" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="C251" t="inlineStr">
-        <is>
-          <t>Remote (US)</t>
-        </is>
-      </c>
-      <c r="D251" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4358835419</t>
-        </is>
-      </c>
-      <c r="E251" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="F251" t="inlineStr">
-        <is>
-          <t>$140,000-$180,000</t>
-        </is>
-      </c>
-      <c r="G251" t="inlineStr">
-        <is>
-          <t>Senior DE; remote US; apply via Ashby.</t>
-        </is>
-      </c>
-      <c r="H251" t="inlineStr">
-        <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="I251" t="inlineStr"/>
-      <c r="J251" t="inlineStr"/>
-      <c r="K251" t="inlineStr"/>
-      <c r="L251" t="inlineStr"/>
-      <c r="M251" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N251" t="inlineStr"/>
-      <c r="O251" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" t="inlineStr">
-        <is>
-          <t>Recharge</t>
-        </is>
-      </c>
-      <c r="B252" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="C252" t="inlineStr">
-        <is>
-          <t>Remote (US)</t>
-        </is>
-      </c>
-      <c r="D252" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4370238059</t>
-        </is>
-      </c>
-      <c r="E252" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="F252" t="inlineStr">
-        <is>
-          <t>$108K-$185K (agg.)</t>
-        </is>
-      </c>
-      <c r="G252" t="inlineStr">
-        <is>
-          <t>Data pipelines + customer-facing data products; remote US.</t>
-        </is>
-      </c>
-      <c r="H252" t="inlineStr">
-        <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="I252" t="inlineStr"/>
-      <c r="J252" t="inlineStr"/>
-      <c r="K252" t="inlineStr"/>
-      <c r="L252" t="inlineStr"/>
-      <c r="M252" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N252" t="inlineStr"/>
-      <c r="O252" t="inlineStr">
+      <c r="N252" s="4" t="inlineStr"/>
+      <c r="O252" s="4" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>

--- a/tracker.xlsx
+++ b/tracker.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Tracker" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tracker" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Tracker'!$A$1:$O$234</definedName>
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:O252"/>
+  <dimension ref="A1:O262"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.453125" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="22" customWidth="1" style="4" min="1" max="1"/>
@@ -13765,6 +13765,552 @@
         </is>
       </c>
     </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>Beazley Security</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Senior Data &amp; AI Platform Engineer</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>United States (Remote)</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4474621181/</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr"/>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>Senior SWE-friendly data+AI platform; Snowflake/relational DBs, pipelines, LLM stack (retrieval, embeddings, agents)</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr"/>
+      <c r="J253" t="inlineStr"/>
+      <c r="K253" t="inlineStr"/>
+      <c r="L253" t="inlineStr"/>
+      <c r="M253" t="inlineStr"/>
+      <c r="N253" t="inlineStr"/>
+      <c r="O253" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>Tria Federal</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Technical Lead ML Engineer</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>United States (Remote)</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4475862081/</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr"/>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>AI/ML technical leadership incl. MLOps, cloud-native architectures, data platforms</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr"/>
+      <c r="J254" t="inlineStr"/>
+      <c r="K254" t="inlineStr"/>
+      <c r="L254" t="inlineStr">
+        <is>
+          <t>Federal consultancy; federal/IC experience preferred, active clearance nice-to-have (not required)</t>
+        </is>
+      </c>
+      <c r="M254" t="inlineStr"/>
+      <c r="N254" t="inlineStr"/>
+      <c r="O254" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>Ladders</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Senior Data and Platform Engineer</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>United States (Remote)</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4473639118/</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>$140K-$270.2K/yr</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>5+ yrs backend systems; distributed workloads, data platform foundations; Spark/Kafka only desired, not core</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr"/>
+      <c r="J255" t="inlineStr"/>
+      <c r="K255" t="inlineStr"/>
+      <c r="L255" t="inlineStr">
+        <is>
+          <t>Client name not disclosed (via Ladders recruiting)</t>
+        </is>
+      </c>
+      <c r="M255" t="inlineStr"/>
+      <c r="N255" t="inlineStr"/>
+      <c r="O255" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>Tessera Labs</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Senior Data Platform Engineer</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>United States (Remote)</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4465169593/</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>$200K-$300K</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>AI enterprise (a16z/NEA-backed); data access services, query execution, connector frameworks, orchestration for AI agents</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr"/>
+      <c r="J256" t="inlineStr"/>
+      <c r="K256" t="inlineStr"/>
+      <c r="L256" t="inlineStr">
+        <is>
+          <t>Listing open to remote but notes Bay Area preference — confirm before applying</t>
+        </is>
+      </c>
+      <c r="M256" t="inlineStr"/>
+      <c r="N256" t="inlineStr"/>
+      <c r="O256" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Lead Cloud &amp; Data Platform Engineer</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Louisville, KY (Remote)</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4463962029/</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>$129.3K-$177.8K/yr</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>Listing confirms remote; cloud data platform (Azure/Snowflake), Terraform, data governance at scale</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr"/>
+      <c r="J257" t="inlineStr"/>
+      <c r="K257" t="inlineStr"/>
+      <c r="L257" t="inlineStr"/>
+      <c r="M257" t="inlineStr"/>
+      <c r="N257" t="inlineStr"/>
+      <c r="O257" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>SentiLink</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Senior Data Platform Engineer</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>Austin, TX (Remote)</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4446361743/</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>$170K-$230K + equity</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>Listing states remote US-based; fraud-prevention fintech; Python/Golang, PostgreSQL, OpenSearch, Redshift/EMR; 5+ yrs</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr"/>
+      <c r="J258" t="inlineStr"/>
+      <c r="K258" t="inlineStr"/>
+      <c r="L258" t="inlineStr"/>
+      <c r="M258" t="inlineStr"/>
+      <c r="N258" t="inlineStr"/>
+      <c r="O258" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>Ladders</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Data and Platform Engineer</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>United States (Remote)</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4473633403/</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>$200K-$322K/yr</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>Data &amp; platform engineering with senior-level comp band (title lacks senior prefix)</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr"/>
+      <c r="J259" t="inlineStr"/>
+      <c r="K259" t="inlineStr"/>
+      <c r="L259" t="inlineStr">
+        <is>
+          <t>Client name not disclosed (via Ladders recruiting)</t>
+        </is>
+      </c>
+      <c r="M259" t="inlineStr"/>
+      <c r="N259" t="inlineStr"/>
+      <c r="O259" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>Robert Half</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Senior MLOps Engineer</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>United States (Remote)</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4472304425/</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>$75-$82/hr</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>Centralized Data &amp; Analytics CoE; ML production deployment, monitoring, CI/CD, Kubernetes</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="I260" t="inlineStr"/>
+      <c r="J260" t="inlineStr"/>
+      <c r="K260" t="inlineStr"/>
+      <c r="L260" t="inlineStr">
+        <is>
+          <t>CONTRACT via staffing firm (Robert Half) — flag before applying</t>
+        </is>
+      </c>
+      <c r="M260" t="inlineStr"/>
+      <c r="N260" t="inlineStr"/>
+      <c r="O260" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>vCluster</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>AI Infrastructure Engineer</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>United States (Remote)</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4417255087/</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>$140K-$165K</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>K8s/GPU/CUDA AI infrastructure; customer-facing (deploying GPU infra for neocloud/AI-factory customers)</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="I261" t="inlineStr"/>
+      <c r="J261" t="inlineStr"/>
+      <c r="K261" t="inlineStr"/>
+      <c r="L261" t="inlineStr"/>
+      <c r="M261" t="inlineStr"/>
+      <c r="N261" t="inlineStr"/>
+      <c r="O261" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>Lyra Health</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>Senior AI/ML Platform Engineer</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>United States (Remote)</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4473077871/</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>$143K-$197K</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>Building ML + generative AI platforms; Python/FastAPI, Kubernetes, vector DBs, RAG/LLM orchestration; 6+ yrs</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr"/>
+      <c r="J262" t="inlineStr"/>
+      <c r="K262" t="inlineStr"/>
+      <c r="L262" t="inlineStr">
+        <is>
+          <t>High applicant volume noted</t>
+        </is>
+      </c>
+      <c r="M262" t="inlineStr"/>
+      <c r="N262" t="inlineStr"/>
+      <c r="O262" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:O234"/>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>

--- a/tracker.xlsx
+++ b/tracker.xlsx
@@ -13689,7 +13689,7 @@
       <c r="K251" s="4" t="inlineStr"/>
       <c r="L251" s="4" t="inlineStr">
         <is>
-          <t>Stretch: wants Redshift/Glue/EventBridge, CDC/streaming. Real posting is on Ashby: https://jobs.ashbyhq.com/foley/d292fa96-260a-4e03-9e39-853d085ff134 (remote US, EST hours, $140-180K)</t>
+          <t>Stretch: wants Redshift/Glue/EventBridge, CDC/streaming. Real posting is on Ashby: https://jobs.ashbyhq.com/foley/d292fa96-260a-4e03-9e39-853d085ff134 (remote US, EST hours, $140-180K) BLOCKED 2026-10-05: form filled but NOT submitted — Ashby asks to confirm residence in one of 25 listed states (AZ CA CO CT FL GA IL IN KS MA MD MI MO NE NH NJ NY NC PA RI SC TN TX VA WI); UT not eligible, truthful answer is No. Awaiting Jack's call.</t>
         </is>
       </c>
       <c r="M251" s="4" t="inlineStr">
@@ -13766,546 +13766,546 @@
       </c>
     </row>
     <row r="253">
-      <c r="A253" t="inlineStr">
+      <c r="A253" s="4" t="inlineStr">
         <is>
           <t>Beazley Security</t>
         </is>
       </c>
-      <c r="B253" t="inlineStr">
+      <c r="B253" s="4" t="inlineStr">
         <is>
           <t>Senior Data &amp; AI Platform Engineer</t>
         </is>
       </c>
-      <c r="C253" t="inlineStr">
+      <c r="C253" s="4" t="inlineStr">
         <is>
           <t>United States (Remote)</t>
         </is>
       </c>
-      <c r="D253" t="inlineStr">
+      <c r="D253" s="4" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4474621181/</t>
         </is>
       </c>
-      <c r="E253" t="inlineStr">
+      <c r="E253" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="F253" t="inlineStr"/>
-      <c r="G253" t="inlineStr">
+      <c r="F253" s="4" t="inlineStr"/>
+      <c r="G253" s="4" t="inlineStr">
         <is>
           <t>Senior SWE-friendly data+AI platform; Snowflake/relational DBs, pipelines, LLM stack (retrieval, embeddings, agents)</t>
         </is>
       </c>
-      <c r="H253" t="inlineStr">
+      <c r="H253" s="4" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="I253" t="inlineStr"/>
-      <c r="J253" t="inlineStr"/>
-      <c r="K253" t="inlineStr"/>
-      <c r="L253" t="inlineStr"/>
-      <c r="M253" t="inlineStr"/>
-      <c r="N253" t="inlineStr"/>
-      <c r="O253" t="inlineStr">
+      <c r="I253" s="4" t="inlineStr"/>
+      <c r="J253" s="4" t="inlineStr"/>
+      <c r="K253" s="4" t="inlineStr"/>
+      <c r="L253" s="4" t="inlineStr"/>
+      <c r="M253" s="4" t="inlineStr"/>
+      <c r="N253" s="4" t="inlineStr"/>
+      <c r="O253" s="4" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
     <row r="254">
-      <c r="A254" t="inlineStr">
+      <c r="A254" s="4" t="inlineStr">
         <is>
           <t>Tria Federal</t>
         </is>
       </c>
-      <c r="B254" t="inlineStr">
+      <c r="B254" s="4" t="inlineStr">
         <is>
           <t>Technical Lead ML Engineer</t>
         </is>
       </c>
-      <c r="C254" t="inlineStr">
+      <c r="C254" s="4" t="inlineStr">
         <is>
           <t>United States (Remote)</t>
         </is>
       </c>
-      <c r="D254" t="inlineStr">
+      <c r="D254" s="4" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4475862081/</t>
         </is>
       </c>
-      <c r="E254" t="inlineStr">
+      <c r="E254" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="F254" t="inlineStr"/>
-      <c r="G254" t="inlineStr">
+      <c r="F254" s="4" t="inlineStr"/>
+      <c r="G254" s="4" t="inlineStr">
         <is>
           <t>AI/ML technical leadership incl. MLOps, cloud-native architectures, data platforms</t>
         </is>
       </c>
-      <c r="H254" t="inlineStr">
+      <c r="H254" s="4" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="I254" t="inlineStr"/>
-      <c r="J254" t="inlineStr"/>
-      <c r="K254" t="inlineStr"/>
-      <c r="L254" t="inlineStr">
+      <c r="I254" s="4" t="inlineStr"/>
+      <c r="J254" s="4" t="inlineStr"/>
+      <c r="K254" s="4" t="inlineStr"/>
+      <c r="L254" s="4" t="inlineStr">
         <is>
           <t>Federal consultancy; federal/IC experience preferred, active clearance nice-to-have (not required)</t>
         </is>
       </c>
-      <c r="M254" t="inlineStr"/>
-      <c r="N254" t="inlineStr"/>
-      <c r="O254" t="inlineStr">
+      <c r="M254" s="4" t="inlineStr"/>
+      <c r="N254" s="4" t="inlineStr"/>
+      <c r="O254" s="4" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
     <row r="255">
-      <c r="A255" t="inlineStr">
+      <c r="A255" s="4" t="inlineStr">
         <is>
           <t>Ladders</t>
         </is>
       </c>
-      <c r="B255" t="inlineStr">
+      <c r="B255" s="4" t="inlineStr">
         <is>
           <t>Senior Data and Platform Engineer</t>
         </is>
       </c>
-      <c r="C255" t="inlineStr">
+      <c r="C255" s="4" t="inlineStr">
         <is>
           <t>United States (Remote)</t>
         </is>
       </c>
-      <c r="D255" t="inlineStr">
+      <c r="D255" s="4" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4473639118/</t>
         </is>
       </c>
-      <c r="E255" t="inlineStr">
+      <c r="E255" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="F255" t="inlineStr">
+      <c r="F255" s="4" t="inlineStr">
         <is>
           <t>$140K-$270.2K/yr</t>
         </is>
       </c>
-      <c r="G255" t="inlineStr">
+      <c r="G255" s="4" t="inlineStr">
         <is>
           <t>5+ yrs backend systems; distributed workloads, data platform foundations; Spark/Kafka only desired, not core</t>
         </is>
       </c>
-      <c r="H255" t="inlineStr">
+      <c r="H255" s="4" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="I255" t="inlineStr"/>
-      <c r="J255" t="inlineStr"/>
-      <c r="K255" t="inlineStr"/>
-      <c r="L255" t="inlineStr">
+      <c r="I255" s="4" t="inlineStr"/>
+      <c r="J255" s="4" t="inlineStr"/>
+      <c r="K255" s="4" t="inlineStr"/>
+      <c r="L255" s="4" t="inlineStr">
         <is>
           <t>Client name not disclosed (via Ladders recruiting)</t>
         </is>
       </c>
-      <c r="M255" t="inlineStr"/>
-      <c r="N255" t="inlineStr"/>
-      <c r="O255" t="inlineStr">
+      <c r="M255" s="4" t="inlineStr"/>
+      <c r="N255" s="4" t="inlineStr"/>
+      <c r="O255" s="4" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
     <row r="256">
-      <c r="A256" t="inlineStr">
+      <c r="A256" s="4" t="inlineStr">
         <is>
           <t>Tessera Labs</t>
         </is>
       </c>
-      <c r="B256" t="inlineStr">
+      <c r="B256" s="4" t="inlineStr">
         <is>
           <t>Senior Data Platform Engineer</t>
         </is>
       </c>
-      <c r="C256" t="inlineStr">
+      <c r="C256" s="4" t="inlineStr">
         <is>
           <t>United States (Remote)</t>
         </is>
       </c>
-      <c r="D256" t="inlineStr">
+      <c r="D256" s="4" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4465169593/</t>
         </is>
       </c>
-      <c r="E256" t="inlineStr">
+      <c r="E256" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="F256" t="inlineStr">
+      <c r="F256" s="4" t="inlineStr">
         <is>
           <t>$200K-$300K</t>
         </is>
       </c>
-      <c r="G256" t="inlineStr">
+      <c r="G256" s="4" t="inlineStr">
         <is>
           <t>AI enterprise (a16z/NEA-backed); data access services, query execution, connector frameworks, orchestration for AI agents</t>
         </is>
       </c>
-      <c r="H256" t="inlineStr">
+      <c r="H256" s="4" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="I256" t="inlineStr"/>
-      <c r="J256" t="inlineStr"/>
-      <c r="K256" t="inlineStr"/>
-      <c r="L256" t="inlineStr">
+      <c r="I256" s="4" t="inlineStr"/>
+      <c r="J256" s="4" t="inlineStr"/>
+      <c r="K256" s="4" t="inlineStr"/>
+      <c r="L256" s="4" t="inlineStr">
         <is>
           <t>Listing open to remote but notes Bay Area preference — confirm before applying</t>
         </is>
       </c>
-      <c r="M256" t="inlineStr"/>
-      <c r="N256" t="inlineStr"/>
-      <c r="O256" t="inlineStr">
+      <c r="M256" s="4" t="inlineStr"/>
+      <c r="N256" s="4" t="inlineStr"/>
+      <c r="O256" s="4" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
     <row r="257">
-      <c r="A257" t="inlineStr">
+      <c r="A257" s="4" t="inlineStr">
         <is>
           <t>Humana</t>
         </is>
       </c>
-      <c r="B257" t="inlineStr">
+      <c r="B257" s="4" t="inlineStr">
         <is>
           <t>Lead Cloud &amp; Data Platform Engineer</t>
         </is>
       </c>
-      <c r="C257" t="inlineStr">
+      <c r="C257" s="4" t="inlineStr">
         <is>
           <t>Louisville, KY (Remote)</t>
         </is>
       </c>
-      <c r="D257" t="inlineStr">
+      <c r="D257" s="4" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463962029/</t>
         </is>
       </c>
-      <c r="E257" t="inlineStr">
+      <c r="E257" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="F257" t="inlineStr">
+      <c r="F257" s="4" t="inlineStr">
         <is>
           <t>$129.3K-$177.8K/yr</t>
         </is>
       </c>
-      <c r="G257" t="inlineStr">
+      <c r="G257" s="4" t="inlineStr">
         <is>
           <t>Listing confirms remote; cloud data platform (Azure/Snowflake), Terraform, data governance at scale</t>
         </is>
       </c>
-      <c r="H257" t="inlineStr">
+      <c r="H257" s="4" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="I257" t="inlineStr"/>
-      <c r="J257" t="inlineStr"/>
-      <c r="K257" t="inlineStr"/>
-      <c r="L257" t="inlineStr"/>
-      <c r="M257" t="inlineStr"/>
-      <c r="N257" t="inlineStr"/>
-      <c r="O257" t="inlineStr">
+      <c r="I257" s="4" t="inlineStr"/>
+      <c r="J257" s="4" t="inlineStr"/>
+      <c r="K257" s="4" t="inlineStr"/>
+      <c r="L257" s="4" t="inlineStr"/>
+      <c r="M257" s="4" t="inlineStr"/>
+      <c r="N257" s="4" t="inlineStr"/>
+      <c r="O257" s="4" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
     <row r="258">
-      <c r="A258" t="inlineStr">
+      <c r="A258" s="4" t="inlineStr">
         <is>
           <t>SentiLink</t>
         </is>
       </c>
-      <c r="B258" t="inlineStr">
+      <c r="B258" s="4" t="inlineStr">
         <is>
           <t>Senior Data Platform Engineer</t>
         </is>
       </c>
-      <c r="C258" t="inlineStr">
+      <c r="C258" s="4" t="inlineStr">
         <is>
           <t>Austin, TX (Remote)</t>
         </is>
       </c>
-      <c r="D258" t="inlineStr">
+      <c r="D258" s="4" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4446361743/</t>
         </is>
       </c>
-      <c r="E258" t="inlineStr">
+      <c r="E258" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="F258" t="inlineStr">
+      <c r="F258" s="4" t="inlineStr">
         <is>
           <t>$170K-$230K + equity</t>
         </is>
       </c>
-      <c r="G258" t="inlineStr">
+      <c r="G258" s="4" t="inlineStr">
         <is>
           <t>Listing states remote US-based; fraud-prevention fintech; Python/Golang, PostgreSQL, OpenSearch, Redshift/EMR; 5+ yrs</t>
         </is>
       </c>
-      <c r="H258" t="inlineStr">
+      <c r="H258" s="4" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="I258" t="inlineStr"/>
-      <c r="J258" t="inlineStr"/>
-      <c r="K258" t="inlineStr"/>
-      <c r="L258" t="inlineStr"/>
-      <c r="M258" t="inlineStr"/>
-      <c r="N258" t="inlineStr"/>
-      <c r="O258" t="inlineStr">
+      <c r="I258" s="4" t="inlineStr"/>
+      <c r="J258" s="4" t="inlineStr"/>
+      <c r="K258" s="4" t="inlineStr"/>
+      <c r="L258" s="4" t="inlineStr"/>
+      <c r="M258" s="4" t="inlineStr"/>
+      <c r="N258" s="4" t="inlineStr"/>
+      <c r="O258" s="4" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
     <row r="259">
-      <c r="A259" t="inlineStr">
+      <c r="A259" s="4" t="inlineStr">
         <is>
           <t>Ladders</t>
         </is>
       </c>
-      <c r="B259" t="inlineStr">
+      <c r="B259" s="4" t="inlineStr">
         <is>
           <t>Data and Platform Engineer</t>
         </is>
       </c>
-      <c r="C259" t="inlineStr">
+      <c r="C259" s="4" t="inlineStr">
         <is>
           <t>United States (Remote)</t>
         </is>
       </c>
-      <c r="D259" t="inlineStr">
+      <c r="D259" s="4" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4473633403/</t>
         </is>
       </c>
-      <c r="E259" t="inlineStr">
+      <c r="E259" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="F259" t="inlineStr">
+      <c r="F259" s="4" t="inlineStr">
         <is>
           <t>$200K-$322K/yr</t>
         </is>
       </c>
-      <c r="G259" t="inlineStr">
+      <c r="G259" s="4" t="inlineStr">
         <is>
           <t>Data &amp; platform engineering with senior-level comp band (title lacks senior prefix)</t>
         </is>
       </c>
-      <c r="H259" t="inlineStr">
+      <c r="H259" s="4" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="I259" t="inlineStr"/>
-      <c r="J259" t="inlineStr"/>
-      <c r="K259" t="inlineStr"/>
-      <c r="L259" t="inlineStr">
+      <c r="I259" s="4" t="inlineStr"/>
+      <c r="J259" s="4" t="inlineStr"/>
+      <c r="K259" s="4" t="inlineStr"/>
+      <c r="L259" s="4" t="inlineStr">
         <is>
           <t>Client name not disclosed (via Ladders recruiting)</t>
         </is>
       </c>
-      <c r="M259" t="inlineStr"/>
-      <c r="N259" t="inlineStr"/>
-      <c r="O259" t="inlineStr">
+      <c r="M259" s="4" t="inlineStr"/>
+      <c r="N259" s="4" t="inlineStr"/>
+      <c r="O259" s="4" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
     <row r="260">
-      <c r="A260" t="inlineStr">
+      <c r="A260" s="4" t="inlineStr">
         <is>
           <t>Robert Half</t>
         </is>
       </c>
-      <c r="B260" t="inlineStr">
+      <c r="B260" s="4" t="inlineStr">
         <is>
           <t>Senior MLOps Engineer</t>
         </is>
       </c>
-      <c r="C260" t="inlineStr">
+      <c r="C260" s="4" t="inlineStr">
         <is>
           <t>United States (Remote)</t>
         </is>
       </c>
-      <c r="D260" t="inlineStr">
+      <c r="D260" s="4" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4472304425/</t>
         </is>
       </c>
-      <c r="E260" t="inlineStr">
+      <c r="E260" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="F260" t="inlineStr">
+      <c r="F260" s="4" t="inlineStr">
         <is>
           <t>$75-$82/hr</t>
         </is>
       </c>
-      <c r="G260" t="inlineStr">
+      <c r="G260" s="4" t="inlineStr">
         <is>
           <t>Centralized Data &amp; Analytics CoE; ML production deployment, monitoring, CI/CD, Kubernetes</t>
         </is>
       </c>
-      <c r="H260" t="inlineStr">
+      <c r="H260" s="4" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="I260" t="inlineStr"/>
-      <c r="J260" t="inlineStr"/>
-      <c r="K260" t="inlineStr"/>
-      <c r="L260" t="inlineStr">
+      <c r="I260" s="4" t="inlineStr"/>
+      <c r="J260" s="4" t="inlineStr"/>
+      <c r="K260" s="4" t="inlineStr"/>
+      <c r="L260" s="4" t="inlineStr">
         <is>
           <t>CONTRACT via staffing firm (Robert Half) — flag before applying</t>
         </is>
       </c>
-      <c r="M260" t="inlineStr"/>
-      <c r="N260" t="inlineStr"/>
-      <c r="O260" t="inlineStr">
+      <c r="M260" s="4" t="inlineStr"/>
+      <c r="N260" s="4" t="inlineStr"/>
+      <c r="O260" s="4" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
     <row r="261">
-      <c r="A261" t="inlineStr">
+      <c r="A261" s="4" t="inlineStr">
         <is>
           <t>vCluster</t>
         </is>
       </c>
-      <c r="B261" t="inlineStr">
+      <c r="B261" s="4" t="inlineStr">
         <is>
           <t>AI Infrastructure Engineer</t>
         </is>
       </c>
-      <c r="C261" t="inlineStr">
+      <c r="C261" s="4" t="inlineStr">
         <is>
           <t>United States (Remote)</t>
         </is>
       </c>
-      <c r="D261" t="inlineStr">
+      <c r="D261" s="4" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4417255087/</t>
         </is>
       </c>
-      <c r="E261" t="inlineStr">
+      <c r="E261" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="F261" t="inlineStr">
+      <c r="F261" s="4" t="inlineStr">
         <is>
           <t>$140K-$165K</t>
         </is>
       </c>
-      <c r="G261" t="inlineStr">
+      <c r="G261" s="4" t="inlineStr">
         <is>
           <t>K8s/GPU/CUDA AI infrastructure; customer-facing (deploying GPU infra for neocloud/AI-factory customers)</t>
         </is>
       </c>
-      <c r="H261" t="inlineStr">
+      <c r="H261" s="4" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="I261" t="inlineStr"/>
-      <c r="J261" t="inlineStr"/>
-      <c r="K261" t="inlineStr"/>
-      <c r="L261" t="inlineStr"/>
-      <c r="M261" t="inlineStr"/>
-      <c r="N261" t="inlineStr"/>
-      <c r="O261" t="inlineStr">
+      <c r="I261" s="4" t="inlineStr"/>
+      <c r="J261" s="4" t="inlineStr"/>
+      <c r="K261" s="4" t="inlineStr"/>
+      <c r="L261" s="4" t="inlineStr"/>
+      <c r="M261" s="4" t="inlineStr"/>
+      <c r="N261" s="4" t="inlineStr"/>
+      <c r="O261" s="4" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
     <row r="262">
-      <c r="A262" t="inlineStr">
+      <c r="A262" s="4" t="inlineStr">
         <is>
           <t>Lyra Health</t>
         </is>
       </c>
-      <c r="B262" t="inlineStr">
+      <c r="B262" s="4" t="inlineStr">
         <is>
           <t>Senior AI/ML Platform Engineer</t>
         </is>
       </c>
-      <c r="C262" t="inlineStr">
+      <c r="C262" s="4" t="inlineStr">
         <is>
           <t>United States (Remote)</t>
         </is>
       </c>
-      <c r="D262" t="inlineStr">
+      <c r="D262" s="4" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4473077871/</t>
         </is>
       </c>
-      <c r="E262" t="inlineStr">
+      <c r="E262" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="F262" t="inlineStr">
+      <c r="F262" s="4" t="inlineStr">
         <is>
           <t>$143K-$197K</t>
         </is>
       </c>
-      <c r="G262" t="inlineStr">
+      <c r="G262" s="4" t="inlineStr">
         <is>
           <t>Building ML + generative AI platforms; Python/FastAPI, Kubernetes, vector DBs, RAG/LLM orchestration; 6+ yrs</t>
         </is>
       </c>
-      <c r="H262" t="inlineStr">
+      <c r="H262" s="4" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="I262" t="inlineStr"/>
-      <c r="J262" t="inlineStr"/>
-      <c r="K262" t="inlineStr"/>
-      <c r="L262" t="inlineStr">
+      <c r="I262" s="4" t="inlineStr"/>
+      <c r="J262" s="4" t="inlineStr"/>
+      <c r="K262" s="4" t="inlineStr"/>
+      <c r="L262" s="4" t="inlineStr">
         <is>
           <t>High applicant volume noted</t>
         </is>
       </c>
-      <c r="M262" t="inlineStr"/>
-      <c r="N262" t="inlineStr"/>
-      <c r="O262" t="inlineStr">
+      <c r="M262" s="4" t="inlineStr"/>
+      <c r="N262" s="4" t="inlineStr"/>
+      <c r="O262" s="4" t="inlineStr">
         <is>
           <t>Low</t>
         </is>

--- a/tracker.xlsx
+++ b/tracker.xlsx
@@ -13689,7 +13689,7 @@
       <c r="K251" s="4" t="inlineStr"/>
       <c r="L251" s="4" t="inlineStr">
         <is>
-          <t>Stretch: wants Redshift/Glue/EventBridge, CDC/streaming. Real posting is on Ashby: https://jobs.ashbyhq.com/foley/d292fa96-260a-4e03-9e39-853d085ff134 (remote US, EST hours, $140-180K) BLOCKED 2026-10-05: form filled but NOT submitted — Ashby asks to confirm residence in one of 25 listed states (AZ CA CO CT FL GA IL IN KS MA MD MI MO NE NH NJ NY NC PA RI SC TN TX VA WI); UT not eligible, truthful answer is No. Awaiting Jack's call.</t>
+          <t>Stretch: wants Redshift/Glue/EventBridge, CDC/streaming. Real posting is on Ashby: https://jobs.ashbyhq.com/foley/d292fa96-260a-4e03-9e39-853d085ff134 (remote US, EST hours, $140-180K) BLOCKED 2026-10-05: form filled but NOT submitted — Ashby asks to confirm residence in one of 25 listed states (AZ CA CO CT FL GA IL IN KS MA MD MI MO NE NH NJ NY NC PA RI SC TN TX VA WI); UT not eligible, truthful answer is No. Awaiting Jack's call. Jack's call 2026-10-05: leave UNsubmitted (UT not an eligible state; truthful 'No' would be screened out).</t>
         </is>
       </c>
       <c r="M251" s="4" t="inlineStr">

--- a/tracker.xlsx
+++ b/tracker.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:O262"/>
+  <dimension ref="A1:O263"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.453125" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="22" customWidth="1" style="4" min="1" max="1"/>
@@ -14311,6 +14311,63 @@
         </is>
       </c>
     </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>Recharge</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>Remote (US)</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/recharge/7c37161f-593d-47a5-a0e3-99a2eed8ae7a</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr"/>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>$148,000–$185,000 USD</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>Remote; AI/LLM data work incl. Claude + MCP interfaces; stack: Snowflake/BigQuery/dbt/Airflow/FiveTran/Python/Postgres/AWS/GCP - partial match, no Spark/Kafka mentioned; no travel listed</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr"/>
+      <c r="J263" t="inlineStr"/>
+      <c r="K263" t="inlineStr"/>
+      <c r="L263" t="inlineStr">
+        <is>
+          <t>Verified live 2026-10-06 via Ashby (official board, linked from getrecharge.com/careers). Real URL for the role whose 2026-10-05 LinkedIn link was bad (row 252).</t>
+        </is>
+      </c>
+      <c r="M263" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N263" t="inlineStr"/>
+      <c r="O263" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:O234"/>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>

--- a/tracker.xlsx
+++ b/tracker.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:O263"/>
+  <dimension ref="A1:O275"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.453125" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="22" customWidth="1" style="4" min="1" max="1"/>
@@ -14312,57 +14312,713 @@
       </c>
     </row>
     <row r="263">
-      <c r="A263" t="inlineStr">
+      <c r="A263" s="4" t="inlineStr">
         <is>
           <t>Recharge</t>
         </is>
       </c>
-      <c r="B263" t="inlineStr">
+      <c r="B263" s="4" t="inlineStr">
         <is>
           <t>Senior Data Engineer</t>
         </is>
       </c>
-      <c r="C263" t="inlineStr">
+      <c r="C263" s="4" t="inlineStr">
         <is>
           <t>Remote (US)</t>
         </is>
       </c>
-      <c r="D263" t="inlineStr">
+      <c r="D263" s="4" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/recharge/7c37161f-593d-47a5-a0e3-99a2eed8ae7a</t>
         </is>
       </c>
-      <c r="E263" t="inlineStr"/>
-      <c r="F263" t="inlineStr">
+      <c r="E263" s="4" t="inlineStr"/>
+      <c r="F263" s="4" t="inlineStr">
         <is>
           <t>$148,000–$185,000 USD</t>
         </is>
       </c>
-      <c r="G263" t="inlineStr">
+      <c r="G263" s="4" t="inlineStr">
         <is>
           <t>Remote; AI/LLM data work incl. Claude + MCP interfaces; stack: Snowflake/BigQuery/dbt/Airflow/FiveTran/Python/Postgres/AWS/GCP - partial match, no Spark/Kafka mentioned; no travel listed</t>
         </is>
       </c>
-      <c r="H263" t="inlineStr">
+      <c r="H263" s="4" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="I263" t="inlineStr"/>
-      <c r="J263" t="inlineStr"/>
-      <c r="K263" t="inlineStr"/>
-      <c r="L263" t="inlineStr">
+      <c r="I263" s="4" t="inlineStr"/>
+      <c r="J263" s="4" t="inlineStr"/>
+      <c r="K263" s="4" t="inlineStr"/>
+      <c r="L263" s="4" t="inlineStr">
         <is>
           <t>Verified live 2026-10-06 via Ashby (official board, linked from getrecharge.com/careers). Real URL for the role whose 2026-10-05 LinkedIn link was bad (row 252).</t>
         </is>
       </c>
-      <c r="M263" t="inlineStr">
+      <c r="M263" s="4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="N263" t="inlineStr"/>
-      <c r="O263" t="inlineStr">
+      <c r="N263" s="4" t="inlineStr"/>
+      <c r="O263" s="4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>Atticus</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Lead Data Engineer</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA (Remote — fully remote)</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4404238044/</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>$174,000–$230,000 base</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>First in-house data engineer; BigQuery, SQL, Python/Golang 4+ yrs; data observability + ML feature pipelines bonus.</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr"/>
+      <c r="J264" t="inlineStr"/>
+      <c r="K264" t="inlineStr"/>
+      <c r="L264" t="inlineStr">
+        <is>
+          <t>LinkedIn 'Verified job' badge.</t>
+        </is>
+      </c>
+      <c r="M264" t="inlineStr"/>
+      <c r="N264" t="inlineStr"/>
+      <c r="O264" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>HavocAI</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>Data and ML Infrastructure Engineer</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>United States (Remote)</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4468269423/</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr"/>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>Near-exact match: Python/SQL, video + telemetry/sensor data, S3 data lakes, Postgres, Spark/Ray/Airflow/Dagster, MLOps, 3+ yrs.</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr"/>
+      <c r="J265" t="inlineStr"/>
+      <c r="K265" t="inlineStr"/>
+      <c r="L265" t="inlineStr">
+        <is>
+          <t>FLAG: US citizenship required + ability to obtain US Govt security clearance (defense).</t>
+        </is>
+      </c>
+      <c r="M265" t="inlineStr"/>
+      <c r="N265" t="inlineStr"/>
+      <c r="O265" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>HavocAI</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>ML Cloud Infrastructure Engineer</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>United States (Remote)</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4467244477/</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr"/>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>Python/Go/C++, K8s, AWS, IaC, multimodal telemetry/imagery/video/sensor data, MLflow/Ray/Airflow, 3+ yrs.</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr"/>
+      <c r="J266" t="inlineStr"/>
+      <c r="K266" t="inlineStr"/>
+      <c r="L266" t="inlineStr">
+        <is>
+          <t>FLAG: US citizenship required (ITAR); ~10% travel to offices/sites.</t>
+        </is>
+      </c>
+      <c r="M266" t="inlineStr"/>
+      <c r="N266" t="inlineStr"/>
+      <c r="O266" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>General Motors</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>Senior ML Infrastructure Engineer - Embodied AI</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>Washington, United States (Remote)</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4389263218/</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>$153,200–$234,100</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>Senior ML infra, large-scale distributed systems, Python/C++, Docker/K8s, model training pipelines, autonomous-driving data, 3+ yrs.</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="I267" t="inlineStr"/>
+      <c r="J267" t="inlineStr"/>
+      <c r="K267" t="inlineStr"/>
+      <c r="L267" t="inlineStr">
+        <is>
+          <t>FLAG: posting says 'fully remote or hybrid' — confirm remote arrangement.</t>
+        </is>
+      </c>
+      <c r="M267" t="inlineStr"/>
+      <c r="N267" t="inlineStr"/>
+      <c r="O267" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>Float.com</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>New York, NY (Remote)</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4477825436/</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>$174,893/yr</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>Production-grade ML-ready data pipelines for AI finance layer; dbt familiarity needed, deep expertise not required.</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="I268" t="inlineStr"/>
+      <c r="J268" t="inlineStr"/>
+      <c r="K268" t="inlineStr"/>
+      <c r="L268" t="inlineStr">
+        <is>
+          <t>Caveat: requires TypeScript/Node.js production experience (JS-heavy for DE).</t>
+        </is>
+      </c>
+      <c r="M268" t="inlineStr"/>
+      <c r="N268" t="inlineStr"/>
+      <c r="O268" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>Torc Robotics</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Software Engineer, II - Autonomy Data</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>Blacksburg, VA (Remote)</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4449330655/</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>$139,000–$166,800</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>Autonomy data pipelines: high-bandwidth sensor logs, Python/SQL, AWS (S3/Glue/Athena/Redshift), Parquet/ORC, ML training-data curation.</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="I269" t="inlineStr"/>
+      <c r="J269" t="inlineStr"/>
+      <c r="K269" t="inlineStr"/>
+      <c r="L269" t="inlineStr">
+        <is>
+          <t>FLAG: US citizenship required; salary mostly at/below target band.</t>
+        </is>
+      </c>
+      <c r="M269" t="inlineStr"/>
+      <c r="N269" t="inlineStr"/>
+      <c r="O269" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>Senior Data and Platform Engineer</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>New York, United States (Remote)</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4474653257/</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr"/>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>DGX Cloud data platform, 8+ yrs, SQL/data modeling, lakehouse architectures, streaming, cloud infra/container orchestration; equity eligible.</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="I270" t="inlineStr"/>
+      <c r="J270" t="inlineStr"/>
+      <c r="K270" t="inlineStr"/>
+      <c r="L270" t="inlineStr"/>
+      <c r="M270" t="inlineStr"/>
+      <c r="N270" t="inlineStr"/>
+      <c r="O270" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>Solace</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>United States (Remote)</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4474643656/</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr"/>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>Python/SQL, Snowflake/Postgres, dbt, Terraform, AWS/GCP, FastAPI data API, observability; US-based applicants.</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr"/>
+      <c r="J271" t="inlineStr"/>
+      <c r="K271" t="inlineStr"/>
+      <c r="L271" t="inlineStr">
+        <is>
+          <t>Note: Airflow orchestration mastery is a core requirement.</t>
+        </is>
+      </c>
+      <c r="M271" t="inlineStr"/>
+      <c r="N271" t="inlineStr"/>
+      <c r="O271" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>Nexcess</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>Lead Data Engineer</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>United States (Remote)</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4468171647/</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr"/>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>7+ yrs incl 2+ leading; SQL, Python/Java/Scala, ETL/ELT, cloud data platforms.</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="I272" t="inlineStr"/>
+      <c r="J272" t="inlineStr"/>
+      <c r="K272" t="inlineStr"/>
+      <c r="L272" t="inlineStr">
+        <is>
+          <t>Spark/Airflow/dbt/Kafka only 'preferred', not core — not a heavy-stack exclusion.</t>
+        </is>
+      </c>
+      <c r="M272" t="inlineStr"/>
+      <c r="N272" t="inlineStr"/>
+      <c r="O272" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>BRG</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>AI Lab Infrastructure Engineer</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>United States (Remote)</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4302560811/</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr"/>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>6-8 yrs, Python, IaC (CDK/Terraform), AWS, GPU infra, LLM deployment (OpenAI/Anthropic).</t>
+        </is>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="I273" t="inlineStr"/>
+      <c r="J273" t="inlineStr"/>
+      <c r="K273" t="inlineStr"/>
+      <c r="L273" t="inlineStr">
+        <is>
+          <t>BRG = Berkeley Research Group (consulting firm).</t>
+        </is>
+      </c>
+      <c r="M273" t="inlineStr"/>
+      <c r="N273" t="inlineStr"/>
+      <c r="O273" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>Modular</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>Inference Systems Engineer</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>United States (Remote)</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4476521567/</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>$148,000–$270,000 base</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>Model-serving/inference infra: vLLM/SGLang/TRT-LLM, Python/Rust/Mojo, GPU programming, 5+ yrs systems.</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="I274" t="inlineStr"/>
+      <c r="J274" t="inlineStr"/>
+      <c r="K274" t="inlineStr"/>
+      <c r="L274" t="inlineStr">
+        <is>
+          <t>Qualcomm company; salary band US-wide regardless of state.</t>
+        </is>
+      </c>
+      <c r="M274" t="inlineStr"/>
+      <c r="N274" t="inlineStr"/>
+      <c r="O274" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>Tessera Labs</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>AI Infrastructure Engineer</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>United States (Remote)</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4457737795/</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>$200,000–$250,000</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>5+ yrs cloud infra, Terraform, K8s, multi-cloud (Azure/OCI/GCP/AWS), CI/CD, GitOps.</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="I275" t="inlineStr"/>
+      <c r="J275" t="inlineStr"/>
+      <c r="K275" t="inlineStr"/>
+      <c r="L275" t="inlineStr">
+        <is>
+          <t>No Bay Area-preference caveat on this posting (unlike their Data Platform Eng posting).</t>
+        </is>
+      </c>
+      <c r="M275" t="inlineStr"/>
+      <c r="N275" t="inlineStr"/>
+      <c r="O275" t="inlineStr">
         <is>
           <t>Low</t>
         </is>

--- a/tracker.xlsx
+++ b/tracker.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tracker" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Tracker" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Tracker'!$A$1:$O$234</definedName>
@@ -15014,15 +15014,22 @@
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="I277" t="inlineStr"/>
-      <c r="J277" t="inlineStr"/>
-      <c r="K277" t="inlineStr"/>
+          <t>reviewing</t>
+        </is>
+      </c>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>resume-ey-agentic-ai-engineer-manager.pdf</t>
+        </is>
+      </c>
+      <c r="J277" t="inlineStr">
+        <is>
+          <t>cover-letter-ey-agentic-ai-engineer-manager.pdf</t>
+        </is>
+      </c>
       <c r="L277" t="inlineStr">
         <is>
-          <t>FLAG: posting requires up to 50% travel + hybrid office flexibility; trip-length pattern not specified - Jack's call before applying. LinkedIn: https://www.linkedin.com/jobs/view/4479463743/ (applies via EY careers, not Easy Apply). EY accepts applications on an ongoing basis; EY asks candidates to limit to 2 applications per 6 months. Found via LinkedIn job alert 2026-10-22; EY careers page opened and verified 2026-10-22 (Job ID 1450048533).</t>
+          <t>FLAG: posting requires up to 50% travel + hybrid office flexibility; trip-length pattern not specified - Jack's call before applying. LinkedIn: https://www.linkedin.com/jobs/view/4479463743/ (applies via EY careers, not Easy Apply). EY accepts applications on an ongoing basis; EY asks candidates to limit to 2 applications per 6 months. Found via LinkedIn job alert 2026-10-22; EY careers page opened and verified 2026-10-22 (Job ID 1450048533). | 2026-10-23: resume + cover letter ready in applications/ey-agentic-ai-engineer-manager. Left at reviewing (not tailoring) so it is not auto-submitted before Jack decides on the 50% travel.</t>
         </is>
       </c>
       <c r="M277" t="inlineStr">

--- a/tracker.xlsx
+++ b/tracker.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Tracker" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tracker" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Tracker'!$A$1:$O$234</definedName>
@@ -409,7 +409,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O277"/>
+  <dimension ref="A1:O288"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.453125" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
     <col width="22" customWidth="1" style="1" min="1" max="1"/>
@@ -15048,6 +15048,721 @@
         </is>
       </c>
     </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>Hudl</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>Remote (UT eligible)</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/hudl/jobs/8162463</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>$112,000-$187,000</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>Sports video + sensor data + agentic AI — closest thematic fit in sweep; TS/React/AWS; 7+ yrs</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="I278" t="inlineStr"/>
+      <c r="J278" t="inlineStr"/>
+      <c r="K278" t="inlineStr"/>
+      <c r="L278" t="inlineStr">
+        <is>
+          <t>Expanded lane: Backend/Full-stack. Remote, UT explicitly eligible.</t>
+        </is>
+      </c>
+      <c r="M278" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="N278" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="O278" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>ParetoHealth</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/paretocaptiveservicesllc/jobs/4705486006</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>Not listed</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>Full-stack TS; AWS S3/Lambda/RDS/Dynamo/AppSync; Angular gap (Jack is React)</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="I279" t="inlineStr"/>
+      <c r="J279" t="inlineStr"/>
+      <c r="K279" t="inlineStr"/>
+      <c r="L279" t="inlineStr">
+        <is>
+          <t>Expanded lane: Backend/Full-stack. Posted date not shown on Greenhouse page; verified live 2026-10-26. Salary not listed.</t>
+        </is>
+      </c>
+      <c r="M279" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="N279" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="O279" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>Manifest</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>Senior Backend Application Engineer</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>Remote - US</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/manifest/jobs/4398657009</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>$150,000-$210,000</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>8+ yrs asked vs Jack's 7 yrs FT; web services + ETL at high throughput; TS/Mongo/Go/Python</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr"/>
+      <c r="J280" t="inlineStr"/>
+      <c r="K280" t="inlineStr"/>
+      <c r="L280" t="inlineStr">
+        <is>
+          <t>Expanded lane: Backend/Full-stack. Still live on Greenhouse board 2026-10-26; BuiltIn listed 2026-05-11.</t>
+        </is>
+      </c>
+      <c r="M280" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="N280" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="O280" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>Coder</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer (Multiple Teams, North America)</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>Remote - US/Canada</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/Coder/cd346ef3-24dd-4e1f-b863-4af569def480</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>$128,000-$247,000</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>Agent harness + MCP (Model Context Protocol) tooling, Go + React/TS, Postgres, AWS — near-perfect fit</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="I281" t="inlineStr"/>
+      <c r="J281" t="inlineStr"/>
+      <c r="K281" t="inlineStr"/>
+      <c r="L281" t="inlineStr">
+        <is>
+          <t>Expanded lane: Backend/Full-stack. Published 2026-09-09 per Ashby.</t>
+        </is>
+      </c>
+      <c r="M281" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="N281" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="O281" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>Healthie</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/healthie/jobs/4412029009?gh_src=c88eeab75us</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>$185,000-$215,000</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>6+ yrs, SQL/Postgres/Snowflake, Terraform, warehouse isolation/RBAC; HIPAA preferred (gap — Jack lacks healthcare)</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="I282" t="inlineStr"/>
+      <c r="J282" t="inlineStr"/>
+      <c r="K282" t="inlineStr"/>
+      <c r="L282" t="inlineStr">
+        <is>
+          <t>Expanded lane: Data. Posted date not shown on Greenhouse page; verified live 2026-10-26. dbt/Kafka only 'plus' skills, not core.</t>
+        </is>
+      </c>
+      <c r="M282" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="N282" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="O282" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>Censys</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>Remote - US</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/censys/jobs/8731027002</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>$151,000-$191,000 (non-HCOL; $174,000-$206,000 HCOL)</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>5+ yrs applied ML, Go/Python, feature pipelines, model evaluation, MLOps familiarity</t>
+        </is>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="I283" t="inlineStr"/>
+      <c r="J283" t="inlineStr"/>
+      <c r="K283" t="inlineStr"/>
+      <c r="L283" t="inlineStr">
+        <is>
+          <t>Expanded lane: ML. Posted date not shown on Greenhouse page; verified live 2026-10-26. In-person onboarding in Ann Arbor (one trip).</t>
+        </is>
+      </c>
+      <c r="M283" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="N283" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="O283" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>Cresta</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>Remote - US/Canada</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/cresta/jobs/4249943008</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>Not listed (base + equity)</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>5-8+ yrs, LLM/RAG/agentic workflows, evaluation frameworks, PyTorch; newly-created role</t>
+        </is>
+      </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="I284" t="inlineStr"/>
+      <c r="J284" t="inlineStr"/>
+      <c r="K284" t="inlineStr"/>
+      <c r="L284" t="inlineStr">
+        <is>
+          <t>Expanded lane: ML. Posted date not shown on Greenhouse page; verified live 2026-10-26. Salary not listed. WFH stipend listed.</t>
+        </is>
+      </c>
+      <c r="M284" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="N284" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="O284" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>Reddit</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>Remote - US</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7131932</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>$185,800-$260,100</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>3-5+ yrs, Python/Go, PyTorch, ML pipelines + model serving, LLM/RAG/agentic preferred</t>
+        </is>
+      </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="I285" t="inlineStr"/>
+      <c r="J285" t="inlineStr"/>
+      <c r="K285" t="inlineStr"/>
+      <c r="L285" t="inlineStr">
+        <is>
+          <t>Expanded lane: ML. Posted date not shown on Greenhouse page; verified live 2026-10-26. Spark/Kafka/Airflow only listed as preferred familiarity, not core.</t>
+        </is>
+      </c>
+      <c r="M285" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="N285" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="O285" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>Manifest</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>Senior Infrastructure Engineer</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/manifest/jobs/4399435009</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>$150,000-$210,000</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>IaC (Terraform/Ansible/Helm/Go), CI/CD; K8s (Kubernetes) depth required — gap for Jack (light K8s, be honest)</t>
+        </is>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="I286" t="inlineStr"/>
+      <c r="J286" t="inlineStr"/>
+      <c r="K286" t="inlineStr"/>
+      <c r="L286" t="inlineStr">
+        <is>
+          <t>Expanded lane: Platform/Infra. Posted date not shown on Greenhouse page; verified live 2026-10-26. FLAG: role requires deploying/operating/troubleshooting K8s in cloud.</t>
+        </is>
+      </c>
+      <c r="M286" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="N286" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="O286" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>Healthie</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>Senior Solutions Engineer</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>Remote - US</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/healthie/jobs/4418836009?gh_src=c88eeab75us</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>$160,000-$190,000</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>4+ yrs full-stack, TS/Postgres; customer-facing technical role</t>
+        </is>
+      </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="I287" t="inlineStr"/>
+      <c r="J287" t="inlineStr"/>
+      <c r="K287" t="inlineStr"/>
+      <c r="L287" t="inlineStr">
+        <is>
+          <t>Expanded lane: Solutions/FDE. Posted date not shown on Greenhouse page; verified live 2026-10-26.</t>
+        </is>
+      </c>
+      <c r="M287" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="N287" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="O287" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>Reddit</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>Senior Forward Deployed Engineer (AI Enablement)</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/8301784</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>$180,200-$252,300</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>5+ yrs, agent dev + MCP (Model Context Protocol) integrations, LLM retrieval, evals — near-perfect fit</t>
+        </is>
+      </c>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="I288" t="inlineStr"/>
+      <c r="J288" t="inlineStr"/>
+      <c r="K288" t="inlineStr"/>
+      <c r="L288" t="inlineStr">
+        <is>
+          <t>Expanded lane: Solutions/FDE. Posted date not shown on Greenhouse page; verified live 2026-10-26.</t>
+        </is>
+      </c>
+      <c r="M288" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="N288" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="O288" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:O234"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/tracker.xlsx
+++ b/tracker.xlsx
@@ -409,7 +409,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O288"/>
+  <dimension ref="A1:O291"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.453125" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
     <col width="22" customWidth="1" style="1" min="1" max="1"/>
@@ -15089,9 +15089,6 @@
           <t>new</t>
         </is>
       </c>
-      <c r="I278" t="inlineStr"/>
-      <c r="J278" t="inlineStr"/>
-      <c r="K278" t="inlineStr"/>
       <c r="L278" t="inlineStr">
         <is>
           <t>Expanded lane: Backend/Full-stack. Remote, UT explicitly eligible.</t>
@@ -15154,9 +15151,6 @@
           <t>new</t>
         </is>
       </c>
-      <c r="I279" t="inlineStr"/>
-      <c r="J279" t="inlineStr"/>
-      <c r="K279" t="inlineStr"/>
       <c r="L279" t="inlineStr">
         <is>
           <t>Expanded lane: Backend/Full-stack. Posted date not shown on Greenhouse page; verified live 2026-10-26. Salary not listed.</t>
@@ -15219,9 +15213,6 @@
           <t>new</t>
         </is>
       </c>
-      <c r="I280" t="inlineStr"/>
-      <c r="J280" t="inlineStr"/>
-      <c r="K280" t="inlineStr"/>
       <c r="L280" t="inlineStr">
         <is>
           <t>Expanded lane: Backend/Full-stack. Still live on Greenhouse board 2026-10-26; BuiltIn listed 2026-05-11.</t>
@@ -15284,9 +15275,6 @@
           <t>new</t>
         </is>
       </c>
-      <c r="I281" t="inlineStr"/>
-      <c r="J281" t="inlineStr"/>
-      <c r="K281" t="inlineStr"/>
       <c r="L281" t="inlineStr">
         <is>
           <t>Expanded lane: Backend/Full-stack. Published 2026-09-09 per Ashby.</t>
@@ -15349,9 +15337,6 @@
           <t>new</t>
         </is>
       </c>
-      <c r="I282" t="inlineStr"/>
-      <c r="J282" t="inlineStr"/>
-      <c r="K282" t="inlineStr"/>
       <c r="L282" t="inlineStr">
         <is>
           <t>Expanded lane: Data. Posted date not shown on Greenhouse page; verified live 2026-10-26. dbt/Kafka only 'plus' skills, not core.</t>
@@ -15414,9 +15399,6 @@
           <t>new</t>
         </is>
       </c>
-      <c r="I283" t="inlineStr"/>
-      <c r="J283" t="inlineStr"/>
-      <c r="K283" t="inlineStr"/>
       <c r="L283" t="inlineStr">
         <is>
           <t>Expanded lane: ML. Posted date not shown on Greenhouse page; verified live 2026-10-26. In-person onboarding in Ann Arbor (one trip).</t>
@@ -15479,9 +15461,6 @@
           <t>new</t>
         </is>
       </c>
-      <c r="I284" t="inlineStr"/>
-      <c r="J284" t="inlineStr"/>
-      <c r="K284" t="inlineStr"/>
       <c r="L284" t="inlineStr">
         <is>
           <t>Expanded lane: ML. Posted date not shown on Greenhouse page; verified live 2026-10-26. Salary not listed. WFH stipend listed.</t>
@@ -15544,9 +15523,6 @@
           <t>new</t>
         </is>
       </c>
-      <c r="I285" t="inlineStr"/>
-      <c r="J285" t="inlineStr"/>
-      <c r="K285" t="inlineStr"/>
       <c r="L285" t="inlineStr">
         <is>
           <t>Expanded lane: ML. Posted date not shown on Greenhouse page; verified live 2026-10-26. Spark/Kafka/Airflow only listed as preferred familiarity, not core.</t>
@@ -15609,9 +15585,6 @@
           <t>new</t>
         </is>
       </c>
-      <c r="I286" t="inlineStr"/>
-      <c r="J286" t="inlineStr"/>
-      <c r="K286" t="inlineStr"/>
       <c r="L286" t="inlineStr">
         <is>
           <t>Expanded lane: Platform/Infra. Posted date not shown on Greenhouse page; verified live 2026-10-26. FLAG: role requires deploying/operating/troubleshooting K8s in cloud.</t>
@@ -15674,9 +15647,6 @@
           <t>new</t>
         </is>
       </c>
-      <c r="I287" t="inlineStr"/>
-      <c r="J287" t="inlineStr"/>
-      <c r="K287" t="inlineStr"/>
       <c r="L287" t="inlineStr">
         <is>
           <t>Expanded lane: Solutions/FDE. Posted date not shown on Greenhouse page; verified live 2026-10-26.</t>
@@ -15739,9 +15709,6 @@
           <t>new</t>
         </is>
       </c>
-      <c r="I288" t="inlineStr"/>
-      <c r="J288" t="inlineStr"/>
-      <c r="K288" t="inlineStr"/>
       <c r="L288" t="inlineStr">
         <is>
           <t>Expanded lane: Solutions/FDE. Posted date not shown on Greenhouse page; verified live 2026-10-26.</t>
@@ -15758,6 +15725,189 @@
         </is>
       </c>
       <c r="O288" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>ElevenLabs</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>Forward Deployed Engineer - Software Engineer - USA</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>Remote US (remote-first, anywhere US; preference NY/SF)</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>https://elevenlabs.io/careers/6c4c57c1-ec72-42ba-af3a-eb7aebbde2e6/forward-deployed-engineer-software-engineer-usa</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr"/>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>Not listed</t>
+        </is>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>Voice platform; Python, APIs, customer-facing; no years threshold; strong fit for voice-pipeline background</t>
+        </is>
+      </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="I289" t="inlineStr"/>
+      <c r="J289" t="inlineStr"/>
+      <c r="K289" t="inlineStr"/>
+      <c r="L289" t="inlineStr">
+        <is>
+          <t>Verified live in browser 2026-10-26. Regular travel for customer onsites, load not quantified; NY/SF preference.</t>
+        </is>
+      </c>
+      <c r="M289" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="N289" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="O289" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Backend (USA Only, 100% Remote)</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>Remote US</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/Close/01fc4ad7-4d33-4f64-919f-502bb2c20efc?gh_jid=5661240002</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr"/>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>Not listed on posting (reported $140k-$210k NOT confirmed)</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>Python backbone, LLM-backed features, MCP surface, Pydantic/Temporal/LangFuse, Postgres, AWS EKS; K8s in stack, not a hard requirement</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="I290" t="inlineStr"/>
+      <c r="J290" t="inlineStr"/>
+      <c r="K290" t="inlineStr"/>
+      <c r="L290" t="inlineStr">
+        <is>
+          <t>Verified live in browser 2026-10-26. No salary band published; no numeric years threshold.</t>
+        </is>
+      </c>
+      <c r="M290" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="N290" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="O290" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>Lunon</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>Forward Deployed AI Engineer</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>Fully remote, US-based (NYC HQ)</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/lunon/706c16cf-f3ec-4a64-aad1-923ad1ce4131</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr"/>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>$160,000-$195,000</t>
+        </is>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>Closest live Lunon role — original FDE posting closed. Model/LLM-focused, not speech/call-analytics; requires fine-tuning/post-training, evals, production model serving — matches LLM fine-tuning on H100s</t>
+        </is>
+      </c>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="I291" t="inlineStr"/>
+      <c r="J291" t="inlineStr"/>
+      <c r="K291" t="inlineStr"/>
+      <c r="L291" t="inlineStr">
+        <is>
+          <t>Verified live in browser 2026-10-26. Original FDE (Ashby 9d93a54c) closed: Job not found / 404. Salary $160-195k, NOT the reported $180-200k.</t>
+        </is>
+      </c>
+      <c r="M291" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="N291" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="O291" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>

--- a/tracker.xlsx
+++ b/tracker.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2667" uniqueCount="1141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2676" uniqueCount="1152">
   <si>
     <t>Company</t>
   </si>
@@ -3232,7 +3232,16 @@
     <t>Sports video + sensor data + agentic AI — closest thematic fit in sweep; TS/React/AWS; 7+ yrs</t>
   </si>
   <si>
-    <t>Expanded lane: Backend/Full-stack. Remote, UT explicitly eligible.</t>
+    <t>ready to apply</t>
+  </si>
+  <si>
+    <t>resume-hudl-senior-software-engineer.pdf</t>
+  </si>
+  <si>
+    <t>cover-letter-hudl-senior-software-engineer.pdf</t>
+  </si>
+  <si>
+    <t>Expanded lane: Backend/Full-stack. Remote, UT explicitly eligible. Greenhouse form checked 2026-10-27: optional cover letter; GitHub link required; optional salary-expectations field and post-employment-restrictions question (Jack to answer). Ready to apply — materials complete, 2026-10-27.</t>
   </si>
   <si>
     <t>https://job-boards.greenhouse.io/paretocaptiveservicesllc/jobs/4705486006</t>
@@ -3292,7 +3301,10 @@
     <t>Agent harness + MCP (Model Context Protocol) tooling, Go + React/TS, Postgres, AWS — near-perfect fit</t>
   </si>
   <si>
-    <t>Expanded lane: Backend/Full-stack. Published 2026-09-09 per Ashby.</t>
+    <t>resume-coder-senior-software-engineer.pdf</t>
+  </si>
+  <si>
+    <t>Expanded lane: Backend/Full-stack. Published 2026-09-09 per Ashby. Ashby form checked 2026-10-27: no cover letter field. Optional long question 'What interests you in Coder?' asks for an answer in Jack's own words without AI, so leave it for Jack. Ready to apply — materials complete, 2026-10-27.</t>
   </si>
   <si>
     <t>https://job-boards.greenhouse.io/healthie/jobs/4412029009?gh_src=c88eeab75us</t>
@@ -3340,7 +3352,13 @@
     <t>3-5+ yrs, Python/Go, PyTorch, ML pipelines + model serving, LLM/RAG/agentic preferred</t>
   </si>
   <si>
-    <t>Expanded lane: ML. Posted date not shown on Greenhouse page; verified live 2026-10-26. Spark/Kafka/Airflow only listed as preferred familiarity, not core.</t>
+    <t>resume-reddit-machine-learning-engineer.pdf</t>
+  </si>
+  <si>
+    <t>cover-letter-reddit-machine-learning-engineer.pdf</t>
+  </si>
+  <si>
+    <t>Expanded lane: ML. Posted date not shown on Greenhouse page; verified live 2026-10-26. Spark/Kafka/Airflow only listed as preferred familiarity, not core. Greenhouse form checked 2026-10-27: optional cover letter; asks current/most recent company. Ready to apply — materials complete, 2026-10-27.</t>
   </si>
   <si>
     <t>Senior Infrastructure Engineer</t>
@@ -3382,6 +3400,15 @@
     <t>5+ yrs, agent dev + MCP (Model Context Protocol) integrations, LLM retrieval, evals — near-perfect fit</t>
   </si>
   <si>
+    <t>resume-reddit-senior-forward-deployed-engineer-ai-enablement.pdf</t>
+  </si>
+  <si>
+    <t>cover-letter-reddit-senior-forward-deployed-engineer-ai-enablement.pdf</t>
+  </si>
+  <si>
+    <t>Expanded lane: Solutions/FDE. Posted date not shown on Greenhouse page; verified live 2026-10-26. Greenhouse form checked 2026-10-27: optional cover letter; asks current/most recent company. Ready to apply — materials complete, 2026-10-27.</t>
+  </si>
+  <si>
     <t>ElevenLabs</t>
   </si>
   <si>
@@ -3397,7 +3424,10 @@
     <t>Voice platform; Python, APIs, customer-facing; no years threshold; strong fit for voice-pipeline background</t>
   </si>
   <si>
-    <t>Verified live in browser 2026-10-26. Regular travel for customer onsites, load not quantified; NY/SF preference.</t>
+    <t>resume-elevenlabs-forward-deployed-engineer.pdf</t>
+  </si>
+  <si>
+    <t>Verified live in browser 2026-10-26. Regular travel for customer onsites, load not quantified; NY/SF preference. Apply form is Ashby: https://jobs.ashbyhq.com/elevenlabs/6c4c57c1-ec72-42ba-af3a-eb7aebbde2e6 (checked 2026-10-27). No cover letter field; GitHub + LinkedIn required; four optional long questions (why ElevenLabs, most impactful build, how you knew it worked, ElevenLabs usage), so leave those for Jack. Ready to apply — materials complete, 2026-10-27.</t>
   </si>
   <si>
     <t>Close</t>
@@ -3418,7 +3448,10 @@
     <t>Python backbone, LLM-backed features, MCP surface, Pydantic/Temporal/LangFuse, Postgres, AWS EKS; K8s in stack, not a hard requirement</t>
   </si>
   <si>
-    <t>Verified live in browser 2026-10-26. No salary band published; no numeric years threshold.</t>
+    <t>resume-close-senior-software-engineer-backend.pdf</t>
+  </si>
+  <si>
+    <t>Verified live in browser 2026-10-26. No salary band published; no numeric years threshold. Ashby form checked 2026-10-27: no cover letter field. Required long answers (remote experience, offsite travel, something you built), an API challenge (GET https://api.close.com/buildwithus/ for a Verification ID, plus share the technique used), and a team pick (CRM/Growth/Agents/Communications). Leave those for Jack. Ready to apply — materials complete, 2026-10-27.</t>
   </si>
   <si>
     <t>Lunon</t>
@@ -13436,19 +13469,25 @@
         <v>1070</v>
       </c>
       <c r="H278" t="s">
-        <v>336</v>
+        <v>1071</v>
+      </c>
+      <c r="I278" s="1" t="s">
+        <v>1072</v>
+      </c>
+      <c r="J278" s="1" t="s">
+        <v>1073</v>
       </c>
       <c r="L278" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="M278" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="N278" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="O278" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
     </row>
     <row r="279" spans="1:15" x14ac:dyDescent="0.25">
@@ -13462,22 +13501,22 @@
         <v>822</v>
       </c>
       <c r="D279" t="s">
-        <v>1072</v>
+        <v>1075</v>
       </c>
       <c r="E279" t="s">
-        <v>1073</v>
+        <v>1076</v>
       </c>
       <c r="F279" t="s">
-        <v>1074</v>
+        <v>1077</v>
       </c>
       <c r="G279" t="s">
-        <v>1075</v>
+        <v>1078</v>
       </c>
       <c r="H279" t="s">
         <v>336</v>
       </c>
       <c r="L279" t="s">
-        <v>1076</v>
+        <v>1079</v>
       </c>
       <c r="M279" t="s">
         <v>22</v>
@@ -13491,31 +13530,31 @@
     </row>
     <row r="280" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>1077</v>
+        <v>1080</v>
       </c>
       <c r="B280" t="s">
-        <v>1078</v>
+        <v>1081</v>
       </c>
       <c r="C280" t="s">
         <v>641</v>
       </c>
       <c r="D280" t="s">
-        <v>1079</v>
+        <v>1082</v>
       </c>
       <c r="E280" t="s">
-        <v>1080</v>
+        <v>1083</v>
       </c>
       <c r="F280" t="s">
-        <v>1081</v>
+        <v>1084</v>
       </c>
       <c r="G280" t="s">
-        <v>1082</v>
+        <v>1085</v>
       </c>
       <c r="H280" t="s">
         <v>336</v>
       </c>
       <c r="L280" t="s">
-        <v>1083</v>
+        <v>1086</v>
       </c>
       <c r="M280" t="s">
         <v>22</v>
@@ -13529,40 +13568,44 @@
     </row>
     <row r="281" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>1084</v>
+        <v>1087</v>
       </c>
       <c r="B281" t="s">
-        <v>1085</v>
+        <v>1088</v>
       </c>
       <c r="C281" t="s">
-        <v>1086</v>
+        <v>1089</v>
       </c>
       <c r="D281" t="s">
-        <v>1087</v>
+        <v>1090</v>
       </c>
       <c r="E281" t="s">
-        <v>1088</v>
+        <v>1091</v>
       </c>
       <c r="F281" t="s">
-        <v>1089</v>
+        <v>1092</v>
       </c>
       <c r="G281" t="s">
-        <v>1090</v>
+        <v>1093</v>
       </c>
       <c r="H281" t="s">
-        <v>336</v>
-      </c>
+        <v>1071</v>
+      </c>
+      <c r="I281" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="J281" s="1"/>
       <c r="L281" t="s">
-        <v>1091</v>
+        <v>1095</v>
       </c>
       <c r="M281" t="s">
-        <v>22</v>
+        <v>69</v>
       </c>
       <c r="N281" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="O281" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
     </row>
     <row r="282" spans="1:15" x14ac:dyDescent="0.25">
@@ -13576,22 +13619,22 @@
         <v>822</v>
       </c>
       <c r="D282" t="s">
-        <v>1092</v>
+        <v>1096</v>
       </c>
       <c r="E282" t="s">
-        <v>1073</v>
+        <v>1076</v>
       </c>
       <c r="F282" t="s">
         <v>899</v>
       </c>
       <c r="G282" t="s">
-        <v>1093</v>
+        <v>1097</v>
       </c>
       <c r="H282" t="s">
         <v>336</v>
       </c>
       <c r="L282" t="s">
-        <v>1094</v>
+        <v>1098</v>
       </c>
       <c r="M282" t="s">
         <v>22</v>
@@ -13605,7 +13648,7 @@
     </row>
     <row r="283" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>1095</v>
+        <v>1099</v>
       </c>
       <c r="B283" t="s">
         <v>427</v>
@@ -13614,22 +13657,22 @@
         <v>641</v>
       </c>
       <c r="D283" t="s">
-        <v>1096</v>
+        <v>1100</v>
       </c>
       <c r="E283" t="s">
-        <v>1073</v>
+        <v>1076</v>
       </c>
       <c r="F283" t="s">
-        <v>1097</v>
+        <v>1101</v>
       </c>
       <c r="G283" t="s">
-        <v>1098</v>
+        <v>1102</v>
       </c>
       <c r="H283" t="s">
         <v>336</v>
       </c>
       <c r="L283" t="s">
-        <v>1099</v>
+        <v>1103</v>
       </c>
       <c r="M283" t="s">
         <v>22</v>
@@ -13649,25 +13692,25 @@
         <v>427</v>
       </c>
       <c r="C284" t="s">
-        <v>1086</v>
+        <v>1089</v>
       </c>
       <c r="D284" t="s">
-        <v>1100</v>
+        <v>1104</v>
       </c>
       <c r="E284" t="s">
-        <v>1073</v>
+        <v>1076</v>
       </c>
       <c r="F284" t="s">
-        <v>1101</v>
+        <v>1105</v>
       </c>
       <c r="G284" t="s">
-        <v>1102</v>
+        <v>1106</v>
       </c>
       <c r="H284" t="s">
         <v>336</v>
       </c>
       <c r="L284" t="s">
-        <v>1103</v>
+        <v>1107</v>
       </c>
       <c r="M284" t="s">
         <v>22</v>
@@ -13690,60 +13733,66 @@
         <v>641</v>
       </c>
       <c r="D285" t="s">
-        <v>1104</v>
+        <v>1108</v>
       </c>
       <c r="E285" t="s">
-        <v>1073</v>
+        <v>1076</v>
       </c>
       <c r="F285" t="s">
-        <v>1105</v>
+        <v>1109</v>
       </c>
       <c r="G285" t="s">
-        <v>1106</v>
+        <v>1110</v>
       </c>
       <c r="H285" t="s">
-        <v>336</v>
+        <v>1071</v>
+      </c>
+      <c r="I285" s="1" t="s">
+        <v>1111</v>
+      </c>
+      <c r="J285" s="1" t="s">
+        <v>1112</v>
       </c>
       <c r="L285" t="s">
-        <v>1107</v>
+        <v>1113</v>
       </c>
       <c r="M285" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="N285" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="O285" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
     </row>
     <row r="286" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>1077</v>
+        <v>1080</v>
       </c>
       <c r="B286" t="s">
-        <v>1108</v>
+        <v>1114</v>
       </c>
       <c r="C286" t="s">
         <v>822</v>
       </c>
       <c r="D286" t="s">
-        <v>1109</v>
+        <v>1115</v>
       </c>
       <c r="E286" t="s">
-        <v>1073</v>
+        <v>1076</v>
       </c>
       <c r="F286" t="s">
-        <v>1081</v>
+        <v>1084</v>
       </c>
       <c r="G286" t="s">
-        <v>1110</v>
+        <v>1116</v>
       </c>
       <c r="H286" t="s">
         <v>336</v>
       </c>
       <c r="L286" t="s">
-        <v>1111</v>
+        <v>1117</v>
       </c>
       <c r="M286" t="s">
         <v>22</v>
@@ -13760,28 +13809,28 @@
         <v>897</v>
       </c>
       <c r="B287" t="s">
-        <v>1112</v>
+        <v>1118</v>
       </c>
       <c r="C287" t="s">
         <v>641</v>
       </c>
       <c r="D287" t="s">
-        <v>1113</v>
+        <v>1119</v>
       </c>
       <c r="E287" t="s">
-        <v>1073</v>
+        <v>1076</v>
       </c>
       <c r="F287" t="s">
-        <v>1114</v>
+        <v>1120</v>
       </c>
       <c r="G287" t="s">
-        <v>1115</v>
+        <v>1121</v>
       </c>
       <c r="H287" t="s">
         <v>336</v>
       </c>
       <c r="L287" t="s">
-        <v>1116</v>
+        <v>1122</v>
       </c>
       <c r="M287" t="s">
         <v>22</v>
@@ -13798,133 +13847,147 @@
         <v>398</v>
       </c>
       <c r="B288" t="s">
-        <v>1117</v>
+        <v>1123</v>
       </c>
       <c r="C288" t="s">
         <v>822</v>
       </c>
       <c r="D288" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="E288" t="s">
-        <v>1073</v>
+        <v>1076</v>
       </c>
       <c r="F288" t="s">
-        <v>1119</v>
+        <v>1125</v>
       </c>
       <c r="G288" t="s">
-        <v>1120</v>
+        <v>1126</v>
       </c>
       <c r="H288" t="s">
-        <v>336</v>
+        <v>1071</v>
+      </c>
+      <c r="I288" s="1" t="s">
+        <v>1127</v>
+      </c>
+      <c r="J288" s="1" t="s">
+        <v>1128</v>
       </c>
       <c r="L288" t="s">
-        <v>1116</v>
+        <v>1129</v>
       </c>
       <c r="M288" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="N288" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="O288" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
     </row>
     <row r="289" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>1121</v>
+        <v>1130</v>
       </c>
       <c r="B289" t="s">
-        <v>1122</v>
+        <v>1131</v>
       </c>
       <c r="C289" t="s">
-        <v>1123</v>
+        <v>1132</v>
       </c>
       <c r="D289" t="s">
-        <v>1124</v>
+        <v>1133</v>
       </c>
       <c r="F289" t="s">
-        <v>1074</v>
+        <v>1077</v>
       </c>
       <c r="G289" t="s">
-        <v>1125</v>
+        <v>1134</v>
       </c>
       <c r="H289" t="s">
-        <v>336</v>
-      </c>
+        <v>1071</v>
+      </c>
+      <c r="I289" s="1" t="s">
+        <v>1135</v>
+      </c>
+      <c r="J289" s="1"/>
       <c r="L289" t="s">
-        <v>1126</v>
+        <v>1136</v>
       </c>
       <c r="M289" t="s">
-        <v>22</v>
+        <v>69</v>
       </c>
       <c r="N289" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="O289" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
     </row>
     <row r="290" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>1127</v>
+        <v>1137</v>
       </c>
       <c r="B290" t="s">
-        <v>1128</v>
+        <v>1138</v>
       </c>
       <c r="C290" t="s">
-        <v>1129</v>
+        <v>1139</v>
       </c>
       <c r="D290" t="s">
-        <v>1130</v>
+        <v>1140</v>
       </c>
       <c r="F290" t="s">
-        <v>1131</v>
+        <v>1141</v>
       </c>
       <c r="G290" t="s">
-        <v>1132</v>
+        <v>1142</v>
       </c>
       <c r="H290" t="s">
-        <v>336</v>
-      </c>
+        <v>1071</v>
+      </c>
+      <c r="I290" s="1" t="s">
+        <v>1143</v>
+      </c>
+      <c r="J290" s="1"/>
       <c r="L290" t="s">
-        <v>1133</v>
+        <v>1144</v>
       </c>
       <c r="M290" t="s">
-        <v>22</v>
+        <v>69</v>
       </c>
       <c r="N290" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="O290" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
     </row>
     <row r="291" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>1134</v>
+        <v>1145</v>
       </c>
       <c r="B291" t="s">
-        <v>1135</v>
+        <v>1146</v>
       </c>
       <c r="C291" t="s">
-        <v>1136</v>
+        <v>1147</v>
       </c>
       <c r="D291" t="s">
-        <v>1137</v>
+        <v>1148</v>
       </c>
       <c r="F291" t="s">
-        <v>1138</v>
+        <v>1149</v>
       </c>
       <c r="G291" t="s">
-        <v>1139</v>
+        <v>1150</v>
       </c>
       <c r="H291" t="s">
         <v>336</v>
       </c>
       <c r="L291" t="s">
-        <v>1140</v>
+        <v>1151</v>
       </c>
       <c r="M291" t="s">
         <v>22</v>

--- a/tracker.xlsx
+++ b/tracker.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2676" uniqueCount="1152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2690" uniqueCount="1167">
   <si>
     <t>Company</t>
   </si>
@@ -2434,10 +2434,13 @@
     <t>Forward-deployed role: customer-facing builds, Python/Node/React, LLM/agent nice-to-have, AWS nice-to-have. Referral via friend.</t>
   </si>
   <si>
-    <t>resume/narmi branch (jack-resume-narmi.pdf)</t>
-  </si>
-  <si>
-    <t>Source: Gem; resume tailored, cover letter not started</t>
+    <t>ready to apply</t>
+  </si>
+  <si>
+    <t>resume-narmi-software-engineer-forward-deployed.pdf</t>
+  </si>
+  <si>
+    <t>Source: Gem; resume tailored, cover letter not started 2026-10-27: resume rebuilt in applications/narmi-software-engineer-forward-deployed/ (black-and-white), replacing the old resume/narmi branch PDF. Gem form checked: no cover letter field; required 1-2 sentence 'proudest accomplishment' + restrictive-agreement questions. FLAG: required 'Are you able to work onsite 3 days a week in New York City?' (posting is in-person-first, Flatiron office, base $91K-$110K); Jack is in Utah, so Jack must confirm before Muse applies. Ready to apply — materials complete, 2026-10-27.</t>
   </si>
   <si>
     <t>SRS Acquiom</t>
@@ -3232,9 +3235,6 @@
     <t>Sports video + sensor data + agentic AI — closest thematic fit in sweep; TS/React/AWS; 7+ yrs</t>
   </si>
   <si>
-    <t>ready to apply</t>
-  </si>
-  <si>
     <t>resume-hudl-senior-software-engineer.pdf</t>
   </si>
   <si>
@@ -3256,7 +3256,13 @@
     <t>Full-stack TS; AWS S3/Lambda/RDS/Dynamo/AppSync; Angular gap (Jack is React)</t>
   </si>
   <si>
-    <t>Expanded lane: Backend/Full-stack. Posted date not shown on Greenhouse page; verified live 2026-10-26. Salary not listed.</t>
+    <t>resume-paretohealth-senior-software-engineer.pdf</t>
+  </si>
+  <si>
+    <t>cover-letter-paretohealth-senior-software-engineer.pdf</t>
+  </si>
+  <si>
+    <t>Expanded lane: Backend/Full-stack. Posted date not shown on Greenhouse page; verified live 2026-10-26. Salary not listed. Greenhouse form checked 2026-10-27: optional cover letter; required Yes/No screens (full-stack TS, Angular, AWS S3/Lambda/RDS/Dynamo/AppSync, AI-assisted dev). Answer truthfully: Angular is No. Ready to apply — materials complete, 2026-10-27.</t>
   </si>
   <si>
     <t>Manifest</t>
@@ -3277,7 +3283,16 @@
     <t>8+ yrs asked vs Jack's 7 yrs FT; web services + ETL at high throughput; TS/Mongo/Go/Python</t>
   </si>
   <si>
-    <t>Expanded lane: Backend/Full-stack. Still live on Greenhouse board 2026-10-26; BuiltIn listed 2026-05-11.</t>
+    <t>resume-manifest-senior-backend-application-engineer.pdf</t>
+  </si>
+  <si>
+    <t>cover-letter-manifest-senior-backend-application-engineer.pdf</t>
+  </si>
+  <si>
+    <t>Expanded lane: Backend/Full-stack. Still live on Greenhouse board 2026-10-26; BuiltIn listed 2026-05-11. Greenhouse form checked 2026-10-27: optional cover letter, no custom questions. Ready to apply — materials complete, 2026-10-27.</t>
+  </si>
+  <si>
+    <t>None</t>
   </si>
   <si>
     <t>Coder</t>
@@ -3313,7 +3328,13 @@
     <t>6+ yrs, SQL/Postgres/Snowflake, Terraform, warehouse isolation/RBAC; HIPAA preferred (gap — Jack lacks healthcare)</t>
   </si>
   <si>
-    <t>Expanded lane: Data. Posted date not shown on Greenhouse page; verified live 2026-10-26. dbt/Kafka only 'plus' skills, not core.</t>
+    <t>resume-healthie-senior-data-engineer.pdf</t>
+  </si>
+  <si>
+    <t>cover-letter-healthie-senior-data-engineer.pdf</t>
+  </si>
+  <si>
+    <t>Expanded lane: Data. Posted date not shown on Greenhouse page; verified live 2026-10-26. dbt/Kafka only 'plus' skills, not core. Greenhouse form checked 2026-10-27: optional cover letter; sponsorship + how-heard are text boxes. Cover letter is upfront about no HIPAA/Snowflake. Ready to apply — materials complete, 2026-10-27.</t>
   </si>
   <si>
     <t>Censys</t>
@@ -3328,7 +3349,13 @@
     <t>5+ yrs applied ML, Go/Python, feature pipelines, model evaluation, MLOps familiarity</t>
   </si>
   <si>
-    <t>Expanded lane: ML. Posted date not shown on Greenhouse page; verified live 2026-10-26. In-person onboarding in Ann Arbor (one trip).</t>
+    <t>resume-censys-senior-machine-learning-engineer.pdf</t>
+  </si>
+  <si>
+    <t>cover-letter-censys-senior-machine-learning-engineer.pdf</t>
+  </si>
+  <si>
+    <t>Expanded lane: ML. Posted date not shown on Greenhouse page; verified live 2026-10-26. In-person onboarding in Ann Arbor (one trip). Greenhouse form checked 2026-10-27: optional cover letter. FLAG: required Yes/No 'Did AI complete this application?' must be answered truthfully based on how it is actually submitted (Muse-submitted = Yes). Ready to apply — materials complete, 2026-10-27.</t>
   </si>
   <si>
     <t>https://job-boards.greenhouse.io/cresta/jobs/4249943008</t>
@@ -3340,7 +3367,10 @@
     <t>5-8+ yrs, LLM/RAG/agentic workflows, evaluation frameworks, PyTorch; newly-created role</t>
   </si>
   <si>
-    <t>Expanded lane: ML. Posted date not shown on Greenhouse page; verified live 2026-10-26. Salary not listed. WFH stipend listed.</t>
+    <t>resume-cresta-senior-machine-learning-engineer.pdf</t>
+  </si>
+  <si>
+    <t>Expanded lane: ML. Posted date not shown on Greenhouse page; verified live 2026-10-26. Salary not listed. WFH stipend listed. Greenhouse form checked 2026-10-27: no cover letter field; only work-auth/sponsorship questions. Ready to apply — materials complete, 2026-10-27.</t>
   </si>
   <si>
     <t>https://job-boards.greenhouse.io/reddit/jobs/7131932</t>
@@ -3370,7 +3400,13 @@
     <t>IaC (Terraform/Ansible/Helm/Go), CI/CD; K8s (Kubernetes) depth required — gap for Jack (light K8s, be honest)</t>
   </si>
   <si>
-    <t>Expanded lane: Platform/Infra. Posted date not shown on Greenhouse page; verified live 2026-10-26. FLAG: role requires deploying/operating/troubleshooting K8s in cloud.</t>
+    <t>resume-manifest-senior-infrastructure-engineer.pdf</t>
+  </si>
+  <si>
+    <t>cover-letter-manifest-senior-infrastructure-engineer.pdf</t>
+  </si>
+  <si>
+    <t>Expanded lane: Platform/Infra. Posted date not shown on Greenhouse page; verified live 2026-10-26. FLAG: role requires deploying/operating/troubleshooting K8s in cloud. Greenhouse form checked 2026-10-27: optional cover letter; work-auth/sponsorship only. Cover letter states K8s depth honestly (ArgoCD deploys only, no Terraform/Ansible/Helm depth). Ready to apply — materials complete, 2026-10-27.</t>
   </si>
   <si>
     <t>Senior Solutions Engineer</t>
@@ -3385,7 +3421,13 @@
     <t>4+ yrs full-stack, TS/Postgres; customer-facing technical role</t>
   </si>
   <si>
-    <t>Expanded lane: Solutions/FDE. Posted date not shown on Greenhouse page; verified live 2026-10-26.</t>
+    <t>resume-healthie-senior-solutions-engineer.pdf</t>
+  </si>
+  <si>
+    <t>cover-letter-healthie-senior-solutions-engineer.pdf</t>
+  </si>
+  <si>
+    <t>Expanded lane: Solutions/FDE. Posted date not shown on Greenhouse page; verified live 2026-10-26. Greenhouse form checked 2026-10-27: optional cover letter. FLAG: required text 'confirm you have a minimum of 4 years of experience with RoR and React'. Jack has React but no Rails, so Jack must answer this himself; likely a screen-out. Ready to apply — materials complete, 2026-10-27.</t>
   </si>
   <si>
     <t>Senior Forward Deployed Engineer (AI Enablement)</t>
@@ -3472,7 +3514,10 @@
     <t>Closest live Lunon role — original FDE posting closed. Model/LLM-focused, not speech/call-analytics; requires fine-tuning/post-training, evals, production model serving — matches LLM fine-tuning on H100s</t>
   </si>
   <si>
-    <t>Verified live in browser 2026-10-26. Original FDE (Ashby 9d93a54c) closed: Job not found / 404. Salary $160-195k, NOT the reported $180-200k.</t>
+    <t>resume-lunon-forward-deployed-ai-engineer.pdf</t>
+  </si>
+  <si>
+    <t>Verified live in browser 2026-10-26. Original FDE (Ashby 9d93a54c) closed: Job not found / 404. Salary $160-195k, NOT the reported $180-200k. Ashby form checked 2026-10-27: no cover letter field. Required: one-sentence 'hardest thing you've built' and a 250-word 'your AI stack and your edge' answer. Leave both for Jack. Ready to apply — materials complete, 2026-10-27.</t>
   </si>
 </sst>
 </file>
@@ -11960,18 +12005,18 @@
         <v>804</v>
       </c>
       <c r="H234" s="4" t="s">
-        <v>336</v>
+        <v>805</v>
       </c>
       <c r="I234" s="4" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="J234" s="4"/>
       <c r="K234" s="4"/>
       <c r="L234" s="4" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="M234" s="4" t="s">
-        <v>22</v>
+        <v>69</v>
       </c>
       <c r="N234" s="4" t="s">
         <v>38</v>
@@ -11982,34 +12027,34 @@
     </row>
     <row r="235" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A235" s="1" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="B235" s="1" t="s">
         <v>660</v>
       </c>
       <c r="C235" s="1" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="D235" s="1" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="F235" s="1" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="G235" s="1" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="H235" s="1" t="s">
         <v>336</v>
       </c>
       <c r="I235" s="1" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="J235" s="1" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="L235" s="1" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="O235" s="1" t="s">
         <v>43</v>
@@ -12017,28 +12062,28 @@
     </row>
     <row r="236" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A236" s="1" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="B236" s="1" t="s">
         <v>660</v>
       </c>
       <c r="C236" s="1" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="D236" s="1" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="F236" s="1" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="G236" s="1" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="H236" s="1" t="s">
         <v>36</v>
       </c>
       <c r="L236" s="1" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="O236" s="1" t="s">
         <v>43</v>
@@ -12046,25 +12091,25 @@
     </row>
     <row r="237" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A237" s="1" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="B237" s="1" t="s">
         <v>660</v>
       </c>
       <c r="C237" s="1" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="D237" s="1" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="G237" s="1" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="H237" s="1" t="s">
         <v>36</v>
       </c>
       <c r="L237" s="1" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="O237" s="1" t="s">
         <v>43</v>
@@ -12072,28 +12117,28 @@
     </row>
     <row r="238" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A238" s="1" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="B238" s="1" t="s">
         <v>660</v>
       </c>
       <c r="C238" s="1" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="D238" s="1" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="F238" s="1" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="G238" s="1" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="H238" s="1" t="s">
         <v>36</v>
       </c>
       <c r="L238" s="1" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="O238" s="1" t="s">
         <v>43</v>
@@ -12101,34 +12146,34 @@
     </row>
     <row r="239" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A239" s="1" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="B239" s="1" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="C239" s="1" t="s">
         <v>126</v>
       </c>
       <c r="D239" s="1" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="F239" s="1" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="G239" s="1" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="H239" s="1" t="s">
         <v>336</v>
       </c>
       <c r="I239" s="1" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="J239" s="1" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="L239" s="1" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="O239" s="1" t="s">
         <v>31</v>
@@ -12136,25 +12181,25 @@
     </row>
     <row r="240" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A240" s="1" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="B240" s="1" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="C240" s="1" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="D240" s="1" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="G240" s="1" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="H240" s="1" t="s">
         <v>36</v>
       </c>
       <c r="L240" s="1" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="O240" s="1" t="s">
         <v>31</v>
@@ -12162,31 +12207,31 @@
     </row>
     <row r="241" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A241" s="1" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="B241" s="1" t="s">
         <v>660</v>
       </c>
       <c r="C241" s="1" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="D241" s="1" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="G241" s="1" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="H241" s="1" t="s">
         <v>336</v>
       </c>
       <c r="I241" s="1" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="J241" s="1" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L241" s="1" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="O241" s="1" t="s">
         <v>43</v>
@@ -12194,28 +12239,28 @@
     </row>
     <row r="242" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A242" s="1" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="B242" s="1" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="C242" s="1" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="D242" s="1" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="F242" s="1" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="G242" s="1" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="H242" s="1" t="s">
         <v>36</v>
       </c>
       <c r="L242" s="1" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="O242" s="1" t="s">
         <v>31</v>
@@ -12223,28 +12268,28 @@
     </row>
     <row r="243" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A243" s="1" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="B243" s="1" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="C243" s="1" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="D243" s="1" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="F243" s="1" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="G243" s="1" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="H243" s="1" t="s">
         <v>36</v>
       </c>
       <c r="L243" s="1" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="O243" s="1" t="s">
         <v>31</v>
@@ -12252,32 +12297,32 @@
     </row>
     <row r="244" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A244" s="1" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="B244" s="1" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="C244" s="1" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="D244" s="1" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="F244" s="1"/>
       <c r="G244" s="1" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="H244" s="1" t="s">
         <v>336</v>
       </c>
       <c r="I244" s="1" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="J244" s="1" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="L244" s="1" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="M244" s="1" t="s">
         <v>22</v>
@@ -12291,39 +12336,39 @@
     </row>
     <row r="245" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A245" s="1" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="B245" s="1" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="C245" s="1" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="D245" s="1" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="E245" s="1"/>
       <c r="F245" s="1" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="G245" s="1" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="H245" s="1" t="s">
         <v>336</v>
       </c>
       <c r="I245" s="1" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="J245" s="1" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="K245" s="1"/>
       <c r="L245" s="1" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="M245" s="1" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="N245" s="1"/>
       <c r="O245" s="1" t="s">
@@ -12332,21 +12377,21 @@
     </row>
     <row r="246" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A246" s="1" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="B246" s="1" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="C246" s="1" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="D246" s="1" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="E246" s="1"/>
       <c r="F246" s="1"/>
       <c r="G246" s="1" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="H246" s="1" t="s">
         <v>36</v>
@@ -12355,10 +12400,10 @@
       <c r="J246" s="1"/>
       <c r="K246" s="1"/>
       <c r="L246" s="1" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="M246" s="1" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="N246" s="1"/>
       <c r="O246" s="1" t="s">
@@ -12367,25 +12412,25 @@
     </row>
     <row r="247" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A247" s="1" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="B247" s="1" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="C247" s="1" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="D247" s="1" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="E247" s="1" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="F247" s="1" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="G247" s="1" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="H247" s="1" t="s">
         <v>36</v>
@@ -12394,10 +12439,10 @@
       <c r="J247" s="1"/>
       <c r="K247" s="1"/>
       <c r="L247" s="1" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="M247" s="1" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="N247" s="1"/>
       <c r="O247" s="1" t="s">
@@ -12406,25 +12451,25 @@
     </row>
     <row r="248" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A248" s="1" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="B248" s="1" t="s">
         <v>660</v>
       </c>
       <c r="C248" s="1" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="D248" s="1" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="E248" s="1" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="F248" s="1" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="G248" s="1" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="H248" s="1" t="s">
         <v>36</v>
@@ -12433,10 +12478,10 @@
       <c r="J248" s="1"/>
       <c r="K248" s="1"/>
       <c r="L248" s="1" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="M248" s="1" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="N248" s="1"/>
       <c r="O248" s="1" t="s">
@@ -12445,25 +12490,25 @@
     </row>
     <row r="249" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A249" s="1" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="B249" s="1" t="s">
         <v>660</v>
       </c>
       <c r="C249" s="1" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="D249" s="1" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="E249" s="1" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="F249" s="1" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="G249" s="1" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="H249" s="1" t="s">
         <v>36</v>
@@ -12472,10 +12517,10 @@
       <c r="J249" s="1"/>
       <c r="K249" s="1"/>
       <c r="L249" s="1" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="M249" s="1" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="N249" s="1"/>
       <c r="O249" s="1" t="s">
@@ -12484,37 +12529,37 @@
     </row>
     <row r="250" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A250" s="1" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="B250" s="1" t="s">
         <v>660</v>
       </c>
       <c r="C250" s="1" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="D250" s="1" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="E250" s="1" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="F250" s="1" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="G250" s="1" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="H250" s="1" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="I250" s="1"/>
       <c r="J250" s="1"/>
       <c r="K250" s="1"/>
       <c r="L250" s="1" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="M250" s="1" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="N250" s="1"/>
       <c r="O250" s="1" t="s">
@@ -12523,41 +12568,41 @@
     </row>
     <row r="251" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A251" s="1" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="B251" s="1" t="s">
         <v>660</v>
       </c>
       <c r="C251" s="1" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="D251" s="1" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="E251" s="1" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="F251" s="1" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="G251" s="1" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="H251" s="1" t="s">
         <v>336</v>
       </c>
       <c r="I251" s="1" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="J251" s="1" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="K251" s="1"/>
       <c r="L251" s="1" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="M251" s="1" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="N251" s="1"/>
       <c r="O251" s="1" t="s">
@@ -12566,25 +12611,25 @@
     </row>
     <row r="252" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A252" s="1" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="B252" s="1" t="s">
         <v>660</v>
       </c>
       <c r="C252" s="1" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="D252" s="1" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="E252" s="1" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="F252" s="1" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="G252" s="1" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="H252" s="1" t="s">
         <v>36</v>
@@ -12593,10 +12638,10 @@
       <c r="J252" s="1"/>
       <c r="K252" s="1"/>
       <c r="L252" s="1" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="M252" s="1" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="N252" s="1"/>
       <c r="O252" s="1" t="s">
@@ -12605,26 +12650,26 @@
     </row>
     <row r="253" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A253" s="1" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="B253" s="1" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="C253" s="1" t="s">
         <v>126</v>
       </c>
       <c r="D253" s="1" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="E253" s="1" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="F253" s="1"/>
       <c r="G253" s="1" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="H253" s="1" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="I253" s="1"/>
       <c r="J253" s="1"/>
@@ -12638,32 +12683,32 @@
     </row>
     <row r="254" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A254" s="1" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="B254" s="1" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="C254" s="1" t="s">
         <v>126</v>
       </c>
       <c r="D254" s="1" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="E254" s="1" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="F254" s="1"/>
       <c r="G254" s="1" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="H254" s="1" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="I254" s="1"/>
       <c r="J254" s="1"/>
       <c r="K254" s="1"/>
       <c r="L254" s="1" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="M254" s="1"/>
       <c r="N254" s="1"/>
@@ -12673,34 +12718,34 @@
     </row>
     <row r="255" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A255" s="1" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="B255" s="1" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="C255" s="1" t="s">
         <v>126</v>
       </c>
       <c r="D255" s="1" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="E255" s="1" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="F255" s="1" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="G255" s="1" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="H255" s="1" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="I255" s="1"/>
       <c r="J255" s="1"/>
       <c r="K255" s="1"/>
       <c r="L255" s="1" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="M255" s="1"/>
       <c r="N255" s="1"/>
@@ -12710,34 +12755,34 @@
     </row>
     <row r="256" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A256" s="1" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="B256" s="1" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="C256" s="1" t="s">
         <v>126</v>
       </c>
       <c r="D256" s="1" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="E256" s="1" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="F256" s="1" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="G256" s="1" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="H256" s="1" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="I256" s="1"/>
       <c r="J256" s="1"/>
       <c r="K256" s="1"/>
       <c r="L256" s="1" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="M256" s="1"/>
       <c r="N256" s="1"/>
@@ -12747,28 +12792,28 @@
     </row>
     <row r="257" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A257" s="1" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B257" s="1" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="C257" s="1" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="D257" s="1" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="E257" s="1" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="F257" s="1" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="G257" s="1" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="H257" s="1" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="I257" s="1"/>
       <c r="J257" s="1"/>
@@ -12782,28 +12827,28 @@
     </row>
     <row r="258" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A258" s="1" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="B258" s="1" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="C258" s="1" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="D258" s="1" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="E258" s="1" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="F258" s="1" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="G258" s="1" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="H258" s="1" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="I258" s="1"/>
       <c r="J258" s="1"/>
@@ -12817,34 +12862,34 @@
     </row>
     <row r="259" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A259" s="1" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="B259" s="1" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="C259" s="1" t="s">
         <v>126</v>
       </c>
       <c r="D259" s="1" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="E259" s="1" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="F259" s="1" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="G259" s="1" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="H259" s="1" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="I259" s="1"/>
       <c r="J259" s="1"/>
       <c r="K259" s="1"/>
       <c r="L259" s="1" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="M259" s="1"/>
       <c r="N259" s="1"/>
@@ -12854,34 +12899,34 @@
     </row>
     <row r="260" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A260" s="1" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="B260" s="1" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="C260" s="1" t="s">
         <v>126</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="E260" s="1" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="F260" s="1" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="G260" s="1" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="H260" s="1" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="I260" s="1"/>
       <c r="J260" s="1"/>
       <c r="K260" s="1"/>
       <c r="L260" s="1" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="M260" s="1"/>
       <c r="N260" s="1"/>
@@ -12891,28 +12936,28 @@
     </row>
     <row r="261" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A261" s="1" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="B261" s="1" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="C261" s="1" t="s">
         <v>126</v>
       </c>
       <c r="D261" s="1" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="E261" s="1" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="F261" s="1" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="G261" s="1" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="H261" s="1" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="I261" s="1"/>
       <c r="J261" s="1"/>
@@ -12926,34 +12971,34 @@
     </row>
     <row r="262" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A262" s="1" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="B262" s="1" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="C262" s="1" t="s">
         <v>126</v>
       </c>
       <c r="D262" s="1" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="E262" s="1" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="F262" s="1" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="G262" s="1" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="H262" s="1" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="I262" s="1"/>
       <c r="J262" s="1"/>
       <c r="K262" s="1"/>
       <c r="L262" s="1" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="M262" s="1"/>
       <c r="N262" s="1"/>
@@ -12963,35 +13008,35 @@
     </row>
     <row r="263" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A263" s="1" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="B263" s="1" t="s">
         <v>660</v>
       </c>
       <c r="C263" s="1" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="D263" s="1" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="E263" s="1"/>
       <c r="F263" s="1" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="G263" s="1" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="H263" s="1" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="I263" s="1"/>
       <c r="J263" s="1"/>
       <c r="K263" s="1"/>
       <c r="L263" s="1" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="M263" s="1" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="N263" s="1"/>
       <c r="O263" s="1" t="s">
@@ -13000,31 +13045,31 @@
     </row>
     <row r="264" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="B264" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="C264" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="D264" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="E264" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="F264" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="G264" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="H264" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="L264" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="O264" t="s">
         <v>43</v>
@@ -13032,28 +13077,28 @@
     </row>
     <row r="265" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="B265" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="C265" t="s">
         <v>126</v>
       </c>
       <c r="D265" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="E265" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="G265" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="H265" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="L265" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="O265" t="s">
         <v>43</v>
@@ -13061,28 +13106,28 @@
     </row>
     <row r="266" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="B266" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="C266" t="s">
         <v>126</v>
       </c>
       <c r="D266" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="E266" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="G266" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="H266" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="L266" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="O266" t="s">
         <v>43</v>
@@ -13090,31 +13135,31 @@
     </row>
     <row r="267" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="B267" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="C267" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="D267" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="E267" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="F267" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="G267" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="H267" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="L267" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="O267" t="s">
         <v>43</v>
@@ -13122,31 +13167,31 @@
     </row>
     <row r="268" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="B268" t="s">
         <v>660</v>
       </c>
       <c r="C268" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="D268" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="E268" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="F268" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="G268" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="H268" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="L268" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="O268" t="s">
         <v>43</v>
@@ -13154,31 +13199,31 @@
     </row>
     <row r="269" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="B269" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="C269" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="D269" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="E269" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="F269" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="G269" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="H269" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="L269" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="O269" t="s">
         <v>43</v>
@@ -13186,25 +13231,25 @@
     </row>
     <row r="270" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="B270" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="C270" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="D270" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="E270" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="G270" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="H270" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="O270" t="s">
         <v>43</v>
@@ -13212,7 +13257,7 @@
     </row>
     <row r="271" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="B271" t="s">
         <v>271</v>
@@ -13221,19 +13266,19 @@
         <v>126</v>
       </c>
       <c r="D271" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="E271" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="G271" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="H271" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="L271" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="O271" t="s">
         <v>43</v>
@@ -13241,28 +13286,28 @@
     </row>
     <row r="272" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="B272" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="C272" t="s">
         <v>126</v>
       </c>
       <c r="D272" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="E272" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="G272" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="H272" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="L272" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="O272" t="s">
         <v>43</v>
@@ -13270,28 +13315,28 @@
     </row>
     <row r="273" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="B273" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="C273" t="s">
         <v>126</v>
       </c>
       <c r="D273" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="E273" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="G273" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="H273" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="L273" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="O273" t="s">
         <v>43</v>
@@ -13299,31 +13344,31 @@
     </row>
     <row r="274" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="B274" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="C274" t="s">
         <v>126</v>
       </c>
       <c r="D274" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="E274" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="F274" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="G274" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="H274" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="L274" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="O274" t="s">
         <v>43</v>
@@ -13331,31 +13376,31 @@
     </row>
     <row r="275" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="B275" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="C275" t="s">
         <v>126</v>
       </c>
       <c r="D275" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="E275" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="F275" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="G275" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="H275" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="L275" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="O275" t="s">
         <v>43</v>
@@ -13363,34 +13408,34 @@
     </row>
     <row r="276" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A276" s="1" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="B276" s="1" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="C276" s="1" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="D276" s="1" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="E276" s="1"/>
       <c r="F276" s="1" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="G276" s="1" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="H276" s="1" t="s">
         <v>336</v>
       </c>
       <c r="I276" s="1" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="J276" s="1"/>
       <c r="K276" s="1"/>
       <c r="L276" s="1" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="M276" s="1" t="s">
         <v>22</v>
@@ -13404,37 +13449,37 @@
     </row>
     <row r="277" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="B277" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="C277" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="D277" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="E277" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="F277" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="G277" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="H277" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="I277" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="J277" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="L277" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="M277" t="s">
         <v>22</v>
@@ -13448,28 +13493,28 @@
     </row>
     <row r="278" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="B278" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="C278" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="D278" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="E278" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="F278" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="G278" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="H278" t="s">
-        <v>1071</v>
+        <v>805</v>
       </c>
       <c r="I278" s="1" t="s">
         <v>1072</v>
@@ -13492,13 +13537,13 @@
     </row>
     <row r="279" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="B279" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="C279" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="D279" t="s">
         <v>1075</v>
@@ -13513,90 +13558,102 @@
         <v>1078</v>
       </c>
       <c r="H279" t="s">
-        <v>336</v>
+        <v>805</v>
+      </c>
+      <c r="I279" s="1" t="s">
+        <v>1079</v>
+      </c>
+      <c r="J279" s="1" t="s">
+        <v>1080</v>
       </c>
       <c r="L279" t="s">
-        <v>1079</v>
+        <v>1081</v>
       </c>
       <c r="M279" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="N279" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="O279" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
     </row>
     <row r="280" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="B280" t="s">
-        <v>1081</v>
+        <v>1083</v>
       </c>
       <c r="C280" t="s">
         <v>641</v>
       </c>
       <c r="D280" t="s">
-        <v>1082</v>
+        <v>1084</v>
       </c>
       <c r="E280" t="s">
-        <v>1083</v>
+        <v>1085</v>
       </c>
       <c r="F280" t="s">
-        <v>1084</v>
+        <v>1086</v>
       </c>
       <c r="G280" t="s">
-        <v>1085</v>
+        <v>1087</v>
       </c>
       <c r="H280" t="s">
-        <v>336</v>
+        <v>805</v>
+      </c>
+      <c r="I280" s="1" t="s">
+        <v>1088</v>
+      </c>
+      <c r="J280" s="1" t="s">
+        <v>1089</v>
       </c>
       <c r="L280" t="s">
-        <v>1086</v>
+        <v>1090</v>
       </c>
       <c r="M280" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="N280" t="s">
-        <v>22</v>
+        <v>1091</v>
       </c>
       <c r="O280" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
     </row>
     <row r="281" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>1087</v>
+        <v>1092</v>
       </c>
       <c r="B281" t="s">
-        <v>1088</v>
+        <v>1093</v>
       </c>
       <c r="C281" t="s">
-        <v>1089</v>
+        <v>1094</v>
       </c>
       <c r="D281" t="s">
-        <v>1090</v>
+        <v>1095</v>
       </c>
       <c r="E281" t="s">
-        <v>1091</v>
+        <v>1096</v>
       </c>
       <c r="F281" t="s">
-        <v>1092</v>
+        <v>1097</v>
       </c>
       <c r="G281" t="s">
-        <v>1093</v>
+        <v>1098</v>
       </c>
       <c r="H281" t="s">
-        <v>1071</v>
+        <v>805</v>
       </c>
       <c r="I281" s="1" t="s">
-        <v>1094</v>
+        <v>1099</v>
       </c>
       <c r="J281" s="1"/>
       <c r="L281" t="s">
-        <v>1095</v>
+        <v>1100</v>
       </c>
       <c r="M281" t="s">
         <v>69</v>
@@ -13610,45 +13667,51 @@
     </row>
     <row r="282" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="B282" t="s">
         <v>660</v>
       </c>
       <c r="C282" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="D282" t="s">
-        <v>1096</v>
+        <v>1101</v>
       </c>
       <c r="E282" t="s">
         <v>1076</v>
       </c>
       <c r="F282" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="G282" t="s">
-        <v>1097</v>
+        <v>1102</v>
       </c>
       <c r="H282" t="s">
-        <v>336</v>
+        <v>805</v>
+      </c>
+      <c r="I282" s="1" t="s">
+        <v>1103</v>
+      </c>
+      <c r="J282" s="1" t="s">
+        <v>1104</v>
       </c>
       <c r="L282" t="s">
-        <v>1098</v>
+        <v>1105</v>
       </c>
       <c r="M282" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="N282" t="s">
-        <v>22</v>
+        <v>1091</v>
       </c>
       <c r="O282" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
     </row>
     <row r="283" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>1099</v>
+        <v>1106</v>
       </c>
       <c r="B283" t="s">
         <v>427</v>
@@ -13657,69 +13720,79 @@
         <v>641</v>
       </c>
       <c r="D283" t="s">
-        <v>1100</v>
+        <v>1107</v>
       </c>
       <c r="E283" t="s">
         <v>1076</v>
       </c>
       <c r="F283" t="s">
-        <v>1101</v>
+        <v>1108</v>
       </c>
       <c r="G283" t="s">
-        <v>1102</v>
+        <v>1109</v>
       </c>
       <c r="H283" t="s">
-        <v>336</v>
+        <v>805</v>
+      </c>
+      <c r="I283" s="1" t="s">
+        <v>1110</v>
+      </c>
+      <c r="J283" s="1" t="s">
+        <v>1111</v>
       </c>
       <c r="L283" t="s">
-        <v>1103</v>
+        <v>1112</v>
       </c>
       <c r="M283" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="N283" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="O283" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
     </row>
     <row r="284" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="B284" t="s">
         <v>427</v>
       </c>
       <c r="C284" t="s">
-        <v>1089</v>
+        <v>1094</v>
       </c>
       <c r="D284" t="s">
-        <v>1104</v>
+        <v>1113</v>
       </c>
       <c r="E284" t="s">
         <v>1076</v>
       </c>
       <c r="F284" t="s">
-        <v>1105</v>
+        <v>1114</v>
       </c>
       <c r="G284" t="s">
-        <v>1106</v>
+        <v>1115</v>
       </c>
       <c r="H284" t="s">
-        <v>336</v>
-      </c>
+        <v>805</v>
+      </c>
+      <c r="I284" s="1" t="s">
+        <v>1116</v>
+      </c>
+      <c r="J284" s="1"/>
       <c r="L284" t="s">
-        <v>1107</v>
+        <v>1117</v>
       </c>
       <c r="M284" t="s">
-        <v>22</v>
+        <v>69</v>
       </c>
       <c r="N284" t="s">
-        <v>22</v>
+        <v>1091</v>
       </c>
       <c r="O284" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
     </row>
     <row r="285" spans="1:15" x14ac:dyDescent="0.25">
@@ -13733,28 +13806,28 @@
         <v>641</v>
       </c>
       <c r="D285" t="s">
-        <v>1108</v>
+        <v>1118</v>
       </c>
       <c r="E285" t="s">
         <v>1076</v>
       </c>
       <c r="F285" t="s">
-        <v>1109</v>
+        <v>1119</v>
       </c>
       <c r="G285" t="s">
-        <v>1110</v>
+        <v>1120</v>
       </c>
       <c r="H285" t="s">
-        <v>1071</v>
+        <v>805</v>
       </c>
       <c r="I285" s="1" t="s">
-        <v>1111</v>
+        <v>1121</v>
       </c>
       <c r="J285" s="1" t="s">
-        <v>1112</v>
+        <v>1122</v>
       </c>
       <c r="L285" t="s">
-        <v>1113</v>
+        <v>1123</v>
       </c>
       <c r="M285" t="s">
         <v>30</v>
@@ -13768,78 +13841,90 @@
     </row>
     <row r="286" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="B286" t="s">
-        <v>1114</v>
+        <v>1124</v>
       </c>
       <c r="C286" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="D286" t="s">
-        <v>1115</v>
+        <v>1125</v>
       </c>
       <c r="E286" t="s">
         <v>1076</v>
       </c>
       <c r="F286" t="s">
-        <v>1084</v>
+        <v>1086</v>
       </c>
       <c r="G286" t="s">
-        <v>1116</v>
+        <v>1126</v>
       </c>
       <c r="H286" t="s">
-        <v>336</v>
+        <v>805</v>
+      </c>
+      <c r="I286" s="1" t="s">
+        <v>1127</v>
+      </c>
+      <c r="J286" s="1" t="s">
+        <v>1128</v>
       </c>
       <c r="L286" t="s">
-        <v>1117</v>
+        <v>1129</v>
       </c>
       <c r="M286" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="N286" t="s">
-        <v>22</v>
+        <v>1091</v>
       </c>
       <c r="O286" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
     </row>
     <row r="287" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="B287" t="s">
-        <v>1118</v>
+        <v>1130</v>
       </c>
       <c r="C287" t="s">
         <v>641</v>
       </c>
       <c r="D287" t="s">
-        <v>1119</v>
+        <v>1131</v>
       </c>
       <c r="E287" t="s">
         <v>1076</v>
       </c>
       <c r="F287" t="s">
-        <v>1120</v>
+        <v>1132</v>
       </c>
       <c r="G287" t="s">
-        <v>1121</v>
+        <v>1133</v>
       </c>
       <c r="H287" t="s">
-        <v>336</v>
+        <v>805</v>
+      </c>
+      <c r="I287" s="1" t="s">
+        <v>1134</v>
+      </c>
+      <c r="J287" s="1" t="s">
+        <v>1135</v>
       </c>
       <c r="L287" t="s">
-        <v>1122</v>
+        <v>1136</v>
       </c>
       <c r="M287" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="N287" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="O287" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
     </row>
     <row r="288" spans="1:15" x14ac:dyDescent="0.25">
@@ -13847,34 +13932,34 @@
         <v>398</v>
       </c>
       <c r="B288" t="s">
-        <v>1123</v>
+        <v>1137</v>
       </c>
       <c r="C288" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="D288" t="s">
-        <v>1124</v>
+        <v>1138</v>
       </c>
       <c r="E288" t="s">
         <v>1076</v>
       </c>
       <c r="F288" t="s">
-        <v>1125</v>
+        <v>1139</v>
       </c>
       <c r="G288" t="s">
-        <v>1126</v>
+        <v>1140</v>
       </c>
       <c r="H288" t="s">
-        <v>1071</v>
+        <v>805</v>
       </c>
       <c r="I288" s="1" t="s">
-        <v>1127</v>
+        <v>1141</v>
       </c>
       <c r="J288" s="1" t="s">
-        <v>1128</v>
+        <v>1142</v>
       </c>
       <c r="L288" t="s">
-        <v>1129</v>
+        <v>1143</v>
       </c>
       <c r="M288" t="s">
         <v>30</v>
@@ -13888,32 +13973,32 @@
     </row>
     <row r="289" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>1130</v>
+        <v>1144</v>
       </c>
       <c r="B289" t="s">
-        <v>1131</v>
+        <v>1145</v>
       </c>
       <c r="C289" t="s">
-        <v>1132</v>
+        <v>1146</v>
       </c>
       <c r="D289" t="s">
-        <v>1133</v>
+        <v>1147</v>
       </c>
       <c r="F289" t="s">
         <v>1077</v>
       </c>
       <c r="G289" t="s">
-        <v>1134</v>
+        <v>1148</v>
       </c>
       <c r="H289" t="s">
-        <v>1071</v>
+        <v>805</v>
       </c>
       <c r="I289" s="1" t="s">
-        <v>1135</v>
+        <v>1149</v>
       </c>
       <c r="J289" s="1"/>
       <c r="L289" t="s">
-        <v>1136</v>
+        <v>1150</v>
       </c>
       <c r="M289" t="s">
         <v>69</v>
@@ -13927,32 +14012,32 @@
     </row>
     <row r="290" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>1137</v>
+        <v>1151</v>
       </c>
       <c r="B290" t="s">
-        <v>1138</v>
+        <v>1152</v>
       </c>
       <c r="C290" t="s">
-        <v>1139</v>
+        <v>1153</v>
       </c>
       <c r="D290" t="s">
-        <v>1140</v>
+        <v>1154</v>
       </c>
       <c r="F290" t="s">
-        <v>1141</v>
+        <v>1155</v>
       </c>
       <c r="G290" t="s">
-        <v>1142</v>
+        <v>1156</v>
       </c>
       <c r="H290" t="s">
-        <v>1071</v>
+        <v>805</v>
       </c>
       <c r="I290" s="1" t="s">
-        <v>1143</v>
+        <v>1157</v>
       </c>
       <c r="J290" s="1"/>
       <c r="L290" t="s">
-        <v>1144</v>
+        <v>1158</v>
       </c>
       <c r="M290" t="s">
         <v>69</v>
@@ -13966,37 +14051,41 @@
     </row>
     <row r="291" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>1145</v>
+        <v>1159</v>
       </c>
       <c r="B291" t="s">
-        <v>1146</v>
+        <v>1160</v>
       </c>
       <c r="C291" t="s">
-        <v>1147</v>
+        <v>1161</v>
       </c>
       <c r="D291" t="s">
-        <v>1148</v>
+        <v>1162</v>
       </c>
       <c r="F291" t="s">
-        <v>1149</v>
+        <v>1163</v>
       </c>
       <c r="G291" t="s">
-        <v>1150</v>
+        <v>1164</v>
       </c>
       <c r="H291" t="s">
-        <v>336</v>
-      </c>
+        <v>805</v>
+      </c>
+      <c r="I291" s="1" t="s">
+        <v>1165</v>
+      </c>
+      <c r="J291" s="1"/>
       <c r="L291" t="s">
-        <v>1151</v>
+        <v>1166</v>
       </c>
       <c r="M291" t="s">
-        <v>22</v>
+        <v>69</v>
       </c>
       <c r="N291" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="O291" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>

--- a/tracker.xlsx
+++ b/tracker.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2690" uniqueCount="1167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2707" uniqueCount="1173">
   <si>
     <t>Company</t>
   </si>
@@ -1027,214 +1027,223 @@
     <t>[B] SF/Palo Alto/Seattle/Remote US.</t>
   </si>
   <si>
+    <t>ready to apply</t>
+  </si>
+  <si>
+    <t>resume-pinterest-machine-learning-engineer-core-engineering.pdf</t>
+  </si>
+  <si>
+    <t>cover-letter-pinterest-machine-learning-engineer-core-engineering.pdf</t>
+  </si>
+  <si>
+    <t>Source: Greenhouse/Lever Audit 2026-10-27: posting live; resume rebuilt black-and-white; form asks current employer + last university (short). Ready to apply — materials complete, 2026-10-27.</t>
+  </si>
+  <si>
+    <t>Machine Learning Engineer II, Responsible AI</t>
+  </si>
+  <si>
+    <t>San Francisco, CA, US; Remote, US</t>
+  </si>
+  <si>
+    <t>https://www.pinterestcareers.com/jobs/?gh_jid=8162046</t>
+  </si>
+  <si>
+    <t>[B] SF/Remote US.</t>
+  </si>
+  <si>
+    <t>resume-pinterest-machine-learning-engineer-ii-responsible-ai.pdf</t>
+  </si>
+  <si>
+    <t>cover-letter-pinterest-machine-learning-engineer-ii-responsible-ai.pdf</t>
+  </si>
+  <si>
+    <t>Stretch: no responsible-AI team experience; Source: Greenhouse/Lever Audit 2026-10-27: posting live; resume rebuilt black-and-white; form asks current employer (short). Ready to apply — materials complete, 2026-10-27.</t>
+  </si>
+  <si>
+    <t>Machine Learning Engineer II, Visual AI</t>
+  </si>
+  <si>
+    <t>https://www.pinterestcareers.com/jobs/?gh_jid=7697137</t>
+  </si>
+  <si>
+    <t>resume-pinterest-machine-learning-engineer-ii-visual-ai.pdf</t>
+  </si>
+  <si>
+    <t>cover-letter-pinterest-machine-learning-engineer-ii-visual-ai.pdf</t>
+  </si>
+  <si>
+    <t>Source: Greenhouse/Lever Audit 2026-10-27: posting live; resume rebuilt black-and-white; form asks current employer (short). Ready to apply — materials complete, 2026-10-27.</t>
+  </si>
+  <si>
+    <t>Machine Learning Engineer, Monetization Engineering</t>
+  </si>
+  <si>
+    <t>https://www.pinterestcareers.com/jobs/?gh_jid=6121543</t>
+  </si>
+  <si>
+    <t>[B] SF/Palo Alto/Seattle.</t>
+  </si>
+  <si>
+    <t>Principal Engineer, Big Data Platform</t>
+  </si>
+  <si>
+    <t>https://www.pinterestcareers.com/jobs/?gh_jid=7683981</t>
+  </si>
+  <si>
+    <t>Skipped: Level too senior (Principal/Staff+); Source: Greenhouse/Lever</t>
+  </si>
+  <si>
+    <t>Principal Machine Learning Engineer, Ads Delivery</t>
+  </si>
+  <si>
+    <t>https://www.pinterestcareers.com/jobs/?gh_jid=6963868</t>
+  </si>
+  <si>
+    <t>[C] SF/Palo Alto/Seattle.</t>
+  </si>
+  <si>
+    <t>Site Reliability Engineer II, tvScientific</t>
+  </si>
+  <si>
+    <t>https://www.pinterestcareers.com/jobs/?gh_jid=7782538</t>
+  </si>
+  <si>
+    <t>Skipped: SRE depth not on resume; Remote (US); Source: Greenhouse/Lever</t>
+  </si>
+  <si>
+    <t>Sr. Data Scientist, Core</t>
+  </si>
+  <si>
+    <t>https://www.pinterestcareers.com/jobs/?gh_jid=6087213</t>
+  </si>
+  <si>
+    <t>Sr. Data Scientist, Infrastructure</t>
+  </si>
+  <si>
+    <t>https://www.pinterestcareers.com/jobs/?gh_jid=8024966</t>
+  </si>
+  <si>
+    <t>Sr. Data Scientist, Marketing</t>
+  </si>
+  <si>
+    <t>https://www.pinterestcareers.com/jobs/?gh_jid=8011376</t>
+  </si>
+  <si>
+    <t>Sr. Data Scientist, Monetization</t>
+  </si>
+  <si>
+    <t>https://www.pinterestcareers.com/jobs/?gh_jid=5740948</t>
+  </si>
+  <si>
+    <t>[C] SF/Seattle.</t>
+  </si>
+  <si>
+    <t>Sr. Data Scientist, tvScientific</t>
+  </si>
+  <si>
+    <t>https://www.pinterestcareers.com/jobs/?gh_jid=7642251</t>
+  </si>
+  <si>
+    <t>Sr. Machine Learning Engineer, Applied Science</t>
+  </si>
+  <si>
+    <t>https://www.pinterestcareers.com/jobs/?gh_jid=6894747</t>
+  </si>
+  <si>
+    <t>Skipped: 5+ yrs computer vision; Remote (US); Source: Greenhouse/Lever</t>
+  </si>
+  <si>
+    <t>Sr. Machine Learning Engineer, Core Engineering</t>
+  </si>
+  <si>
+    <t>San Francisco, CA, US; Palo Alto, CA, US; Seattle, WA, US</t>
+  </si>
+  <si>
+    <t>https://www.pinterestcareers.com/jobs/?gh_jid=6121464</t>
+  </si>
+  <si>
+    <t>resume-pinterest-sr-machine-learning-engineer-core-engineering.pdf</t>
+  </si>
+  <si>
+    <t>cover-letter-pinterest-sr-machine-learning-engineer-core-engineering.pdf</t>
+  </si>
+  <si>
+    <t>Sr. Machine Learning Engineer, Monetization Engineering</t>
+  </si>
+  <si>
+    <t>https://www.pinterestcareers.com/jobs/?gh_jid=6121551</t>
+  </si>
+  <si>
+    <t>Sr. Site Reliability Engineer, tvScientific</t>
+  </si>
+  <si>
+    <t>https://www.pinterestcareers.com/jobs/?gh_jid=7782550</t>
+  </si>
+  <si>
+    <t>Skipped: SRE depth not on resume; Source: Greenhouse/Lever</t>
+  </si>
+  <si>
+    <t>Staff Data Scientist, Ads Delivery</t>
+  </si>
+  <si>
+    <t>https://www.pinterestcareers.com/jobs/?gh_jid=8026607</t>
+  </si>
+  <si>
+    <t>Staff Data Scientist, Ads Product</t>
+  </si>
+  <si>
+    <t>https://www.pinterestcareers.com/jobs/?gh_jid=7963755</t>
+  </si>
+  <si>
+    <t>Staff Data Scientist, Forecasting</t>
+  </si>
+  <si>
+    <t>https://www.pinterestcareers.com/jobs/?gh_jid=8001932</t>
+  </si>
+  <si>
+    <t>Staff Data Scientist, Notifications</t>
+  </si>
+  <si>
+    <t>https://www.pinterestcareers.com/jobs/?gh_jid=8095343</t>
+  </si>
+  <si>
+    <t>Staff Machine Learning Engineer, Ads Conversion Core Modeling</t>
+  </si>
+  <si>
+    <t>https://www.pinterestcareers.com/jobs/?gh_jid=8011452</t>
+  </si>
+  <si>
+    <t>Staff Machine Learning Engineer, Shopping Ads</t>
+  </si>
+  <si>
+    <t>https://www.pinterestcareers.com/jobs/?gh_jid=8049465</t>
+  </si>
+  <si>
+    <t>Reddit</t>
+  </si>
+  <si>
+    <t>Backend Engineer, IAM</t>
+  </si>
+  <si>
+    <t>Remote - United States</t>
+  </si>
+  <si>
+    <t>https://job-boards.greenhouse.io/reddit/jobs/8189317</t>
+  </si>
+  <si>
+    <t>[B] Remote - US.</t>
+  </si>
+  <si>
     <t>tailoring</t>
   </si>
   <si>
-    <t>resume-pinterest-machine-learning-engineer-core-engineering.pdf</t>
-  </si>
-  <si>
-    <t>cover-letter-pinterest-machine-learning-engineer-core-engineering.pdf</t>
-  </si>
-  <si>
-    <t>Machine Learning Engineer II, Responsible AI</t>
-  </si>
-  <si>
-    <t>San Francisco, CA, US; Remote, US</t>
-  </si>
-  <si>
-    <t>https://www.pinterestcareers.com/jobs/?gh_jid=8162046</t>
-  </si>
-  <si>
-    <t>[B] SF/Remote US.</t>
-  </si>
-  <si>
-    <t>resume-pinterest-machine-learning-engineer-ii-responsible-ai.pdf</t>
-  </si>
-  <si>
-    <t>cover-letter-pinterest-machine-learning-engineer-ii-responsible-ai.pdf</t>
-  </si>
-  <si>
-    <t>Stretch: no responsible-AI team experience; Source: Greenhouse/Lever</t>
-  </si>
-  <si>
-    <t>Machine Learning Engineer II, Visual AI</t>
-  </si>
-  <si>
-    <t>https://www.pinterestcareers.com/jobs/?gh_jid=7697137</t>
-  </si>
-  <si>
-    <t>resume-pinterest-machine-learning-engineer-ii-visual-ai.pdf</t>
-  </si>
-  <si>
-    <t>cover-letter-pinterest-machine-learning-engineer-ii-visual-ai.pdf</t>
-  </si>
-  <si>
-    <t>Machine Learning Engineer, Monetization Engineering</t>
-  </si>
-  <si>
-    <t>https://www.pinterestcareers.com/jobs/?gh_jid=6121543</t>
-  </si>
-  <si>
-    <t>[B] SF/Palo Alto/Seattle.</t>
-  </si>
-  <si>
-    <t>Principal Engineer, Big Data Platform</t>
-  </si>
-  <si>
-    <t>https://www.pinterestcareers.com/jobs/?gh_jid=7683981</t>
-  </si>
-  <si>
-    <t>Skipped: Level too senior (Principal/Staff+); Source: Greenhouse/Lever</t>
-  </si>
-  <si>
-    <t>Principal Machine Learning Engineer, Ads Delivery</t>
-  </si>
-  <si>
-    <t>https://www.pinterestcareers.com/jobs/?gh_jid=6963868</t>
-  </si>
-  <si>
-    <t>[C] SF/Palo Alto/Seattle.</t>
-  </si>
-  <si>
-    <t>Site Reliability Engineer II, tvScientific</t>
-  </si>
-  <si>
-    <t>https://www.pinterestcareers.com/jobs/?gh_jid=7782538</t>
-  </si>
-  <si>
-    <t>Skipped: SRE depth not on resume; Remote (US); Source: Greenhouse/Lever</t>
-  </si>
-  <si>
-    <t>Sr. Data Scientist, Core</t>
-  </si>
-  <si>
-    <t>https://www.pinterestcareers.com/jobs/?gh_jid=6087213</t>
-  </si>
-  <si>
-    <t>Sr. Data Scientist, Infrastructure</t>
-  </si>
-  <si>
-    <t>https://www.pinterestcareers.com/jobs/?gh_jid=8024966</t>
-  </si>
-  <si>
-    <t>Sr. Data Scientist, Marketing</t>
-  </si>
-  <si>
-    <t>https://www.pinterestcareers.com/jobs/?gh_jid=8011376</t>
-  </si>
-  <si>
-    <t>Sr. Data Scientist, Monetization</t>
-  </si>
-  <si>
-    <t>https://www.pinterestcareers.com/jobs/?gh_jid=5740948</t>
-  </si>
-  <si>
-    <t>[C] SF/Seattle.</t>
-  </si>
-  <si>
-    <t>Sr. Data Scientist, tvScientific</t>
-  </si>
-  <si>
-    <t>https://www.pinterestcareers.com/jobs/?gh_jid=7642251</t>
-  </si>
-  <si>
-    <t>Sr. Machine Learning Engineer, Applied Science</t>
-  </si>
-  <si>
-    <t>https://www.pinterestcareers.com/jobs/?gh_jid=6894747</t>
-  </si>
-  <si>
-    <t>Skipped: 5+ yrs computer vision; Remote (US); Source: Greenhouse/Lever</t>
-  </si>
-  <si>
-    <t>Sr. Machine Learning Engineer, Core Engineering</t>
-  </si>
-  <si>
-    <t>San Francisco, CA, US; Palo Alto, CA, US; Seattle, WA, US</t>
-  </si>
-  <si>
-    <t>https://www.pinterestcareers.com/jobs/?gh_jid=6121464</t>
-  </si>
-  <si>
-    <t>resume-pinterest-sr-machine-learning-engineer-core-engineering.pdf</t>
-  </si>
-  <si>
-    <t>cover-letter-pinterest-sr-machine-learning-engineer-core-engineering.pdf</t>
-  </si>
-  <si>
-    <t>Sr. Machine Learning Engineer, Monetization Engineering</t>
-  </si>
-  <si>
-    <t>https://www.pinterestcareers.com/jobs/?gh_jid=6121551</t>
-  </si>
-  <si>
-    <t>Sr. Site Reliability Engineer, tvScientific</t>
-  </si>
-  <si>
-    <t>https://www.pinterestcareers.com/jobs/?gh_jid=7782550</t>
-  </si>
-  <si>
-    <t>Skipped: SRE depth not on resume; Source: Greenhouse/Lever</t>
-  </si>
-  <si>
-    <t>Staff Data Scientist, Ads Delivery</t>
-  </si>
-  <si>
-    <t>https://www.pinterestcareers.com/jobs/?gh_jid=8026607</t>
-  </si>
-  <si>
-    <t>Staff Data Scientist, Ads Product</t>
-  </si>
-  <si>
-    <t>https://www.pinterestcareers.com/jobs/?gh_jid=7963755</t>
-  </si>
-  <si>
-    <t>Staff Data Scientist, Forecasting</t>
-  </si>
-  <si>
-    <t>https://www.pinterestcareers.com/jobs/?gh_jid=8001932</t>
-  </si>
-  <si>
-    <t>Staff Data Scientist, Notifications</t>
-  </si>
-  <si>
-    <t>https://www.pinterestcareers.com/jobs/?gh_jid=8095343</t>
-  </si>
-  <si>
-    <t>Staff Machine Learning Engineer, Ads Conversion Core Modeling</t>
-  </si>
-  <si>
-    <t>https://www.pinterestcareers.com/jobs/?gh_jid=8011452</t>
-  </si>
-  <si>
-    <t>Staff Machine Learning Engineer, Shopping Ads</t>
-  </si>
-  <si>
-    <t>https://www.pinterestcareers.com/jobs/?gh_jid=8049465</t>
-  </si>
-  <si>
-    <t>Reddit</t>
-  </si>
-  <si>
-    <t>Backend Engineer, IAM</t>
-  </si>
-  <si>
-    <t>Remote - United States</t>
-  </si>
-  <si>
-    <t>https://job-boards.greenhouse.io/reddit/jobs/8189317</t>
-  </si>
-  <si>
-    <t>[B] Remote - US.</t>
-  </si>
-  <si>
     <t>resume-reddit-backend-engineer-iam.pdf</t>
   </si>
   <si>
     <t>cover-letter-reddit-backend-engineer-iam.pdf</t>
   </si>
   <si>
-    <t>Good-ish: scoped-token gateway; no IAM-at-scale; Source: Greenhouse/Lever</t>
+    <t>Good-ish: scoped-token gateway; no IAM-at-scale; Source: Greenhouse/Lever Audit 2026-10-27: posting CLOSED (Greenhouse job not found; board redirects with error). Not marked ready. Resume rebuilt black-and-white in case it reopens.</t>
   </si>
   <si>
     <t>Principal Data Scientist, Ads</t>
@@ -1255,7 +1264,7 @@
     <t>cover-letter-reddit-senior-backend-engineer-compliance-engineering.pdf</t>
   </si>
   <si>
-    <t>Remote (US); Stretch: short of years listed; Source: Greenhouse/Lever</t>
+    <t>Remote (US); Stretch: short of years listed; Source: Greenhouse/Lever Audit 2026-10-27: posting live; resume rebuilt black-and-white; form asks current/most recent company. Ready to apply — materials complete, 2026-10-27.</t>
   </si>
   <si>
     <t>Senior Backend Engineer, IAM</t>
@@ -1282,6 +1291,9 @@
     <t>cover-letter-reddit-senior-backend-engineer-safety.pdf</t>
   </si>
   <si>
+    <t>Source: Greenhouse/Lever Audit 2026-10-27: posting CLOSED (Greenhouse job not found; board redirects with error). Not marked ready. Resume rebuilt black-and-white in case it reopens.</t>
+  </si>
+  <si>
     <t>Senior Data Scientist, Ads</t>
   </si>
   <si>
@@ -1312,6 +1324,9 @@
     <t>cover-letter-reddit-senior-machine-learning-engineer.pdf</t>
   </si>
   <si>
+    <t>Source: Greenhouse/Lever Audit 2026-10-27: posting live; resume rebuilt black-and-white; form asks current/most recent company. Ready to apply — materials complete, 2026-10-27.</t>
+  </si>
+  <si>
     <t>Senior Machine Learning Engineer, Ads Optimization</t>
   </si>
   <si>
@@ -1747,7 +1762,7 @@
     <t>cover-letter-zscaler-ai-devops-engineer.pdf</t>
   </si>
   <si>
-    <t>Stretch: 5+ yrs multi-cloud infra; Source: Greenhouse/Lever</t>
+    <t>Stretch: 5+ yrs multi-cloud infra; Source: Greenhouse/Lever Audit 2026-10-27: posting live; resume rebuilt black-and-white. Form has required Yes/No screens incl. '5+ years multi-cloud infrastructure at scale' and 'hands-on Terraform module design/state' (answer truthfully, likely No), plus home address, current company/title. Ready to apply — materials complete, 2026-10-27.</t>
   </si>
   <si>
     <t>Senior Software Architect, Platform Engineering</t>
@@ -1852,7 +1867,7 @@
     <t>cover-letter-airbnb-senior-machine-learning-engineer-trust-genai.pdf</t>
   </si>
   <si>
-    <t>Stretch: wants 5-10 yrs applied ML; SF; Source: Greenhouse/Lever</t>
+    <t>Stretch: wants 5-10 yrs applied ML; SF; Source: Greenhouse/Lever Audit 2026-10-27: posting live; resume rebuilt black-and-white; form has non-compete + prior-Airbnb Yes/No. Ready to apply — materials complete, 2026-10-27.</t>
   </si>
   <si>
     <t>https://careers.airbnb.com/positions/8232153?gh_jid=8232153</t>
@@ -1954,6 +1969,9 @@
     <t>cover-letter-samsara-ai-engineer-customer-success.pdf</t>
   </si>
   <si>
+    <t>Source: Greenhouse/Lever Audit 2026-10-27: posting live; resume rebuilt black-and-white; form asks zip code, most recent employer, AI-policy acknowledgment. Ready to apply — materials complete, 2026-10-27.</t>
+  </si>
+  <si>
     <t>https://www.samsara.com/company/careers/roles/7859702?gh_jid=7859702</t>
   </si>
   <si>
@@ -1963,7 +1981,7 @@
     <t>cover-letter-samsara-data-engineer.pdf</t>
   </si>
   <si>
-    <t>Stretch: wants 4+ yrs data engineering; Source: Greenhouse/Lever</t>
+    <t>Stretch: wants 4+ yrs data engineering; Source: Greenhouse/Lever Audit 2026-10-27: posting CLOSED (Greenhouse job not found). Not marked ready. Possible repost: Samsara 'Data Engineer' Remote - US, Greenhouse job 8141959; Muse to verify and add as a new row if wanted.</t>
   </si>
   <si>
     <t>Finance &amp; Strategy AI Engineer</t>
@@ -2026,7 +2044,7 @@
     <t>cover-letter-samsara-senior-machine-learning-engineer.pdf</t>
   </si>
   <si>
-    <t>Stretch: wants 6+ yrs ML; Source: Greenhouse/Lever</t>
+    <t>Stretch: wants 6+ yrs ML; Source: Greenhouse/Lever Audit 2026-10-27: posting live; resume rebuilt black-and-white; form asks zip, employer, relocation, and 'Do you accept the listed salary range?' (Jack to answer). Ready to apply — materials complete, 2026-10-27.</t>
   </si>
   <si>
     <t>https://www.samsara.com/company/careers/roles/7922530?gh_jid=7922530</t>
@@ -2038,6 +2056,9 @@
     <t>cover-letter-samsara-software-engineer-data-platform.pdf</t>
   </si>
   <si>
+    <t>Source: Greenhouse/Lever Audit 2026-10-27: posting live; resume rebuilt black-and-white; form asks years in a data software engineering role (select), US residence, and 'Do you accept the listed salary range?' (Jack to answer). Ready to apply — materials complete, 2026-10-27.</t>
+  </si>
+  <si>
     <t>Staff Machine Learning Engineer - Edge AI</t>
   </si>
   <si>
@@ -2434,9 +2455,6 @@
     <t>Forward-deployed role: customer-facing builds, Python/Node/React, LLM/agent nice-to-have, AWS nice-to-have. Referral via friend.</t>
   </si>
   <si>
-    <t>ready to apply</t>
-  </si>
-  <si>
     <t>resume-narmi-software-engineer-forward-deployed.pdf</t>
   </si>
   <si>
@@ -2464,7 +2482,7 @@
     <t>cover-letter-srs-acquiom-senior-data-engineer.pdf</t>
   </si>
   <si>
-    <t>Stretch: 6+ yrs SQL/Postgres; no Kafka/Glue/Terraform. Form has a "which core value resonates" question</t>
+    <t>Stretch: 6+ yrs SQL/Postgres; no Kafka/Glue/Terraform. Form has a "which core value resonates" question Audit 2026-10-27: posting CLOSED (Greenhouse job not found; board redirects with error). Not marked ready.</t>
   </si>
   <si>
     <t>SERHANT.</t>
@@ -2536,7 +2554,10 @@
     <t>cover-letter-cresta-senior-infrastructure-engineer-sre.pdf</t>
   </si>
   <si>
-    <t>Stretch: 5+ yrs DevOps/SRE; multi-cloud Terraform</t>
+    <t>Stretch: 5+ yrs DevOps/SRE; multi-cloud Terraform Audit 2026-10-27: posting live; resume rebuilt black-and-white; Greenhouse form has optional cover letter and no custom questions (Effort re-triaged Medium -&gt; Low). Ready to apply — materials complete, 2026-10-27.</t>
+  </si>
+  <si>
+    <t>None</t>
   </si>
   <si>
     <t>Render</t>
@@ -2572,7 +2593,7 @@
     <t>cover-letter-cortex-senior-data-engineer.pdf</t>
   </si>
   <si>
-    <t>Stretch: no dbt/BigQuery. Form asks "tell us about a data pipeline you built" (Ralli ESPN ETL) and years as a DE</t>
+    <t>Stretch: no dbt/BigQuery. Form asks "tell us about a data pipeline you built" (Ralli ESPN ETL) and years as a DE Audit 2026-10-27: posting live; resume rebuilt black-and-white. Greenhouse form: optional cover letter; required long answers (years as a DE, a pipeline you built and owned, cleaning up a messy data setup, dbt/BigQuery/Segment use), so Jack writes those. Ready to apply — materials complete, 2026-10-27.</t>
   </si>
   <si>
     <t>Webflow</t>
@@ -2632,7 +2653,7 @@
     <t>cover-letter-cricut-ai-engineering-lead-manager.pdf</t>
   </si>
   <si>
-    <t>Added by Jack via LinkedIn. Stretch: no AI image generation or MCP in production; has led teams as CTO, not formal manager. Source: LinkedIn</t>
+    <t>Added by Jack via LinkedIn. Stretch: no AI image generation or MCP in production; has led teams as CTO, not formal manager. Source: LinkedIn Audit 2026-10-27: resume rebuilt black-and-white; cover letter on file. Real ATS not found (LinkedIn-only link; no Greenhouse/Ashby/Workday board found), so form fields are Unknown; check at apply time. Ready to apply — materials complete, 2026-10-27.</t>
   </si>
   <si>
     <t>Taulia</t>
@@ -2656,7 +2677,7 @@
     <t>cover-letter-taulia-ai-data-engineer.pdf</t>
   </si>
   <si>
-    <t>Strong-ish fit: RAG/vector/embeddings + ETL + REST. URL is an aggregator (obtainjob): find the real Taulia careers/apply page. No SAP/enterprise warehouse experience</t>
+    <t>Strong-ish fit: RAG/vector/embeddings + ETL + REST. URL is an aggregator (obtainjob): find the real Taulia careers/apply page. No SAP/enterprise warehouse experience Verified 2026-10-27: SuccessFactors confirmation email 'Your Application for the Position AI Data Engineer' from Taulia Talent Team received 2026-10-06. Do not resubmit.</t>
   </si>
   <si>
     <t>Yes</t>
@@ -2764,7 +2785,7 @@
     <t>cover-letter-foley-senior-data-engineer.pdf</t>
   </si>
   <si>
-    <t>Stretch: wants Redshift/Glue/EventBridge, CDC/streaming. Real posting is on Ashby: https://jobs.ashbyhq.com/foley/d292fa96-260a-4e03-9e39-853d085ff134 (remote US, EST hours, $140-180K) BLOCKED 2026-10-05: form filled but NOT submitted — Ashby asks to confirm residence in one of 25 listed states (AZ CA CO CT FL GA IL IN KS MA MD MI MO NE NH NJ NY NC PA RI SC TN TX VA WI); UT not eligible, truthful answer is No. Awaiting Jack's call. Jack's call 2026-10-05: leave UNsubmitted (UT not an eligible state; truthful 'No' would be screened out).</t>
+    <t>Stretch: wants Redshift/Glue/EventBridge, CDC/streaming. Real posting is on Ashby: https://jobs.ashbyhq.com/foley/d292fa96-260a-4e03-9e39-853d085ff134 (remote US, EST hours, $140-180K) BLOCKED 2026-10-05: form filled but NOT submitted — Ashby asks to confirm residence in one of 25 listed states (AZ CA CO CT FL GA IL IN KS MA MD MI MO NE NH NJ NY NC PA RI SC TN TX VA WI); UT not eligible, truthful answer is No. Awaiting Jack's call. Jack's call 2026-10-05: leave UNsubmitted (UT not an eligible state; truthful 'No' would be screened out). Audit 2026-10-27: still NOT ready and must not be submitted (UT is not an eligible state, per Jack's 2026-10-05 call). Status left as is.</t>
   </si>
   <si>
     <t>Recharge</t>
@@ -3178,7 +3199,7 @@
     <t>resume-neumont-computer-science-adjunct.pdf</t>
   </si>
   <si>
-    <t>Apply manually: text ADJUNCT to the number on the GrabJobs page, or email resume to info@neumont.edu (888-638-6668). Subject list: https://www.talent.com/view?id=8d7c247922d2. Next intake January (courses from 2026-01-05). Interview includes a short teaching demo. Muse: do not submit (no web form).</t>
+    <t>Apply manually: text ADJUNCT to the number on the GrabJobs page, or email resume to info@neumont.edu (888-638-6668). Subject list: https://www.talent.com/view?id=8d7c247922d2. Next intake January (courses from 2026-01-05). Interview includes a short teaching demo. Muse: do not submit (no web form). Audit 2026-10-27: resume verified final (black-and-white print, Turbin3 teaching section, commit 7e392e2). No cover letter on file. Manual apply only (email/text); deliberately NOT marked ready to apply so Muse does not auto-apply.</t>
   </si>
   <si>
     <t>EY</t>
@@ -3292,9 +3313,6 @@
     <t>Expanded lane: Backend/Full-stack. Still live on Greenhouse board 2026-10-26; BuiltIn listed 2026-05-11. Greenhouse form checked 2026-10-27: optional cover letter, no custom questions. Ready to apply — materials complete, 2026-10-27.</t>
   </si>
   <si>
-    <t>None</t>
-  </si>
-  <si>
     <t>Coder</t>
   </si>
   <si>
@@ -3427,7 +3445,7 @@
     <t>cover-letter-healthie-senior-solutions-engineer.pdf</t>
   </si>
   <si>
-    <t>Expanded lane: Solutions/FDE. Posted date not shown on Greenhouse page; verified live 2026-10-26. Greenhouse form checked 2026-10-27: optional cover letter. FLAG: required text 'confirm you have a minimum of 4 years of experience with RoR and React'. Jack has React but no Rails, so Jack must answer this himself; likely a screen-out. Ready to apply — materials complete, 2026-10-27.</t>
+    <t>Expanded lane: Solutions/FDE. Posted date not shown on Greenhouse page; verified live 2026-10-26. Greenhouse form checked 2026-10-27: optional cover letter. FLAG: required text 'confirm you have a minimum of 4 years of experience with RoR and React'. Jack has React but no Rails, so Jack must answer it personally; likely a screen-out. Ready to apply — materials complete, 2026-10-27.</t>
   </si>
   <si>
     <t>Senior Forward Deployed Engineer (AI Enablement)</t>
@@ -6763,12 +6781,14 @@
       </c>
       <c r="K82" s="4"/>
       <c r="L82" s="4" t="s">
-        <v>229</v>
+        <v>339</v>
       </c>
       <c r="M82" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="N82" s="4"/>
+      <c r="N82" s="4" t="s">
+        <v>38</v>
+      </c>
       <c r="O82" s="4" t="s">
         <v>43</v>
       </c>
@@ -6778,36 +6798,38 @@
         <v>324</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E83" s="4"/>
       <c r="F83" s="4"/>
       <c r="G83" s="4" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H83" s="4" t="s">
         <v>336</v>
       </c>
       <c r="I83" s="4" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="J83" s="4" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="K83" s="4"/>
       <c r="L83" s="4" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="M83" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="N83" s="4"/>
+      <c r="N83" s="4" t="s">
+        <v>38</v>
+      </c>
       <c r="O83" s="4" t="s">
         <v>43</v>
       </c>
@@ -6817,36 +6839,38 @@
         <v>324</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E84" s="4"/>
       <c r="F84" s="4"/>
       <c r="G84" s="4" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H84" s="4" t="s">
         <v>336</v>
       </c>
       <c r="I84" s="4" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="J84" s="4" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K84" s="4"/>
       <c r="L84" s="4" t="s">
-        <v>229</v>
+        <v>351</v>
       </c>
       <c r="M84" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="N84" s="4"/>
+      <c r="N84" s="4" t="s">
+        <v>38</v>
+      </c>
       <c r="O84" s="4" t="s">
         <v>43</v>
       </c>
@@ -6856,16 +6880,16 @@
         <v>324</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C85" s="4"/>
       <c r="D85" s="4" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="E85" s="4"/>
       <c r="F85" s="4"/>
       <c r="G85" s="4" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="H85" s="4" t="s">
         <v>36</v>
@@ -6889,11 +6913,11 @@
         <v>324</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C86" s="4"/>
       <c r="D86" s="4" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="E86" s="4"/>
       <c r="F86" s="4"/>
@@ -6907,7 +6931,7 @@
       <c r="J86" s="4"/>
       <c r="K86" s="4"/>
       <c r="L86" s="4" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="M86" s="4" t="s">
         <v>30</v>
@@ -6922,16 +6946,16 @@
         <v>324</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="C87" s="4"/>
       <c r="D87" s="4" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="E87" s="4"/>
       <c r="F87" s="4"/>
       <c r="G87" s="4" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="H87" s="4" t="s">
         <v>36</v>
@@ -6940,7 +6964,7 @@
       <c r="J87" s="4"/>
       <c r="K87" s="4"/>
       <c r="L87" s="4" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="M87" s="4" t="s">
         <v>30</v>
@@ -6955,16 +6979,16 @@
         <v>324</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C88" s="4"/>
       <c r="D88" s="4" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="E88" s="4"/>
       <c r="F88" s="4"/>
       <c r="G88" s="4" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H88" s="4" t="s">
         <v>36</v>
@@ -6973,7 +6997,7 @@
       <c r="J88" s="4"/>
       <c r="K88" s="4"/>
       <c r="L88" s="4" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="M88" s="4" t="s">
         <v>30</v>
@@ -6988,11 +7012,11 @@
         <v>324</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="C89" s="4"/>
       <c r="D89" s="4" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="E89" s="4"/>
       <c r="F89" s="4"/>
@@ -7021,11 +7045,11 @@
         <v>324</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="C90" s="4"/>
       <c r="D90" s="4" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="E90" s="4"/>
       <c r="F90" s="4"/>
@@ -7054,11 +7078,11 @@
         <v>324</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="C91" s="4"/>
       <c r="D91" s="4" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="E91" s="4"/>
       <c r="F91" s="4"/>
@@ -7087,16 +7111,16 @@
         <v>324</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="C92" s="4"/>
       <c r="D92" s="4" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="E92" s="4"/>
       <c r="F92" s="4"/>
       <c r="G92" s="4" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="H92" s="4" t="s">
         <v>36</v>
@@ -7120,11 +7144,11 @@
         <v>324</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C93" s="4"/>
       <c r="D93" s="4" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="E93" s="4"/>
       <c r="F93" s="4"/>
@@ -7155,16 +7179,16 @@
         <v>324</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="C94" s="4"/>
       <c r="D94" s="4" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="E94" s="4"/>
       <c r="F94" s="4"/>
       <c r="G94" s="4" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H94" s="4" t="s">
         <v>36</v>
@@ -7173,7 +7197,7 @@
       <c r="J94" s="4"/>
       <c r="K94" s="4"/>
       <c r="L94" s="4" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="M94" s="4" t="s">
         <v>30</v>
@@ -7188,27 +7212,27 @@
         <v>324</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="E95" s="4"/>
       <c r="F95" s="4"/>
       <c r="G95" s="4" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="H95" s="4" t="s">
         <v>36</v>
       </c>
       <c r="I95" s="4" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="J95" s="4" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="K95" s="4"/>
       <c r="L95" s="4" t="s">
@@ -7227,16 +7251,16 @@
         <v>324</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="C96" s="4"/>
       <c r="D96" s="4" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="E96" s="4"/>
       <c r="F96" s="4"/>
       <c r="G96" s="4" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="H96" s="4" t="s">
         <v>36</v>
@@ -7260,16 +7284,16 @@
         <v>324</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="C97" s="4"/>
       <c r="D97" s="4" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="E97" s="4"/>
       <c r="F97" s="4"/>
       <c r="G97" s="4" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H97" s="4" t="s">
         <v>36</v>
@@ -7278,7 +7302,7 @@
       <c r="J97" s="4"/>
       <c r="K97" s="4"/>
       <c r="L97" s="4" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="M97" s="4" t="s">
         <v>30</v>
@@ -7293,11 +7317,11 @@
         <v>324</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="C98" s="4"/>
       <c r="D98" s="4" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="E98" s="4"/>
       <c r="F98" s="4"/>
@@ -7326,16 +7350,16 @@
         <v>324</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C99" s="4"/>
       <c r="D99" s="4" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="E99" s="4"/>
       <c r="F99" s="4"/>
       <c r="G99" s="4" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="H99" s="4" t="s">
         <v>36</v>
@@ -7359,11 +7383,11 @@
         <v>324</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C100" s="4"/>
       <c r="D100" s="4" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="E100" s="4"/>
       <c r="F100" s="4"/>
@@ -7392,11 +7416,11 @@
         <v>324</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C101" s="4"/>
       <c r="D101" s="4" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="E101" s="4"/>
       <c r="F101" s="4"/>
@@ -7425,16 +7449,16 @@
         <v>324</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="C102" s="4"/>
       <c r="D102" s="4" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="E102" s="4"/>
       <c r="F102" s="4"/>
       <c r="G102" s="4" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="H102" s="4" t="s">
         <v>36</v>
@@ -7458,16 +7482,16 @@
         <v>324</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C103" s="4"/>
       <c r="D103" s="4" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="E103" s="4"/>
       <c r="F103" s="4"/>
       <c r="G103" s="4" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="H103" s="4" t="s">
         <v>36</v>
@@ -7488,34 +7512,34 @@
     </row>
     <row r="104" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="E104" s="4"/>
       <c r="F104" s="4"/>
       <c r="G104" s="4" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="H104" s="4" t="s">
-        <v>336</v>
+        <v>405</v>
       </c>
       <c r="I104" s="4" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="J104" s="4" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="K104" s="4"/>
       <c r="L104" s="4" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="M104" s="4" t="s">
         <v>30</v>
@@ -7527,14 +7551,14 @@
     </row>
     <row r="105" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A105" s="4" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="C105" s="4"/>
       <c r="D105" s="4" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="E105" s="4"/>
       <c r="F105" s="4"/>
@@ -7548,7 +7572,7 @@
       <c r="J105" s="4"/>
       <c r="K105" s="4"/>
       <c r="L105" s="4" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="M105" s="4" t="s">
         <v>30</v>
@@ -7560,112 +7584,116 @@
     </row>
     <row r="106" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="C106" s="4" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="D106" s="4" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="E106" s="4"/>
       <c r="F106" s="4"/>
       <c r="G106" s="4" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="H106" s="4" t="s">
         <v>336</v>
       </c>
       <c r="I106" s="4" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="J106" s="4" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="K106" s="4"/>
       <c r="L106" s="4" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="M106" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="N106" s="4"/>
+      <c r="N106" s="4" t="s">
+        <v>38</v>
+      </c>
       <c r="O106" s="4" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="107" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A107" s="4" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="C107" s="4" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="D107" s="4" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E107" s="4"/>
       <c r="F107" s="4"/>
       <c r="G107" s="4" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="H107" s="4" t="s">
         <v>336</v>
       </c>
       <c r="I107" s="4" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="J107" s="4" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="K107" s="4"/>
       <c r="L107" s="4" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="M107" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="N107" s="4"/>
+      <c r="N107" s="4" t="s">
+        <v>38</v>
+      </c>
       <c r="O107" s="4" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="108" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="D108" s="4" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="E108" s="4"/>
       <c r="F108" s="4"/>
       <c r="G108" s="4" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="H108" s="4" t="s">
-        <v>336</v>
+        <v>405</v>
       </c>
       <c r="I108" s="4" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="J108" s="4" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="K108" s="4"/>
       <c r="L108" s="4" t="s">
-        <v>229</v>
+        <v>424</v>
       </c>
       <c r="M108" s="4" t="s">
         <v>30</v>
@@ -7677,14 +7705,14 @@
     </row>
     <row r="109" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A109" s="4" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="C109" s="4"/>
       <c r="D109" s="4" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="E109" s="4"/>
       <c r="F109" s="4"/>
@@ -7710,14 +7738,14 @@
     </row>
     <row r="110" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="C110" s="4"/>
       <c r="D110" s="4" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="E110" s="4"/>
       <c r="F110" s="4"/>
@@ -7743,14 +7771,14 @@
     </row>
     <row r="111" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A111" s="4" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="C111" s="4"/>
       <c r="D111" s="4" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="E111" s="4"/>
       <c r="F111" s="4"/>
@@ -7776,58 +7804,60 @@
     </row>
     <row r="112" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="C112" s="4" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="D112" s="4" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="E112" s="4"/>
       <c r="F112" s="4"/>
       <c r="G112" s="4" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="H112" s="4" t="s">
         <v>336</v>
       </c>
       <c r="I112" s="4" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="J112" s="4" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="K112" s="4"/>
       <c r="L112" s="4" t="s">
-        <v>229</v>
+        <v>435</v>
       </c>
       <c r="M112" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="N112" s="4"/>
+      <c r="N112" s="4" t="s">
+        <v>38</v>
+      </c>
       <c r="O112" s="4" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="113" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A113" s="4" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="C113" s="4"/>
       <c r="D113" s="4" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="E113" s="4"/>
       <c r="F113" s="4"/>
       <c r="G113" s="4" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="H113" s="4" t="s">
         <v>36</v>
@@ -7836,7 +7866,7 @@
       <c r="J113" s="4"/>
       <c r="K113" s="4"/>
       <c r="L113" s="4" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="M113" s="4" t="s">
         <v>30</v>
@@ -7848,58 +7878,60 @@
     </row>
     <row r="114" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="C114" s="4" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="D114" s="4" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="E114" s="4"/>
       <c r="F114" s="4"/>
       <c r="G114" s="4" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="H114" s="4" t="s">
         <v>336</v>
       </c>
       <c r="I114" s="4" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="J114" s="4" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="K114" s="4"/>
       <c r="L114" s="4" t="s">
-        <v>229</v>
+        <v>435</v>
       </c>
       <c r="M114" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="N114" s="4"/>
+      <c r="N114" s="4" t="s">
+        <v>38</v>
+      </c>
       <c r="O114" s="4" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="115" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A115" s="4" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="C115" s="4"/>
       <c r="D115" s="4" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="E115" s="4"/>
       <c r="F115" s="4"/>
       <c r="G115" s="4" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="H115" s="4" t="s">
         <v>36</v>
@@ -7922,19 +7954,19 @@
     </row>
     <row r="116" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="C116" s="4"/>
       <c r="D116" s="4" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="E116" s="4"/>
       <c r="F116" s="4"/>
       <c r="G116" s="4" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="H116" s="4" t="s">
         <v>36</v>
@@ -7943,7 +7975,7 @@
       <c r="J116" s="4"/>
       <c r="K116" s="4"/>
       <c r="L116" s="4" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="M116" s="4" t="s">
         <v>30</v>
@@ -7955,19 +7987,19 @@
     </row>
     <row r="117" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A117" s="4" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="C117" s="4"/>
       <c r="D117" s="4" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="E117" s="4"/>
       <c r="F117" s="4"/>
       <c r="G117" s="4" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="H117" s="4" t="s">
         <v>36</v>
@@ -7976,7 +8008,7 @@
       <c r="J117" s="4"/>
       <c r="K117" s="4"/>
       <c r="L117" s="4" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="M117" s="4" t="s">
         <v>30</v>
@@ -7988,19 +8020,19 @@
     </row>
     <row r="118" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="C118" s="4"/>
       <c r="D118" s="4" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="E118" s="4"/>
       <c r="F118" s="4"/>
       <c r="G118" s="4" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="H118" s="4" t="s">
         <v>36</v>
@@ -8009,7 +8041,7 @@
       <c r="J118" s="4"/>
       <c r="K118" s="4"/>
       <c r="L118" s="4" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="M118" s="4" t="s">
         <v>30</v>
@@ -8021,19 +8053,19 @@
     </row>
     <row r="119" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A119" s="4" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="C119" s="4"/>
       <c r="D119" s="4" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="E119" s="4"/>
       <c r="F119" s="4"/>
       <c r="G119" s="4" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="H119" s="4" t="s">
         <v>36</v>
@@ -8042,7 +8074,7 @@
       <c r="J119" s="4"/>
       <c r="K119" s="4"/>
       <c r="L119" s="4" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="M119" s="4" t="s">
         <v>30</v>
@@ -8054,19 +8086,19 @@
     </row>
     <row r="120" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="C120" s="4"/>
       <c r="D120" s="4" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="E120" s="4"/>
       <c r="F120" s="4"/>
       <c r="G120" s="4" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="H120" s="4" t="s">
         <v>36</v>
@@ -8075,7 +8107,7 @@
       <c r="J120" s="4"/>
       <c r="K120" s="4"/>
       <c r="L120" s="4" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="M120" s="4" t="s">
         <v>30</v>
@@ -8087,19 +8119,19 @@
     </row>
     <row r="121" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A121" s="4" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="C121" s="4"/>
       <c r="D121" s="4" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="E121" s="4"/>
       <c r="F121" s="4"/>
       <c r="G121" s="4" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="H121" s="4" t="s">
         <v>36</v>
@@ -8108,7 +8140,7 @@
       <c r="J121" s="4"/>
       <c r="K121" s="4"/>
       <c r="L121" s="4" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="M121" s="4" t="s">
         <v>22</v>
@@ -8122,14 +8154,14 @@
     </row>
     <row r="122" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="C122" s="4"/>
       <c r="D122" s="4" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="E122" s="4"/>
       <c r="F122" s="4"/>
@@ -8155,14 +8187,14 @@
     </row>
     <row r="123" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A123" s="4" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="C123" s="4"/>
       <c r="D123" s="4" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="E123" s="4"/>
       <c r="F123" s="4"/>
@@ -8188,14 +8220,14 @@
     </row>
     <row r="124" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="C124" s="4"/>
       <c r="D124" s="4" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="E124" s="4"/>
       <c r="F124" s="4"/>
@@ -8221,19 +8253,19 @@
     </row>
     <row r="125" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A125" s="4" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="C125" s="4"/>
       <c r="D125" s="4" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="E125" s="4"/>
       <c r="F125" s="4"/>
       <c r="G125" s="4" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="H125" s="4" t="s">
         <v>36</v>
@@ -8242,7 +8274,7 @@
       <c r="J125" s="4"/>
       <c r="K125" s="4"/>
       <c r="L125" s="4" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="M125" s="4" t="s">
         <v>30</v>
@@ -8254,19 +8286,19 @@
     </row>
     <row r="126" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="C126" s="4"/>
       <c r="D126" s="4" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="E126" s="4"/>
       <c r="F126" s="4"/>
       <c r="G126" s="4" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="H126" s="4" t="s">
         <v>36</v>
@@ -8287,19 +8319,19 @@
     </row>
     <row r="127" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A127" s="4" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="C127" s="4"/>
       <c r="D127" s="4" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="E127" s="4"/>
       <c r="F127" s="4"/>
       <c r="G127" s="4" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="H127" s="4" t="s">
         <v>36</v>
@@ -8308,7 +8340,7 @@
       <c r="J127" s="4"/>
       <c r="K127" s="4"/>
       <c r="L127" s="4" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="M127" s="4" t="s">
         <v>69</v>
@@ -8320,19 +8352,19 @@
     </row>
     <row r="128" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="C128" s="4"/>
       <c r="D128" s="4" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="E128" s="4"/>
       <c r="F128" s="4"/>
       <c r="G128" s="4" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="H128" s="4" t="s">
         <v>36</v>
@@ -8341,7 +8373,7 @@
       <c r="J128" s="4"/>
       <c r="K128" s="4"/>
       <c r="L128" s="4" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="M128" s="4" t="s">
         <v>30</v>
@@ -8353,19 +8385,19 @@
     </row>
     <row r="129" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A129" s="4" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="C129" s="4"/>
       <c r="D129" s="4" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="E129" s="4"/>
       <c r="F129" s="4"/>
       <c r="G129" s="4" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="H129" s="4" t="s">
         <v>36</v>
@@ -8374,7 +8406,7 @@
       <c r="J129" s="4"/>
       <c r="K129" s="4"/>
       <c r="L129" s="4" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="M129" s="4" t="s">
         <v>30</v>
@@ -8386,19 +8418,19 @@
     </row>
     <row r="130" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="B130" s="4" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="C130" s="4"/>
       <c r="D130" s="4" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="E130" s="4"/>
       <c r="F130" s="4"/>
       <c r="G130" s="4" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="H130" s="4" t="s">
         <v>36</v>
@@ -8407,7 +8439,7 @@
       <c r="J130" s="4"/>
       <c r="K130" s="4"/>
       <c r="L130" s="4" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="M130" s="4" t="s">
         <v>30</v>
@@ -8419,19 +8451,19 @@
     </row>
     <row r="131" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A131" s="4" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="B131" s="4" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="C131" s="4"/>
       <c r="D131" s="4" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="E131" s="4"/>
       <c r="F131" s="4"/>
       <c r="G131" s="4" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="H131" s="4" t="s">
         <v>36</v>
@@ -8440,7 +8472,7 @@
       <c r="J131" s="4"/>
       <c r="K131" s="4"/>
       <c r="L131" s="4" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="M131" s="4" t="s">
         <v>30</v>
@@ -8452,19 +8484,19 @@
     </row>
     <row r="132" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="B132" s="4" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="C132" s="4"/>
       <c r="D132" s="4" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="E132" s="4"/>
       <c r="F132" s="4"/>
       <c r="G132" s="4" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="H132" s="4" t="s">
         <v>36</v>
@@ -8473,7 +8505,7 @@
       <c r="J132" s="4"/>
       <c r="K132" s="4"/>
       <c r="L132" s="4" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="M132" s="4" t="s">
         <v>30</v>
@@ -8485,19 +8517,19 @@
     </row>
     <row r="133" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A133" s="4" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="C133" s="4"/>
       <c r="D133" s="4" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="E133" s="4"/>
       <c r="F133" s="4"/>
       <c r="G133" s="4" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="H133" s="4" t="s">
         <v>36</v>
@@ -8506,7 +8538,7 @@
       <c r="J133" s="4"/>
       <c r="K133" s="4"/>
       <c r="L133" s="4" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="M133" s="4" t="s">
         <v>30</v>
@@ -8518,19 +8550,19 @@
     </row>
     <row r="134" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="C134" s="4"/>
       <c r="D134" s="4" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="E134" s="4"/>
       <c r="F134" s="4"/>
       <c r="G134" s="4" t="s">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="H134" s="4" t="s">
         <v>36</v>
@@ -8539,7 +8571,7 @@
       <c r="J134" s="4"/>
       <c r="K134" s="4"/>
       <c r="L134" s="4" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="M134" s="4" t="s">
         <v>30</v>
@@ -8551,19 +8583,19 @@
     </row>
     <row r="135" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A135" s="4" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="C135" s="4"/>
       <c r="D135" s="4" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="E135" s="4"/>
       <c r="F135" s="4"/>
       <c r="G135" s="4" t="s">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="H135" s="4" t="s">
         <v>36</v>
@@ -8584,30 +8616,30 @@
     </row>
     <row r="136" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="C136" s="4" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="D136" s="4" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="E136" s="4"/>
       <c r="F136" s="4"/>
       <c r="G136" s="4" t="s">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="H136" s="4" t="s">
         <v>36</v>
       </c>
       <c r="I136" s="4" t="s">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="J136" s="4" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="K136" s="4"/>
       <c r="L136" s="4" t="s">
@@ -8623,19 +8655,19 @@
     </row>
     <row r="137" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A137" s="4" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="B137" s="4" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="C137" s="4"/>
       <c r="D137" s="4" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="E137" s="4"/>
       <c r="F137" s="4"/>
       <c r="G137" s="4" t="s">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="H137" s="4" t="s">
         <v>36</v>
@@ -8644,7 +8676,7 @@
       <c r="J137" s="4"/>
       <c r="K137" s="4"/>
       <c r="L137" s="4" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="M137" s="4" t="s">
         <v>30</v>
@@ -8656,19 +8688,19 @@
     </row>
     <row r="138" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="B138" s="4" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="C138" s="4"/>
       <c r="D138" s="4" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="E138" s="4"/>
       <c r="F138" s="4"/>
       <c r="G138" s="4" t="s">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="H138" s="4" t="s">
         <v>36</v>
@@ -8677,7 +8709,7 @@
       <c r="J138" s="4"/>
       <c r="K138" s="4"/>
       <c r="L138" s="4" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="M138" s="4" t="s">
         <v>30</v>
@@ -8689,19 +8721,19 @@
     </row>
     <row r="139" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A139" s="4" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="B139" s="4" t="s">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="C139" s="4"/>
       <c r="D139" s="4" t="s">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="E139" s="4"/>
       <c r="F139" s="4"/>
       <c r="G139" s="4" t="s">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="H139" s="4" t="s">
         <v>36</v>
@@ -8710,7 +8742,7 @@
       <c r="J139" s="4"/>
       <c r="K139" s="4"/>
       <c r="L139" s="4" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="M139" s="4" t="s">
         <v>30</v>
@@ -8722,19 +8754,19 @@
     </row>
     <row r="140" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>501</v>
+        <v>506</v>
       </c>
       <c r="C140" s="4"/>
       <c r="D140" s="4" t="s">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="E140" s="4"/>
       <c r="F140" s="4"/>
       <c r="G140" s="4" t="s">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="H140" s="4" t="s">
         <v>36</v>
@@ -8743,7 +8775,7 @@
       <c r="J140" s="4"/>
       <c r="K140" s="4"/>
       <c r="L140" s="4" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="M140" s="4" t="s">
         <v>30</v>
@@ -8755,19 +8787,19 @@
     </row>
     <row r="141" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A141" s="4" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="C141" s="4"/>
       <c r="D141" s="4" t="s">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="E141" s="4"/>
       <c r="F141" s="4"/>
       <c r="G141" s="4" t="s">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="H141" s="4" t="s">
         <v>36</v>
@@ -8776,7 +8808,7 @@
       <c r="J141" s="4"/>
       <c r="K141" s="4"/>
       <c r="L141" s="4" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="M141" s="4" t="s">
         <v>30</v>
@@ -8788,19 +8820,19 @@
     </row>
     <row r="142" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="B142" s="4" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="C142" s="4"/>
       <c r="D142" s="4" t="s">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="E142" s="4"/>
       <c r="F142" s="4"/>
       <c r="G142" s="4" t="s">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="H142" s="4" t="s">
         <v>36</v>
@@ -8809,7 +8841,7 @@
       <c r="J142" s="4"/>
       <c r="K142" s="4"/>
       <c r="L142" s="4" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="M142" s="4" t="s">
         <v>30</v>
@@ -8821,19 +8853,19 @@
     </row>
     <row r="143" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A143" s="4" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="B143" s="4" t="s">
-        <v>507</v>
+        <v>512</v>
       </c>
       <c r="C143" s="4"/>
       <c r="D143" s="4" t="s">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="E143" s="4"/>
       <c r="F143" s="4"/>
       <c r="G143" s="4" t="s">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="H143" s="4" t="s">
         <v>36</v>
@@ -8842,7 +8874,7 @@
       <c r="J143" s="4"/>
       <c r="K143" s="4"/>
       <c r="L143" s="4" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="M143" s="4" t="s">
         <v>30</v>
@@ -8854,19 +8886,19 @@
     </row>
     <row r="144" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="B144" s="4" t="s">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="C144" s="4"/>
       <c r="D144" s="4" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="E144" s="4"/>
       <c r="F144" s="4"/>
       <c r="G144" s="4" t="s">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="H144" s="4" t="s">
         <v>36</v>
@@ -8875,7 +8907,7 @@
       <c r="J144" s="4"/>
       <c r="K144" s="4"/>
       <c r="L144" s="4" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="M144" s="4" t="s">
         <v>30</v>
@@ -8887,19 +8919,19 @@
     </row>
     <row r="145" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A145" s="4" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="C145" s="4"/>
       <c r="D145" s="4" t="s">
-        <v>512</v>
+        <v>517</v>
       </c>
       <c r="E145" s="4"/>
       <c r="F145" s="4"/>
       <c r="G145" s="4" t="s">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="H145" s="4" t="s">
         <v>36</v>
@@ -8908,7 +8940,7 @@
       <c r="J145" s="4"/>
       <c r="K145" s="4"/>
       <c r="L145" s="4" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="M145" s="4" t="s">
         <v>30</v>
@@ -8920,19 +8952,19 @@
     </row>
     <row r="146" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="B146" s="4" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="C146" s="4"/>
       <c r="D146" s="4" t="s">
-        <v>514</v>
+        <v>519</v>
       </c>
       <c r="E146" s="4"/>
       <c r="F146" s="4"/>
       <c r="G146" s="4" t="s">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="H146" s="4" t="s">
         <v>36</v>
@@ -8941,7 +8973,7 @@
       <c r="J146" s="4"/>
       <c r="K146" s="4"/>
       <c r="L146" s="4" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="M146" s="4" t="s">
         <v>30</v>
@@ -8953,19 +8985,19 @@
     </row>
     <row r="147" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A147" s="4" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="B147" s="4" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="C147" s="4"/>
       <c r="D147" s="4" t="s">
-        <v>516</v>
+        <v>521</v>
       </c>
       <c r="E147" s="4"/>
       <c r="F147" s="4"/>
       <c r="G147" s="4" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="H147" s="4" t="s">
         <v>36</v>
@@ -8974,7 +9006,7 @@
       <c r="J147" s="4"/>
       <c r="K147" s="4"/>
       <c r="L147" s="4" t="s">
-        <v>518</v>
+        <v>523</v>
       </c>
       <c r="M147" s="4" t="s">
         <v>30</v>
@@ -8986,19 +9018,19 @@
     </row>
     <row r="148" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="B148" s="4" t="s">
-        <v>519</v>
+        <v>524</v>
       </c>
       <c r="C148" s="4"/>
       <c r="D148" s="4" t="s">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="E148" s="4"/>
       <c r="F148" s="4"/>
       <c r="G148" s="4" t="s">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="H148" s="4" t="s">
         <v>36</v>
@@ -9019,19 +9051,19 @@
     </row>
     <row r="149" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A149" s="4" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="B149" s="4" t="s">
-        <v>521</v>
+        <v>526</v>
       </c>
       <c r="C149" s="4"/>
       <c r="D149" s="4" t="s">
-        <v>522</v>
+        <v>527</v>
       </c>
       <c r="E149" s="4"/>
       <c r="F149" s="4"/>
       <c r="G149" s="4" t="s">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="H149" s="4" t="s">
         <v>36</v>
@@ -9052,19 +9084,19 @@
     </row>
     <row r="150" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="B150" s="4" t="s">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="C150" s="4"/>
       <c r="D150" s="4" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="E150" s="4"/>
       <c r="F150" s="4"/>
       <c r="G150" s="4" t="s">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="H150" s="4" t="s">
         <v>36</v>
@@ -9085,19 +9117,19 @@
     </row>
     <row r="151" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A151" s="4" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="B151" s="4" t="s">
-        <v>525</v>
+        <v>530</v>
       </c>
       <c r="C151" s="4"/>
       <c r="D151" s="4" t="s">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="E151" s="4"/>
       <c r="F151" s="4"/>
       <c r="G151" s="4" t="s">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="H151" s="4" t="s">
         <v>36</v>
@@ -9118,19 +9150,19 @@
     </row>
     <row r="152" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="B152" s="4" t="s">
-        <v>527</v>
+        <v>532</v>
       </c>
       <c r="C152" s="4"/>
       <c r="D152" s="4" t="s">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="E152" s="4"/>
       <c r="F152" s="4"/>
       <c r="G152" s="4" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="H152" s="4" t="s">
         <v>36</v>
@@ -9151,19 +9183,19 @@
     </row>
     <row r="153" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A153" s="4" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="B153" s="4" t="s">
-        <v>529</v>
+        <v>534</v>
       </c>
       <c r="C153" s="4"/>
       <c r="D153" s="4" t="s">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="E153" s="4"/>
       <c r="F153" s="4"/>
       <c r="G153" s="4" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="H153" s="4" t="s">
         <v>36</v>
@@ -9172,7 +9204,7 @@
       <c r="J153" s="4"/>
       <c r="K153" s="4"/>
       <c r="L153" s="4" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="M153" s="4" t="s">
         <v>30</v>
@@ -9184,30 +9216,30 @@
     </row>
     <row r="154" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A154" s="4" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="B154" s="4" t="s">
-        <v>531</v>
+        <v>536</v>
       </c>
       <c r="C154" s="4" t="s">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="D154" s="4" t="s">
-        <v>533</v>
+        <v>538</v>
       </c>
       <c r="E154" s="4"/>
       <c r="F154" s="4"/>
       <c r="G154" s="4" t="s">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="H154" s="4" t="s">
         <v>36</v>
       </c>
       <c r="I154" s="4" t="s">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="J154" s="4" t="s">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="K154" s="4"/>
       <c r="L154" s="4" t="s">
@@ -9223,19 +9255,19 @@
     </row>
     <row r="155" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A155" s="4" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="B155" s="4" t="s">
-        <v>536</v>
+        <v>541</v>
       </c>
       <c r="C155" s="4"/>
       <c r="D155" s="4" t="s">
-        <v>537</v>
+        <v>542</v>
       </c>
       <c r="E155" s="4"/>
       <c r="F155" s="4"/>
       <c r="G155" s="4" t="s">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="H155" s="4" t="s">
         <v>36</v>
@@ -9244,7 +9276,7 @@
       <c r="J155" s="4"/>
       <c r="K155" s="4"/>
       <c r="L155" s="4" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="M155" s="4" t="s">
         <v>30</v>
@@ -9256,30 +9288,30 @@
     </row>
     <row r="156" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A156" s="4" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="B156" s="4" t="s">
-        <v>538</v>
+        <v>543</v>
       </c>
       <c r="C156" s="4" t="s">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="D156" s="4" t="s">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="E156" s="4"/>
       <c r="F156" s="4"/>
       <c r="G156" s="4" t="s">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="H156" s="4" t="s">
         <v>36</v>
       </c>
       <c r="I156" s="4" t="s">
-        <v>540</v>
+        <v>545</v>
       </c>
       <c r="J156" s="4" t="s">
-        <v>541</v>
+        <v>546</v>
       </c>
       <c r="K156" s="4"/>
       <c r="L156" s="4" t="s">
@@ -9295,19 +9327,19 @@
     </row>
     <row r="157" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A157" s="4" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="B157" s="4" t="s">
-        <v>542</v>
+        <v>547</v>
       </c>
       <c r="C157" s="4"/>
       <c r="D157" s="4" t="s">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="E157" s="4"/>
       <c r="F157" s="4"/>
       <c r="G157" s="4" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="H157" s="4" t="s">
         <v>36</v>
@@ -9316,7 +9348,7 @@
       <c r="J157" s="4"/>
       <c r="K157" s="4"/>
       <c r="L157" s="4" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="M157" s="4" t="s">
         <v>30</v>
@@ -9328,30 +9360,30 @@
     </row>
     <row r="158" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A158" s="4" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="B158" s="4" t="s">
-        <v>544</v>
+        <v>549</v>
       </c>
       <c r="C158" s="4" t="s">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="D158" s="4" t="s">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="E158" s="4"/>
       <c r="F158" s="4"/>
       <c r="G158" s="4" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="H158" s="4" t="s">
         <v>36</v>
       </c>
       <c r="I158" s="4" t="s">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="J158" s="4" t="s">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="K158" s="4"/>
       <c r="L158" s="4" t="s">
@@ -9367,30 +9399,30 @@
     </row>
     <row r="159" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A159" s="4" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="B159" s="4" t="s">
-        <v>548</v>
+        <v>553</v>
       </c>
       <c r="C159" s="4" t="s">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="D159" s="4" t="s">
-        <v>549</v>
+        <v>554</v>
       </c>
       <c r="E159" s="4"/>
       <c r="F159" s="4"/>
       <c r="G159" s="4" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="H159" s="4" t="s">
         <v>36</v>
       </c>
       <c r="I159" s="4" t="s">
-        <v>550</v>
+        <v>555</v>
       </c>
       <c r="J159" s="4" t="s">
-        <v>551</v>
+        <v>556</v>
       </c>
       <c r="K159" s="4"/>
       <c r="L159" s="4" t="s">
@@ -9406,30 +9438,30 @@
     </row>
     <row r="160" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A160" s="4" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="B160" s="4" t="s">
-        <v>552</v>
+        <v>557</v>
       </c>
       <c r="C160" s="4" t="s">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="D160" s="4" t="s">
-        <v>553</v>
+        <v>558</v>
       </c>
       <c r="E160" s="4"/>
       <c r="F160" s="4"/>
       <c r="G160" s="4" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="H160" s="4" t="s">
         <v>36</v>
       </c>
       <c r="I160" s="4" t="s">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="J160" s="4" t="s">
-        <v>555</v>
+        <v>560</v>
       </c>
       <c r="K160" s="4"/>
       <c r="L160" s="4" t="s">
@@ -9445,14 +9477,14 @@
     </row>
     <row r="161" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A161" s="4" t="s">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="B161" s="4" t="s">
         <v>285</v>
       </c>
       <c r="C161" s="4"/>
       <c r="D161" s="4" t="s">
-        <v>557</v>
+        <v>562</v>
       </c>
       <c r="E161" s="4"/>
       <c r="F161" s="4"/>
@@ -9478,19 +9510,19 @@
     </row>
     <row r="162" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A162" s="4" t="s">
-        <v>558</v>
+        <v>563</v>
       </c>
       <c r="B162" s="4" t="s">
-        <v>559</v>
+        <v>564</v>
       </c>
       <c r="C162" s="4"/>
       <c r="D162" s="4" t="s">
-        <v>560</v>
+        <v>565</v>
       </c>
       <c r="E162" s="4"/>
       <c r="F162" s="4"/>
       <c r="G162" s="4" t="s">
-        <v>561</v>
+        <v>566</v>
       </c>
       <c r="H162" s="4" t="s">
         <v>36</v>
@@ -9499,7 +9531,7 @@
       <c r="J162" s="4"/>
       <c r="K162" s="4"/>
       <c r="L162" s="4" t="s">
-        <v>562</v>
+        <v>567</v>
       </c>
       <c r="M162" s="4" t="s">
         <v>30</v>
@@ -9511,19 +9543,19 @@
     </row>
     <row r="163" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A163" s="4" t="s">
-        <v>563</v>
+        <v>568</v>
       </c>
       <c r="B163" s="4" t="s">
-        <v>564</v>
+        <v>569</v>
       </c>
       <c r="C163" s="4"/>
       <c r="D163" s="4" t="s">
-        <v>565</v>
+        <v>570</v>
       </c>
       <c r="E163" s="4"/>
       <c r="F163" s="4"/>
       <c r="G163" s="4" t="s">
-        <v>566</v>
+        <v>571</v>
       </c>
       <c r="H163" s="4" t="s">
         <v>36</v>
@@ -9544,19 +9576,19 @@
     </row>
     <row r="164" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A164" s="4" t="s">
-        <v>563</v>
+        <v>568</v>
       </c>
       <c r="B164" s="4" t="s">
-        <v>567</v>
+        <v>572</v>
       </c>
       <c r="C164" s="4"/>
       <c r="D164" s="4" t="s">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="E164" s="4"/>
       <c r="F164" s="4"/>
       <c r="G164" s="4" t="s">
-        <v>566</v>
+        <v>571</v>
       </c>
       <c r="H164" s="4" t="s">
         <v>36</v>
@@ -9577,58 +9609,60 @@
     </row>
     <row r="165" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A165" s="4" t="s">
-        <v>569</v>
+        <v>574</v>
       </c>
       <c r="B165" s="4" t="s">
-        <v>570</v>
+        <v>575</v>
       </c>
       <c r="C165" s="4" t="s">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="D165" s="4" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="E165" s="4"/>
       <c r="F165" s="4"/>
       <c r="G165" s="4" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="H165" s="4" t="s">
         <v>336</v>
       </c>
       <c r="I165" s="4" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="J165" s="4" t="s">
-        <v>575</v>
+        <v>580</v>
       </c>
       <c r="K165" s="4"/>
       <c r="L165" s="4" t="s">
-        <v>576</v>
+        <v>581</v>
       </c>
       <c r="M165" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="N165" s="4"/>
+      <c r="N165" s="4" t="s">
+        <v>38</v>
+      </c>
       <c r="O165" s="4" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="166" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A166" s="4" t="s">
-        <v>569</v>
+        <v>574</v>
       </c>
       <c r="B166" s="4" t="s">
-        <v>577</v>
+        <v>582</v>
       </c>
       <c r="C166" s="4"/>
       <c r="D166" s="4" t="s">
-        <v>578</v>
+        <v>583</v>
       </c>
       <c r="E166" s="4"/>
       <c r="F166" s="4"/>
       <c r="G166" s="4" t="s">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c r="H166" s="4" t="s">
         <v>36</v>
@@ -9637,7 +9671,7 @@
       <c r="J166" s="4"/>
       <c r="K166" s="4"/>
       <c r="L166" s="4" t="s">
-        <v>580</v>
+        <v>585</v>
       </c>
       <c r="M166" s="4" t="s">
         <v>30</v>
@@ -9649,19 +9683,19 @@
     </row>
     <row r="167" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A167" s="4" t="s">
-        <v>569</v>
+        <v>574</v>
       </c>
       <c r="B167" s="4" t="s">
-        <v>581</v>
+        <v>586</v>
       </c>
       <c r="C167" s="4"/>
       <c r="D167" s="4" t="s">
-        <v>582</v>
+        <v>587</v>
       </c>
       <c r="E167" s="4"/>
       <c r="F167" s="4"/>
       <c r="G167" s="4" t="s">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c r="H167" s="4" t="s">
         <v>36</v>
@@ -9670,7 +9704,7 @@
       <c r="J167" s="4"/>
       <c r="K167" s="4"/>
       <c r="L167" s="4" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="M167" s="4" t="s">
         <v>30</v>
@@ -9682,19 +9716,19 @@
     </row>
     <row r="168" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A168" s="4" t="s">
-        <v>569</v>
+        <v>574</v>
       </c>
       <c r="B168" s="4" t="s">
-        <v>584</v>
+        <v>589</v>
       </c>
       <c r="C168" s="4"/>
       <c r="D168" s="4" t="s">
-        <v>585</v>
+        <v>590</v>
       </c>
       <c r="E168" s="4"/>
       <c r="F168" s="4"/>
       <c r="G168" s="4" t="s">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c r="H168" s="4" t="s">
         <v>36</v>
@@ -9703,7 +9737,7 @@
       <c r="J168" s="4"/>
       <c r="K168" s="4"/>
       <c r="L168" s="4" t="s">
-        <v>586</v>
+        <v>591</v>
       </c>
       <c r="M168" s="4" t="s">
         <v>30</v>
@@ -9715,14 +9749,14 @@
     </row>
     <row r="169" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A169" s="4" t="s">
-        <v>569</v>
+        <v>574</v>
       </c>
       <c r="B169" s="4" t="s">
-        <v>587</v>
+        <v>592</v>
       </c>
       <c r="C169" s="4"/>
       <c r="D169" s="4" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="E169" s="4"/>
       <c r="F169" s="4"/>
@@ -9736,7 +9770,7 @@
       <c r="J169" s="4"/>
       <c r="K169" s="4"/>
       <c r="L169" s="4" t="s">
-        <v>589</v>
+        <v>594</v>
       </c>
       <c r="M169" s="4" t="s">
         <v>30</v>
@@ -9748,14 +9782,14 @@
     </row>
     <row r="170" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A170" s="4" t="s">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="B170" s="4" t="s">
         <v>285</v>
       </c>
       <c r="C170" s="4"/>
       <c r="D170" s="4" t="s">
-        <v>591</v>
+        <v>596</v>
       </c>
       <c r="E170" s="4"/>
       <c r="F170" s="4"/>
@@ -9781,14 +9815,14 @@
     </row>
     <row r="171" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A171" s="4" t="s">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="B171" s="4" t="s">
         <v>219</v>
       </c>
       <c r="C171" s="4"/>
       <c r="D171" s="4" t="s">
-        <v>592</v>
+        <v>597</v>
       </c>
       <c r="E171" s="4"/>
       <c r="F171" s="4"/>
@@ -9802,7 +9836,7 @@
       <c r="J171" s="4"/>
       <c r="K171" s="4"/>
       <c r="L171" s="4" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="M171" s="4" t="s">
         <v>30</v>
@@ -9814,30 +9848,30 @@
     </row>
     <row r="172" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A172" s="4" t="s">
-        <v>593</v>
+        <v>598</v>
       </c>
       <c r="B172" s="4" t="s">
         <v>262</v>
       </c>
       <c r="C172" s="4" t="s">
-        <v>594</v>
+        <v>599</v>
       </c>
       <c r="D172" s="4" t="s">
-        <v>595</v>
+        <v>600</v>
       </c>
       <c r="E172" s="4"/>
       <c r="F172" s="4"/>
       <c r="G172" s="4" t="s">
-        <v>596</v>
+        <v>601</v>
       </c>
       <c r="H172" s="4" t="s">
         <v>36</v>
       </c>
       <c r="I172" s="4" t="s">
-        <v>597</v>
+        <v>602</v>
       </c>
       <c r="J172" s="4" t="s">
-        <v>598</v>
+        <v>603</v>
       </c>
       <c r="K172" s="4"/>
       <c r="L172" s="4" t="s">
@@ -9853,14 +9887,14 @@
     </row>
     <row r="173" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A173" s="4" t="s">
-        <v>599</v>
+        <v>604</v>
       </c>
       <c r="B173" s="4" t="s">
-        <v>600</v>
+        <v>605</v>
       </c>
       <c r="C173" s="4"/>
       <c r="D173" s="4" t="s">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c r="E173" s="4"/>
       <c r="F173" s="4"/>
@@ -9888,16 +9922,16 @@
     </row>
     <row r="174" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A174" s="4" t="s">
-        <v>599</v>
+        <v>604</v>
       </c>
       <c r="B174" s="4" t="s">
-        <v>602</v>
+        <v>607</v>
       </c>
       <c r="C174" s="4" t="s">
-        <v>603</v>
+        <v>608</v>
       </c>
       <c r="D174" s="4" t="s">
-        <v>604</v>
+        <v>609</v>
       </c>
       <c r="E174" s="4"/>
       <c r="F174" s="4"/>
@@ -9908,7 +9942,7 @@
         <v>36</v>
       </c>
       <c r="I174" s="4" t="s">
-        <v>605</v>
+        <v>610</v>
       </c>
       <c r="J174" s="4"/>
       <c r="K174" s="4"/>
@@ -9930,13 +9964,13 @@
         <v>147</v>
       </c>
       <c r="B175" s="4" t="s">
-        <v>606</v>
+        <v>611</v>
       </c>
       <c r="C175" s="4" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="D175" s="4" t="s">
-        <v>608</v>
+        <v>613</v>
       </c>
       <c r="E175" s="4"/>
       <c r="F175" s="4"/>
@@ -9947,19 +9981,21 @@
         <v>336</v>
       </c>
       <c r="I175" s="4" t="s">
-        <v>609</v>
+        <v>614</v>
       </c>
       <c r="J175" s="4" t="s">
-        <v>610</v>
+        <v>615</v>
       </c>
       <c r="K175" s="4"/>
       <c r="L175" s="4" t="s">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="M175" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="N175" s="4"/>
+      <c r="N175" s="4" t="s">
+        <v>38</v>
+      </c>
       <c r="O175" s="4" t="s">
         <v>43</v>
       </c>
@@ -9969,11 +10005,11 @@
         <v>147</v>
       </c>
       <c r="B176" s="4" t="s">
-        <v>606</v>
+        <v>611</v>
       </c>
       <c r="C176" s="4"/>
       <c r="D176" s="4" t="s">
-        <v>612</v>
+        <v>617</v>
       </c>
       <c r="E176" s="4"/>
       <c r="F176" s="4"/>
@@ -9987,7 +10023,7 @@
       <c r="J176" s="4"/>
       <c r="K176" s="4"/>
       <c r="L176" s="4" t="s">
-        <v>613</v>
+        <v>618</v>
       </c>
       <c r="M176" s="4" t="s">
         <v>30</v>
@@ -10002,16 +10038,16 @@
         <v>147</v>
       </c>
       <c r="B177" s="4" t="s">
-        <v>614</v>
+        <v>619</v>
       </c>
       <c r="C177" s="4"/>
       <c r="D177" s="4" t="s">
-        <v>615</v>
+        <v>620</v>
       </c>
       <c r="E177" s="4"/>
       <c r="F177" s="4"/>
       <c r="G177" s="4" t="s">
-        <v>616</v>
+        <v>621</v>
       </c>
       <c r="H177" s="4" t="s">
         <v>36</v>
@@ -10020,7 +10056,7 @@
       <c r="J177" s="4"/>
       <c r="K177" s="4"/>
       <c r="L177" s="4" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="M177" s="4" t="s">
         <v>30</v>
@@ -10035,11 +10071,11 @@
         <v>147</v>
       </c>
       <c r="B178" s="4" t="s">
-        <v>617</v>
+        <v>622</v>
       </c>
       <c r="C178" s="4"/>
       <c r="D178" s="4" t="s">
-        <v>618</v>
+        <v>623</v>
       </c>
       <c r="E178" s="4"/>
       <c r="F178" s="4"/>
@@ -10053,7 +10089,7 @@
       <c r="J178" s="4"/>
       <c r="K178" s="4"/>
       <c r="L178" s="4" t="s">
-        <v>619</v>
+        <v>624</v>
       </c>
       <c r="M178" s="4" t="s">
         <v>30</v>
@@ -10065,14 +10101,14 @@
     </row>
     <row r="179" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A179" s="4" t="s">
-        <v>620</v>
+        <v>625</v>
       </c>
       <c r="B179" s="4" t="s">
-        <v>621</v>
+        <v>626</v>
       </c>
       <c r="C179" s="4"/>
       <c r="D179" s="4" t="s">
-        <v>622</v>
+        <v>627</v>
       </c>
       <c r="E179" s="4"/>
       <c r="F179" s="4"/>
@@ -10098,14 +10134,14 @@
     </row>
     <row r="180" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A180" s="4" t="s">
-        <v>620</v>
+        <v>625</v>
       </c>
       <c r="B180" s="4" t="s">
-        <v>623</v>
+        <v>628</v>
       </c>
       <c r="C180" s="4"/>
       <c r="D180" s="4" t="s">
-        <v>624</v>
+        <v>629</v>
       </c>
       <c r="E180" s="4"/>
       <c r="F180" s="4"/>
@@ -10131,19 +10167,19 @@
     </row>
     <row r="181" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A181" s="4" t="s">
-        <v>620</v>
+        <v>625</v>
       </c>
       <c r="B181" s="4" t="s">
-        <v>623</v>
+        <v>628</v>
       </c>
       <c r="C181" s="4"/>
       <c r="D181" s="4" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="E181" s="4"/>
       <c r="F181" s="4"/>
       <c r="G181" s="4" t="s">
-        <v>626</v>
+        <v>631</v>
       </c>
       <c r="H181" s="4" t="s">
         <v>36</v>
@@ -10164,16 +10200,16 @@
     </row>
     <row r="182" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A182" s="4" t="s">
-        <v>620</v>
+        <v>625</v>
       </c>
       <c r="B182" s="4" t="s">
-        <v>627</v>
+        <v>632</v>
       </c>
       <c r="C182" s="4" t="s">
-        <v>603</v>
+        <v>608</v>
       </c>
       <c r="D182" s="4" t="s">
-        <v>628</v>
+        <v>633</v>
       </c>
       <c r="E182" s="4"/>
       <c r="F182" s="4"/>
@@ -10184,7 +10220,7 @@
         <v>36</v>
       </c>
       <c r="I182" s="4" t="s">
-        <v>629</v>
+        <v>634</v>
       </c>
       <c r="J182" s="4"/>
       <c r="K182" s="4"/>
@@ -10201,16 +10237,16 @@
     </row>
     <row r="183" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A183" s="4" t="s">
-        <v>620</v>
+        <v>625</v>
       </c>
       <c r="B183" s="4" t="s">
-        <v>630</v>
+        <v>635</v>
       </c>
       <c r="C183" s="4" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="D183" s="4" t="s">
-        <v>631</v>
+        <v>636</v>
       </c>
       <c r="E183" s="4"/>
       <c r="F183" s="4"/>
@@ -10221,7 +10257,7 @@
         <v>36</v>
       </c>
       <c r="I183" s="4" t="s">
-        <v>632</v>
+        <v>637</v>
       </c>
       <c r="J183" s="4"/>
       <c r="K183" s="4"/>
@@ -10238,14 +10274,14 @@
     </row>
     <row r="184" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A184" s="4" t="s">
-        <v>620</v>
+        <v>625</v>
       </c>
       <c r="B184" s="4" t="s">
-        <v>633</v>
+        <v>638</v>
       </c>
       <c r="C184" s="4"/>
       <c r="D184" s="4" t="s">
-        <v>634</v>
+        <v>639</v>
       </c>
       <c r="E184" s="4"/>
       <c r="F184" s="4"/>
@@ -10271,19 +10307,19 @@
     </row>
     <row r="185" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A185" s="4" t="s">
-        <v>620</v>
+        <v>625</v>
       </c>
       <c r="B185" s="4" t="s">
-        <v>633</v>
+        <v>638</v>
       </c>
       <c r="C185" s="4"/>
       <c r="D185" s="4" t="s">
-        <v>635</v>
+        <v>640</v>
       </c>
       <c r="E185" s="4"/>
       <c r="F185" s="4"/>
       <c r="G185" s="4" t="s">
-        <v>626</v>
+        <v>631</v>
       </c>
       <c r="H185" s="4" t="s">
         <v>36</v>
@@ -10304,14 +10340,14 @@
     </row>
     <row r="186" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A186" s="4" t="s">
-        <v>620</v>
+        <v>625</v>
       </c>
       <c r="B186" s="4" t="s">
-        <v>633</v>
+        <v>638</v>
       </c>
       <c r="C186" s="4"/>
       <c r="D186" s="4" t="s">
-        <v>636</v>
+        <v>641</v>
       </c>
       <c r="E186" s="4"/>
       <c r="F186" s="4"/>
@@ -10337,14 +10373,14 @@
     </row>
     <row r="187" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A187" s="4" t="s">
-        <v>620</v>
+        <v>625</v>
       </c>
       <c r="B187" s="4" t="s">
-        <v>637</v>
+        <v>642</v>
       </c>
       <c r="C187" s="4"/>
       <c r="D187" s="4" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="E187" s="4"/>
       <c r="F187" s="4"/>
@@ -10370,73 +10406,75 @@
     </row>
     <row r="188" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A188" s="4" t="s">
-        <v>639</v>
+        <v>644</v>
       </c>
       <c r="B188" s="4" t="s">
-        <v>640</v>
+        <v>645</v>
       </c>
       <c r="C188" s="4" t="s">
-        <v>641</v>
+        <v>646</v>
       </c>
       <c r="D188" s="4" t="s">
-        <v>642</v>
+        <v>647</v>
       </c>
       <c r="E188" s="4"/>
       <c r="F188" s="4"/>
       <c r="G188" s="4" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="H188" s="4" t="s">
         <v>336</v>
       </c>
       <c r="I188" s="4" t="s">
-        <v>643</v>
+        <v>648</v>
       </c>
       <c r="J188" s="4" t="s">
-        <v>644</v>
+        <v>649</v>
       </c>
       <c r="K188" s="4"/>
       <c r="L188" s="4" t="s">
-        <v>229</v>
+        <v>650</v>
       </c>
       <c r="M188" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="N188" s="4"/>
+      <c r="N188" s="4" t="s">
+        <v>38</v>
+      </c>
       <c r="O188" s="4" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="189" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A189" s="4" t="s">
-        <v>639</v>
+        <v>644</v>
       </c>
       <c r="B189" s="4" t="s">
         <v>271</v>
       </c>
       <c r="C189" s="4" t="s">
-        <v>641</v>
+        <v>646</v>
       </c>
       <c r="D189" s="4" t="s">
-        <v>645</v>
+        <v>651</v>
       </c>
       <c r="E189" s="4"/>
       <c r="F189" s="4"/>
       <c r="G189" s="4" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="H189" s="4" t="s">
-        <v>336</v>
+        <v>405</v>
       </c>
       <c r="I189" s="4" t="s">
-        <v>646</v>
+        <v>652</v>
       </c>
       <c r="J189" s="4" t="s">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="K189" s="4"/>
       <c r="L189" s="4" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="M189" s="4" t="s">
         <v>30</v>
@@ -10448,19 +10486,19 @@
     </row>
     <row r="190" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A190" s="4" t="s">
-        <v>639</v>
+        <v>644</v>
       </c>
       <c r="B190" s="4" t="s">
-        <v>649</v>
+        <v>655</v>
       </c>
       <c r="C190" s="4"/>
       <c r="D190" s="4" t="s">
-        <v>650</v>
+        <v>656</v>
       </c>
       <c r="E190" s="4"/>
       <c r="F190" s="4"/>
       <c r="G190" s="4" t="s">
-        <v>651</v>
+        <v>657</v>
       </c>
       <c r="H190" s="4" t="s">
         <v>36</v>
@@ -10469,7 +10507,7 @@
       <c r="J190" s="4"/>
       <c r="K190" s="4"/>
       <c r="L190" s="4" t="s">
-        <v>652</v>
+        <v>658</v>
       </c>
       <c r="M190" s="4" t="s">
         <v>30</v>
@@ -10481,19 +10519,19 @@
     </row>
     <row r="191" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A191" s="4" t="s">
-        <v>639</v>
+        <v>644</v>
       </c>
       <c r="B191" s="4" t="s">
-        <v>653</v>
+        <v>659</v>
       </c>
       <c r="C191" s="4"/>
       <c r="D191" s="4" t="s">
-        <v>654</v>
+        <v>660</v>
       </c>
       <c r="E191" s="4"/>
       <c r="F191" s="4"/>
       <c r="G191" s="4" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="H191" s="4" t="s">
         <v>36</v>
@@ -10502,7 +10540,7 @@
       <c r="J191" s="4"/>
       <c r="K191" s="4"/>
       <c r="L191" s="4" t="s">
-        <v>655</v>
+        <v>661</v>
       </c>
       <c r="M191" s="4" t="s">
         <v>30</v>
@@ -10514,19 +10552,19 @@
     </row>
     <row r="192" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A192" s="4" t="s">
-        <v>639</v>
+        <v>644</v>
       </c>
       <c r="B192" s="4" t="s">
-        <v>656</v>
+        <v>662</v>
       </c>
       <c r="C192" s="4"/>
       <c r="D192" s="4" t="s">
-        <v>657</v>
+        <v>663</v>
       </c>
       <c r="E192" s="4"/>
       <c r="F192" s="4"/>
       <c r="G192" s="4" t="s">
-        <v>658</v>
+        <v>664</v>
       </c>
       <c r="H192" s="4" t="s">
         <v>36</v>
@@ -10535,7 +10573,7 @@
       <c r="J192" s="4"/>
       <c r="K192" s="4"/>
       <c r="L192" s="4" t="s">
-        <v>659</v>
+        <v>665</v>
       </c>
       <c r="M192" s="4" t="s">
         <v>30</v>
@@ -10547,19 +10585,19 @@
     </row>
     <row r="193" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A193" s="4" t="s">
-        <v>639</v>
+        <v>644</v>
       </c>
       <c r="B193" s="4" t="s">
-        <v>660</v>
+        <v>666</v>
       </c>
       <c r="C193" s="4"/>
       <c r="D193" s="4" t="s">
-        <v>661</v>
+        <v>667</v>
       </c>
       <c r="E193" s="4"/>
       <c r="F193" s="4"/>
       <c r="G193" s="4" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="H193" s="4" t="s">
         <v>36</v>
@@ -10568,7 +10606,7 @@
       <c r="J193" s="4"/>
       <c r="K193" s="4"/>
       <c r="L193" s="4" t="s">
-        <v>662</v>
+        <v>668</v>
       </c>
       <c r="M193" s="4" t="s">
         <v>30</v>
@@ -10580,19 +10618,19 @@
     </row>
     <row r="194" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A194" s="4" t="s">
-        <v>639</v>
+        <v>644</v>
       </c>
       <c r="B194" s="4" t="s">
-        <v>663</v>
+        <v>669</v>
       </c>
       <c r="C194" s="4"/>
       <c r="D194" s="4" t="s">
-        <v>664</v>
+        <v>670</v>
       </c>
       <c r="E194" s="4"/>
       <c r="F194" s="4"/>
       <c r="G194" s="4" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="H194" s="4" t="s">
         <v>36</v>
@@ -10601,7 +10639,7 @@
       <c r="J194" s="4"/>
       <c r="K194" s="4"/>
       <c r="L194" s="4" t="s">
-        <v>665</v>
+        <v>671</v>
       </c>
       <c r="M194" s="4" t="s">
         <v>30</v>
@@ -10613,97 +10651,101 @@
     </row>
     <row r="195" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A195" s="4" t="s">
-        <v>639</v>
+        <v>644</v>
       </c>
       <c r="B195" s="4" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="C195" s="4" t="s">
-        <v>641</v>
+        <v>646</v>
       </c>
       <c r="D195" s="4" t="s">
-        <v>666</v>
+        <v>672</v>
       </c>
       <c r="E195" s="4"/>
       <c r="F195" s="4"/>
       <c r="G195" s="4" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="H195" s="4" t="s">
         <v>336</v>
       </c>
       <c r="I195" s="4" t="s">
-        <v>667</v>
+        <v>673</v>
       </c>
       <c r="J195" s="4" t="s">
-        <v>668</v>
+        <v>674</v>
       </c>
       <c r="K195" s="4"/>
       <c r="L195" s="4" t="s">
-        <v>669</v>
+        <v>675</v>
       </c>
       <c r="M195" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="N195" s="4"/>
+      <c r="N195" s="4" t="s">
+        <v>38</v>
+      </c>
       <c r="O195" s="4" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="196" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A196" s="4" t="s">
-        <v>639</v>
+        <v>644</v>
       </c>
       <c r="B196" s="4" t="s">
         <v>89</v>
       </c>
       <c r="C196" s="4" t="s">
-        <v>641</v>
+        <v>646</v>
       </c>
       <c r="D196" s="4" t="s">
-        <v>670</v>
+        <v>676</v>
       </c>
       <c r="E196" s="4"/>
       <c r="F196" s="4"/>
       <c r="G196" s="4" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="H196" s="4" t="s">
         <v>336</v>
       </c>
       <c r="I196" s="4" t="s">
-        <v>671</v>
+        <v>677</v>
       </c>
       <c r="J196" s="4" t="s">
-        <v>672</v>
+        <v>678</v>
       </c>
       <c r="K196" s="4"/>
       <c r="L196" s="4" t="s">
-        <v>229</v>
+        <v>679</v>
       </c>
       <c r="M196" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="N196" s="4"/>
+      <c r="N196" s="4" t="s">
+        <v>38</v>
+      </c>
       <c r="O196" s="4" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="197" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A197" s="4" t="s">
-        <v>639</v>
+        <v>644</v>
       </c>
       <c r="B197" s="4" t="s">
-        <v>673</v>
+        <v>680</v>
       </c>
       <c r="C197" s="4"/>
       <c r="D197" s="4" t="s">
-        <v>674</v>
+        <v>681</v>
       </c>
       <c r="E197" s="4"/>
       <c r="F197" s="4"/>
       <c r="G197" s="4" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="H197" s="4" t="s">
         <v>36</v>
@@ -10712,7 +10754,7 @@
       <c r="J197" s="4"/>
       <c r="K197" s="4"/>
       <c r="L197" s="4" t="s">
-        <v>675</v>
+        <v>682</v>
       </c>
       <c r="M197" s="4" t="s">
         <v>30</v>
@@ -10724,14 +10766,14 @@
     </row>
     <row r="198" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A198" s="4" t="s">
-        <v>676</v>
+        <v>683</v>
       </c>
       <c r="B198" s="4" t="s">
-        <v>677</v>
+        <v>684</v>
       </c>
       <c r="C198" s="4"/>
       <c r="D198" s="4" t="s">
-        <v>678</v>
+        <v>685</v>
       </c>
       <c r="E198" s="4"/>
       <c r="F198" s="4"/>
@@ -10757,14 +10799,14 @@
     </row>
     <row r="199" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A199" s="4" t="s">
-        <v>676</v>
+        <v>683</v>
       </c>
       <c r="B199" s="4" t="s">
-        <v>679</v>
+        <v>686</v>
       </c>
       <c r="C199" s="4"/>
       <c r="D199" s="4" t="s">
-        <v>680</v>
+        <v>687</v>
       </c>
       <c r="E199" s="4"/>
       <c r="F199" s="4"/>
@@ -10790,19 +10832,19 @@
     </row>
     <row r="200" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A200" s="4" t="s">
-        <v>676</v>
+        <v>683</v>
       </c>
       <c r="B200" s="4" t="s">
-        <v>681</v>
+        <v>688</v>
       </c>
       <c r="C200" s="4"/>
       <c r="D200" s="4" t="s">
-        <v>682</v>
+        <v>689</v>
       </c>
       <c r="E200" s="4"/>
       <c r="F200" s="4"/>
       <c r="G200" s="4" t="s">
-        <v>683</v>
+        <v>690</v>
       </c>
       <c r="H200" s="4" t="s">
         <v>36</v>
@@ -10823,19 +10865,19 @@
     </row>
     <row r="201" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A201" s="4" t="s">
-        <v>676</v>
+        <v>683</v>
       </c>
       <c r="B201" s="4" t="s">
-        <v>684</v>
+        <v>691</v>
       </c>
       <c r="C201" s="4"/>
       <c r="D201" s="4" t="s">
-        <v>685</v>
+        <v>692</v>
       </c>
       <c r="E201" s="4"/>
       <c r="F201" s="4"/>
       <c r="G201" s="4" t="s">
-        <v>686</v>
+        <v>693</v>
       </c>
       <c r="H201" s="4" t="s">
         <v>36</v>
@@ -10844,7 +10886,7 @@
       <c r="J201" s="4"/>
       <c r="K201" s="4"/>
       <c r="L201" s="4" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="M201" s="4" t="s">
         <v>30</v>
@@ -10856,14 +10898,14 @@
     </row>
     <row r="202" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A202" s="4" t="s">
-        <v>676</v>
+        <v>683</v>
       </c>
       <c r="B202" s="4" t="s">
-        <v>687</v>
+        <v>694</v>
       </c>
       <c r="C202" s="4"/>
       <c r="D202" s="4" t="s">
-        <v>688</v>
+        <v>695</v>
       </c>
       <c r="E202" s="4"/>
       <c r="F202" s="4"/>
@@ -10877,7 +10919,7 @@
       <c r="J202" s="4"/>
       <c r="K202" s="4"/>
       <c r="L202" s="4" t="s">
-        <v>689</v>
+        <v>696</v>
       </c>
       <c r="M202" s="4" t="s">
         <v>30</v>
@@ -10889,19 +10931,19 @@
     </row>
     <row r="203" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A203" s="4" t="s">
-        <v>690</v>
+        <v>697</v>
       </c>
       <c r="B203" s="4" t="s">
-        <v>691</v>
+        <v>698</v>
       </c>
       <c r="C203" s="4"/>
       <c r="D203" s="4" t="s">
-        <v>692</v>
+        <v>699</v>
       </c>
       <c r="E203" s="4"/>
       <c r="F203" s="4"/>
       <c r="G203" s="4" t="s">
-        <v>693</v>
+        <v>700</v>
       </c>
       <c r="H203" s="4" t="s">
         <v>36</v>
@@ -10922,19 +10964,19 @@
     </row>
     <row r="204" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A204" s="4" t="s">
-        <v>690</v>
+        <v>697</v>
       </c>
       <c r="B204" s="4" t="s">
-        <v>694</v>
+        <v>701</v>
       </c>
       <c r="C204" s="4"/>
       <c r="D204" s="4" t="s">
-        <v>695</v>
+        <v>702</v>
       </c>
       <c r="E204" s="4"/>
       <c r="F204" s="4"/>
       <c r="G204" s="4" t="s">
-        <v>696</v>
+        <v>703</v>
       </c>
       <c r="H204" s="4" t="s">
         <v>36</v>
@@ -10943,7 +10985,7 @@
       <c r="J204" s="4"/>
       <c r="K204" s="4"/>
       <c r="L204" s="4" t="s">
-        <v>697</v>
+        <v>704</v>
       </c>
       <c r="M204" s="4" t="s">
         <v>30</v>
@@ -10957,19 +10999,19 @@
     </row>
     <row r="205" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A205" s="4" t="s">
-        <v>690</v>
+        <v>697</v>
       </c>
       <c r="B205" s="4" t="s">
-        <v>660</v>
+        <v>666</v>
       </c>
       <c r="C205" s="4"/>
       <c r="D205" s="4" t="s">
-        <v>698</v>
+        <v>705</v>
       </c>
       <c r="E205" s="4"/>
       <c r="F205" s="4"/>
       <c r="G205" s="4" t="s">
-        <v>699</v>
+        <v>706</v>
       </c>
       <c r="H205" s="4" t="s">
         <v>36</v>
@@ -10978,7 +11020,7 @@
       <c r="J205" s="4"/>
       <c r="K205" s="4"/>
       <c r="L205" s="4" t="s">
-        <v>700</v>
+        <v>707</v>
       </c>
       <c r="M205" s="4" t="s">
         <v>30</v>
@@ -10992,19 +11034,19 @@
     </row>
     <row r="206" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A206" s="4" t="s">
-        <v>690</v>
+        <v>697</v>
       </c>
       <c r="B206" s="4" t="s">
-        <v>701</v>
+        <v>708</v>
       </c>
       <c r="C206" s="4"/>
       <c r="D206" s="4" t="s">
-        <v>702</v>
+        <v>709</v>
       </c>
       <c r="E206" s="4"/>
       <c r="F206" s="4"/>
       <c r="G206" s="4" t="s">
-        <v>703</v>
+        <v>710</v>
       </c>
       <c r="H206" s="4" t="s">
         <v>36</v>
@@ -11013,7 +11055,7 @@
       <c r="J206" s="4"/>
       <c r="K206" s="4"/>
       <c r="L206" s="4" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="M206" s="4" t="s">
         <v>30</v>
@@ -11025,30 +11067,30 @@
     </row>
     <row r="207" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A207" s="4" t="s">
-        <v>690</v>
+        <v>697</v>
       </c>
       <c r="B207" s="4" t="s">
-        <v>704</v>
+        <v>711</v>
       </c>
       <c r="C207" s="4" t="s">
-        <v>705</v>
+        <v>712</v>
       </c>
       <c r="D207" s="4" t="s">
-        <v>706</v>
+        <v>713</v>
       </c>
       <c r="E207" s="4"/>
       <c r="F207" s="4"/>
       <c r="G207" s="4" t="s">
-        <v>707</v>
+        <v>714</v>
       </c>
       <c r="H207" s="4" t="s">
         <v>36</v>
       </c>
       <c r="I207" s="4" t="s">
-        <v>708</v>
+        <v>715</v>
       </c>
       <c r="J207" s="4" t="s">
-        <v>709</v>
+        <v>716</v>
       </c>
       <c r="K207" s="4"/>
       <c r="L207" s="4" t="s">
@@ -11064,19 +11106,19 @@
     </row>
     <row r="208" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A208" s="4" t="s">
-        <v>710</v>
+        <v>717</v>
       </c>
       <c r="B208" s="4" t="s">
         <v>285</v>
       </c>
       <c r="C208" s="4"/>
       <c r="D208" s="4" t="s">
-        <v>711</v>
+        <v>718</v>
       </c>
       <c r="E208" s="4"/>
       <c r="F208" s="4"/>
       <c r="G208" s="4" t="s">
-        <v>712</v>
+        <v>719</v>
       </c>
       <c r="H208" s="4" t="s">
         <v>36</v>
@@ -11097,16 +11139,16 @@
     </row>
     <row r="209" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A209" s="4" t="s">
-        <v>713</v>
+        <v>720</v>
       </c>
       <c r="B209" s="4" t="s">
-        <v>714</v>
+        <v>721</v>
       </c>
       <c r="C209" s="4" t="s">
-        <v>715</v>
+        <v>722</v>
       </c>
       <c r="D209" s="4" t="s">
-        <v>716</v>
+        <v>723</v>
       </c>
       <c r="E209" s="4"/>
       <c r="F209" s="4"/>
@@ -11117,10 +11159,10 @@
         <v>36</v>
       </c>
       <c r="I209" s="4" t="s">
-        <v>717</v>
+        <v>724</v>
       </c>
       <c r="J209" s="4" t="s">
-        <v>718</v>
+        <v>725</v>
       </c>
       <c r="K209" s="4"/>
       <c r="L209" s="4" t="s">
@@ -11136,16 +11178,16 @@
     </row>
     <row r="210" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A210" s="4" t="s">
-        <v>713</v>
+        <v>720</v>
       </c>
       <c r="B210" s="4" t="s">
         <v>271</v>
       </c>
       <c r="C210" s="4" t="s">
-        <v>715</v>
+        <v>722</v>
       </c>
       <c r="D210" s="4" t="s">
-        <v>719</v>
+        <v>726</v>
       </c>
       <c r="E210" s="4"/>
       <c r="F210" s="4"/>
@@ -11156,10 +11198,10 @@
         <v>36</v>
       </c>
       <c r="I210" s="4" t="s">
-        <v>720</v>
+        <v>727</v>
       </c>
       <c r="J210" s="4" t="s">
-        <v>721</v>
+        <v>728</v>
       </c>
       <c r="K210" s="4"/>
       <c r="L210" s="4" t="s">
@@ -11175,14 +11217,14 @@
     </row>
     <row r="211" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A211" s="4" t="s">
-        <v>713</v>
+        <v>720</v>
       </c>
       <c r="B211" s="4" t="s">
-        <v>722</v>
+        <v>729</v>
       </c>
       <c r="C211" s="4"/>
       <c r="D211" s="4" t="s">
-        <v>723</v>
+        <v>730</v>
       </c>
       <c r="E211" s="4"/>
       <c r="F211" s="4"/>
@@ -11196,10 +11238,10 @@
       <c r="J211" s="4"/>
       <c r="K211" s="4"/>
       <c r="L211" s="4" t="s">
-        <v>724</v>
+        <v>731</v>
       </c>
       <c r="M211" s="4" t="s">
-        <v>725</v>
+        <v>732</v>
       </c>
       <c r="N211" s="4"/>
       <c r="O211" s="4" t="s">
@@ -11208,14 +11250,14 @@
     </row>
     <row r="212" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A212" s="4" t="s">
-        <v>713</v>
+        <v>720</v>
       </c>
       <c r="B212" s="4" t="s">
-        <v>722</v>
+        <v>729</v>
       </c>
       <c r="C212" s="4"/>
       <c r="D212" s="4" t="s">
-        <v>726</v>
+        <v>733</v>
       </c>
       <c r="E212" s="4"/>
       <c r="F212" s="4"/>
@@ -11229,10 +11271,10 @@
       <c r="J212" s="4"/>
       <c r="K212" s="4"/>
       <c r="L212" s="4" t="s">
-        <v>727</v>
+        <v>734</v>
       </c>
       <c r="M212" s="4" t="s">
-        <v>725</v>
+        <v>732</v>
       </c>
       <c r="N212" s="4"/>
       <c r="O212" s="4" t="s">
@@ -11241,27 +11283,27 @@
     </row>
     <row r="213" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A213" s="4" t="s">
-        <v>728</v>
+        <v>735</v>
       </c>
       <c r="B213" s="4" t="s">
-        <v>729</v>
+        <v>736</v>
       </c>
       <c r="C213" s="4" t="s">
-        <v>730</v>
+        <v>737</v>
       </c>
       <c r="D213" s="4" t="s">
-        <v>731</v>
+        <v>738</v>
       </c>
       <c r="E213" s="4"/>
       <c r="F213" s="4"/>
       <c r="G213" s="4" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="H213" s="4" t="s">
         <v>36</v>
       </c>
       <c r="I213" s="4" t="s">
-        <v>732</v>
+        <v>739</v>
       </c>
       <c r="J213" s="4"/>
       <c r="K213" s="4"/>
@@ -11278,30 +11320,30 @@
     </row>
     <row r="214" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A214" s="4" t="s">
-        <v>728</v>
+        <v>735</v>
       </c>
       <c r="B214" s="4" t="s">
-        <v>733</v>
+        <v>740</v>
       </c>
       <c r="C214" s="4" t="s">
-        <v>730</v>
+        <v>737</v>
       </c>
       <c r="D214" s="4" t="s">
-        <v>734</v>
+        <v>741</v>
       </c>
       <c r="E214" s="4"/>
       <c r="F214" s="4"/>
       <c r="G214" s="4" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="H214" s="4" t="s">
         <v>36</v>
       </c>
       <c r="I214" s="4" t="s">
-        <v>735</v>
+        <v>742</v>
       </c>
       <c r="J214" s="4" t="s">
-        <v>736</v>
+        <v>743</v>
       </c>
       <c r="K214" s="4"/>
       <c r="L214" s="4" t="s">
@@ -11317,30 +11359,30 @@
     </row>
     <row r="215" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A215" s="4" t="s">
-        <v>728</v>
+        <v>735</v>
       </c>
       <c r="B215" s="4" t="s">
+        <v>744</v>
+      </c>
+      <c r="C215" s="4" t="s">
         <v>737</v>
       </c>
-      <c r="C215" s="4" t="s">
-        <v>730</v>
-      </c>
       <c r="D215" s="4" t="s">
-        <v>738</v>
+        <v>745</v>
       </c>
       <c r="E215" s="4"/>
       <c r="F215" s="4"/>
       <c r="G215" s="4" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="H215" s="4" t="s">
         <v>36</v>
       </c>
       <c r="I215" s="4" t="s">
-        <v>739</v>
+        <v>746</v>
       </c>
       <c r="J215" s="4" t="s">
-        <v>740</v>
+        <v>747</v>
       </c>
       <c r="K215" s="4"/>
       <c r="L215" s="4" t="s">
@@ -11356,30 +11398,30 @@
     </row>
     <row r="216" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A216" s="4" t="s">
-        <v>728</v>
+        <v>735</v>
       </c>
       <c r="B216" s="4" t="s">
-        <v>741</v>
+        <v>748</v>
       </c>
       <c r="C216" s="4" t="s">
-        <v>730</v>
+        <v>737</v>
       </c>
       <c r="D216" s="4" t="s">
-        <v>742</v>
+        <v>749</v>
       </c>
       <c r="E216" s="4"/>
       <c r="F216" s="4"/>
       <c r="G216" s="4" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="H216" s="4" t="s">
         <v>36</v>
       </c>
       <c r="I216" s="4" t="s">
-        <v>743</v>
+        <v>750</v>
       </c>
       <c r="J216" s="4" t="s">
-        <v>744</v>
+        <v>751</v>
       </c>
       <c r="K216" s="4"/>
       <c r="L216" s="4" t="s">
@@ -11395,30 +11437,30 @@
     </row>
     <row r="217" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A217" s="4" t="s">
-        <v>728</v>
+        <v>735</v>
       </c>
       <c r="B217" s="4" t="s">
-        <v>745</v>
+        <v>752</v>
       </c>
       <c r="C217" s="4" t="s">
-        <v>730</v>
+        <v>737</v>
       </c>
       <c r="D217" s="4" t="s">
-        <v>746</v>
+        <v>753</v>
       </c>
       <c r="E217" s="4"/>
       <c r="F217" s="4"/>
       <c r="G217" s="4" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="H217" s="4" t="s">
         <v>36</v>
       </c>
       <c r="I217" s="4" t="s">
-        <v>747</v>
+        <v>754</v>
       </c>
       <c r="J217" s="4" t="s">
-        <v>748</v>
+        <v>755</v>
       </c>
       <c r="K217" s="4"/>
       <c r="L217" s="4" t="s">
@@ -11434,30 +11476,30 @@
     </row>
     <row r="218" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A218" s="4" t="s">
-        <v>728</v>
+        <v>735</v>
       </c>
       <c r="B218" s="4" t="s">
         <v>89</v>
       </c>
       <c r="C218" s="4" t="s">
-        <v>730</v>
+        <v>737</v>
       </c>
       <c r="D218" s="4" t="s">
-        <v>749</v>
+        <v>756</v>
       </c>
       <c r="E218" s="4"/>
       <c r="F218" s="4"/>
       <c r="G218" s="4" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="H218" s="4" t="s">
         <v>36</v>
       </c>
       <c r="I218" s="4" t="s">
-        <v>750</v>
+        <v>757</v>
       </c>
       <c r="J218" s="4" t="s">
-        <v>751</v>
+        <v>758</v>
       </c>
       <c r="K218" s="4"/>
       <c r="L218" s="4" t="s">
@@ -11473,19 +11515,19 @@
     </row>
     <row r="219" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A219" s="4" t="s">
-        <v>728</v>
+        <v>735</v>
       </c>
       <c r="B219" s="4" t="s">
-        <v>752</v>
+        <v>759</v>
       </c>
       <c r="C219" s="4"/>
       <c r="D219" s="4" t="s">
-        <v>753</v>
+        <v>760</v>
       </c>
       <c r="E219" s="4"/>
       <c r="F219" s="4"/>
       <c r="G219" s="4" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="H219" s="4" t="s">
         <v>36</v>
@@ -11494,7 +11536,7 @@
       <c r="J219" s="4"/>
       <c r="K219" s="4"/>
       <c r="L219" s="4" t="s">
-        <v>754</v>
+        <v>761</v>
       </c>
       <c r="M219" s="4" t="s">
         <v>30</v>
@@ -11506,19 +11548,19 @@
     </row>
     <row r="220" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A220" s="4" t="s">
-        <v>728</v>
+        <v>735</v>
       </c>
       <c r="B220" s="4" t="s">
-        <v>755</v>
+        <v>762</v>
       </c>
       <c r="C220" s="4"/>
       <c r="D220" s="4" t="s">
-        <v>756</v>
+        <v>763</v>
       </c>
       <c r="E220" s="4"/>
       <c r="F220" s="4"/>
       <c r="G220" s="4" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="H220" s="4" t="s">
         <v>36</v>
@@ -11527,7 +11569,7 @@
       <c r="J220" s="4"/>
       <c r="K220" s="4"/>
       <c r="L220" s="4" t="s">
-        <v>757</v>
+        <v>764</v>
       </c>
       <c r="M220" s="4" t="s">
         <v>69</v>
@@ -11539,19 +11581,19 @@
     </row>
     <row r="221" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A221" s="4" t="s">
-        <v>728</v>
+        <v>735</v>
       </c>
       <c r="B221" s="4" t="s">
-        <v>758</v>
+        <v>765</v>
       </c>
       <c r="C221" s="4"/>
       <c r="D221" s="4" t="s">
-        <v>759</v>
+        <v>766</v>
       </c>
       <c r="E221" s="4"/>
       <c r="F221" s="4"/>
       <c r="G221" s="4" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="H221" s="4" t="s">
         <v>36</v>
@@ -11560,7 +11602,7 @@
       <c r="J221" s="4"/>
       <c r="K221" s="4"/>
       <c r="L221" s="4" t="s">
-        <v>760</v>
+        <v>767</v>
       </c>
       <c r="M221" s="4" t="s">
         <v>30</v>
@@ -11572,19 +11614,19 @@
     </row>
     <row r="222" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A222" s="4" t="s">
-        <v>761</v>
+        <v>768</v>
       </c>
       <c r="B222" s="4" t="s">
-        <v>762</v>
+        <v>769</v>
       </c>
       <c r="C222" s="4"/>
       <c r="D222" s="4" t="s">
-        <v>763</v>
+        <v>770</v>
       </c>
       <c r="E222" s="4"/>
       <c r="F222" s="4"/>
       <c r="G222" s="4" t="s">
-        <v>764</v>
+        <v>771</v>
       </c>
       <c r="H222" s="4" t="s">
         <v>36</v>
@@ -11593,7 +11635,7 @@
       <c r="J222" s="4"/>
       <c r="K222" s="4"/>
       <c r="L222" s="4" t="s">
-        <v>765</v>
+        <v>772</v>
       </c>
       <c r="M222" s="4" t="s">
         <v>30</v>
@@ -11605,19 +11647,19 @@
     </row>
     <row r="223" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A223" s="4" t="s">
-        <v>761</v>
+        <v>768</v>
       </c>
       <c r="B223" s="4" t="s">
-        <v>766</v>
+        <v>773</v>
       </c>
       <c r="C223" s="4"/>
       <c r="D223" s="4" t="s">
-        <v>767</v>
+        <v>774</v>
       </c>
       <c r="E223" s="4"/>
       <c r="F223" s="4"/>
       <c r="G223" s="4" t="s">
-        <v>768</v>
+        <v>775</v>
       </c>
       <c r="H223" s="4" t="s">
         <v>36</v>
@@ -11626,7 +11668,7 @@
       <c r="J223" s="4"/>
       <c r="K223" s="4"/>
       <c r="L223" s="4" t="s">
-        <v>769</v>
+        <v>776</v>
       </c>
       <c r="M223" s="4" t="s">
         <v>30</v>
@@ -11638,19 +11680,19 @@
     </row>
     <row r="224" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A224" s="4" t="s">
-        <v>761</v>
+        <v>768</v>
       </c>
       <c r="B224" s="4" t="s">
-        <v>770</v>
+        <v>777</v>
       </c>
       <c r="C224" s="4"/>
       <c r="D224" s="4" t="s">
-        <v>771</v>
+        <v>778</v>
       </c>
       <c r="E224" s="4"/>
       <c r="F224" s="4"/>
       <c r="G224" s="4" t="s">
-        <v>768</v>
+        <v>775</v>
       </c>
       <c r="H224" s="4" t="s">
         <v>36</v>
@@ -11659,7 +11701,7 @@
       <c r="J224" s="4"/>
       <c r="K224" s="4"/>
       <c r="L224" s="4" t="s">
-        <v>772</v>
+        <v>779</v>
       </c>
       <c r="M224" s="4" t="s">
         <v>30</v>
@@ -11671,19 +11713,19 @@
     </row>
     <row r="225" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A225" s="4" t="s">
-        <v>761</v>
+        <v>768</v>
       </c>
       <c r="B225" s="4" t="s">
-        <v>773</v>
+        <v>780</v>
       </c>
       <c r="C225" s="4"/>
       <c r="D225" s="4" t="s">
-        <v>774</v>
+        <v>781</v>
       </c>
       <c r="E225" s="4"/>
       <c r="F225" s="4"/>
       <c r="G225" s="4" t="s">
-        <v>775</v>
+        <v>782</v>
       </c>
       <c r="H225" s="4" t="s">
         <v>36</v>
@@ -11692,7 +11734,7 @@
       <c r="J225" s="4"/>
       <c r="K225" s="4"/>
       <c r="L225" s="4" t="s">
-        <v>776</v>
+        <v>783</v>
       </c>
       <c r="M225" s="4" t="s">
         <v>30</v>
@@ -11704,19 +11746,19 @@
     </row>
     <row r="226" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A226" s="4" t="s">
-        <v>761</v>
+        <v>768</v>
       </c>
       <c r="B226" s="4" t="s">
-        <v>777</v>
+        <v>784</v>
       </c>
       <c r="C226" s="4"/>
       <c r="D226" s="4" t="s">
-        <v>778</v>
+        <v>785</v>
       </c>
       <c r="E226" s="4"/>
       <c r="F226" s="4"/>
       <c r="G226" s="4" t="s">
-        <v>779</v>
+        <v>786</v>
       </c>
       <c r="H226" s="4" t="s">
         <v>36</v>
@@ -11725,7 +11767,7 @@
       <c r="J226" s="4"/>
       <c r="K226" s="4"/>
       <c r="L226" s="4" t="s">
-        <v>780</v>
+        <v>787</v>
       </c>
       <c r="M226" s="4" t="s">
         <v>30</v>
@@ -11737,19 +11779,19 @@
     </row>
     <row r="227" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A227" s="4" t="s">
-        <v>781</v>
+        <v>788</v>
       </c>
       <c r="B227" s="4" t="s">
-        <v>782</v>
+        <v>789</v>
       </c>
       <c r="C227" s="4"/>
       <c r="D227" s="4" t="s">
-        <v>783</v>
+        <v>790</v>
       </c>
       <c r="E227" s="4"/>
       <c r="F227" s="4"/>
       <c r="G227" s="4" t="s">
-        <v>626</v>
+        <v>631</v>
       </c>
       <c r="H227" s="4" t="s">
         <v>36</v>
@@ -11772,19 +11814,19 @@
     </row>
     <row r="228" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A228" s="4" t="s">
-        <v>781</v>
+        <v>788</v>
       </c>
       <c r="B228" s="4" t="s">
-        <v>784</v>
+        <v>791</v>
       </c>
       <c r="C228" s="4"/>
       <c r="D228" s="4" t="s">
-        <v>785</v>
+        <v>792</v>
       </c>
       <c r="E228" s="4"/>
       <c r="F228" s="4"/>
       <c r="G228" s="4" t="s">
-        <v>626</v>
+        <v>631</v>
       </c>
       <c r="H228" s="4" t="s">
         <v>36</v>
@@ -11807,16 +11849,16 @@
     </row>
     <row r="229" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A229" s="4" t="s">
-        <v>781</v>
+        <v>788</v>
       </c>
       <c r="B229" s="4" t="s">
-        <v>786</v>
+        <v>793</v>
       </c>
       <c r="C229" s="4" t="s">
-        <v>603</v>
+        <v>608</v>
       </c>
       <c r="D229" s="4" t="s">
-        <v>787</v>
+        <v>794</v>
       </c>
       <c r="E229" s="4"/>
       <c r="F229" s="4"/>
@@ -11827,7 +11869,7 @@
         <v>36</v>
       </c>
       <c r="I229" s="4" t="s">
-        <v>788</v>
+        <v>795</v>
       </c>
       <c r="J229" s="4"/>
       <c r="K229" s="4"/>
@@ -11846,14 +11888,14 @@
     </row>
     <row r="230" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A230" s="4" t="s">
-        <v>781</v>
+        <v>788</v>
       </c>
       <c r="B230" s="4" t="s">
-        <v>789</v>
+        <v>796</v>
       </c>
       <c r="C230" s="4"/>
       <c r="D230" s="4" t="s">
-        <v>790</v>
+        <v>797</v>
       </c>
       <c r="E230" s="4"/>
       <c r="F230" s="4"/>
@@ -11867,7 +11909,7 @@
       <c r="J230" s="4"/>
       <c r="K230" s="4"/>
       <c r="L230" s="4" t="s">
-        <v>791</v>
+        <v>798</v>
       </c>
       <c r="M230" s="4" t="s">
         <v>69</v>
@@ -11881,14 +11923,14 @@
     </row>
     <row r="231" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A231" s="4" t="s">
-        <v>781</v>
+        <v>788</v>
       </c>
       <c r="B231" s="4" t="s">
-        <v>792</v>
+        <v>799</v>
       </c>
       <c r="C231" s="4"/>
       <c r="D231" s="4" t="s">
-        <v>793</v>
+        <v>800</v>
       </c>
       <c r="E231" s="4"/>
       <c r="F231" s="4"/>
@@ -11902,7 +11944,7 @@
       <c r="J231" s="4"/>
       <c r="K231" s="4"/>
       <c r="L231" s="4" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="M231" s="4" t="s">
         <v>69</v>
@@ -11916,14 +11958,14 @@
     </row>
     <row r="232" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A232" s="4" t="s">
-        <v>781</v>
+        <v>788</v>
       </c>
       <c r="B232" s="4" t="s">
-        <v>794</v>
+        <v>801</v>
       </c>
       <c r="C232" s="4"/>
       <c r="D232" s="4" t="s">
-        <v>795</v>
+        <v>802</v>
       </c>
       <c r="E232" s="4"/>
       <c r="F232" s="4"/>
@@ -11937,7 +11979,7 @@
       <c r="J232" s="4"/>
       <c r="K232" s="4"/>
       <c r="L232" s="4" t="s">
-        <v>796</v>
+        <v>803</v>
       </c>
       <c r="M232" s="4" t="s">
         <v>69</v>
@@ -11951,14 +11993,14 @@
     </row>
     <row r="233" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A233" s="4" t="s">
-        <v>781</v>
+        <v>788</v>
       </c>
       <c r="B233" s="4" t="s">
-        <v>797</v>
+        <v>804</v>
       </c>
       <c r="C233" s="4"/>
       <c r="D233" s="4" t="s">
-        <v>798</v>
+        <v>805</v>
       </c>
       <c r="E233" s="4"/>
       <c r="F233" s="4"/>
@@ -11986,34 +12028,34 @@
     </row>
     <row r="234" ht="15" customHeight="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A234" s="4" t="s">
-        <v>799</v>
+        <v>806</v>
       </c>
       <c r="B234" s="4" t="s">
-        <v>800</v>
+        <v>807</v>
       </c>
       <c r="C234" s="4" t="s">
-        <v>801</v>
+        <v>808</v>
       </c>
       <c r="D234" s="4" t="s">
-        <v>802</v>
+        <v>809</v>
       </c>
       <c r="E234" s="4"/>
       <c r="F234" s="4" t="s">
-        <v>803</v>
+        <v>810</v>
       </c>
       <c r="G234" s="4" t="s">
-        <v>804</v>
+        <v>811</v>
       </c>
       <c r="H234" s="4" t="s">
-        <v>805</v>
+        <v>336</v>
       </c>
       <c r="I234" s="4" t="s">
-        <v>806</v>
+        <v>812</v>
       </c>
       <c r="J234" s="4"/>
       <c r="K234" s="4"/>
       <c r="L234" s="4" t="s">
-        <v>807</v>
+        <v>813</v>
       </c>
       <c r="M234" s="4" t="s">
         <v>69</v>
@@ -12027,34 +12069,37 @@
     </row>
     <row r="235" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A235" s="1" t="s">
-        <v>808</v>
+        <v>814</v>
       </c>
       <c r="B235" s="1" t="s">
-        <v>660</v>
+        <v>666</v>
       </c>
       <c r="C235" s="1" t="s">
-        <v>809</v>
+        <v>815</v>
       </c>
       <c r="D235" s="1" t="s">
-        <v>810</v>
+        <v>816</v>
       </c>
       <c r="F235" s="1" t="s">
-        <v>811</v>
+        <v>817</v>
       </c>
       <c r="G235" s="1" t="s">
-        <v>812</v>
+        <v>818</v>
       </c>
       <c r="H235" s="1" t="s">
-        <v>336</v>
+        <v>405</v>
       </c>
       <c r="I235" s="1" t="s">
-        <v>813</v>
+        <v>819</v>
       </c>
       <c r="J235" s="1" t="s">
-        <v>814</v>
+        <v>820</v>
       </c>
       <c r="L235" s="1" t="s">
-        <v>815</v>
+        <v>821</v>
+      </c>
+      <c r="M235" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="O235" s="1" t="s">
         <v>43</v>
@@ -12062,28 +12107,28 @@
     </row>
     <row r="236" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A236" s="1" t="s">
-        <v>816</v>
+        <v>822</v>
       </c>
       <c r="B236" s="1" t="s">
-        <v>660</v>
+        <v>666</v>
       </c>
       <c r="C236" s="1" t="s">
-        <v>817</v>
+        <v>823</v>
       </c>
       <c r="D236" s="1" t="s">
-        <v>818</v>
+        <v>824</v>
       </c>
       <c r="F236" s="1" t="s">
-        <v>819</v>
+        <v>825</v>
       </c>
       <c r="G236" s="1" t="s">
-        <v>820</v>
+        <v>826</v>
       </c>
       <c r="H236" s="1" t="s">
         <v>36</v>
       </c>
       <c r="L236" s="1" t="s">
-        <v>821</v>
+        <v>827</v>
       </c>
       <c r="O236" s="1" t="s">
         <v>43</v>
@@ -12091,25 +12136,25 @@
     </row>
     <row r="237" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A237" s="1" t="s">
-        <v>822</v>
+        <v>828</v>
       </c>
       <c r="B237" s="1" t="s">
-        <v>660</v>
+        <v>666</v>
       </c>
       <c r="C237" s="1" t="s">
-        <v>823</v>
+        <v>829</v>
       </c>
       <c r="D237" s="1" t="s">
-        <v>824</v>
+        <v>830</v>
       </c>
       <c r="G237" s="1" t="s">
-        <v>825</v>
+        <v>831</v>
       </c>
       <c r="H237" s="1" t="s">
         <v>36</v>
       </c>
       <c r="L237" s="1" t="s">
-        <v>826</v>
+        <v>832</v>
       </c>
       <c r="O237" s="1" t="s">
         <v>43</v>
@@ -12117,28 +12162,28 @@
     </row>
     <row r="238" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A238" s="1" t="s">
-        <v>827</v>
+        <v>833</v>
       </c>
       <c r="B238" s="1" t="s">
-        <v>660</v>
+        <v>666</v>
       </c>
       <c r="C238" s="1" t="s">
-        <v>823</v>
+        <v>829</v>
       </c>
       <c r="D238" s="1" t="s">
-        <v>828</v>
+        <v>834</v>
       </c>
       <c r="F238" s="1" t="s">
-        <v>829</v>
+        <v>835</v>
       </c>
       <c r="G238" s="1" t="s">
-        <v>830</v>
+        <v>836</v>
       </c>
       <c r="H238" s="1" t="s">
         <v>36</v>
       </c>
       <c r="L238" s="1" t="s">
-        <v>831</v>
+        <v>837</v>
       </c>
       <c r="O238" s="1" t="s">
         <v>43</v>
@@ -12146,60 +12191,66 @@
     </row>
     <row r="239" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A239" s="1" t="s">
-        <v>832</v>
+        <v>838</v>
       </c>
       <c r="B239" s="1" t="s">
-        <v>833</v>
+        <v>839</v>
       </c>
       <c r="C239" s="1" t="s">
         <v>126</v>
       </c>
       <c r="D239" s="1" t="s">
-        <v>834</v>
+        <v>840</v>
       </c>
       <c r="F239" s="1" t="s">
-        <v>835</v>
+        <v>841</v>
       </c>
       <c r="G239" s="1" t="s">
-        <v>836</v>
+        <v>842</v>
       </c>
       <c r="H239" s="1" t="s">
         <v>336</v>
       </c>
       <c r="I239" s="1" t="s">
-        <v>837</v>
+        <v>843</v>
       </c>
       <c r="J239" s="1" t="s">
-        <v>838</v>
+        <v>844</v>
       </c>
       <c r="L239" s="1" t="s">
-        <v>839</v>
+        <v>845</v>
+      </c>
+      <c r="M239" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="N239" s="1" t="s">
+        <v>846</v>
       </c>
       <c r="O239" s="1" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
     </row>
     <row r="240" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A240" s="1" t="s">
-        <v>840</v>
+        <v>847</v>
       </c>
       <c r="B240" s="1" t="s">
-        <v>841</v>
+        <v>848</v>
       </c>
       <c r="C240" s="1" t="s">
-        <v>842</v>
+        <v>849</v>
       </c>
       <c r="D240" s="1" t="s">
-        <v>843</v>
+        <v>850</v>
       </c>
       <c r="G240" s="1" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
       <c r="H240" s="1" t="s">
         <v>36</v>
       </c>
       <c r="L240" s="1" t="s">
-        <v>845</v>
+        <v>852</v>
       </c>
       <c r="O240" s="1" t="s">
         <v>31</v>
@@ -12207,60 +12258,66 @@
     </row>
     <row r="241" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A241" s="1" t="s">
-        <v>846</v>
+        <v>853</v>
       </c>
       <c r="B241" s="1" t="s">
-        <v>660</v>
+        <v>666</v>
       </c>
       <c r="C241" s="1" t="s">
-        <v>817</v>
+        <v>823</v>
       </c>
       <c r="D241" s="1" t="s">
-        <v>847</v>
+        <v>854</v>
       </c>
       <c r="G241" s="1" t="s">
-        <v>848</v>
+        <v>855</v>
       </c>
       <c r="H241" s="1" t="s">
         <v>336</v>
       </c>
       <c r="I241" s="1" t="s">
-        <v>849</v>
+        <v>856</v>
       </c>
       <c r="J241" s="1" t="s">
-        <v>850</v>
+        <v>857</v>
       </c>
       <c r="L241" s="1" t="s">
-        <v>851</v>
+        <v>858</v>
+      </c>
+      <c r="M241" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="N241" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="O241" s="1" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
     </row>
     <row r="242" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A242" s="1" t="s">
-        <v>852</v>
+        <v>859</v>
       </c>
       <c r="B242" s="1" t="s">
-        <v>853</v>
+        <v>860</v>
       </c>
       <c r="C242" s="1" t="s">
-        <v>854</v>
+        <v>861</v>
       </c>
       <c r="D242" s="1" t="s">
-        <v>855</v>
+        <v>862</v>
       </c>
       <c r="F242" s="1" t="s">
-        <v>856</v>
+        <v>863</v>
       </c>
       <c r="G242" s="1" t="s">
-        <v>857</v>
+        <v>864</v>
       </c>
       <c r="H242" s="1" t="s">
         <v>36</v>
       </c>
       <c r="L242" s="1" t="s">
-        <v>858</v>
+        <v>865</v>
       </c>
       <c r="O242" s="1" t="s">
         <v>31</v>
@@ -12268,28 +12325,28 @@
     </row>
     <row r="243" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A243" s="1" t="s">
-        <v>859</v>
+        <v>866</v>
       </c>
       <c r="B243" s="1" t="s">
-        <v>853</v>
+        <v>860</v>
       </c>
       <c r="C243" s="1" t="s">
-        <v>817</v>
+        <v>823</v>
       </c>
       <c r="D243" s="1" t="s">
-        <v>860</v>
+        <v>867</v>
       </c>
       <c r="F243" s="1" t="s">
-        <v>861</v>
+        <v>868</v>
       </c>
       <c r="G243" s="1" t="s">
-        <v>862</v>
+        <v>869</v>
       </c>
       <c r="H243" s="1" t="s">
         <v>36</v>
       </c>
       <c r="L243" s="1" t="s">
-        <v>863</v>
+        <v>870</v>
       </c>
       <c r="O243" s="1" t="s">
         <v>31</v>
@@ -12297,32 +12354,32 @@
     </row>
     <row r="244" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A244" s="1" t="s">
-        <v>864</v>
+        <v>871</v>
       </c>
       <c r="B244" s="1" t="s">
-        <v>865</v>
+        <v>872</v>
       </c>
       <c r="C244" s="1" t="s">
-        <v>866</v>
+        <v>873</v>
       </c>
       <c r="D244" s="1" t="s">
-        <v>867</v>
+        <v>874</v>
       </c>
       <c r="F244" s="1"/>
       <c r="G244" s="1" t="s">
-        <v>868</v>
+        <v>875</v>
       </c>
       <c r="H244" s="1" t="s">
         <v>336</v>
       </c>
       <c r="I244" s="1" t="s">
-        <v>869</v>
+        <v>876</v>
       </c>
       <c r="J244" s="1" t="s">
-        <v>870</v>
+        <v>877</v>
       </c>
       <c r="L244" s="1" t="s">
-        <v>871</v>
+        <v>878</v>
       </c>
       <c r="M244" s="1" t="s">
         <v>22</v>
@@ -12336,39 +12393,41 @@
     </row>
     <row r="245" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A245" s="1" t="s">
-        <v>872</v>
+        <v>879</v>
       </c>
       <c r="B245" s="1" t="s">
-        <v>873</v>
+        <v>880</v>
       </c>
       <c r="C245" s="1" t="s">
-        <v>817</v>
+        <v>823</v>
       </c>
       <c r="D245" s="1" t="s">
-        <v>874</v>
+        <v>881</v>
       </c>
       <c r="E245" s="1"/>
       <c r="F245" s="1" t="s">
-        <v>875</v>
+        <v>882</v>
       </c>
       <c r="G245" s="1" t="s">
-        <v>876</v>
+        <v>883</v>
       </c>
       <c r="H245" s="1" t="s">
-        <v>336</v>
+        <v>20</v>
       </c>
       <c r="I245" s="1" t="s">
-        <v>877</v>
+        <v>884</v>
       </c>
       <c r="J245" s="1" t="s">
-        <v>878</v>
-      </c>
-      <c r="K245" s="1"/>
+        <v>885</v>
+      </c>
+      <c r="K245" s="1">
+        <v>46301</v>
+      </c>
       <c r="L245" s="1" t="s">
-        <v>879</v>
+        <v>886</v>
       </c>
       <c r="M245" s="1" t="s">
-        <v>880</v>
+        <v>887</v>
       </c>
       <c r="N245" s="1"/>
       <c r="O245" s="1" t="s">
@@ -12377,21 +12436,21 @@
     </row>
     <row r="246" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A246" s="1" t="s">
-        <v>881</v>
+        <v>888</v>
       </c>
       <c r="B246" s="1" t="s">
-        <v>882</v>
+        <v>889</v>
       </c>
       <c r="C246" s="1" t="s">
-        <v>817</v>
+        <v>823</v>
       </c>
       <c r="D246" s="1" t="s">
-        <v>883</v>
+        <v>890</v>
       </c>
       <c r="E246" s="1"/>
       <c r="F246" s="1"/>
       <c r="G246" s="1" t="s">
-        <v>884</v>
+        <v>891</v>
       </c>
       <c r="H246" s="1" t="s">
         <v>36</v>
@@ -12400,10 +12459,10 @@
       <c r="J246" s="1"/>
       <c r="K246" s="1"/>
       <c r="L246" s="1" t="s">
-        <v>885</v>
+        <v>892</v>
       </c>
       <c r="M246" s="1" t="s">
-        <v>880</v>
+        <v>887</v>
       </c>
       <c r="N246" s="1"/>
       <c r="O246" s="1" t="s">
@@ -12412,25 +12471,25 @@
     </row>
     <row r="247" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A247" s="1" t="s">
-        <v>886</v>
+        <v>893</v>
       </c>
       <c r="B247" s="1" t="s">
-        <v>887</v>
+        <v>894</v>
       </c>
       <c r="C247" s="1" t="s">
-        <v>817</v>
+        <v>823</v>
       </c>
       <c r="D247" s="1" t="s">
-        <v>888</v>
+        <v>895</v>
       </c>
       <c r="E247" s="1" t="s">
-        <v>889</v>
+        <v>896</v>
       </c>
       <c r="F247" s="1" t="s">
-        <v>890</v>
+        <v>897</v>
       </c>
       <c r="G247" s="1" t="s">
-        <v>891</v>
+        <v>898</v>
       </c>
       <c r="H247" s="1" t="s">
         <v>36</v>
@@ -12439,10 +12498,10 @@
       <c r="J247" s="1"/>
       <c r="K247" s="1"/>
       <c r="L247" s="1" t="s">
-        <v>892</v>
+        <v>899</v>
       </c>
       <c r="M247" s="1" t="s">
-        <v>880</v>
+        <v>887</v>
       </c>
       <c r="N247" s="1"/>
       <c r="O247" s="1" t="s">
@@ -12451,25 +12510,25 @@
     </row>
     <row r="248" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A248" s="1" t="s">
-        <v>893</v>
+        <v>900</v>
       </c>
       <c r="B248" s="1" t="s">
-        <v>660</v>
+        <v>666</v>
       </c>
       <c r="C248" s="1" t="s">
-        <v>817</v>
+        <v>823</v>
       </c>
       <c r="D248" s="1" t="s">
-        <v>894</v>
+        <v>901</v>
       </c>
       <c r="E248" s="1" t="s">
-        <v>889</v>
+        <v>896</v>
       </c>
       <c r="F248" s="1" t="s">
-        <v>895</v>
+        <v>902</v>
       </c>
       <c r="G248" s="1" t="s">
-        <v>896</v>
+        <v>903</v>
       </c>
       <c r="H248" s="1" t="s">
         <v>36</v>
@@ -12478,10 +12537,10 @@
       <c r="J248" s="1"/>
       <c r="K248" s="1"/>
       <c r="L248" s="1" t="s">
-        <v>897</v>
+        <v>904</v>
       </c>
       <c r="M248" s="1" t="s">
-        <v>880</v>
+        <v>887</v>
       </c>
       <c r="N248" s="1"/>
       <c r="O248" s="1" t="s">
@@ -12490,25 +12549,25 @@
     </row>
     <row r="249" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A249" s="1" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="B249" s="1" t="s">
-        <v>660</v>
+        <v>666</v>
       </c>
       <c r="C249" s="1" t="s">
-        <v>817</v>
+        <v>823</v>
       </c>
       <c r="D249" s="1" t="s">
-        <v>899</v>
+        <v>906</v>
       </c>
       <c r="E249" s="1" t="s">
-        <v>889</v>
+        <v>896</v>
       </c>
       <c r="F249" s="1" t="s">
-        <v>900</v>
+        <v>907</v>
       </c>
       <c r="G249" s="1" t="s">
-        <v>901</v>
+        <v>908</v>
       </c>
       <c r="H249" s="1" t="s">
         <v>36</v>
@@ -12517,10 +12576,10 @@
       <c r="J249" s="1"/>
       <c r="K249" s="1"/>
       <c r="L249" s="1" t="s">
-        <v>902</v>
+        <v>909</v>
       </c>
       <c r="M249" s="1" t="s">
-        <v>880</v>
+        <v>887</v>
       </c>
       <c r="N249" s="1"/>
       <c r="O249" s="1" t="s">
@@ -12529,37 +12588,37 @@
     </row>
     <row r="250" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A250" s="1" t="s">
-        <v>903</v>
+        <v>910</v>
       </c>
       <c r="B250" s="1" t="s">
-        <v>660</v>
+        <v>666</v>
       </c>
       <c r="C250" s="1" t="s">
-        <v>823</v>
+        <v>829</v>
       </c>
       <c r="D250" s="1" t="s">
-        <v>904</v>
+        <v>911</v>
       </c>
       <c r="E250" s="1" t="s">
-        <v>889</v>
+        <v>896</v>
       </c>
       <c r="F250" s="1" t="s">
-        <v>905</v>
+        <v>912</v>
       </c>
       <c r="G250" s="1" t="s">
-        <v>906</v>
+        <v>913</v>
       </c>
       <c r="H250" s="1" t="s">
-        <v>907</v>
+        <v>914</v>
       </c>
       <c r="I250" s="1"/>
       <c r="J250" s="1"/>
       <c r="K250" s="1"/>
       <c r="L250" s="1" t="s">
-        <v>908</v>
+        <v>915</v>
       </c>
       <c r="M250" s="1" t="s">
-        <v>880</v>
+        <v>887</v>
       </c>
       <c r="N250" s="1"/>
       <c r="O250" s="1" t="s">
@@ -12568,41 +12627,41 @@
     </row>
     <row r="251" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A251" s="1" t="s">
-        <v>909</v>
+        <v>916</v>
       </c>
       <c r="B251" s="1" t="s">
-        <v>660</v>
+        <v>666</v>
       </c>
       <c r="C251" s="1" t="s">
-        <v>817</v>
+        <v>823</v>
       </c>
       <c r="D251" s="1" t="s">
-        <v>910</v>
+        <v>917</v>
       </c>
       <c r="E251" s="1" t="s">
-        <v>889</v>
+        <v>896</v>
       </c>
       <c r="F251" s="1" t="s">
-        <v>911</v>
+        <v>918</v>
       </c>
       <c r="G251" s="1" t="s">
-        <v>912</v>
+        <v>919</v>
       </c>
       <c r="H251" s="1" t="s">
-        <v>336</v>
+        <v>405</v>
       </c>
       <c r="I251" s="1" t="s">
-        <v>913</v>
+        <v>920</v>
       </c>
       <c r="J251" s="1" t="s">
-        <v>914</v>
+        <v>921</v>
       </c>
       <c r="K251" s="1"/>
       <c r="L251" s="1" t="s">
-        <v>915</v>
+        <v>922</v>
       </c>
       <c r="M251" s="1" t="s">
-        <v>880</v>
+        <v>887</v>
       </c>
       <c r="N251" s="1"/>
       <c r="O251" s="1" t="s">
@@ -12611,25 +12670,25 @@
     </row>
     <row r="252" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A252" s="1" t="s">
-        <v>916</v>
+        <v>923</v>
       </c>
       <c r="B252" s="1" t="s">
-        <v>660</v>
+        <v>666</v>
       </c>
       <c r="C252" s="1" t="s">
-        <v>817</v>
+        <v>823</v>
       </c>
       <c r="D252" s="1" t="s">
-        <v>917</v>
+        <v>924</v>
       </c>
       <c r="E252" s="1" t="s">
-        <v>889</v>
+        <v>896</v>
       </c>
       <c r="F252" s="1" t="s">
-        <v>918</v>
+        <v>925</v>
       </c>
       <c r="G252" s="1" t="s">
-        <v>919</v>
+        <v>926</v>
       </c>
       <c r="H252" s="1" t="s">
         <v>36</v>
@@ -12638,10 +12697,10 @@
       <c r="J252" s="1"/>
       <c r="K252" s="1"/>
       <c r="L252" s="1" t="s">
-        <v>920</v>
+        <v>927</v>
       </c>
       <c r="M252" s="1" t="s">
-        <v>880</v>
+        <v>887</v>
       </c>
       <c r="N252" s="1"/>
       <c r="O252" s="1" t="s">
@@ -12650,26 +12709,26 @@
     </row>
     <row r="253" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A253" s="1" t="s">
-        <v>921</v>
+        <v>928</v>
       </c>
       <c r="B253" s="1" t="s">
-        <v>922</v>
+        <v>929</v>
       </c>
       <c r="C253" s="1" t="s">
         <v>126</v>
       </c>
       <c r="D253" s="1" t="s">
-        <v>923</v>
+        <v>930</v>
       </c>
       <c r="E253" s="1" t="s">
-        <v>889</v>
+        <v>896</v>
       </c>
       <c r="F253" s="1"/>
       <c r="G253" s="1" t="s">
-        <v>924</v>
+        <v>931</v>
       </c>
       <c r="H253" s="1" t="s">
-        <v>907</v>
+        <v>914</v>
       </c>
       <c r="I253" s="1"/>
       <c r="J253" s="1"/>
@@ -12683,32 +12742,32 @@
     </row>
     <row r="254" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A254" s="1" t="s">
-        <v>925</v>
+        <v>932</v>
       </c>
       <c r="B254" s="1" t="s">
-        <v>926</v>
+        <v>933</v>
       </c>
       <c r="C254" s="1" t="s">
         <v>126</v>
       </c>
       <c r="D254" s="1" t="s">
-        <v>927</v>
+        <v>934</v>
       </c>
       <c r="E254" s="1" t="s">
-        <v>889</v>
+        <v>896</v>
       </c>
       <c r="F254" s="1"/>
       <c r="G254" s="1" t="s">
-        <v>928</v>
+        <v>935</v>
       </c>
       <c r="H254" s="1" t="s">
-        <v>907</v>
+        <v>914</v>
       </c>
       <c r="I254" s="1"/>
       <c r="J254" s="1"/>
       <c r="K254" s="1"/>
       <c r="L254" s="1" t="s">
-        <v>929</v>
+        <v>936</v>
       </c>
       <c r="M254" s="1"/>
       <c r="N254" s="1"/>
@@ -12718,34 +12777,34 @@
     </row>
     <row r="255" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A255" s="1" t="s">
-        <v>930</v>
+        <v>937</v>
       </c>
       <c r="B255" s="1" t="s">
-        <v>931</v>
+        <v>938</v>
       </c>
       <c r="C255" s="1" t="s">
         <v>126</v>
       </c>
       <c r="D255" s="1" t="s">
-        <v>932</v>
+        <v>939</v>
       </c>
       <c r="E255" s="1" t="s">
-        <v>889</v>
+        <v>896</v>
       </c>
       <c r="F255" s="1" t="s">
-        <v>933</v>
+        <v>940</v>
       </c>
       <c r="G255" s="1" t="s">
-        <v>934</v>
+        <v>941</v>
       </c>
       <c r="H255" s="1" t="s">
-        <v>907</v>
+        <v>914</v>
       </c>
       <c r="I255" s="1"/>
       <c r="J255" s="1"/>
       <c r="K255" s="1"/>
       <c r="L255" s="1" t="s">
-        <v>935</v>
+        <v>942</v>
       </c>
       <c r="M255" s="1"/>
       <c r="N255" s="1"/>
@@ -12755,34 +12814,34 @@
     </row>
     <row r="256" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A256" s="1" t="s">
-        <v>936</v>
+        <v>943</v>
       </c>
       <c r="B256" s="1" t="s">
-        <v>937</v>
+        <v>944</v>
       </c>
       <c r="C256" s="1" t="s">
         <v>126</v>
       </c>
       <c r="D256" s="1" t="s">
-        <v>938</v>
+        <v>945</v>
       </c>
       <c r="E256" s="1" t="s">
-        <v>889</v>
+        <v>896</v>
       </c>
       <c r="F256" s="1" t="s">
-        <v>939</v>
+        <v>946</v>
       </c>
       <c r="G256" s="1" t="s">
-        <v>940</v>
+        <v>947</v>
       </c>
       <c r="H256" s="1" t="s">
-        <v>907</v>
+        <v>914</v>
       </c>
       <c r="I256" s="1"/>
       <c r="J256" s="1"/>
       <c r="K256" s="1"/>
       <c r="L256" s="1" t="s">
-        <v>941</v>
+        <v>948</v>
       </c>
       <c r="M256" s="1"/>
       <c r="N256" s="1"/>
@@ -12792,28 +12851,28 @@
     </row>
     <row r="257" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A257" s="1" t="s">
-        <v>942</v>
+        <v>949</v>
       </c>
       <c r="B257" s="1" t="s">
-        <v>943</v>
+        <v>950</v>
       </c>
       <c r="C257" s="1" t="s">
-        <v>944</v>
+        <v>951</v>
       </c>
       <c r="D257" s="1" t="s">
-        <v>945</v>
+        <v>952</v>
       </c>
       <c r="E257" s="1" t="s">
-        <v>889</v>
+        <v>896</v>
       </c>
       <c r="F257" s="1" t="s">
-        <v>946</v>
+        <v>953</v>
       </c>
       <c r="G257" s="1" t="s">
-        <v>947</v>
+        <v>954</v>
       </c>
       <c r="H257" s="1" t="s">
-        <v>907</v>
+        <v>914</v>
       </c>
       <c r="I257" s="1"/>
       <c r="J257" s="1"/>
@@ -12827,28 +12886,28 @@
     </row>
     <row r="258" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A258" s="1" t="s">
-        <v>948</v>
+        <v>955</v>
       </c>
       <c r="B258" s="1" t="s">
-        <v>937</v>
+        <v>944</v>
       </c>
       <c r="C258" s="1" t="s">
-        <v>949</v>
+        <v>956</v>
       </c>
       <c r="D258" s="1" t="s">
-        <v>950</v>
+        <v>957</v>
       </c>
       <c r="E258" s="1" t="s">
-        <v>889</v>
+        <v>896</v>
       </c>
       <c r="F258" s="1" t="s">
-        <v>951</v>
+        <v>958</v>
       </c>
       <c r="G258" s="1" t="s">
-        <v>952</v>
+        <v>959</v>
       </c>
       <c r="H258" s="1" t="s">
-        <v>907</v>
+        <v>914</v>
       </c>
       <c r="I258" s="1"/>
       <c r="J258" s="1"/>
@@ -12862,34 +12921,34 @@
     </row>
     <row r="259" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A259" s="1" t="s">
-        <v>930</v>
+        <v>937</v>
       </c>
       <c r="B259" s="1" t="s">
-        <v>953</v>
+        <v>960</v>
       </c>
       <c r="C259" s="1" t="s">
         <v>126</v>
       </c>
       <c r="D259" s="1" t="s">
-        <v>954</v>
+        <v>961</v>
       </c>
       <c r="E259" s="1" t="s">
-        <v>889</v>
+        <v>896</v>
       </c>
       <c r="F259" s="1" t="s">
-        <v>955</v>
+        <v>962</v>
       </c>
       <c r="G259" s="1" t="s">
-        <v>956</v>
+        <v>963</v>
       </c>
       <c r="H259" s="1" t="s">
-        <v>907</v>
+        <v>914</v>
       </c>
       <c r="I259" s="1"/>
       <c r="J259" s="1"/>
       <c r="K259" s="1"/>
       <c r="L259" s="1" t="s">
-        <v>935</v>
+        <v>942</v>
       </c>
       <c r="M259" s="1"/>
       <c r="N259" s="1"/>
@@ -12899,34 +12958,34 @@
     </row>
     <row r="260" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A260" s="1" t="s">
-        <v>957</v>
+        <v>964</v>
       </c>
       <c r="B260" s="1" t="s">
-        <v>958</v>
+        <v>965</v>
       </c>
       <c r="C260" s="1" t="s">
         <v>126</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>959</v>
+        <v>966</v>
       </c>
       <c r="E260" s="1" t="s">
-        <v>889</v>
+        <v>896</v>
       </c>
       <c r="F260" s="1" t="s">
-        <v>960</v>
+        <v>967</v>
       </c>
       <c r="G260" s="1" t="s">
-        <v>961</v>
+        <v>968</v>
       </c>
       <c r="H260" s="1" t="s">
-        <v>907</v>
+        <v>914</v>
       </c>
       <c r="I260" s="1"/>
       <c r="J260" s="1"/>
       <c r="K260" s="1"/>
       <c r="L260" s="1" t="s">
-        <v>962</v>
+        <v>969</v>
       </c>
       <c r="M260" s="1"/>
       <c r="N260" s="1"/>
@@ -12936,28 +12995,28 @@
     </row>
     <row r="261" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A261" s="1" t="s">
-        <v>963</v>
+        <v>970</v>
       </c>
       <c r="B261" s="1" t="s">
-        <v>964</v>
+        <v>971</v>
       </c>
       <c r="C261" s="1" t="s">
         <v>126</v>
       </c>
       <c r="D261" s="1" t="s">
-        <v>965</v>
+        <v>972</v>
       </c>
       <c r="E261" s="1" t="s">
-        <v>889</v>
+        <v>896</v>
       </c>
       <c r="F261" s="1" t="s">
-        <v>966</v>
+        <v>973</v>
       </c>
       <c r="G261" s="1" t="s">
-        <v>967</v>
+        <v>974</v>
       </c>
       <c r="H261" s="1" t="s">
-        <v>907</v>
+        <v>914</v>
       </c>
       <c r="I261" s="1"/>
       <c r="J261" s="1"/>
@@ -12971,34 +13030,34 @@
     </row>
     <row r="262" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A262" s="1" t="s">
-        <v>968</v>
+        <v>975</v>
       </c>
       <c r="B262" s="1" t="s">
-        <v>969</v>
+        <v>976</v>
       </c>
       <c r="C262" s="1" t="s">
         <v>126</v>
       </c>
       <c r="D262" s="1" t="s">
-        <v>970</v>
+        <v>977</v>
       </c>
       <c r="E262" s="1" t="s">
-        <v>889</v>
+        <v>896</v>
       </c>
       <c r="F262" s="1" t="s">
-        <v>971</v>
+        <v>978</v>
       </c>
       <c r="G262" s="1" t="s">
-        <v>972</v>
+        <v>979</v>
       </c>
       <c r="H262" s="1" t="s">
-        <v>907</v>
+        <v>914</v>
       </c>
       <c r="I262" s="1"/>
       <c r="J262" s="1"/>
       <c r="K262" s="1"/>
       <c r="L262" s="1" t="s">
-        <v>973</v>
+        <v>980</v>
       </c>
       <c r="M262" s="1"/>
       <c r="N262" s="1"/>
@@ -13008,35 +13067,35 @@
     </row>
     <row r="263" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A263" s="1" t="s">
-        <v>916</v>
+        <v>923</v>
       </c>
       <c r="B263" s="1" t="s">
-        <v>660</v>
+        <v>666</v>
       </c>
       <c r="C263" s="1" t="s">
-        <v>817</v>
+        <v>823</v>
       </c>
       <c r="D263" s="1" t="s">
-        <v>974</v>
+        <v>981</v>
       </c>
       <c r="E263" s="1"/>
       <c r="F263" s="1" t="s">
-        <v>975</v>
+        <v>982</v>
       </c>
       <c r="G263" s="1" t="s">
-        <v>976</v>
+        <v>983</v>
       </c>
       <c r="H263" s="1" t="s">
-        <v>907</v>
+        <v>914</v>
       </c>
       <c r="I263" s="1"/>
       <c r="J263" s="1"/>
       <c r="K263" s="1"/>
       <c r="L263" s="1" t="s">
-        <v>977</v>
+        <v>984</v>
       </c>
       <c r="M263" s="1" t="s">
-        <v>880</v>
+        <v>887</v>
       </c>
       <c r="N263" s="1"/>
       <c r="O263" s="1" t="s">
@@ -13045,31 +13104,31 @@
     </row>
     <row r="264" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>978</v>
+        <v>985</v>
       </c>
       <c r="B264" t="s">
-        <v>979</v>
+        <v>986</v>
       </c>
       <c r="C264" t="s">
-        <v>980</v>
+        <v>987</v>
       </c>
       <c r="D264" t="s">
-        <v>981</v>
+        <v>988</v>
       </c>
       <c r="E264" t="s">
-        <v>982</v>
+        <v>989</v>
       </c>
       <c r="F264" t="s">
-        <v>983</v>
+        <v>990</v>
       </c>
       <c r="G264" t="s">
-        <v>984</v>
+        <v>991</v>
       </c>
       <c r="H264" t="s">
-        <v>907</v>
+        <v>914</v>
       </c>
       <c r="L264" t="s">
-        <v>985</v>
+        <v>992</v>
       </c>
       <c r="O264" t="s">
         <v>43</v>
@@ -13077,28 +13136,28 @@
     </row>
     <row r="265" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>986</v>
+        <v>993</v>
       </c>
       <c r="B265" t="s">
-        <v>987</v>
+        <v>994</v>
       </c>
       <c r="C265" t="s">
         <v>126</v>
       </c>
       <c r="D265" t="s">
-        <v>988</v>
+        <v>995</v>
       </c>
       <c r="E265" t="s">
-        <v>989</v>
+        <v>996</v>
       </c>
       <c r="G265" t="s">
-        <v>990</v>
+        <v>997</v>
       </c>
       <c r="H265" t="s">
-        <v>907</v>
+        <v>914</v>
       </c>
       <c r="L265" t="s">
-        <v>991</v>
+        <v>998</v>
       </c>
       <c r="O265" t="s">
         <v>43</v>
@@ -13106,28 +13165,28 @@
     </row>
     <row r="266" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>986</v>
+        <v>993</v>
       </c>
       <c r="B266" t="s">
-        <v>992</v>
+        <v>999</v>
       </c>
       <c r="C266" t="s">
         <v>126</v>
       </c>
       <c r="D266" t="s">
-        <v>993</v>
+        <v>1000</v>
       </c>
       <c r="E266" t="s">
-        <v>994</v>
+        <v>1001</v>
       </c>
       <c r="G266" t="s">
-        <v>995</v>
+        <v>1002</v>
       </c>
       <c r="H266" t="s">
-        <v>907</v>
+        <v>914</v>
       </c>
       <c r="L266" t="s">
-        <v>996</v>
+        <v>1003</v>
       </c>
       <c r="O266" t="s">
         <v>43</v>
@@ -13135,31 +13194,31 @@
     </row>
     <row r="267" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>997</v>
+        <v>1004</v>
       </c>
       <c r="B267" t="s">
-        <v>998</v>
+        <v>1005</v>
       </c>
       <c r="C267" t="s">
-        <v>999</v>
+        <v>1006</v>
       </c>
       <c r="D267" t="s">
-        <v>1000</v>
+        <v>1007</v>
       </c>
       <c r="E267" t="s">
-        <v>889</v>
+        <v>896</v>
       </c>
       <c r="F267" t="s">
-        <v>1001</v>
+        <v>1008</v>
       </c>
       <c r="G267" t="s">
-        <v>1002</v>
+        <v>1009</v>
       </c>
       <c r="H267" t="s">
-        <v>907</v>
+        <v>914</v>
       </c>
       <c r="L267" t="s">
-        <v>1003</v>
+        <v>1010</v>
       </c>
       <c r="O267" t="s">
         <v>43</v>
@@ -13167,31 +13226,31 @@
     </row>
     <row r="268" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>1004</v>
+        <v>1011</v>
       </c>
       <c r="B268" t="s">
-        <v>660</v>
+        <v>666</v>
       </c>
       <c r="C268" t="s">
-        <v>1005</v>
+        <v>1012</v>
       </c>
       <c r="D268" t="s">
-        <v>1006</v>
+        <v>1013</v>
       </c>
       <c r="E268" t="s">
-        <v>1007</v>
+        <v>1014</v>
       </c>
       <c r="F268" t="s">
-        <v>1008</v>
+        <v>1015</v>
       </c>
       <c r="G268" t="s">
-        <v>1009</v>
+        <v>1016</v>
       </c>
       <c r="H268" t="s">
-        <v>907</v>
+        <v>914</v>
       </c>
       <c r="L268" t="s">
-        <v>1010</v>
+        <v>1017</v>
       </c>
       <c r="O268" t="s">
         <v>43</v>
@@ -13199,31 +13258,31 @@
     </row>
     <row r="269" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>1011</v>
+        <v>1018</v>
       </c>
       <c r="B269" t="s">
-        <v>1012</v>
+        <v>1019</v>
       </c>
       <c r="C269" t="s">
-        <v>1013</v>
+        <v>1020</v>
       </c>
       <c r="D269" t="s">
-        <v>1014</v>
+        <v>1021</v>
       </c>
       <c r="E269" t="s">
-        <v>989</v>
+        <v>996</v>
       </c>
       <c r="F269" t="s">
-        <v>1015</v>
+        <v>1022</v>
       </c>
       <c r="G269" t="s">
-        <v>1016</v>
+        <v>1023</v>
       </c>
       <c r="H269" t="s">
-        <v>907</v>
+        <v>914</v>
       </c>
       <c r="L269" t="s">
-        <v>1017</v>
+        <v>1024</v>
       </c>
       <c r="O269" t="s">
         <v>43</v>
@@ -13231,25 +13290,25 @@
     </row>
     <row r="270" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>1018</v>
+        <v>1025</v>
       </c>
       <c r="B270" t="s">
-        <v>931</v>
+        <v>938</v>
       </c>
       <c r="C270" t="s">
-        <v>1019</v>
+        <v>1026</v>
       </c>
       <c r="D270" t="s">
-        <v>1020</v>
+        <v>1027</v>
       </c>
       <c r="E270" t="s">
-        <v>994</v>
+        <v>1001</v>
       </c>
       <c r="G270" t="s">
-        <v>1021</v>
+        <v>1028</v>
       </c>
       <c r="H270" t="s">
-        <v>907</v>
+        <v>914</v>
       </c>
       <c r="O270" t="s">
         <v>43</v>
@@ -13257,7 +13316,7 @@
     </row>
     <row r="271" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>1022</v>
+        <v>1029</v>
       </c>
       <c r="B271" t="s">
         <v>271</v>
@@ -13266,19 +13325,19 @@
         <v>126</v>
       </c>
       <c r="D271" t="s">
-        <v>1023</v>
+        <v>1030</v>
       </c>
       <c r="E271" t="s">
-        <v>994</v>
+        <v>1001</v>
       </c>
       <c r="G271" t="s">
-        <v>1024</v>
+        <v>1031</v>
       </c>
       <c r="H271" t="s">
-        <v>907</v>
+        <v>914</v>
       </c>
       <c r="L271" t="s">
-        <v>1025</v>
+        <v>1032</v>
       </c>
       <c r="O271" t="s">
         <v>43</v>
@@ -13286,28 +13345,28 @@
     </row>
     <row r="272" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>1026</v>
+        <v>1033</v>
       </c>
       <c r="B272" t="s">
-        <v>979</v>
+        <v>986</v>
       </c>
       <c r="C272" t="s">
         <v>126</v>
       </c>
       <c r="D272" t="s">
-        <v>1027</v>
+        <v>1034</v>
       </c>
       <c r="E272" t="s">
-        <v>994</v>
+        <v>1001</v>
       </c>
       <c r="G272" t="s">
-        <v>1028</v>
+        <v>1035</v>
       </c>
       <c r="H272" t="s">
-        <v>907</v>
+        <v>914</v>
       </c>
       <c r="L272" t="s">
-        <v>1029</v>
+        <v>1036</v>
       </c>
       <c r="O272" t="s">
         <v>43</v>
@@ -13315,28 +13374,28 @@
     </row>
     <row r="273" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>1030</v>
+        <v>1037</v>
       </c>
       <c r="B273" t="s">
-        <v>1031</v>
+        <v>1038</v>
       </c>
       <c r="C273" t="s">
         <v>126</v>
       </c>
       <c r="D273" t="s">
-        <v>1032</v>
+        <v>1039</v>
       </c>
       <c r="E273" t="s">
-        <v>989</v>
+        <v>996</v>
       </c>
       <c r="G273" t="s">
-        <v>1033</v>
+        <v>1040</v>
       </c>
       <c r="H273" t="s">
-        <v>907</v>
+        <v>914</v>
       </c>
       <c r="L273" t="s">
-        <v>1034</v>
+        <v>1041</v>
       </c>
       <c r="O273" t="s">
         <v>43</v>
@@ -13344,31 +13403,31 @@
     </row>
     <row r="274" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>1035</v>
+        <v>1042</v>
       </c>
       <c r="B274" t="s">
-        <v>1036</v>
+        <v>1043</v>
       </c>
       <c r="C274" t="s">
         <v>126</v>
       </c>
       <c r="D274" t="s">
-        <v>1037</v>
+        <v>1044</v>
       </c>
       <c r="E274" t="s">
-        <v>1038</v>
+        <v>1045</v>
       </c>
       <c r="F274" t="s">
-        <v>1039</v>
+        <v>1046</v>
       </c>
       <c r="G274" t="s">
-        <v>1040</v>
+        <v>1047</v>
       </c>
       <c r="H274" t="s">
-        <v>907</v>
+        <v>914</v>
       </c>
       <c r="L274" t="s">
-        <v>1041</v>
+        <v>1048</v>
       </c>
       <c r="O274" t="s">
         <v>43</v>
@@ -13376,31 +13435,31 @@
     </row>
     <row r="275" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>936</v>
+        <v>943</v>
       </c>
       <c r="B275" t="s">
-        <v>964</v>
+        <v>971</v>
       </c>
       <c r="C275" t="s">
         <v>126</v>
       </c>
       <c r="D275" t="s">
-        <v>1042</v>
+        <v>1049</v>
       </c>
       <c r="E275" t="s">
-        <v>989</v>
+        <v>996</v>
       </c>
       <c r="F275" t="s">
-        <v>1043</v>
+        <v>1050</v>
       </c>
       <c r="G275" t="s">
-        <v>1044</v>
+        <v>1051</v>
       </c>
       <c r="H275" t="s">
-        <v>907</v>
+        <v>914</v>
       </c>
       <c r="L275" t="s">
-        <v>1045</v>
+        <v>1052</v>
       </c>
       <c r="O275" t="s">
         <v>43</v>
@@ -13408,34 +13467,34 @@
     </row>
     <row r="276" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A276" s="1" t="s">
-        <v>1046</v>
+        <v>1053</v>
       </c>
       <c r="B276" s="1" t="s">
-        <v>1047</v>
+        <v>1054</v>
       </c>
       <c r="C276" s="1" t="s">
-        <v>1048</v>
+        <v>1055</v>
       </c>
       <c r="D276" s="1" t="s">
-        <v>1049</v>
+        <v>1056</v>
       </c>
       <c r="E276" s="1"/>
       <c r="F276" s="1" t="s">
-        <v>1050</v>
+        <v>1057</v>
       </c>
       <c r="G276" s="1" t="s">
-        <v>1051</v>
+        <v>1058</v>
       </c>
       <c r="H276" s="1" t="s">
-        <v>336</v>
+        <v>405</v>
       </c>
       <c r="I276" s="1" t="s">
-        <v>1052</v>
+        <v>1059</v>
       </c>
       <c r="J276" s="1"/>
       <c r="K276" s="1"/>
       <c r="L276" s="1" t="s">
-        <v>1053</v>
+        <v>1060</v>
       </c>
       <c r="M276" s="1" t="s">
         <v>22</v>
@@ -13449,37 +13508,37 @@
     </row>
     <row r="277" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>1054</v>
+        <v>1061</v>
       </c>
       <c r="B277" t="s">
-        <v>1055</v>
+        <v>1062</v>
       </c>
       <c r="C277" t="s">
-        <v>1056</v>
+        <v>1063</v>
       </c>
       <c r="D277" t="s">
-        <v>1057</v>
+        <v>1064</v>
       </c>
       <c r="E277" t="s">
-        <v>1058</v>
+        <v>1065</v>
       </c>
       <c r="F277" t="s">
-        <v>1059</v>
+        <v>1066</v>
       </c>
       <c r="G277" t="s">
-        <v>1060</v>
+        <v>1067</v>
       </c>
       <c r="H277" t="s">
-        <v>1061</v>
+        <v>1068</v>
       </c>
       <c r="I277" t="s">
-        <v>1062</v>
+        <v>1069</v>
       </c>
       <c r="J277" t="s">
-        <v>1063</v>
+        <v>1070</v>
       </c>
       <c r="L277" t="s">
-        <v>1064</v>
+        <v>1071</v>
       </c>
       <c r="M277" t="s">
         <v>22</v>
@@ -13493,37 +13552,37 @@
     </row>
     <row r="278" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>1065</v>
+        <v>1072</v>
       </c>
       <c r="B278" t="s">
-        <v>1066</v>
+        <v>1073</v>
       </c>
       <c r="C278" t="s">
-        <v>1067</v>
+        <v>1074</v>
       </c>
       <c r="D278" t="s">
-        <v>1068</v>
+        <v>1075</v>
       </c>
       <c r="E278" t="s">
-        <v>1069</v>
+        <v>1076</v>
       </c>
       <c r="F278" t="s">
-        <v>1070</v>
+        <v>1077</v>
       </c>
       <c r="G278" t="s">
-        <v>1071</v>
+        <v>1078</v>
       </c>
       <c r="H278" t="s">
-        <v>805</v>
+        <v>336</v>
       </c>
       <c r="I278" s="1" t="s">
-        <v>1072</v>
+        <v>1079</v>
       </c>
       <c r="J278" s="1" t="s">
-        <v>1073</v>
+        <v>1080</v>
       </c>
       <c r="L278" t="s">
-        <v>1074</v>
+        <v>1081</v>
       </c>
       <c r="M278" t="s">
         <v>30</v>
@@ -13537,37 +13596,37 @@
     </row>
     <row r="279" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>822</v>
+        <v>828</v>
       </c>
       <c r="B279" t="s">
-        <v>1066</v>
+        <v>1073</v>
       </c>
       <c r="C279" t="s">
-        <v>823</v>
+        <v>829</v>
       </c>
       <c r="D279" t="s">
-        <v>1075</v>
+        <v>1082</v>
       </c>
       <c r="E279" t="s">
-        <v>1076</v>
+        <v>1083</v>
       </c>
       <c r="F279" t="s">
-        <v>1077</v>
+        <v>1084</v>
       </c>
       <c r="G279" t="s">
-        <v>1078</v>
+        <v>1085</v>
       </c>
       <c r="H279" t="s">
-        <v>805</v>
+        <v>336</v>
       </c>
       <c r="I279" s="1" t="s">
-        <v>1079</v>
+        <v>1086</v>
       </c>
       <c r="J279" s="1" t="s">
-        <v>1080</v>
+        <v>1087</v>
       </c>
       <c r="L279" t="s">
-        <v>1081</v>
+        <v>1088</v>
       </c>
       <c r="M279" t="s">
         <v>30</v>
@@ -13581,43 +13640,43 @@
     </row>
     <row r="280" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>1082</v>
+        <v>1089</v>
       </c>
       <c r="B280" t="s">
-        <v>1083</v>
+        <v>1090</v>
       </c>
       <c r="C280" t="s">
-        <v>641</v>
+        <v>646</v>
       </c>
       <c r="D280" t="s">
-        <v>1084</v>
+        <v>1091</v>
       </c>
       <c r="E280" t="s">
-        <v>1085</v>
+        <v>1092</v>
       </c>
       <c r="F280" t="s">
-        <v>1086</v>
+        <v>1093</v>
       </c>
       <c r="G280" t="s">
-        <v>1087</v>
+        <v>1094</v>
       </c>
       <c r="H280" t="s">
-        <v>805</v>
+        <v>336</v>
       </c>
       <c r="I280" s="1" t="s">
-        <v>1088</v>
+        <v>1095</v>
       </c>
       <c r="J280" s="1" t="s">
-        <v>1089</v>
+        <v>1096</v>
       </c>
       <c r="L280" t="s">
-        <v>1090</v>
+        <v>1097</v>
       </c>
       <c r="M280" t="s">
         <v>30</v>
       </c>
       <c r="N280" t="s">
-        <v>1091</v>
+        <v>846</v>
       </c>
       <c r="O280" t="s">
         <v>43</v>
@@ -13625,35 +13684,35 @@
     </row>
     <row r="281" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>1092</v>
+        <v>1098</v>
       </c>
       <c r="B281" t="s">
-        <v>1093</v>
+        <v>1099</v>
       </c>
       <c r="C281" t="s">
-        <v>1094</v>
+        <v>1100</v>
       </c>
       <c r="D281" t="s">
-        <v>1095</v>
+        <v>1101</v>
       </c>
       <c r="E281" t="s">
-        <v>1096</v>
+        <v>1102</v>
       </c>
       <c r="F281" t="s">
-        <v>1097</v>
+        <v>1103</v>
       </c>
       <c r="G281" t="s">
-        <v>1098</v>
+        <v>1104</v>
       </c>
       <c r="H281" t="s">
-        <v>805</v>
+        <v>336</v>
       </c>
       <c r="I281" s="1" t="s">
-        <v>1099</v>
+        <v>1105</v>
       </c>
       <c r="J281" s="1"/>
       <c r="L281" t="s">
-        <v>1100</v>
+        <v>1106</v>
       </c>
       <c r="M281" t="s">
         <v>69</v>
@@ -13667,43 +13726,43 @@
     </row>
     <row r="282" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="B282" t="s">
-        <v>660</v>
+        <v>666</v>
       </c>
       <c r="C282" t="s">
-        <v>823</v>
+        <v>829</v>
       </c>
       <c r="D282" t="s">
-        <v>1101</v>
+        <v>1107</v>
       </c>
       <c r="E282" t="s">
-        <v>1076</v>
+        <v>1083</v>
       </c>
       <c r="F282" t="s">
-        <v>900</v>
+        <v>907</v>
       </c>
       <c r="G282" t="s">
-        <v>1102</v>
+        <v>1108</v>
       </c>
       <c r="H282" t="s">
-        <v>805</v>
+        <v>336</v>
       </c>
       <c r="I282" s="1" t="s">
-        <v>1103</v>
+        <v>1109</v>
       </c>
       <c r="J282" s="1" t="s">
-        <v>1104</v>
+        <v>1110</v>
       </c>
       <c r="L282" t="s">
-        <v>1105</v>
+        <v>1111</v>
       </c>
       <c r="M282" t="s">
         <v>30</v>
       </c>
       <c r="N282" t="s">
-        <v>1091</v>
+        <v>846</v>
       </c>
       <c r="O282" t="s">
         <v>43</v>
@@ -13711,37 +13770,37 @@
     </row>
     <row r="283" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>1106</v>
+        <v>1112</v>
       </c>
       <c r="B283" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="C283" t="s">
-        <v>641</v>
+        <v>646</v>
       </c>
       <c r="D283" t="s">
-        <v>1107</v>
+        <v>1113</v>
       </c>
       <c r="E283" t="s">
-        <v>1076</v>
+        <v>1083</v>
       </c>
       <c r="F283" t="s">
-        <v>1108</v>
+        <v>1114</v>
       </c>
       <c r="G283" t="s">
-        <v>1109</v>
+        <v>1115</v>
       </c>
       <c r="H283" t="s">
-        <v>805</v>
+        <v>336</v>
       </c>
       <c r="I283" s="1" t="s">
-        <v>1110</v>
+        <v>1116</v>
       </c>
       <c r="J283" s="1" t="s">
-        <v>1111</v>
+        <v>1117</v>
       </c>
       <c r="L283" t="s">
-        <v>1112</v>
+        <v>1118</v>
       </c>
       <c r="M283" t="s">
         <v>30</v>
@@ -13755,41 +13814,41 @@
     </row>
     <row r="284" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>832</v>
+        <v>838</v>
       </c>
       <c r="B284" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="C284" t="s">
-        <v>1094</v>
+        <v>1100</v>
       </c>
       <c r="D284" t="s">
-        <v>1113</v>
+        <v>1119</v>
       </c>
       <c r="E284" t="s">
-        <v>1076</v>
+        <v>1083</v>
       </c>
       <c r="F284" t="s">
-        <v>1114</v>
+        <v>1120</v>
       </c>
       <c r="G284" t="s">
-        <v>1115</v>
+        <v>1121</v>
       </c>
       <c r="H284" t="s">
-        <v>805</v>
+        <v>336</v>
       </c>
       <c r="I284" s="1" t="s">
-        <v>1116</v>
+        <v>1122</v>
       </c>
       <c r="J284" s="1"/>
       <c r="L284" t="s">
-        <v>1117</v>
+        <v>1123</v>
       </c>
       <c r="M284" t="s">
         <v>69</v>
       </c>
       <c r="N284" t="s">
-        <v>1091</v>
+        <v>846</v>
       </c>
       <c r="O284" t="s">
         <v>43</v>
@@ -13797,37 +13856,37 @@
     </row>
     <row r="285" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B285" t="s">
-        <v>627</v>
+        <v>632</v>
       </c>
       <c r="C285" t="s">
-        <v>641</v>
+        <v>646</v>
       </c>
       <c r="D285" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="E285" t="s">
-        <v>1076</v>
+        <v>1083</v>
       </c>
       <c r="F285" t="s">
-        <v>1119</v>
+        <v>1125</v>
       </c>
       <c r="G285" t="s">
-        <v>1120</v>
+        <v>1126</v>
       </c>
       <c r="H285" t="s">
-        <v>805</v>
+        <v>336</v>
       </c>
       <c r="I285" s="1" t="s">
-        <v>1121</v>
+        <v>1127</v>
       </c>
       <c r="J285" s="1" t="s">
-        <v>1122</v>
+        <v>1128</v>
       </c>
       <c r="L285" t="s">
-        <v>1123</v>
+        <v>1129</v>
       </c>
       <c r="M285" t="s">
         <v>30</v>
@@ -13841,43 +13900,43 @@
     </row>
     <row r="286" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>1082</v>
+        <v>1089</v>
       </c>
       <c r="B286" t="s">
-        <v>1124</v>
+        <v>1130</v>
       </c>
       <c r="C286" t="s">
-        <v>823</v>
+        <v>829</v>
       </c>
       <c r="D286" t="s">
-        <v>1125</v>
+        <v>1131</v>
       </c>
       <c r="E286" t="s">
-        <v>1076</v>
+        <v>1083</v>
       </c>
       <c r="F286" t="s">
-        <v>1086</v>
+        <v>1093</v>
       </c>
       <c r="G286" t="s">
-        <v>1126</v>
+        <v>1132</v>
       </c>
       <c r="H286" t="s">
-        <v>805</v>
+        <v>336</v>
       </c>
       <c r="I286" s="1" t="s">
-        <v>1127</v>
+        <v>1133</v>
       </c>
       <c r="J286" s="1" t="s">
-        <v>1128</v>
+        <v>1134</v>
       </c>
       <c r="L286" t="s">
-        <v>1129</v>
+        <v>1135</v>
       </c>
       <c r="M286" t="s">
         <v>30</v>
       </c>
       <c r="N286" t="s">
-        <v>1091</v>
+        <v>846</v>
       </c>
       <c r="O286" t="s">
         <v>43</v>
@@ -13885,37 +13944,37 @@
     </row>
     <row r="287" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="B287" t="s">
-        <v>1130</v>
+        <v>1136</v>
       </c>
       <c r="C287" t="s">
-        <v>641</v>
+        <v>646</v>
       </c>
       <c r="D287" t="s">
-        <v>1131</v>
+        <v>1137</v>
       </c>
       <c r="E287" t="s">
-        <v>1076</v>
+        <v>1083</v>
       </c>
       <c r="F287" t="s">
-        <v>1132</v>
+        <v>1138</v>
       </c>
       <c r="G287" t="s">
-        <v>1133</v>
+        <v>1139</v>
       </c>
       <c r="H287" t="s">
-        <v>805</v>
+        <v>336</v>
       </c>
       <c r="I287" s="1" t="s">
-        <v>1134</v>
+        <v>1140</v>
       </c>
       <c r="J287" s="1" t="s">
-        <v>1135</v>
+        <v>1141</v>
       </c>
       <c r="L287" t="s">
-        <v>1136</v>
+        <v>1142</v>
       </c>
       <c r="M287" t="s">
         <v>30</v>
@@ -13929,37 +13988,37 @@
     </row>
     <row r="288" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B288" t="s">
-        <v>1137</v>
+        <v>1143</v>
       </c>
       <c r="C288" t="s">
-        <v>823</v>
+        <v>829</v>
       </c>
       <c r="D288" t="s">
-        <v>1138</v>
+        <v>1144</v>
       </c>
       <c r="E288" t="s">
-        <v>1076</v>
+        <v>1083</v>
       </c>
       <c r="F288" t="s">
-        <v>1139</v>
+        <v>1145</v>
       </c>
       <c r="G288" t="s">
-        <v>1140</v>
+        <v>1146</v>
       </c>
       <c r="H288" t="s">
-        <v>805</v>
+        <v>336</v>
       </c>
       <c r="I288" s="1" t="s">
-        <v>1141</v>
+        <v>1147</v>
       </c>
       <c r="J288" s="1" t="s">
-        <v>1142</v>
+        <v>1148</v>
       </c>
       <c r="L288" t="s">
-        <v>1143</v>
+        <v>1149</v>
       </c>
       <c r="M288" t="s">
         <v>30</v>
@@ -13973,32 +14032,32 @@
     </row>
     <row r="289" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>1144</v>
+        <v>1150</v>
       </c>
       <c r="B289" t="s">
-        <v>1145</v>
+        <v>1151</v>
       </c>
       <c r="C289" t="s">
-        <v>1146</v>
+        <v>1152</v>
       </c>
       <c r="D289" t="s">
-        <v>1147</v>
+        <v>1153</v>
       </c>
       <c r="F289" t="s">
-        <v>1077</v>
+        <v>1084</v>
       </c>
       <c r="G289" t="s">
-        <v>1148</v>
+        <v>1154</v>
       </c>
       <c r="H289" t="s">
-        <v>805</v>
+        <v>336</v>
       </c>
       <c r="I289" s="1" t="s">
-        <v>1149</v>
+        <v>1155</v>
       </c>
       <c r="J289" s="1"/>
       <c r="L289" t="s">
-        <v>1150</v>
+        <v>1156</v>
       </c>
       <c r="M289" t="s">
         <v>69</v>
@@ -14012,32 +14071,32 @@
     </row>
     <row r="290" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>1151</v>
+        <v>1157</v>
       </c>
       <c r="B290" t="s">
-        <v>1152</v>
+        <v>1158</v>
       </c>
       <c r="C290" t="s">
-        <v>1153</v>
+        <v>1159</v>
       </c>
       <c r="D290" t="s">
-        <v>1154</v>
+        <v>1160</v>
       </c>
       <c r="F290" t="s">
-        <v>1155</v>
+        <v>1161</v>
       </c>
       <c r="G290" t="s">
-        <v>1156</v>
+        <v>1162</v>
       </c>
       <c r="H290" t="s">
-        <v>805</v>
+        <v>336</v>
       </c>
       <c r="I290" s="1" t="s">
-        <v>1157</v>
+        <v>1163</v>
       </c>
       <c r="J290" s="1"/>
       <c r="L290" t="s">
-        <v>1158</v>
+        <v>1164</v>
       </c>
       <c r="M290" t="s">
         <v>69</v>
@@ -14051,32 +14110,32 @@
     </row>
     <row r="291" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>1159</v>
+        <v>1165</v>
       </c>
       <c r="B291" t="s">
-        <v>1160</v>
+        <v>1166</v>
       </c>
       <c r="C291" t="s">
-        <v>1161</v>
+        <v>1167</v>
       </c>
       <c r="D291" t="s">
-        <v>1162</v>
+        <v>1168</v>
       </c>
       <c r="F291" t="s">
-        <v>1163</v>
+        <v>1169</v>
       </c>
       <c r="G291" t="s">
-        <v>1164</v>
+        <v>1170</v>
       </c>
       <c r="H291" t="s">
-        <v>805</v>
+        <v>336</v>
       </c>
       <c r="I291" s="1" t="s">
-        <v>1165</v>
+        <v>1171</v>
       </c>
       <c r="J291" s="1"/>
       <c r="L291" t="s">
-        <v>1166</v>
+        <v>1172</v>
       </c>
       <c r="M291" t="s">
         <v>69</v>

--- a/tracker.xlsx
+++ b/tracker.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2707" uniqueCount="1173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2707" uniqueCount="1174">
   <si>
     <t>Company</t>
   </si>
@@ -2455,10 +2455,13 @@
     <t>Forward-deployed role: customer-facing builds, Python/Node/React, LLM/agent nice-to-have, AWS nice-to-have. Referral via friend.</t>
   </si>
   <si>
+    <t>rejected</t>
+  </si>
+  <si>
     <t>resume-narmi-software-engineer-forward-deployed.pdf</t>
   </si>
   <si>
-    <t>Source: Gem; resume tailored, cover letter not started 2026-10-27: resume rebuilt in applications/narmi-software-engineer-forward-deployed/ (black-and-white), replacing the old resume/narmi branch PDF. Gem form checked: no cover letter field; required 1-2 sentence 'proudest accomplishment' + restrictive-agreement questions. FLAG: required 'Are you able to work onsite 3 days a week in New York City?' (posting is in-person-first, Flatiron office, base $91K-$110K); Jack is in Utah, so Jack must confirm before Muse applies. Ready to apply — materials complete, 2026-10-27.</t>
+    <t>Source: Gem; resume tailored, cover letter not started 2026-10-27: resume rebuilt in applications/narmi-software-engineer-forward-deployed/ (black-and-white), replacing the old resume/narmi branch PDF. Gem form checked: no cover letter field; required 1-2 sentence 'proudest accomplishment' + restrictive-agreement questions. FLAG: required 'Are you able to work onsite 3 days a week in New York City?' (posting is in-person-first, Flatiron office, base $91K-$110K); Jack is in Utah, so Jack must confirm before Muse applies. Ready to apply — materials complete, 2026-10-27. 2026-10-27: Narmi passed (per Jack). Do not apply.</t>
   </si>
   <si>
     <t>SRS Acquiom</t>
@@ -12047,15 +12050,15 @@
         <v>811</v>
       </c>
       <c r="H234" s="4" t="s">
-        <v>336</v>
+        <v>812</v>
       </c>
       <c r="I234" s="4" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="J234" s="4"/>
       <c r="K234" s="4"/>
       <c r="L234" s="4" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="M234" s="4" t="s">
         <v>69</v>
@@ -12069,34 +12072,34 @@
     </row>
     <row r="235" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A235" s="1" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="B235" s="1" t="s">
         <v>666</v>
       </c>
       <c r="C235" s="1" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="D235" s="1" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="F235" s="1" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="G235" s="1" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="H235" s="1" t="s">
         <v>405</v>
       </c>
       <c r="I235" s="1" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="J235" s="1" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="L235" s="1" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="M235" s="1" t="s">
         <v>22</v>
@@ -12107,28 +12110,28 @@
     </row>
     <row r="236" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A236" s="1" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="B236" s="1" t="s">
         <v>666</v>
       </c>
       <c r="C236" s="1" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D236" s="1" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="F236" s="1" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="G236" s="1" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="H236" s="1" t="s">
         <v>36</v>
       </c>
       <c r="L236" s="1" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="O236" s="1" t="s">
         <v>43</v>
@@ -12136,25 +12139,25 @@
     </row>
     <row r="237" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A237" s="1" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="B237" s="1" t="s">
         <v>666</v>
       </c>
       <c r="C237" s="1" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="D237" s="1" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="G237" s="1" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="H237" s="1" t="s">
         <v>36</v>
       </c>
       <c r="L237" s="1" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="O237" s="1" t="s">
         <v>43</v>
@@ -12162,28 +12165,28 @@
     </row>
     <row r="238" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A238" s="1" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="B238" s="1" t="s">
         <v>666</v>
       </c>
       <c r="C238" s="1" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="D238" s="1" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="F238" s="1" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="G238" s="1" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="H238" s="1" t="s">
         <v>36</v>
       </c>
       <c r="L238" s="1" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="O238" s="1" t="s">
         <v>43</v>
@@ -12191,40 +12194,40 @@
     </row>
     <row r="239" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A239" s="1" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B239" s="1" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="C239" s="1" t="s">
         <v>126</v>
       </c>
       <c r="D239" s="1" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="F239" s="1" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="G239" s="1" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="H239" s="1" t="s">
         <v>336</v>
       </c>
       <c r="I239" s="1" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="J239" s="1" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="L239" s="1" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="M239" s="1" t="s">
         <v>30</v>
       </c>
       <c r="N239" s="1" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="O239" s="1" t="s">
         <v>43</v>
@@ -12232,25 +12235,25 @@
     </row>
     <row r="240" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A240" s="1" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="B240" s="1" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="C240" s="1" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="D240" s="1" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="G240" s="1" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="H240" s="1" t="s">
         <v>36</v>
       </c>
       <c r="L240" s="1" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="O240" s="1" t="s">
         <v>31</v>
@@ -12258,31 +12261,31 @@
     </row>
     <row r="241" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A241" s="1" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="B241" s="1" t="s">
         <v>666</v>
       </c>
       <c r="C241" s="1" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D241" s="1" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="G241" s="1" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="H241" s="1" t="s">
         <v>336</v>
       </c>
       <c r="I241" s="1" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="J241" s="1" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="L241" s="1" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="M241" s="1" t="s">
         <v>30</v>
@@ -12296,28 +12299,28 @@
     </row>
     <row r="242" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A242" s="1" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="B242" s="1" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="C242" s="1" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="D242" s="1" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="F242" s="1" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="G242" s="1" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="H242" s="1" t="s">
         <v>36</v>
       </c>
       <c r="L242" s="1" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="O242" s="1" t="s">
         <v>31</v>
@@ -12325,28 +12328,28 @@
     </row>
     <row r="243" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A243" s="1" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="B243" s="1" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="C243" s="1" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D243" s="1" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="F243" s="1" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="G243" s="1" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="H243" s="1" t="s">
         <v>36</v>
       </c>
       <c r="L243" s="1" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="O243" s="1" t="s">
         <v>31</v>
@@ -12354,32 +12357,32 @@
     </row>
     <row r="244" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A244" s="1" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="B244" s="1" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="C244" s="1" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="D244" s="1" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="F244" s="1"/>
       <c r="G244" s="1" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="H244" s="1" t="s">
         <v>336</v>
       </c>
       <c r="I244" s="1" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="J244" s="1" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="L244" s="1" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="M244" s="1" t="s">
         <v>22</v>
@@ -12393,41 +12396,41 @@
     </row>
     <row r="245" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A245" s="1" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="B245" s="1" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="C245" s="1" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D245" s="1" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="E245" s="1"/>
       <c r="F245" s="1" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="G245" s="1" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="H245" s="1" t="s">
         <v>20</v>
       </c>
       <c r="I245" s="1" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="J245" s="1" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="K245" s="1">
         <v>46301</v>
       </c>
       <c r="L245" s="1" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="M245" s="1" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="N245" s="1"/>
       <c r="O245" s="1" t="s">
@@ -12436,21 +12439,21 @@
     </row>
     <row r="246" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A246" s="1" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="B246" s="1" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="C246" s="1" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D246" s="1" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="E246" s="1"/>
       <c r="F246" s="1"/>
       <c r="G246" s="1" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="H246" s="1" t="s">
         <v>36</v>
@@ -12459,10 +12462,10 @@
       <c r="J246" s="1"/>
       <c r="K246" s="1"/>
       <c r="L246" s="1" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="M246" s="1" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="N246" s="1"/>
       <c r="O246" s="1" t="s">
@@ -12471,25 +12474,25 @@
     </row>
     <row r="247" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A247" s="1" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="B247" s="1" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="C247" s="1" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D247" s="1" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="E247" s="1" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="F247" s="1" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="G247" s="1" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="H247" s="1" t="s">
         <v>36</v>
@@ -12498,10 +12501,10 @@
       <c r="J247" s="1"/>
       <c r="K247" s="1"/>
       <c r="L247" s="1" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="M247" s="1" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="N247" s="1"/>
       <c r="O247" s="1" t="s">
@@ -12510,25 +12513,25 @@
     </row>
     <row r="248" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A248" s="1" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="B248" s="1" t="s">
         <v>666</v>
       </c>
       <c r="C248" s="1" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D248" s="1" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="E248" s="1" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="F248" s="1" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="G248" s="1" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="H248" s="1" t="s">
         <v>36</v>
@@ -12537,10 +12540,10 @@
       <c r="J248" s="1"/>
       <c r="K248" s="1"/>
       <c r="L248" s="1" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="M248" s="1" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="N248" s="1"/>
       <c r="O248" s="1" t="s">
@@ -12549,25 +12552,25 @@
     </row>
     <row r="249" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A249" s="1" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="B249" s="1" t="s">
         <v>666</v>
       </c>
       <c r="C249" s="1" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D249" s="1" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="E249" s="1" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="F249" s="1" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="G249" s="1" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="H249" s="1" t="s">
         <v>36</v>
@@ -12576,10 +12579,10 @@
       <c r="J249" s="1"/>
       <c r="K249" s="1"/>
       <c r="L249" s="1" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="M249" s="1" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="N249" s="1"/>
       <c r="O249" s="1" t="s">
@@ -12588,37 +12591,37 @@
     </row>
     <row r="250" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A250" s="1" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="B250" s="1" t="s">
         <v>666</v>
       </c>
       <c r="C250" s="1" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="D250" s="1" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="E250" s="1" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="F250" s="1" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="G250" s="1" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="H250" s="1" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="I250" s="1"/>
       <c r="J250" s="1"/>
       <c r="K250" s="1"/>
       <c r="L250" s="1" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="M250" s="1" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="N250" s="1"/>
       <c r="O250" s="1" t="s">
@@ -12627,41 +12630,41 @@
     </row>
     <row r="251" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A251" s="1" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="B251" s="1" t="s">
         <v>666</v>
       </c>
       <c r="C251" s="1" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D251" s="1" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="E251" s="1" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="F251" s="1" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="G251" s="1" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="H251" s="1" t="s">
         <v>405</v>
       </c>
       <c r="I251" s="1" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="J251" s="1" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="K251" s="1"/>
       <c r="L251" s="1" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="M251" s="1" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="N251" s="1"/>
       <c r="O251" s="1" t="s">
@@ -12670,25 +12673,25 @@
     </row>
     <row r="252" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A252" s="1" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="B252" s="1" t="s">
         <v>666</v>
       </c>
       <c r="C252" s="1" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D252" s="1" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="E252" s="1" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="F252" s="1" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="G252" s="1" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="H252" s="1" t="s">
         <v>36</v>
@@ -12697,10 +12700,10 @@
       <c r="J252" s="1"/>
       <c r="K252" s="1"/>
       <c r="L252" s="1" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="M252" s="1" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="N252" s="1"/>
       <c r="O252" s="1" t="s">
@@ -12709,26 +12712,26 @@
     </row>
     <row r="253" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A253" s="1" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="B253" s="1" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="C253" s="1" t="s">
         <v>126</v>
       </c>
       <c r="D253" s="1" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="E253" s="1" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="F253" s="1"/>
       <c r="G253" s="1" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="H253" s="1" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="I253" s="1"/>
       <c r="J253" s="1"/>
@@ -12742,32 +12745,32 @@
     </row>
     <row r="254" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A254" s="1" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="B254" s="1" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="C254" s="1" t="s">
         <v>126</v>
       </c>
       <c r="D254" s="1" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="E254" s="1" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="F254" s="1"/>
       <c r="G254" s="1" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="H254" s="1" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="I254" s="1"/>
       <c r="J254" s="1"/>
       <c r="K254" s="1"/>
       <c r="L254" s="1" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="M254" s="1"/>
       <c r="N254" s="1"/>
@@ -12777,34 +12780,34 @@
     </row>
     <row r="255" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A255" s="1" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="B255" s="1" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="C255" s="1" t="s">
         <v>126</v>
       </c>
       <c r="D255" s="1" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="E255" s="1" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="F255" s="1" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="G255" s="1" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="H255" s="1" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="I255" s="1"/>
       <c r="J255" s="1"/>
       <c r="K255" s="1"/>
       <c r="L255" s="1" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="M255" s="1"/>
       <c r="N255" s="1"/>
@@ -12814,34 +12817,34 @@
     </row>
     <row r="256" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A256" s="1" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="B256" s="1" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="C256" s="1" t="s">
         <v>126</v>
       </c>
       <c r="D256" s="1" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="E256" s="1" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="F256" s="1" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="G256" s="1" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="H256" s="1" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="I256" s="1"/>
       <c r="J256" s="1"/>
       <c r="K256" s="1"/>
       <c r="L256" s="1" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="M256" s="1"/>
       <c r="N256" s="1"/>
@@ -12851,28 +12854,28 @@
     </row>
     <row r="257" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A257" s="1" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="B257" s="1" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="C257" s="1" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="D257" s="1" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="E257" s="1" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="F257" s="1" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="G257" s="1" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="H257" s="1" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="I257" s="1"/>
       <c r="J257" s="1"/>
@@ -12886,28 +12889,28 @@
     </row>
     <row r="258" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A258" s="1" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="B258" s="1" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="C258" s="1" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="D258" s="1" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="E258" s="1" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="F258" s="1" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="G258" s="1" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="H258" s="1" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="I258" s="1"/>
       <c r="J258" s="1"/>
@@ -12921,34 +12924,34 @@
     </row>
     <row r="259" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A259" s="1" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="B259" s="1" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="C259" s="1" t="s">
         <v>126</v>
       </c>
       <c r="D259" s="1" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="E259" s="1" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="F259" s="1" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="G259" s="1" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="H259" s="1" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="I259" s="1"/>
       <c r="J259" s="1"/>
       <c r="K259" s="1"/>
       <c r="L259" s="1" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="M259" s="1"/>
       <c r="N259" s="1"/>
@@ -12958,34 +12961,34 @@
     </row>
     <row r="260" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A260" s="1" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="B260" s="1" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="C260" s="1" t="s">
         <v>126</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="E260" s="1" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="F260" s="1" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="G260" s="1" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="H260" s="1" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="I260" s="1"/>
       <c r="J260" s="1"/>
       <c r="K260" s="1"/>
       <c r="L260" s="1" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="M260" s="1"/>
       <c r="N260" s="1"/>
@@ -12995,28 +12998,28 @@
     </row>
     <row r="261" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A261" s="1" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="B261" s="1" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="C261" s="1" t="s">
         <v>126</v>
       </c>
       <c r="D261" s="1" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="E261" s="1" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="F261" s="1" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="G261" s="1" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="H261" s="1" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="I261" s="1"/>
       <c r="J261" s="1"/>
@@ -13030,34 +13033,34 @@
     </row>
     <row r="262" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A262" s="1" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="B262" s="1" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="C262" s="1" t="s">
         <v>126</v>
       </c>
       <c r="D262" s="1" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="E262" s="1" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="F262" s="1" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="G262" s="1" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H262" s="1" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="I262" s="1"/>
       <c r="J262" s="1"/>
       <c r="K262" s="1"/>
       <c r="L262" s="1" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="M262" s="1"/>
       <c r="N262" s="1"/>
@@ -13067,35 +13070,35 @@
     </row>
     <row r="263" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A263" s="1" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="B263" s="1" t="s">
         <v>666</v>
       </c>
       <c r="C263" s="1" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D263" s="1" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="E263" s="1"/>
       <c r="F263" s="1" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="G263" s="1" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="H263" s="1" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="I263" s="1"/>
       <c r="J263" s="1"/>
       <c r="K263" s="1"/>
       <c r="L263" s="1" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="M263" s="1" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="N263" s="1"/>
       <c r="O263" s="1" t="s">
@@ -13104,31 +13107,31 @@
     </row>
     <row r="264" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="B264" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="C264" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="D264" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="E264" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="F264" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="G264" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="H264" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="L264" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="O264" t="s">
         <v>43</v>
@@ -13136,28 +13139,28 @@
     </row>
     <row r="265" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="B265" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="C265" t="s">
         <v>126</v>
       </c>
       <c r="D265" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="E265" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="G265" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="H265" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="L265" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="O265" t="s">
         <v>43</v>
@@ -13165,28 +13168,28 @@
     </row>
     <row r="266" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="B266" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="C266" t="s">
         <v>126</v>
       </c>
       <c r="D266" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="E266" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="G266" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="H266" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="L266" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="O266" t="s">
         <v>43</v>
@@ -13194,31 +13197,31 @@
     </row>
     <row r="267" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="B267" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="C267" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="D267" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="E267" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="F267" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="G267" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="H267" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="L267" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="O267" t="s">
         <v>43</v>
@@ -13226,31 +13229,31 @@
     </row>
     <row r="268" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="B268" t="s">
         <v>666</v>
       </c>
       <c r="C268" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="D268" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="E268" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="F268" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="G268" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="H268" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="L268" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="O268" t="s">
         <v>43</v>
@@ -13258,31 +13261,31 @@
     </row>
     <row r="269" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="B269" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="C269" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="D269" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="E269" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="F269" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="G269" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="H269" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="L269" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="O269" t="s">
         <v>43</v>
@@ -13290,25 +13293,25 @@
     </row>
     <row r="270" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="B270" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="C270" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="D270" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="E270" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="G270" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="H270" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="O270" t="s">
         <v>43</v>
@@ -13316,7 +13319,7 @@
     </row>
     <row r="271" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="B271" t="s">
         <v>271</v>
@@ -13325,19 +13328,19 @@
         <v>126</v>
       </c>
       <c r="D271" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="E271" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="G271" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="H271" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="L271" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="O271" t="s">
         <v>43</v>
@@ -13345,28 +13348,28 @@
     </row>
     <row r="272" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="B272" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="C272" t="s">
         <v>126</v>
       </c>
       <c r="D272" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="E272" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="G272" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="H272" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="L272" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="O272" t="s">
         <v>43</v>
@@ -13374,28 +13377,28 @@
     </row>
     <row r="273" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="B273" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="C273" t="s">
         <v>126</v>
       </c>
       <c r="D273" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="E273" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="G273" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="H273" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="L273" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="O273" t="s">
         <v>43</v>
@@ -13403,31 +13406,31 @@
     </row>
     <row r="274" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="B274" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="C274" t="s">
         <v>126</v>
       </c>
       <c r="D274" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="E274" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="F274" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="G274" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="H274" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="L274" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="O274" t="s">
         <v>43</v>
@@ -13435,31 +13438,31 @@
     </row>
     <row r="275" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="B275" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="C275" t="s">
         <v>126</v>
       </c>
       <c r="D275" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="E275" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="F275" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="G275" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="H275" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="L275" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="O275" t="s">
         <v>43</v>
@@ -13467,34 +13470,34 @@
     </row>
     <row r="276" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A276" s="1" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="B276" s="1" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="C276" s="1" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="D276" s="1" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="E276" s="1"/>
       <c r="F276" s="1" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="G276" s="1" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="H276" s="1" t="s">
         <v>405</v>
       </c>
       <c r="I276" s="1" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="J276" s="1"/>
       <c r="K276" s="1"/>
       <c r="L276" s="1" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="M276" s="1" t="s">
         <v>22</v>
@@ -13508,37 +13511,37 @@
     </row>
     <row r="277" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="B277" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="C277" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="D277" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="E277" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="F277" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="G277" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="H277" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="I277" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="J277" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="L277" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="M277" t="s">
         <v>22</v>
@@ -13552,37 +13555,37 @@
     </row>
     <row r="278" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="B278" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="C278" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="D278" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="E278" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="F278" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="G278" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="H278" t="s">
         <v>336</v>
       </c>
       <c r="I278" s="1" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="J278" s="1" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="L278" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="M278" t="s">
         <v>30</v>
@@ -13596,37 +13599,37 @@
     </row>
     <row r="279" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="B279" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="C279" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="D279" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="E279" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="F279" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="G279" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="H279" t="s">
         <v>336</v>
       </c>
       <c r="I279" s="1" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="J279" s="1" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="L279" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="M279" t="s">
         <v>30</v>
@@ -13640,43 +13643,43 @@
     </row>
     <row r="280" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="B280" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="C280" t="s">
         <v>646</v>
       </c>
       <c r="D280" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="E280" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="F280" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="G280" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="H280" t="s">
         <v>336</v>
       </c>
       <c r="I280" s="1" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="J280" s="1" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="L280" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="M280" t="s">
         <v>30</v>
       </c>
       <c r="N280" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="O280" t="s">
         <v>43</v>
@@ -13684,35 +13687,35 @@
     </row>
     <row r="281" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="B281" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="C281" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="D281" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="E281" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="F281" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="G281" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="H281" t="s">
         <v>336</v>
       </c>
       <c r="I281" s="1" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="J281" s="1"/>
       <c r="L281" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="M281" t="s">
         <v>69</v>
@@ -13726,43 +13729,43 @@
     </row>
     <row r="282" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="B282" t="s">
         <v>666</v>
       </c>
       <c r="C282" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="D282" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="E282" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="F282" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="G282" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="H282" t="s">
         <v>336</v>
       </c>
       <c r="I282" s="1" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="J282" s="1" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="L282" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="M282" t="s">
         <v>30</v>
       </c>
       <c r="N282" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="O282" t="s">
         <v>43</v>
@@ -13770,7 +13773,7 @@
     </row>
     <row r="283" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="B283" t="s">
         <v>431</v>
@@ -13779,28 +13782,28 @@
         <v>646</v>
       </c>
       <c r="D283" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="E283" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="F283" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="G283" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="H283" t="s">
         <v>336</v>
       </c>
       <c r="I283" s="1" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="J283" s="1" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="L283" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="M283" t="s">
         <v>30</v>
@@ -13814,41 +13817,41 @@
     </row>
     <row r="284" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B284" t="s">
         <v>431</v>
       </c>
       <c r="C284" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="D284" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="E284" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="F284" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="G284" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="H284" t="s">
         <v>336</v>
       </c>
       <c r="I284" s="1" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="J284" s="1"/>
       <c r="L284" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="M284" t="s">
         <v>69</v>
       </c>
       <c r="N284" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="O284" t="s">
         <v>43</v>
@@ -13865,28 +13868,28 @@
         <v>646</v>
       </c>
       <c r="D285" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="E285" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="F285" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="G285" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="H285" t="s">
         <v>336</v>
       </c>
       <c r="I285" s="1" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="J285" s="1" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="L285" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="M285" t="s">
         <v>30</v>
@@ -13900,43 +13903,43 @@
     </row>
     <row r="286" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="B286" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="C286" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="D286" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="E286" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="F286" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="G286" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="H286" t="s">
         <v>336</v>
       </c>
       <c r="I286" s="1" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="J286" s="1" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="L286" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="M286" t="s">
         <v>30</v>
       </c>
       <c r="N286" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="O286" t="s">
         <v>43</v>
@@ -13944,37 +13947,37 @@
     </row>
     <row r="287" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="B287" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="C287" t="s">
         <v>646</v>
       </c>
       <c r="D287" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="E287" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="F287" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="G287" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="H287" t="s">
         <v>336</v>
       </c>
       <c r="I287" s="1" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="J287" s="1" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="L287" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="M287" t="s">
         <v>30</v>
@@ -13991,34 +13994,34 @@
         <v>400</v>
       </c>
       <c r="B288" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="C288" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="D288" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="E288" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="F288" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="G288" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="H288" t="s">
         <v>336</v>
       </c>
       <c r="I288" s="1" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="J288" s="1" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="L288" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="M288" t="s">
         <v>30</v>
@@ -14032,32 +14035,32 @@
     </row>
     <row r="289" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="B289" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="C289" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="D289" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="F289" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="G289" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="H289" t="s">
         <v>336</v>
       </c>
       <c r="I289" s="1" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="J289" s="1"/>
       <c r="L289" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="M289" t="s">
         <v>69</v>
@@ -14071,32 +14074,32 @@
     </row>
     <row r="290" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="B290" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="C290" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="D290" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="F290" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="G290" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="H290" t="s">
         <v>336</v>
       </c>
       <c r="I290" s="1" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="J290" s="1"/>
       <c r="L290" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="M290" t="s">
         <v>69</v>
@@ -14110,32 +14113,32 @@
     </row>
     <row r="291" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="B291" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="C291" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="D291" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="F291" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="G291" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="H291" t="s">
         <v>336</v>
       </c>
       <c r="I291" s="1" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="J291" s="1"/>
       <c r="L291" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="M291" t="s">
         <v>69</v>

--- a/tracker.xlsx
+++ b/tracker.xlsx
@@ -409,7 +409,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O428"/>
+  <dimension ref="A1:O430"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.453125" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
     <col width="22" customWidth="1" style="1" min="1" max="1"/>
@@ -18495,7 +18495,6 @@
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="F323" t="inlineStr"/>
       <c r="G323" t="inlineStr">
         <is>
           <t>Agents framework, durable agentic workflows, agent-to-agent comms; Python/TypeScript; LLM agentic systems - direct Jack lane</t>
@@ -18506,16 +18505,11 @@
           <t>new</t>
         </is>
       </c>
-      <c r="I323" t="inlineStr"/>
-      <c r="J323" t="inlineStr"/>
-      <c r="K323" t="inlineStr"/>
       <c r="L323" t="inlineStr">
         <is>
           <t>Remote North America</t>
         </is>
       </c>
-      <c r="M323" t="inlineStr"/>
-      <c r="N323" t="inlineStr"/>
       <c r="O323" t="inlineStr">
         <is>
           <t>Low</t>
@@ -18548,7 +18542,6 @@
           <t>2026-03-17</t>
         </is>
       </c>
-      <c r="F324" t="inlineStr"/>
       <c r="G324" t="inlineStr">
         <is>
           <t>FDE, 7+ yrs backend/infra, Go/Python/Node/Rust/C++, WebRTC/voice AI, customer implementations</t>
@@ -18559,16 +18552,11 @@
           <t>new</t>
         </is>
       </c>
-      <c r="I324" t="inlineStr"/>
-      <c r="J324" t="inlineStr"/>
-      <c r="K324" t="inlineStr"/>
       <c r="L324" t="inlineStr">
         <is>
           <t>Remotely or on-site when necessary - some customer on-site travel; hiring across FDE/Senior/Staff levels</t>
         </is>
       </c>
-      <c r="M324" t="inlineStr"/>
-      <c r="N324" t="inlineStr"/>
       <c r="O324" t="inlineStr">
         <is>
           <t>Low</t>
@@ -18601,7 +18589,6 @@
           <t>2026-06-03</t>
         </is>
       </c>
-      <c r="F325" t="inlineStr"/>
       <c r="G325" t="inlineStr">
         <is>
           <t>Core services, telephony, observability; Go, gRPC, Raft, NATS, ClickHouse, OTel; small senior team, end-to-end ownership</t>
@@ -18612,16 +18599,11 @@
           <t>new</t>
         </is>
       </c>
-      <c r="I325" t="inlineStr"/>
-      <c r="J325" t="inlineStr"/>
-      <c r="K325" t="inlineStr"/>
       <c r="L325" t="inlineStr">
         <is>
           <t>K8s listed among stack (Jack light on K8s - honest framing, not a hard req)</t>
         </is>
       </c>
-      <c r="M325" t="inlineStr"/>
-      <c r="N325" t="inlineStr"/>
       <c r="O325" t="inlineStr">
         <is>
           <t>Low</t>
@@ -18654,7 +18636,6 @@
           <t>2026-05-23</t>
         </is>
       </c>
-      <c r="F326" t="inlineStr"/>
       <c r="G326" t="inlineStr">
         <is>
           <t>Full-stack product eng, TypeScript + Go, dashboards/CLI/observability surfaces for dev platform; 6+ yrs</t>
@@ -18665,16 +18646,11 @@
           <t>new</t>
         </is>
       </c>
-      <c r="I326" t="inlineStr"/>
-      <c r="J326" t="inlineStr"/>
-      <c r="K326" t="inlineStr"/>
       <c r="L326" t="inlineStr">
         <is>
           <t>Remote OK; SF HQ hybrid optional</t>
         </is>
       </c>
-      <c r="M326" t="inlineStr"/>
-      <c r="N326" t="inlineStr"/>
       <c r="O326" t="inlineStr">
         <is>
           <t>Low</t>
@@ -18707,7 +18683,6 @@
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="F327" t="inlineStr"/>
       <c r="G327" t="inlineStr">
         <is>
           <t>Same platform team as Senior Distributed Systems role, at staff level; core services/telepathy/observability; Go, Raft, NATS, ClickHouse</t>
@@ -18718,16 +18693,11 @@
           <t>new</t>
         </is>
       </c>
-      <c r="I327" t="inlineStr"/>
-      <c r="J327" t="inlineStr"/>
-      <c r="K327" t="inlineStr"/>
       <c r="L327" t="inlineStr">
         <is>
           <t>Staff-level - stretch on seniority vs Jack's 7 yrs + lead experience</t>
         </is>
       </c>
-      <c r="M327" t="inlineStr"/>
-      <c r="N327" t="inlineStr"/>
       <c r="O327" t="inlineStr">
         <is>
           <t>Low</t>
@@ -18775,16 +18745,11 @@
           <t>new</t>
         </is>
       </c>
-      <c r="I328" t="inlineStr"/>
-      <c r="J328" t="inlineStr"/>
-      <c r="K328" t="inlineStr"/>
       <c r="L328" t="inlineStr">
         <is>
           <t>Frontend/design-heavy, marketing-site work; salary band from aggregator mirrors, not the Ashby posting</t>
         </is>
       </c>
-      <c r="M328" t="inlineStr"/>
-      <c r="N328" t="inlineStr"/>
       <c r="O328" t="inlineStr">
         <is>
           <t>Low</t>
@@ -18817,7 +18782,6 @@
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="F329" t="inlineStr"/>
       <c r="G329" t="inlineStr">
         <is>
           <t>Post-training eng - synthetic data pipelines, evals/verifiers, vLLM/SGLang, FSDP, ship models to prod; strong Python eng who carried a model raw-data-to-prod - matches Jack's LLM fine-tuning on H100s</t>
@@ -18828,16 +18792,11 @@
           <t>new</t>
         </is>
       </c>
-      <c r="I329" t="inlineStr"/>
-      <c r="J329" t="inlineStr"/>
-      <c r="K329" t="inlineStr"/>
       <c r="L329" t="inlineStr">
         <is>
           <t>RL/post-training focus; GRPO/TRL nice-to-have, not required</t>
         </is>
       </c>
-      <c r="M329" t="inlineStr"/>
-      <c r="N329" t="inlineStr"/>
       <c r="O329" t="inlineStr">
         <is>
           <t>Low</t>
@@ -18885,16 +18844,11 @@
           <t>new</t>
         </is>
       </c>
-      <c r="I330" t="inlineStr"/>
-      <c r="J330" t="inlineStr"/>
-      <c r="K330" t="inlineStr"/>
       <c r="L330" t="inlineStr">
         <is>
           <t>US salary range stated in posting</t>
         </is>
       </c>
-      <c r="M330" t="inlineStr"/>
-      <c r="N330" t="inlineStr"/>
       <c r="O330" t="inlineStr">
         <is>
           <t>Low</t>
@@ -18942,16 +18896,11 @@
           <t>new</t>
         </is>
       </c>
-      <c r="I331" t="inlineStr"/>
-      <c r="J331" t="inlineStr"/>
-      <c r="K331" t="inlineStr"/>
       <c r="L331" t="inlineStr">
         <is>
           <t>USD range in posting (CAD C$225,000-$285,000 also listed)</t>
         </is>
       </c>
-      <c r="M331" t="inlineStr"/>
-      <c r="N331" t="inlineStr"/>
       <c r="O331" t="inlineStr">
         <is>
           <t>Low</t>
@@ -18984,7 +18933,6 @@
           <t>2026-04-15</t>
         </is>
       </c>
-      <c r="F332" t="inlineStr"/>
       <c r="G332" t="inlineStr">
         <is>
           <t>Founding eng, Data Intelligence team; 5+ yrs Data/AI Eng, SQL+Python, RAG/agentic on structured data, dbt semantic layers, Athena - direct SQL/Python/ETL+RAG fit</t>
@@ -18995,16 +18943,11 @@
           <t>new</t>
         </is>
       </c>
-      <c r="I332" t="inlineStr"/>
-      <c r="J332" t="inlineStr"/>
-      <c r="K332" t="inlineStr"/>
       <c r="L332" t="inlineStr">
         <is>
           <t>Apr 2026 posting - confirm still open at apply</t>
         </is>
       </c>
-      <c r="M332" t="inlineStr"/>
-      <c r="N332" t="inlineStr"/>
       <c r="O332" t="inlineStr">
         <is>
           <t>Low</t>
@@ -19037,7 +18980,6 @@
           <t>2026-04-21</t>
         </is>
       </c>
-      <c r="F333" t="inlineStr"/>
       <c r="G333" t="inlineStr">
         <is>
           <t>Usage-metering/billing pipeline end-to-end (event ingestion, aggregation, rating/invoicing via M3ter/Metronome/Stripe); 5+ yrs billing/metering/financial-data systems, Postgres, data pipelines, Rust preferred + Python/TS/Go</t>
@@ -19048,16 +18990,11 @@
           <t>new</t>
         </is>
       </c>
-      <c r="I333" t="inlineStr"/>
-      <c r="J333" t="inlineStr"/>
-      <c r="K333" t="inlineStr"/>
       <c r="L333" t="inlineStr">
         <is>
           <t>No billing-systems background stated for Jack; Rust preferred</t>
         </is>
       </c>
-      <c r="M333" t="inlineStr"/>
-      <c r="N333" t="inlineStr"/>
       <c r="O333" t="inlineStr">
         <is>
           <t>Low</t>
@@ -19090,7 +19027,6 @@
           <t>2026-04-06</t>
         </is>
       </c>
-      <c r="F334" t="inlineStr"/>
       <c r="G334" t="inlineStr">
         <is>
           <t>ML-platform - CI/CD for model delivery, deployment pipelines, A/B rollout, model monitoring/drift, retraining, Triton/TensorRT nice-to-have; 4+ yrs MLOps/DevOps, Python, Docker</t>
@@ -19101,16 +19037,11 @@
           <t>new</t>
         </is>
       </c>
-      <c r="I334" t="inlineStr"/>
-      <c r="J334" t="inlineStr"/>
-      <c r="K334" t="inlineStr"/>
       <c r="L334" t="inlineStr">
         <is>
           <t>Posting explicitly requires hands-on Docker + K8s - Jack light on K8s, do not claim; Apr 2026 posting</t>
         </is>
       </c>
-      <c r="M334" t="inlineStr"/>
-      <c r="N334" t="inlineStr"/>
       <c r="O334" t="inlineStr">
         <is>
           <t>Low</t>
@@ -19143,7 +19074,6 @@
           <t>2026-02-18</t>
         </is>
       </c>
-      <c r="F335" t="inlineStr"/>
       <c r="G335" t="inlineStr">
         <is>
           <t>Voice-agent backend - speech services, telephony + RAG integrations, multi-model orchestration, observability; 3+ yrs, Rust (or C/C++) + Python</t>
@@ -19154,16 +19084,11 @@
           <t>new</t>
         </is>
       </c>
-      <c r="I335" t="inlineStr"/>
-      <c r="J335" t="inlineStr"/>
-      <c r="K335" t="inlineStr"/>
       <c r="L335" t="inlineStr">
         <is>
           <t>Rust required; Feb 2026 posting</t>
         </is>
       </c>
-      <c r="M335" t="inlineStr"/>
-      <c r="N335" t="inlineStr"/>
       <c r="O335" t="inlineStr">
         <is>
           <t>Low</t>
@@ -19196,7 +19121,6 @@
           <t>2026-07-09</t>
         </is>
       </c>
-      <c r="F336" t="inlineStr"/>
       <c r="G336" t="inlineStr">
         <is>
           <t>Core inference services - networking, speech processing, audio transcoding, latency/memory optimization; 3+ yrs, Rust (or C/C++) + Python, Torch/transformers plus - matches VLM/video inference-pipeline background</t>
@@ -19207,16 +19131,11 @@
           <t>new</t>
         </is>
       </c>
-      <c r="I336" t="inlineStr"/>
-      <c r="J336" t="inlineStr"/>
-      <c r="K336" t="inlineStr"/>
       <c r="L336" t="inlineStr">
         <is>
           <t>Rust required</t>
         </is>
       </c>
-      <c r="M336" t="inlineStr"/>
-      <c r="N336" t="inlineStr"/>
       <c r="O336" t="inlineStr">
         <is>
           <t>Low</t>
@@ -19249,7 +19168,6 @@
           <t>2026-07-10</t>
         </is>
       </c>
-      <c r="F337" t="inlineStr"/>
       <c r="G337" t="inlineStr">
         <is>
           <t>Senior backend, Engine team, same req template as Inference Services role (Rust/C++ + Python, 3+ yrs, inference services)</t>
@@ -19260,16 +19178,11 @@
           <t>new</t>
         </is>
       </c>
-      <c r="I337" t="inlineStr"/>
-      <c r="J337" t="inlineStr"/>
-      <c r="K337" t="inlineStr"/>
       <c r="L337" t="inlineStr">
         <is>
           <t>Rust required; near-duplicate scope to Inference Services role, different requisition</t>
         </is>
       </c>
-      <c r="M337" t="inlineStr"/>
-      <c r="N337" t="inlineStr"/>
       <c r="O337" t="inlineStr">
         <is>
           <t>Low</t>
@@ -19302,7 +19215,6 @@
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="F338" t="inlineStr"/>
       <c r="G338" t="inlineStr">
         <is>
           <t>Player-coach Director owning GTM systems/data/automation/AI workflows (CRM, CPQ, forecasting, usage/billing integrations); still writes production code, ships agents/internal tools; GTM eng is a wanted lane</t>
@@ -19313,16 +19225,11 @@
           <t>new</t>
         </is>
       </c>
-      <c r="I338" t="inlineStr"/>
-      <c r="J338" t="inlineStr"/>
-      <c r="K338" t="inlineStr"/>
       <c r="L338" t="inlineStr">
         <is>
           <t>Director-level; requires prior GTM Eng / RevOps / Sales Ops leadership - stretch for Jack</t>
         </is>
       </c>
-      <c r="M338" t="inlineStr"/>
-      <c r="N338" t="inlineStr"/>
       <c r="O338" t="inlineStr">
         <is>
           <t>Medium</t>
@@ -19355,7 +19262,6 @@
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="F339" t="inlineStr"/>
       <c r="G339" t="inlineStr">
         <is>
           <t>Title-verified on live Ashby feed (USA-Remote, Engineering); description not read</t>
@@ -19366,16 +19272,11 @@
           <t>new</t>
         </is>
       </c>
-      <c r="I339" t="inlineStr"/>
-      <c r="J339" t="inlineStr"/>
-      <c r="K339" t="inlineStr"/>
       <c r="L339" t="inlineStr">
         <is>
           <t>Edge/on-device ML likely leans embedded/C++ and model optimization; inference-pipeline experience partially transfers; posted date is fallback (not retrieved)</t>
         </is>
       </c>
-      <c r="M339" t="inlineStr"/>
-      <c r="N339" t="inlineStr"/>
       <c r="O339" t="inlineStr">
         <is>
           <t>Low</t>
@@ -19408,7 +19309,6 @@
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="F340" t="inlineStr"/>
       <c r="G340" t="inlineStr">
         <is>
           <t>Title-verified on live Ashby feed (USA-Remote, Research dept); description not read</t>
@@ -19419,16 +19319,11 @@
           <t>new</t>
         </is>
       </c>
-      <c r="I340" t="inlineStr"/>
-      <c r="J340" t="inlineStr"/>
-      <c r="K340" t="inlineStr"/>
       <c r="L340" t="inlineStr">
         <is>
           <t>Research-dept role; verify degree/research expectations before applying; posted date is fallback (not retrieved)</t>
         </is>
       </c>
-      <c r="M340" t="inlineStr"/>
-      <c r="N340" t="inlineStr"/>
       <c r="O340" t="inlineStr">
         <is>
           <t>Low</t>
@@ -19461,7 +19356,6 @@
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="F341" t="inlineStr"/>
       <c r="G341" t="inlineStr">
         <is>
           <t>Title-verified on live Ashby feed (USA-Remote, Customer Success); description not read</t>
@@ -19472,16 +19366,11 @@
           <t>new</t>
         </is>
       </c>
-      <c r="I341" t="inlineStr"/>
-      <c r="J341" t="inlineStr"/>
-      <c r="K341" t="inlineStr"/>
       <c r="L341" t="inlineStr">
         <is>
           <t>Customer-facing technical role; verify how much hands-on coding vs support; posted date is fallback (not retrieved)</t>
         </is>
       </c>
-      <c r="M341" t="inlineStr"/>
-      <c r="N341" t="inlineStr"/>
       <c r="O341" t="inlineStr">
         <is>
           <t>Low</t>
@@ -19529,16 +19418,11 @@
           <t>new</t>
         </is>
       </c>
-      <c r="I342" t="inlineStr"/>
-      <c r="J342" t="inlineStr"/>
-      <c r="K342" t="inlineStr"/>
       <c r="L342" t="inlineStr">
         <is>
           <t>Pay band below $150k-$200k target; on-call incl weekends/holidays; East Coast hours; occasional travel (not &gt;2 wks)</t>
         </is>
       </c>
-      <c r="M342" t="inlineStr"/>
-      <c r="N342" t="inlineStr"/>
       <c r="O342" t="inlineStr">
         <is>
           <t>Low</t>
@@ -19571,7 +19455,6 @@
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="F343" t="inlineStr"/>
       <c r="G343" t="inlineStr">
         <is>
           <t>Platform-eng lane; title/location/URL API-verified; description not read</t>
@@ -19582,16 +19465,11 @@
           <t>new</t>
         </is>
       </c>
-      <c r="I343" t="inlineStr"/>
-      <c r="J343" t="inlineStr"/>
-      <c r="K343" t="inlineStr"/>
       <c r="L343" t="inlineStr">
         <is>
           <t>L2 junior-mid level vs Jack's 7 yrs - verify team/scope at apply</t>
         </is>
       </c>
-      <c r="M343" t="inlineStr"/>
-      <c r="N343" t="inlineStr"/>
       <c r="O343" t="inlineStr">
         <is>
           <t>Low</t>
@@ -19624,7 +19502,6 @@
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="F344" t="inlineStr"/>
       <c r="G344" t="inlineStr">
         <is>
           <t>Solutions/presales-eng lane; title/location/URL API-verified; description not read</t>
@@ -19635,16 +19512,11 @@
           <t>new</t>
         </is>
       </c>
-      <c r="I344" t="inlineStr"/>
-      <c r="J344" t="inlineStr"/>
-      <c r="K344" t="inlineStr"/>
       <c r="L344" t="inlineStr">
         <is>
           <t>Verify requirements at apply</t>
         </is>
       </c>
-      <c r="M344" t="inlineStr"/>
-      <c r="N344" t="inlineStr"/>
       <c r="O344" t="inlineStr">
         <is>
           <t>Low</t>
@@ -19677,7 +19549,6 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="F345" t="inlineStr"/>
       <c r="G345" t="inlineStr">
         <is>
           <t>Data/analytics-eng lane (SQL/dbt-style work typical for the title); title/location/URL API-verified; description not read</t>
@@ -19688,12 +19559,6 @@
           <t>new</t>
         </is>
       </c>
-      <c r="I345" t="inlineStr"/>
-      <c r="J345" t="inlineStr"/>
-      <c r="K345" t="inlineStr"/>
-      <c r="L345" t="inlineStr"/>
-      <c r="M345" t="inlineStr"/>
-      <c r="N345" t="inlineStr"/>
       <c r="O345" t="inlineStr">
         <is>
           <t>Low</t>
@@ -19726,7 +19591,6 @@
           <t>2026-07-24</t>
         </is>
       </c>
-      <c r="F346" t="inlineStr"/>
       <c r="G346" t="inlineStr">
         <is>
           <t>Conversational-AI architecture - closest Twilio match to LLM-agent/voice-pipeline work at senior/architect level; title/location/URL API-verified; description not read</t>
@@ -19737,16 +19601,11 @@
           <t>new</t>
         </is>
       </c>
-      <c r="I346" t="inlineStr"/>
-      <c r="J346" t="inlineStr"/>
-      <c r="K346" t="inlineStr"/>
       <c r="L346" t="inlineStr">
         <is>
           <t>Verify stack/seniority expectations at apply</t>
         </is>
       </c>
-      <c r="M346" t="inlineStr"/>
-      <c r="N346" t="inlineStr"/>
       <c r="O346" t="inlineStr">
         <is>
           <t>Low</t>
@@ -19779,7 +19638,6 @@
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="F347" t="inlineStr"/>
       <c r="G347" t="inlineStr">
         <is>
           <t>Mid-level backend SWE; title/location/URL API-verified; description not read</t>
@@ -19790,16 +19648,11 @@
           <t>new</t>
         </is>
       </c>
-      <c r="I347" t="inlineStr"/>
-      <c r="J347" t="inlineStr"/>
-      <c r="K347" t="inlineStr"/>
       <c r="L347" t="inlineStr">
         <is>
           <t>Generic posting, no team in title; L3 below Jack's seniority - verify team/scope</t>
         </is>
       </c>
-      <c r="M347" t="inlineStr"/>
-      <c r="N347" t="inlineStr"/>
       <c r="O347" t="inlineStr">
         <is>
           <t>Low</t>
@@ -19832,7 +19685,6 @@
           <t>2026-02-27</t>
         </is>
       </c>
-      <c r="F348" t="inlineStr"/>
       <c r="G348" t="inlineStr">
         <is>
           <t>Video engineering - matches video-pipeline background; title/location/URL API-verified; description not read</t>
@@ -19843,16 +19695,11 @@
           <t>new</t>
         </is>
       </c>
-      <c r="I348" t="inlineStr"/>
-      <c r="J348" t="inlineStr"/>
-      <c r="K348" t="inlineStr"/>
       <c r="L348" t="inlineStr">
         <is>
           <t>Posted Feb 2026, may be stale</t>
         </is>
       </c>
-      <c r="M348" t="inlineStr"/>
-      <c r="N348" t="inlineStr"/>
       <c r="O348" t="inlineStr">
         <is>
           <t>Low</t>
@@ -19885,7 +19732,6 @@
           <t>2026-07-15</t>
         </is>
       </c>
-      <c r="F349" t="inlineStr"/>
       <c r="G349" t="inlineStr">
         <is>
           <t>Solutions-architecture lane at meeting-transcription AI company - only Otter role with a remote option; description not read</t>
@@ -19896,16 +19742,11 @@
           <t>new</t>
         </is>
       </c>
-      <c r="I349" t="inlineStr"/>
-      <c r="J349" t="inlineStr"/>
-      <c r="K349" t="inlineStr"/>
       <c r="L349" t="inlineStr">
         <is>
           <t>Listing shows both Mountain View and Remote - verify fully-remote-from-Utah eligibility before applying</t>
         </is>
       </c>
-      <c r="M349" t="inlineStr"/>
-      <c r="N349" t="inlineStr"/>
       <c r="O349" t="inlineStr">
         <is>
           <t>Low</t>
@@ -19953,16 +19794,11 @@
           <t>new</t>
         </is>
       </c>
-      <c r="I350" t="inlineStr"/>
-      <c r="J350" t="inlineStr"/>
-      <c r="K350" t="inlineStr"/>
       <c r="L350" t="inlineStr">
         <is>
           <t>Travel up to 20%. CAVEAT: requires strong Kubernetes experience (GKE/EKS/AKS) incl cluster design, autoscaling, multi-zone - Jack light on K8s, do not claim hands-on</t>
         </is>
       </c>
-      <c r="M350" t="inlineStr"/>
-      <c r="N350" t="inlineStr"/>
       <c r="O350" t="inlineStr">
         <is>
           <t>Low</t>
@@ -20010,16 +19846,11 @@
           <t>new</t>
         </is>
       </c>
-      <c r="I351" t="inlineStr"/>
-      <c r="J351" t="inlineStr"/>
-      <c r="K351" t="inlineStr"/>
       <c r="L351" t="inlineStr">
         <is>
           <t>Travel up to 20%. CAVEAT: board lists 10 hub cities (Atlanta, Austin, Boston, Dallas, Denver, Detroit, Las Vegas, Nashville, San Diego, Seattle) - SLC NOT listed; posting says Remote, confirm Utah eligibility at application</t>
         </is>
       </c>
-      <c r="M351" t="inlineStr"/>
-      <c r="N351" t="inlineStr"/>
       <c r="O351" t="inlineStr">
         <is>
           <t>Low</t>
@@ -20067,16 +19898,11 @@
           <t>new</t>
         </is>
       </c>
-      <c r="I352" t="inlineStr"/>
-      <c r="J352" t="inlineStr"/>
-      <c r="K352" t="inlineStr"/>
       <c r="L352" t="inlineStr">
         <is>
           <t>dbt-modeling-centric - dbt is a gap for Jack</t>
         </is>
       </c>
-      <c r="M352" t="inlineStr"/>
-      <c r="N352" t="inlineStr"/>
       <c r="O352" t="inlineStr">
         <is>
           <t>Low</t>
@@ -20124,16 +19950,11 @@
           <t>new</t>
         </is>
       </c>
-      <c r="I353" t="inlineStr"/>
-      <c r="J353" t="inlineStr"/>
-      <c r="K353" t="inlineStr"/>
       <c r="L353" t="inlineStr">
         <is>
           <t>Frontend-only role; TS secondary to Jack's backend/data strengths</t>
         </is>
       </c>
-      <c r="M353" t="inlineStr"/>
-      <c r="N353" t="inlineStr"/>
       <c r="O353" t="inlineStr">
         <is>
           <t>Low</t>
@@ -20181,12 +20002,6 @@
           <t>new</t>
         </is>
       </c>
-      <c r="I354" t="inlineStr"/>
-      <c r="J354" t="inlineStr"/>
-      <c r="K354" t="inlineStr"/>
-      <c r="L354" t="inlineStr"/>
-      <c r="M354" t="inlineStr"/>
-      <c r="N354" t="inlineStr"/>
       <c r="O354" t="inlineStr">
         <is>
           <t>Low</t>
@@ -20234,16 +20049,11 @@
           <t>new</t>
         </is>
       </c>
-      <c r="I355" t="inlineStr"/>
-      <c r="J355" t="inlineStr"/>
-      <c r="K355" t="inlineStr"/>
       <c r="L355" t="inlineStr">
         <is>
           <t>Senior/Staff level, typically 6+ yrs shipping production backends at scale; Jack has 7 yrs; retrieval-intuition requirement plays to vector-search/RAG experience</t>
         </is>
       </c>
-      <c r="M355" t="inlineStr"/>
-      <c r="N355" t="inlineStr"/>
       <c r="O355" t="inlineStr">
         <is>
           <t>Low</t>
@@ -20291,16 +20101,11 @@
           <t>new</t>
         </is>
       </c>
-      <c r="I356" t="inlineStr"/>
-      <c r="J356" t="inlineStr"/>
-      <c r="K356" t="inlineStr"/>
       <c r="L356" t="inlineStr">
         <is>
           <t>Old posting (Jan 2025) but still listed open on live board. Identity/access focus (SCIM, SAML, SSO, LDAP, OAuth2) is a gap area; scheduled on-call rotations</t>
         </is>
       </c>
-      <c r="M356" t="inlineStr"/>
-      <c r="N356" t="inlineStr"/>
       <c r="O356" t="inlineStr">
         <is>
           <t>Low</t>
@@ -20333,7 +20138,6 @@
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="F357" t="inlineStr"/>
       <c r="G357" t="inlineStr">
         <is>
           <t>Own the Python SDK (DB, auth, storage, realtime, edge functions, sync+async), library authoring in the open, typing/asyncio/packaging depth, AI-agent consumers - direct Python + Postgres-platform match</t>
@@ -20344,12 +20148,6 @@
           <t>new</t>
         </is>
       </c>
-      <c r="I357" t="inlineStr"/>
-      <c r="J357" t="inlineStr"/>
-      <c r="K357" t="inlineStr"/>
-      <c r="L357" t="inlineStr"/>
-      <c r="M357" t="inlineStr"/>
-      <c r="N357" t="inlineStr"/>
       <c r="O357" t="inlineStr">
         <is>
           <t>Low</t>
@@ -20382,7 +20180,6 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="F358" t="inlineStr"/>
       <c r="G358" t="inlineStr">
         <is>
           <t>Platform engineering - AWS/GCP governance, IaC, self-service platform primitives, security boundaries, on-call; 5+ yrs cloud/platform/ops</t>
@@ -20393,16 +20190,11 @@
           <t>new</t>
         </is>
       </c>
-      <c r="I358" t="inlineStr"/>
-      <c r="J358" t="inlineStr"/>
-      <c r="K358" t="inlineStr"/>
       <c r="L358" t="inlineStr">
         <is>
           <t>Cloud-governance/IAM-SSO depth and on-call central; Jack's AWS/GCP + CI/CD adjacent but governance not his core</t>
         </is>
       </c>
-      <c r="M358" t="inlineStr"/>
-      <c r="N358" t="inlineStr"/>
       <c r="O358" t="inlineStr">
         <is>
           <t>Low</t>
@@ -20435,7 +20227,6 @@
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="F359" t="inlineStr"/>
       <c r="G359" t="inlineStr">
         <is>
           <t>Build high-performance CI/CD execution platform (Buildkite/GitHub-Actions-style runners): orchestration engine, ephemeral sandboxes on EKS/ECS, job scheduling at scale; Go + TypeScript, AWS, IaC (Pulumi/Terraform) - matches Go backend + CI/CD + AWS</t>
@@ -20446,12 +20237,6 @@
           <t>new</t>
         </is>
       </c>
-      <c r="I359" t="inlineStr"/>
-      <c r="J359" t="inlineStr"/>
-      <c r="K359" t="inlineStr"/>
-      <c r="L359" t="inlineStr"/>
-      <c r="M359" t="inlineStr"/>
-      <c r="N359" t="inlineStr"/>
       <c r="O359" t="inlineStr">
         <is>
           <t>Low</t>
@@ -20484,7 +20269,6 @@
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="F360" t="inlineStr"/>
       <c r="G360" t="inlineStr">
         <is>
           <t>Hands-on data eng - BigQuery/dbt cost models and pipelines, Python/Terraform/Lambda automation, AWS/GCP billing data; Python/SQL/ETL/AWS fit the mechanics</t>
@@ -20495,16 +20279,11 @@
           <t>new</t>
         </is>
       </c>
-      <c r="I360" t="inlineStr"/>
-      <c r="J360" t="inlineStr"/>
-      <c r="K360" t="inlineStr"/>
       <c r="L360" t="inlineStr">
         <is>
           <t>dbt/BigQuery-centric and FinOps/cloud-cost specialization is a real gap area</t>
         </is>
       </c>
-      <c r="M360" t="inlineStr"/>
-      <c r="N360" t="inlineStr"/>
       <c r="O360" t="inlineStr">
         <is>
           <t>Low</t>
@@ -20537,7 +20316,6 @@
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="F361" t="inlineStr"/>
       <c r="G361" t="inlineStr">
         <is>
           <t>Lead/EM-adjacent - general EM pipeline across backend/platform/database teams; 5+ yrs engineering depth, people/delivery/technical role</t>
@@ -20548,16 +20326,11 @@
           <t>new</t>
         </is>
       </c>
-      <c r="I361" t="inlineStr"/>
-      <c r="J361" t="inlineStr"/>
-      <c r="K361" t="inlineStr"/>
       <c r="L361" t="inlineStr">
         <is>
           <t>Requires 3+ years managing remote engineering teams; Jack's management experience is founder/lead-scale (small teams), not 3 yrs formal remote-team management</t>
         </is>
       </c>
-      <c r="M361" t="inlineStr"/>
-      <c r="N361" t="inlineStr"/>
       <c r="O361" t="inlineStr">
         <is>
           <t>Low</t>
@@ -20605,16 +20378,11 @@
           <t>new</t>
         </is>
       </c>
-      <c r="I362" t="inlineStr"/>
-      <c r="J362" t="inlineStr"/>
-      <c r="K362" t="inlineStr"/>
       <c r="L362" t="inlineStr">
         <is>
           <t>Old evergreen posting (Jul 2024). Board marks Hybrid with Remote as a location option - confirm fully-remote-from-Utah eligibility</t>
         </is>
       </c>
-      <c r="M362" t="inlineStr"/>
-      <c r="N362" t="inlineStr"/>
       <c r="O362" t="inlineStr">
         <is>
           <t>Low</t>
@@ -20662,16 +20430,11 @@
           <t>new</t>
         </is>
       </c>
-      <c r="I363" t="inlineStr"/>
-      <c r="J363" t="inlineStr"/>
-      <c r="K363" t="inlineStr"/>
       <c r="L363" t="inlineStr">
         <is>
           <t>Board marks Hybrid with Remote as a location option - confirm fully-remote-from-Utah eligibility</t>
         </is>
       </c>
-      <c r="M363" t="inlineStr"/>
-      <c r="N363" t="inlineStr"/>
       <c r="O363" t="inlineStr">
         <is>
           <t>Low</t>
@@ -20719,16 +20482,11 @@
           <t>new</t>
         </is>
       </c>
-      <c r="I364" t="inlineStr"/>
-      <c r="J364" t="inlineStr"/>
-      <c r="K364" t="inlineStr"/>
       <c r="L364" t="inlineStr">
         <is>
           <t>Description identical to AI Inference Engineer posting; old evergreen posting (Mar 2024). Same Hybrid/Remote caveat</t>
         </is>
       </c>
-      <c r="M364" t="inlineStr"/>
-      <c r="N364" t="inlineStr"/>
       <c r="O364" t="inlineStr">
         <is>
           <t>Low</t>
@@ -20776,16 +20534,11 @@
           <t>new</t>
         </is>
       </c>
-      <c r="I365" t="inlineStr"/>
-      <c r="J365" t="inlineStr"/>
-      <c r="K365" t="inlineStr"/>
       <c r="L365" t="inlineStr">
         <is>
           <t>Same Hybrid/Remote caveat</t>
         </is>
       </c>
-      <c r="M365" t="inlineStr"/>
-      <c r="N365" t="inlineStr"/>
       <c r="O365" t="inlineStr">
         <is>
           <t>Low</t>
@@ -20833,16 +20586,11 @@
           <t>new</t>
         </is>
       </c>
-      <c r="I366" t="inlineStr"/>
-      <c r="J366" t="inlineStr"/>
-      <c r="K366" t="inlineStr"/>
       <c r="L366" t="inlineStr">
         <is>
           <t>FLAG TRAVEL: explicitly requires spending time on-site with customers / embedding with their teams - confirm travel cadence does not exceed 2-weeks-at-a-time threshold</t>
         </is>
       </c>
-      <c r="M366" t="inlineStr"/>
-      <c r="N366" t="inlineStr"/>
       <c r="O366" t="inlineStr">
         <is>
           <t>Low</t>
@@ -20875,7 +20623,6 @@
           <t>2026-05-28</t>
         </is>
       </c>
-      <c r="F367" t="inlineStr"/>
       <c r="G367" t="inlineStr">
         <is>
           <t>Open-source ML eng on Transformers/Datasets/PyTorch/vLLM; Jack's LLM fine-tuning (H100s) and VLM inference background relevant</t>
@@ -20886,9 +20633,6 @@
           <t>new</t>
         </is>
       </c>
-      <c r="I367" t="inlineStr"/>
-      <c r="J367" t="inlineStr"/>
-      <c r="K367" t="inlineStr"/>
       <c r="L367" t="inlineStr">
         <is>
           <t>Posting requires a cover letter on why he wants to work in open-source at HF; first application question must start with 'GPU-poor and proud'. Requires deep PyTorch + public track record of open-source ML contributions (merged PRs) - gap area. URGENT: mirror lists Oct 30, 2026 apply-by date</t>
@@ -20899,7 +20643,6 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="N367" t="inlineStr"/>
       <c r="O367" t="inlineStr">
         <is>
           <t>Medium</t>
@@ -20932,7 +20675,6 @@
           <t>2026-03-05</t>
         </is>
       </c>
-      <c r="F368" t="inlineStr"/>
       <c r="G368" t="inlineStr">
         <is>
           <t>Go + AWS/Azure/GCP + Terraform; K8s 'preferably' (preference, not hard req) - strong infra fit</t>
@@ -20943,12 +20685,6 @@
           <t>new</t>
         </is>
       </c>
-      <c r="I368" t="inlineStr"/>
-      <c r="J368" t="inlineStr"/>
-      <c r="K368" t="inlineStr"/>
-      <c r="L368" t="inlineStr"/>
-      <c r="M368" t="inlineStr"/>
-      <c r="N368" t="inlineStr"/>
       <c r="O368" t="inlineStr">
         <is>
           <t>Low</t>
@@ -20981,7 +20717,6 @@
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="F369" t="inlineStr"/>
       <c r="G369" t="inlineStr">
         <is>
           <t>Python/PyTorch/Ray, inference APIs, vector DBs, embeddings; daytime on-call</t>
@@ -20992,16 +20727,11 @@
           <t>new</t>
         </is>
       </c>
-      <c r="I369" t="inlineStr"/>
-      <c r="J369" t="inlineStr"/>
-      <c r="K369" t="inlineStr"/>
       <c r="L369" t="inlineStr">
         <is>
           <t>UT/SLC not in listed locations - confirm eligibility before applying</t>
         </is>
       </c>
-      <c r="M369" t="inlineStr"/>
-      <c r="N369" t="inlineStr"/>
       <c r="O369" t="inlineStr">
         <is>
           <t>Low</t>
@@ -21034,7 +20764,6 @@
           <t>2026-07-09</t>
         </is>
       </c>
-      <c r="F370" t="inlineStr"/>
       <c r="G370" t="inlineStr">
         <is>
           <t>AI/ML integrations; Python/Go + APIs - direct fit</t>
@@ -21045,12 +20774,6 @@
           <t>new</t>
         </is>
       </c>
-      <c r="I370" t="inlineStr"/>
-      <c r="J370" t="inlineStr"/>
-      <c r="K370" t="inlineStr"/>
-      <c r="L370" t="inlineStr"/>
-      <c r="M370" t="inlineStr"/>
-      <c r="N370" t="inlineStr"/>
       <c r="O370" t="inlineStr">
         <is>
           <t>Low</t>
@@ -21083,7 +20806,6 @@
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="F371" t="inlineStr"/>
       <c r="G371" t="inlineStr">
         <is>
           <t>TS frontend on AI/ML surface; Jack has TS - fit, frontend-leaning</t>
@@ -21094,12 +20816,6 @@
           <t>new</t>
         </is>
       </c>
-      <c r="I371" t="inlineStr"/>
-      <c r="J371" t="inlineStr"/>
-      <c r="K371" t="inlineStr"/>
-      <c r="L371" t="inlineStr"/>
-      <c r="M371" t="inlineStr"/>
-      <c r="N371" t="inlineStr"/>
       <c r="O371" t="inlineStr">
         <is>
           <t>Low</t>
@@ -21132,7 +20848,6 @@
           <t>2025-07-11</t>
         </is>
       </c>
-      <c r="F372" t="inlineStr"/>
       <c r="G372" t="inlineStr">
         <is>
           <t>Full-stack control plane; Go/TS - fit</t>
@@ -21143,12 +20858,6 @@
           <t>new</t>
         </is>
       </c>
-      <c r="I372" t="inlineStr"/>
-      <c r="J372" t="inlineStr"/>
-      <c r="K372" t="inlineStr"/>
-      <c r="L372" t="inlineStr"/>
-      <c r="M372" t="inlineStr"/>
-      <c r="N372" t="inlineStr"/>
       <c r="O372" t="inlineStr">
         <is>
           <t>Low</t>
@@ -21181,7 +20890,6 @@
           <t>2025-11-20</t>
         </is>
       </c>
-      <c r="F373" t="inlineStr"/>
       <c r="G373" t="inlineStr">
         <is>
           <t>Postgres infra - Jack's core DB skill, direct fit</t>
@@ -21192,12 +20900,6 @@
           <t>new</t>
         </is>
       </c>
-      <c r="I373" t="inlineStr"/>
-      <c r="J373" t="inlineStr"/>
-      <c r="K373" t="inlineStr"/>
-      <c r="L373" t="inlineStr"/>
-      <c r="M373" t="inlineStr"/>
-      <c r="N373" t="inlineStr"/>
       <c r="O373" t="inlineStr">
         <is>
           <t>Low</t>
@@ -21230,7 +20932,6 @@
           <t>2026-01-05</t>
         </is>
       </c>
-      <c r="F374" t="inlineStr"/>
       <c r="G374" t="inlineStr">
         <is>
           <t>Full-stack on ClickStack product - fit</t>
@@ -21241,12 +20942,6 @@
           <t>new</t>
         </is>
       </c>
-      <c r="I374" t="inlineStr"/>
-      <c r="J374" t="inlineStr"/>
-      <c r="K374" t="inlineStr"/>
-      <c r="L374" t="inlineStr"/>
-      <c r="M374" t="inlineStr"/>
-      <c r="N374" t="inlineStr"/>
       <c r="O374" t="inlineStr">
         <is>
           <t>Low</t>
@@ -21279,7 +20974,6 @@
           <t>2026-01-26</t>
         </is>
       </c>
-      <c r="F375" t="inlineStr"/>
       <c r="G375" t="inlineStr">
         <is>
           <t>Full-stack, data-pipelines product (ClickPipes) - strong fit</t>
@@ -21290,12 +20984,6 @@
           <t>new</t>
         </is>
       </c>
-      <c r="I375" t="inlineStr"/>
-      <c r="J375" t="inlineStr"/>
-      <c r="K375" t="inlineStr"/>
-      <c r="L375" t="inlineStr"/>
-      <c r="M375" t="inlineStr"/>
-      <c r="N375" t="inlineStr"/>
       <c r="O375" t="inlineStr">
         <is>
           <t>Low</t>
@@ -21328,7 +21016,6 @@
           <t>2026-04-02</t>
         </is>
       </c>
-      <c r="F376" t="inlineStr"/>
       <c r="G376" t="inlineStr">
         <is>
           <t>Backend, Go - direct fit</t>
@@ -21339,12 +21026,6 @@
           <t>new</t>
         </is>
       </c>
-      <c r="I376" t="inlineStr"/>
-      <c r="J376" t="inlineStr"/>
-      <c r="K376" t="inlineStr"/>
-      <c r="L376" t="inlineStr"/>
-      <c r="M376" t="inlineStr"/>
-      <c r="N376" t="inlineStr"/>
       <c r="O376" t="inlineStr">
         <is>
           <t>Low</t>
@@ -21377,7 +21058,6 @@
           <t>2026-07-15</t>
         </is>
       </c>
-      <c r="F377" t="inlineStr"/>
       <c r="G377" t="inlineStr">
         <is>
           <t>Cloud partner integrations - fit</t>
@@ -21388,12 +21068,6 @@
           <t>new</t>
         </is>
       </c>
-      <c r="I377" t="inlineStr"/>
-      <c r="J377" t="inlineStr"/>
-      <c r="K377" t="inlineStr"/>
-      <c r="L377" t="inlineStr"/>
-      <c r="M377" t="inlineStr"/>
-      <c r="N377" t="inlineStr"/>
       <c r="O377" t="inlineStr">
         <is>
           <t>Low</t>
@@ -21426,7 +21100,6 @@
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="F378" t="inlineStr"/>
       <c r="G378" t="inlineStr">
         <is>
           <t>Observability platform, cloud - fit</t>
@@ -21437,12 +21110,6 @@
           <t>new</t>
         </is>
       </c>
-      <c r="I378" t="inlineStr"/>
-      <c r="J378" t="inlineStr"/>
-      <c r="K378" t="inlineStr"/>
-      <c r="L378" t="inlineStr"/>
-      <c r="M378" t="inlineStr"/>
-      <c r="N378" t="inlineStr"/>
       <c r="O378" t="inlineStr">
         <is>
           <t>Low</t>
@@ -21475,7 +21142,6 @@
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="F379" t="inlineStr"/>
       <c r="G379" t="inlineStr">
         <is>
           <t>Cloud data infra - direct fit</t>
@@ -21486,12 +21152,6 @@
           <t>new</t>
         </is>
       </c>
-      <c r="I379" t="inlineStr"/>
-      <c r="J379" t="inlineStr"/>
-      <c r="K379" t="inlineStr"/>
-      <c r="L379" t="inlineStr"/>
-      <c r="M379" t="inlineStr"/>
-      <c r="N379" t="inlineStr"/>
       <c r="O379" t="inlineStr">
         <is>
           <t>Low</t>
@@ -21524,7 +21184,6 @@
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="F380" t="inlineStr"/>
       <c r="G380" t="inlineStr">
         <is>
           <t>Backend, data pipelines - direct fit</t>
@@ -21535,12 +21194,6 @@
           <t>new</t>
         </is>
       </c>
-      <c r="I380" t="inlineStr"/>
-      <c r="J380" t="inlineStr"/>
-      <c r="K380" t="inlineStr"/>
-      <c r="L380" t="inlineStr"/>
-      <c r="M380" t="inlineStr"/>
-      <c r="N380" t="inlineStr"/>
       <c r="O380" t="inlineStr">
         <is>
           <t>Low</t>
@@ -21573,7 +21226,6 @@
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="F381" t="inlineStr"/>
       <c r="G381" t="inlineStr">
         <is>
           <t>Cloud eng, product metrics/telemetry - fit</t>
@@ -21584,12 +21236,6 @@
           <t>new</t>
         </is>
       </c>
-      <c r="I381" t="inlineStr"/>
-      <c r="J381" t="inlineStr"/>
-      <c r="K381" t="inlineStr"/>
-      <c r="L381" t="inlineStr"/>
-      <c r="M381" t="inlineStr"/>
-      <c r="N381" t="inlineStr"/>
       <c r="O381" t="inlineStr">
         <is>
           <t>Low</t>
@@ -21622,7 +21268,6 @@
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="F382" t="inlineStr"/>
       <c r="G382" t="inlineStr">
         <is>
           <t>Backend AI/ML - direct fit</t>
@@ -21633,12 +21278,6 @@
           <t>new</t>
         </is>
       </c>
-      <c r="I382" t="inlineStr"/>
-      <c r="J382" t="inlineStr"/>
-      <c r="K382" t="inlineStr"/>
-      <c r="L382" t="inlineStr"/>
-      <c r="M382" t="inlineStr"/>
-      <c r="N382" t="inlineStr"/>
       <c r="O382" t="inlineStr">
         <is>
           <t>Low</t>
@@ -21671,7 +21310,6 @@
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="F383" t="inlineStr"/>
       <c r="G383" t="inlineStr">
         <is>
           <t>Go, cloud, K8s preferably - fit</t>
@@ -21682,12 +21320,6 @@
           <t>new</t>
         </is>
       </c>
-      <c r="I383" t="inlineStr"/>
-      <c r="J383" t="inlineStr"/>
-      <c r="K383" t="inlineStr"/>
-      <c r="L383" t="inlineStr"/>
-      <c r="M383" t="inlineStr"/>
-      <c r="N383" t="inlineStr"/>
       <c r="O383" t="inlineStr">
         <is>
           <t>Low</t>
@@ -21720,7 +21352,6 @@
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="F384" t="inlineStr"/>
       <c r="G384" t="inlineStr">
         <is>
           <t>50% project eng/consulting + 50% consultative support (L1-L3)</t>
@@ -21731,16 +21362,11 @@
           <t>new</t>
         </is>
       </c>
-      <c r="I384" t="inlineStr"/>
-      <c r="J384" t="inlineStr"/>
-      <c r="K384" t="inlineStr"/>
       <c r="L384" t="inlineStr">
         <is>
           <t>FLAG TRAVEL: up to 35% onsite regional travel; 24x7 on-call; support-heavy</t>
         </is>
       </c>
-      <c r="M384" t="inlineStr"/>
-      <c r="N384" t="inlineStr"/>
       <c r="O384" t="inlineStr">
         <is>
           <t>Low</t>
@@ -21773,7 +21399,6 @@
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="F385" t="inlineStr"/>
       <c r="G385" t="inlineStr">
         <is>
           <t>Partner-facing technical architecture on the data platform - GTM-eng lane fit</t>
@@ -21784,16 +21409,11 @@
           <t>new</t>
         </is>
       </c>
-      <c r="I385" t="inlineStr"/>
-      <c r="J385" t="inlineStr"/>
-      <c r="K385" t="inlineStr"/>
       <c r="L385" t="inlineStr">
         <is>
           <t>dbt Labs and Census hiring also run on Fivetran's board</t>
         </is>
       </c>
-      <c r="M385" t="inlineStr"/>
-      <c r="N385" t="inlineStr"/>
       <c r="O385" t="inlineStr">
         <is>
           <t>Low</t>
@@ -21826,7 +21446,6 @@
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="F386" t="inlineStr"/>
       <c r="G386" t="inlineStr">
         <is>
           <t>Cloud onboarding architecture; 'Lead' title but IC/architect scope - fit</t>
@@ -21837,12 +21456,6 @@
           <t>new</t>
         </is>
       </c>
-      <c r="I386" t="inlineStr"/>
-      <c r="J386" t="inlineStr"/>
-      <c r="K386" t="inlineStr"/>
-      <c r="L386" t="inlineStr"/>
-      <c r="M386" t="inlineStr"/>
-      <c r="N386" t="inlineStr"/>
       <c r="O386" t="inlineStr">
         <is>
           <t>Low</t>
@@ -21890,16 +21503,11 @@
           <t>new</t>
         </is>
       </c>
-      <c r="I387" t="inlineStr"/>
-      <c r="J387" t="inlineStr"/>
-      <c r="K387" t="inlineStr"/>
       <c r="L387" t="inlineStr">
         <is>
           <t>Staff-level; salary band is Denver/Chicago/Atlanta &amp; all other US metros (i.e. SLC band)</t>
         </is>
       </c>
-      <c r="M387" t="inlineStr"/>
-      <c r="N387" t="inlineStr"/>
       <c r="O387" t="inlineStr">
         <is>
           <t>Low</t>
@@ -21947,16 +21555,11 @@
           <t>new</t>
         </is>
       </c>
-      <c r="I388" t="inlineStr"/>
-      <c r="J388" t="inlineStr"/>
-      <c r="K388" t="inlineStr"/>
       <c r="L388" t="inlineStr">
         <is>
           <t>Requires a public body of technical work + on-camera/stage comfort; event travel + a few days/quarter in recording studio</t>
         </is>
       </c>
-      <c r="M388" t="inlineStr"/>
-      <c r="N388" t="inlineStr"/>
       <c r="O388" t="inlineStr">
         <is>
           <t>Low</t>
@@ -22004,12 +21607,6 @@
           <t>new</t>
         </is>
       </c>
-      <c r="I389" t="inlineStr"/>
-      <c r="J389" t="inlineStr"/>
-      <c r="K389" t="inlineStr"/>
-      <c r="L389" t="inlineStr"/>
-      <c r="M389" t="inlineStr"/>
-      <c r="N389" t="inlineStr"/>
       <c r="O389" t="inlineStr">
         <is>
           <t>Low</t>
@@ -22057,16 +21654,11 @@
           <t>new</t>
         </is>
       </c>
-      <c r="I390" t="inlineStr"/>
-      <c r="J390" t="inlineStr"/>
-      <c r="K390" t="inlineStr"/>
       <c r="L390" t="inlineStr">
         <is>
           <t>No prior formal SE experience - founder/CTO customer work is the closest match</t>
         </is>
       </c>
-      <c r="M390" t="inlineStr"/>
-      <c r="N390" t="inlineStr"/>
       <c r="O390" t="inlineStr">
         <is>
           <t>Low</t>
@@ -22114,16 +21706,11 @@
           <t>new</t>
         </is>
       </c>
-      <c r="I391" t="inlineStr"/>
-      <c r="J391" t="inlineStr"/>
-      <c r="K391" t="inlineStr"/>
       <c r="L391" t="inlineStr">
         <is>
           <t>Hightouch caps at 3 applications per candidate - auto-reject above 3; pick max 3. Salary band from mirrors, not the posting.</t>
         </is>
       </c>
-      <c r="M391" t="inlineStr"/>
-      <c r="N391" t="inlineStr"/>
       <c r="O391" t="inlineStr">
         <is>
           <t>Low</t>
@@ -22156,7 +21743,6 @@
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="F392" t="inlineStr"/>
       <c r="G392" t="inlineStr">
         <is>
           <t>Strong fit: data architecture + identity matching for enterprise customers, SQL, dbt/SQLMesh bonus, directs agents; 5+ yrs customer-facing technical role</t>
@@ -22167,16 +21753,11 @@
           <t>new</t>
         </is>
       </c>
-      <c r="I392" t="inlineStr"/>
-      <c r="J392" t="inlineStr"/>
-      <c r="K392" t="inlineStr"/>
       <c r="L392" t="inlineStr">
         <is>
           <t>Hightouch caps at 3 applications per candidate - auto-reject above 3; pick max 3.</t>
         </is>
       </c>
-      <c r="M392" t="inlineStr"/>
-      <c r="N392" t="inlineStr"/>
       <c r="O392" t="inlineStr">
         <is>
           <t>Low</t>
@@ -22224,16 +21805,11 @@
           <t>new</t>
         </is>
       </c>
-      <c r="I393" t="inlineStr"/>
-      <c r="J393" t="inlineStr"/>
-      <c r="K393" t="inlineStr"/>
       <c r="L393" t="inlineStr">
         <is>
           <t>Hightouch caps at 3 applications per candidate - auto-reject above 3; pick max 3. Senior role, research/experimental leaning.</t>
         </is>
       </c>
-      <c r="M393" t="inlineStr"/>
-      <c r="N393" t="inlineStr"/>
       <c r="O393" t="inlineStr">
         <is>
           <t>Low</t>
@@ -22266,7 +21842,6 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="F394" t="inlineStr"/>
       <c r="G394" t="inlineStr">
         <is>
           <t>AI agents SWE - direct LLM-agent fit</t>
@@ -22277,16 +21852,11 @@
           <t>new</t>
         </is>
       </c>
-      <c r="I394" t="inlineStr"/>
-      <c r="J394" t="inlineStr"/>
-      <c r="K394" t="inlineStr"/>
       <c r="L394" t="inlineStr">
         <is>
           <t>Hightouch caps at 3 applications per candidate - auto-reject above 3; pick max 3.</t>
         </is>
       </c>
-      <c r="M394" t="inlineStr"/>
-      <c r="N394" t="inlineStr"/>
       <c r="O394" t="inlineStr">
         <is>
           <t>Low</t>
@@ -22319,7 +21889,6 @@
           <t>2026-04-28</t>
         </is>
       </c>
-      <c r="F395" t="inlineStr"/>
       <c r="G395" t="inlineStr">
         <is>
           <t>Platform/control-plane SWE - fit</t>
@@ -22330,16 +21899,11 @@
           <t>new</t>
         </is>
       </c>
-      <c r="I395" t="inlineStr"/>
-      <c r="J395" t="inlineStr"/>
-      <c r="K395" t="inlineStr"/>
       <c r="L395" t="inlineStr">
         <is>
           <t>Hightouch caps at 3 applications per candidate - auto-reject above 3; pick max 3.</t>
         </is>
       </c>
-      <c r="M395" t="inlineStr"/>
-      <c r="N395" t="inlineStr"/>
       <c r="O395" t="inlineStr">
         <is>
           <t>Low</t>
@@ -22372,7 +21936,6 @@
           <t>2026-04-28</t>
         </is>
       </c>
-      <c r="F396" t="inlineStr"/>
       <c r="G396" t="inlineStr">
         <is>
           <t>Backend SWE - fit</t>
@@ -22383,16 +21946,11 @@
           <t>new</t>
         </is>
       </c>
-      <c r="I396" t="inlineStr"/>
-      <c r="J396" t="inlineStr"/>
-      <c r="K396" t="inlineStr"/>
       <c r="L396" t="inlineStr">
         <is>
           <t>Hightouch caps at 3 applications per candidate - auto-reject above 3; pick max 3.</t>
         </is>
       </c>
-      <c r="M396" t="inlineStr"/>
-      <c r="N396" t="inlineStr"/>
       <c r="O396" t="inlineStr">
         <is>
           <t>Low</t>
@@ -22425,7 +21983,6 @@
           <t>2023-01-25</t>
         </is>
       </c>
-      <c r="F397" t="inlineStr"/>
       <c r="G397" t="inlineStr">
         <is>
           <t>Distributed systems SWE - fit</t>
@@ -22436,16 +21993,11 @@
           <t>new</t>
         </is>
       </c>
-      <c r="I397" t="inlineStr"/>
-      <c r="J397" t="inlineStr"/>
-      <c r="K397" t="inlineStr"/>
       <c r="L397" t="inlineStr">
         <is>
           <t>Hightouch caps at 3 applications per candidate - auto-reject above 3; pick max 3. Evergreen posting (first published 2023).</t>
         </is>
       </c>
-      <c r="M397" t="inlineStr"/>
-      <c r="N397" t="inlineStr"/>
       <c r="O397" t="inlineStr">
         <is>
           <t>Low</t>
@@ -22478,7 +22030,6 @@
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="F398" t="inlineStr"/>
       <c r="G398" t="inlineStr">
         <is>
           <t>SWE, data delivery - fit</t>
@@ -22489,16 +22040,11 @@
           <t>new</t>
         </is>
       </c>
-      <c r="I398" t="inlineStr"/>
-      <c r="J398" t="inlineStr"/>
-      <c r="K398" t="inlineStr"/>
       <c r="L398" t="inlineStr">
         <is>
           <t>Hightouch caps at 3 applications per candidate - auto-reject above 3; pick max 3.</t>
         </is>
       </c>
-      <c r="M398" t="inlineStr"/>
-      <c r="N398" t="inlineStr"/>
       <c r="O398" t="inlineStr">
         <is>
           <t>Low</t>
@@ -22531,7 +22077,6 @@
           <t>2026-04-28</t>
         </is>
       </c>
-      <c r="F399" t="inlineStr"/>
       <c r="G399" t="inlineStr">
         <is>
           <t>Streaming SWE - fit</t>
@@ -22542,16 +22087,11 @@
           <t>new</t>
         </is>
       </c>
-      <c r="I399" t="inlineStr"/>
-      <c r="J399" t="inlineStr"/>
-      <c r="K399" t="inlineStr"/>
       <c r="L399" t="inlineStr">
         <is>
           <t>Hightouch caps at 3 applications per candidate - auto-reject above 3; pick max 3.</t>
         </is>
       </c>
-      <c r="M399" t="inlineStr"/>
-      <c r="N399" t="inlineStr"/>
       <c r="O399" t="inlineStr">
         <is>
           <t>Low</t>
@@ -22584,7 +22124,6 @@
           <t>2022-08-10</t>
         </is>
       </c>
-      <c r="F400" t="inlineStr"/>
       <c r="G400" t="inlineStr">
         <is>
           <t>Full-stack product eng - fit</t>
@@ -22595,16 +22134,11 @@
           <t>new</t>
         </is>
       </c>
-      <c r="I400" t="inlineStr"/>
-      <c r="J400" t="inlineStr"/>
-      <c r="K400" t="inlineStr"/>
       <c r="L400" t="inlineStr">
         <is>
           <t>Hightouch caps at 3 applications per candidate - auto-reject above 3; pick max 3. Evergreen posting (first published 2022).</t>
         </is>
       </c>
-      <c r="M400" t="inlineStr"/>
-      <c r="N400" t="inlineStr"/>
       <c r="O400" t="inlineStr">
         <is>
           <t>Low</t>
@@ -22637,7 +22171,6 @@
           <t>2025-11-06</t>
         </is>
       </c>
-      <c r="F401" t="inlineStr"/>
       <c r="G401" t="inlineStr">
         <is>
           <t>Dev-infra / developer productivity - platform-lane fit</t>
@@ -22648,16 +22181,11 @@
           <t>new</t>
         </is>
       </c>
-      <c r="I401" t="inlineStr"/>
-      <c r="J401" t="inlineStr"/>
-      <c r="K401" t="inlineStr"/>
       <c r="L401" t="inlineStr">
         <is>
           <t>Hightouch caps at 3 applications per candidate - auto-reject above 3; pick max 3.</t>
         </is>
       </c>
-      <c r="M401" t="inlineStr"/>
-      <c r="N401" t="inlineStr"/>
       <c r="O401" t="inlineStr">
         <is>
           <t>Low</t>
@@ -22690,7 +22218,6 @@
           <t>2026-06-11</t>
         </is>
       </c>
-      <c r="F402" t="inlineStr"/>
       <c r="G402" t="inlineStr">
         <is>
           <t>AI productivity eng</t>
@@ -22701,16 +22228,11 @@
           <t>new</t>
         </is>
       </c>
-      <c r="I402" t="inlineStr"/>
-      <c r="J402" t="inlineStr"/>
-      <c r="K402" t="inlineStr"/>
       <c r="L402" t="inlineStr">
         <is>
           <t>Hightouch caps at 3 applications per candidate - auto-reject above 3; pick max 3. Staff-level.</t>
         </is>
       </c>
-      <c r="M402" t="inlineStr"/>
-      <c r="N402" t="inlineStr"/>
       <c r="O402" t="inlineStr">
         <is>
           <t>Low</t>
@@ -22743,7 +22265,6 @@
           <t>2026-06-11</t>
         </is>
       </c>
-      <c r="F403" t="inlineStr"/>
       <c r="G403" t="inlineStr">
         <is>
           <t>EM, AI agents team - lead/EM-adjacent fit</t>
@@ -22754,16 +22275,11 @@
           <t>new</t>
         </is>
       </c>
-      <c r="I403" t="inlineStr"/>
-      <c r="J403" t="inlineStr"/>
-      <c r="K403" t="inlineStr"/>
       <c r="L403" t="inlineStr">
         <is>
           <t>Hightouch caps at 3 applications per candidate - auto-reject above 3; pick max 3.</t>
         </is>
       </c>
-      <c r="M403" t="inlineStr"/>
-      <c r="N403" t="inlineStr"/>
       <c r="O403" t="inlineStr">
         <is>
           <t>Low</t>
@@ -22796,7 +22312,6 @@
           <t>2026-06-11</t>
         </is>
       </c>
-      <c r="F404" t="inlineStr"/>
       <c r="G404" t="inlineStr">
         <is>
           <t>EM, Customer Studio (API title 'Customer Studios') - EM-adjacent fit</t>
@@ -22807,16 +22322,11 @@
           <t>new</t>
         </is>
       </c>
-      <c r="I404" t="inlineStr"/>
-      <c r="J404" t="inlineStr"/>
-      <c r="K404" t="inlineStr"/>
       <c r="L404" t="inlineStr">
         <is>
           <t>Hightouch caps at 3 applications per candidate - auto-reject above 3; pick max 3.</t>
         </is>
       </c>
-      <c r="M404" t="inlineStr"/>
-      <c r="N404" t="inlineStr"/>
       <c r="O404" t="inlineStr">
         <is>
           <t>Low</t>
@@ -22864,16 +22374,11 @@
           <t>new</t>
         </is>
       </c>
-      <c r="I405" t="inlineStr"/>
-      <c r="J405" t="inlineStr"/>
-      <c r="K405" t="inlineStr"/>
       <c r="L405" t="inlineStr">
         <is>
           <t>Hightouch caps at 3 applications per candidate - auto-reject above 3; pick max 3. Direct job page resolves, but role didn't render on the Oct 28 careers-page list - verify still open at apply time.</t>
         </is>
       </c>
-      <c r="M405" t="inlineStr"/>
-      <c r="N405" t="inlineStr"/>
       <c r="O405" t="inlineStr">
         <is>
           <t>Low</t>
@@ -22921,16 +22426,11 @@
           <t>new</t>
         </is>
       </c>
-      <c r="I406" t="inlineStr"/>
-      <c r="J406" t="inlineStr"/>
-      <c r="K406" t="inlineStr"/>
       <c r="L406" t="inlineStr">
         <is>
           <t>Hightouch caps at 3 applications per candidate - auto-reject above 3; pick max 3. Requires proven technical-team management + pre/post-sales client experience.</t>
         </is>
       </c>
-      <c r="M406" t="inlineStr"/>
-      <c r="N406" t="inlineStr"/>
       <c r="O406" t="inlineStr">
         <is>
           <t>Low</t>
@@ -22963,7 +22463,6 @@
           <t>2026-05-21</t>
         </is>
       </c>
-      <c r="F407" t="inlineStr"/>
       <c r="G407" t="inlineStr">
         <is>
           <t>Leads mid-market SE team - EM-adjacent fit</t>
@@ -22974,16 +22473,11 @@
           <t>new</t>
         </is>
       </c>
-      <c r="I407" t="inlineStr"/>
-      <c r="J407" t="inlineStr"/>
-      <c r="K407" t="inlineStr"/>
       <c r="L407" t="inlineStr">
         <is>
           <t>Hightouch caps at 3 applications per candidate - auto-reject above 3; pick max 3. Same management caveat as Manager, Solutions Engineering.</t>
         </is>
       </c>
-      <c r="M407" t="inlineStr"/>
-      <c r="N407" t="inlineStr"/>
       <c r="O407" t="inlineStr">
         <is>
           <t>Low</t>
@@ -23016,7 +22510,6 @@
           <t>2026-01-12</t>
         </is>
       </c>
-      <c r="F408" t="inlineStr"/>
       <c r="G408" t="inlineStr">
         <is>
           <t>Implementation/onboarding architecture - forward-deployed lane; implementation-heavy</t>
@@ -23027,16 +22520,11 @@
           <t>new</t>
         </is>
       </c>
-      <c r="I408" t="inlineStr"/>
-      <c r="J408" t="inlineStr"/>
-      <c r="K408" t="inlineStr"/>
       <c r="L408" t="inlineStr">
         <is>
           <t>Hightouch caps at 3 applications per candidate - auto-reject above 3; pick max 3.</t>
         </is>
       </c>
-      <c r="M408" t="inlineStr"/>
-      <c r="N408" t="inlineStr"/>
       <c r="O408" t="inlineStr">
         <is>
           <t>Low</t>
@@ -23084,16 +22572,11 @@
           <t>new</t>
         </is>
       </c>
-      <c r="I409" t="inlineStr"/>
-      <c r="J409" t="inlineStr"/>
-      <c r="K409" t="inlineStr"/>
       <c r="L409" t="inlineStr">
         <is>
           <t>Hightouch caps at 3 applications per candidate - auto-reject above 3; pick max 3. Weak fit: niche ESP/messaging domain (10DLC, deliverability, Braze/SFMC), 5-10 yrs in that niche required.</t>
         </is>
       </c>
-      <c r="M409" t="inlineStr"/>
-      <c r="N409" t="inlineStr"/>
       <c r="O409" t="inlineStr">
         <is>
           <t>Low</t>
@@ -23126,7 +22609,6 @@
           <t>2026-06-02</t>
         </is>
       </c>
-      <c r="F410" t="inlineStr"/>
       <c r="G410" t="inlineStr">
         <is>
           <t>Partner-facing technical (Snowflake/Databricks/BigQuery); careers site now titles it 'Partner Solutions Engineer'</t>
@@ -23137,16 +22619,11 @@
           <t>new</t>
         </is>
       </c>
-      <c r="I410" t="inlineStr"/>
-      <c r="J410" t="inlineStr"/>
-      <c r="K410" t="inlineStr"/>
       <c r="L410" t="inlineStr">
         <is>
           <t>Hightouch caps at 3 applications per candidate - auto-reject above 3; pick max 3. Partner/alliances focus, up to 30% travel.</t>
         </is>
       </c>
-      <c r="M410" t="inlineStr"/>
-      <c r="N410" t="inlineStr"/>
       <c r="O410" t="inlineStr">
         <is>
           <t>Low</t>
@@ -23179,7 +22656,6 @@
           <t>2025-05-08</t>
         </is>
       </c>
-      <c r="F411" t="inlineStr"/>
       <c r="G411" t="inlineStr">
         <is>
           <t>Pre-sales SE, data ecosystems</t>
@@ -23190,16 +22666,11 @@
           <t>new</t>
         </is>
       </c>
-      <c r="I411" t="inlineStr"/>
-      <c r="J411" t="inlineStr"/>
-      <c r="K411" t="inlineStr"/>
       <c r="L411" t="inlineStr">
         <is>
           <t>Hightouch caps at 3 applications per candidate - auto-reject above 3; pick max 3. Requires 2+ yrs pre-sales/SE experience - founder/CTO customer work is the closest match; stretch.</t>
         </is>
       </c>
-      <c r="M411" t="inlineStr"/>
-      <c r="N411" t="inlineStr"/>
       <c r="O411" t="inlineStr">
         <is>
           <t>Low</t>
@@ -23232,7 +22703,6 @@
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="F412" t="inlineStr"/>
       <c r="G412" t="inlineStr">
         <is>
           <t>Backend, analytics - Go/Python, direct fit</t>
@@ -23243,12 +22713,6 @@
           <t>new</t>
         </is>
       </c>
-      <c r="I412" t="inlineStr"/>
-      <c r="J412" t="inlineStr"/>
-      <c r="K412" t="inlineStr"/>
-      <c r="L412" t="inlineStr"/>
-      <c r="M412" t="inlineStr"/>
-      <c r="N412" t="inlineStr"/>
       <c r="O412" t="inlineStr">
         <is>
           <t>Low</t>
@@ -23281,7 +22745,6 @@
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="F413" t="inlineStr"/>
       <c r="G413" t="inlineStr">
         <is>
           <t>Backend, Tempo (tracing DB) - direct fit; note the Staff-level Tempo posting is gone from the board and this Senior one replaced it</t>
@@ -23292,12 +22755,6 @@
           <t>new</t>
         </is>
       </c>
-      <c r="I413" t="inlineStr"/>
-      <c r="J413" t="inlineStr"/>
-      <c r="K413" t="inlineStr"/>
-      <c r="L413" t="inlineStr"/>
-      <c r="M413" t="inlineStr"/>
-      <c r="N413" t="inlineStr"/>
       <c r="O413" t="inlineStr">
         <is>
           <t>Low</t>
@@ -23330,7 +22787,6 @@
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="F414" t="inlineStr"/>
       <c r="G414" t="inlineStr">
         <is>
           <t>Backend, Loki (logs) - fit</t>
@@ -23341,16 +22797,11 @@
           <t>new</t>
         </is>
       </c>
-      <c r="I414" t="inlineStr"/>
-      <c r="J414" t="inlineStr"/>
-      <c r="K414" t="inlineStr"/>
       <c r="L414" t="inlineStr">
         <is>
           <t>'NASA' is the customer/team tag on the posting</t>
         </is>
       </c>
-      <c r="M414" t="inlineStr"/>
-      <c r="N414" t="inlineStr"/>
       <c r="O414" t="inlineStr">
         <is>
           <t>Low</t>
@@ -23383,7 +22834,6 @@
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="F415" t="inlineStr"/>
       <c r="G415" t="inlineStr">
         <is>
           <t>Backend, Loki</t>
@@ -23394,16 +22844,11 @@
           <t>new</t>
         </is>
       </c>
-      <c r="I415" t="inlineStr"/>
-      <c r="J415" t="inlineStr"/>
-      <c r="K415" t="inlineStr"/>
       <c r="L415" t="inlineStr">
         <is>
           <t>Staff-level; 'NASA' is the customer/team tag on the posting</t>
         </is>
       </c>
-      <c r="M415" t="inlineStr"/>
-      <c r="N415" t="inlineStr"/>
       <c r="O415" t="inlineStr">
         <is>
           <t>Low</t>
@@ -23436,7 +22881,6 @@
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="F416" t="inlineStr"/>
       <c r="G416" t="inlineStr">
         <is>
           <t>Frontend, data viz</t>
@@ -23447,16 +22891,11 @@
           <t>new</t>
         </is>
       </c>
-      <c r="I416" t="inlineStr"/>
-      <c r="J416" t="inlineStr"/>
-      <c r="K416" t="inlineStr"/>
       <c r="L416" t="inlineStr">
         <is>
           <t>Staff-level + frontend</t>
         </is>
       </c>
-      <c r="M416" t="inlineStr"/>
-      <c r="N416" t="inlineStr"/>
       <c r="O416" t="inlineStr">
         <is>
           <t>Low</t>
@@ -23489,7 +22928,6 @@
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="F417" t="inlineStr"/>
       <c r="G417" t="inlineStr">
         <is>
           <t>Full-stack, core services</t>
@@ -23500,16 +22938,11 @@
           <t>new</t>
         </is>
       </c>
-      <c r="I417" t="inlineStr"/>
-      <c r="J417" t="inlineStr"/>
-      <c r="K417" t="inlineStr"/>
       <c r="L417" t="inlineStr">
         <is>
           <t>Staff-level</t>
         </is>
       </c>
-      <c r="M417" t="inlineStr"/>
-      <c r="N417" t="inlineStr"/>
       <c r="O417" t="inlineStr">
         <is>
           <t>Low</t>
@@ -23542,7 +22975,6 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F418" t="inlineStr"/>
       <c r="G418" t="inlineStr">
         <is>
           <t>SWE, core services</t>
@@ -23553,16 +22985,11 @@
           <t>new</t>
         </is>
       </c>
-      <c r="I418" t="inlineStr"/>
-      <c r="J418" t="inlineStr"/>
-      <c r="K418" t="inlineStr"/>
       <c r="L418" t="inlineStr">
         <is>
           <t>Staff-level</t>
         </is>
       </c>
-      <c r="M418" t="inlineStr"/>
-      <c r="N418" t="inlineStr"/>
       <c r="O418" t="inlineStr">
         <is>
           <t>Low</t>
@@ -23595,7 +23022,6 @@
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="F419" t="inlineStr"/>
       <c r="G419" t="inlineStr">
         <is>
           <t>EM, Grafana frontend - EM-adjacent fit</t>
@@ -23606,16 +23032,11 @@
           <t>new</t>
         </is>
       </c>
-      <c r="I419" t="inlineStr"/>
-      <c r="J419" t="inlineStr"/>
-      <c r="K419" t="inlineStr"/>
       <c r="L419" t="inlineStr">
         <is>
           <t>Frontend-team caveat</t>
         </is>
       </c>
-      <c r="M419" t="inlineStr"/>
-      <c r="N419" t="inlineStr"/>
       <c r="O419" t="inlineStr">
         <is>
           <t>Low</t>
@@ -23648,7 +23069,6 @@
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="F420" t="inlineStr"/>
       <c r="G420" t="inlineStr">
         <is>
           <t>Full-stack, cloud observability - fit</t>
@@ -23659,12 +23079,6 @@
           <t>new</t>
         </is>
       </c>
-      <c r="I420" t="inlineStr"/>
-      <c r="J420" t="inlineStr"/>
-      <c r="K420" t="inlineStr"/>
-      <c r="L420" t="inlineStr"/>
-      <c r="M420" t="inlineStr"/>
-      <c r="N420" t="inlineStr"/>
       <c r="O420" t="inlineStr">
         <is>
           <t>Low</t>
@@ -23697,7 +23111,6 @@
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="F421" t="inlineStr"/>
       <c r="G421" t="inlineStr">
         <is>
           <t>Full-stack, data-source plugins - fit</t>
@@ -23708,16 +23121,11 @@
           <t>new</t>
         </is>
       </c>
-      <c r="I421" t="inlineStr"/>
-      <c r="J421" t="inlineStr"/>
-      <c r="K421" t="inlineStr"/>
       <c r="L421" t="inlineStr">
         <is>
           <t>'NASA' is the customer/team tag on the posting</t>
         </is>
       </c>
-      <c r="M421" t="inlineStr"/>
-      <c r="N421" t="inlineStr"/>
       <c r="O421" t="inlineStr">
         <is>
           <t>Low</t>
@@ -23750,7 +23158,6 @@
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="F422" t="inlineStr"/>
       <c r="G422" t="inlineStr">
         <is>
           <t>Backend, search &amp; storage - direct fit</t>
@@ -23761,12 +23168,6 @@
           <t>new</t>
         </is>
       </c>
-      <c r="I422" t="inlineStr"/>
-      <c r="J422" t="inlineStr"/>
-      <c r="K422" t="inlineStr"/>
-      <c r="L422" t="inlineStr"/>
-      <c r="M422" t="inlineStr"/>
-      <c r="N422" t="inlineStr"/>
       <c r="O422" t="inlineStr">
         <is>
           <t>Low</t>
@@ -23799,7 +23200,6 @@
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="F423" t="inlineStr"/>
       <c r="G423" t="inlineStr">
         <is>
           <t>Frontend observability (session replay), TS - fit, frontend-leaning</t>
@@ -23810,12 +23210,6 @@
           <t>new</t>
         </is>
       </c>
-      <c r="I423" t="inlineStr"/>
-      <c r="J423" t="inlineStr"/>
-      <c r="K423" t="inlineStr"/>
-      <c r="L423" t="inlineStr"/>
-      <c r="M423" t="inlineStr"/>
-      <c r="N423" t="inlineStr"/>
       <c r="O423" t="inlineStr">
         <is>
           <t>Low</t>
@@ -23848,7 +23242,6 @@
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="F424" t="inlineStr"/>
       <c r="G424" t="inlineStr">
         <is>
           <t>SE, West Coast territory - GTM-eng lane fit</t>
@@ -23859,12 +23252,6 @@
           <t>new</t>
         </is>
       </c>
-      <c r="I424" t="inlineStr"/>
-      <c r="J424" t="inlineStr"/>
-      <c r="K424" t="inlineStr"/>
-      <c r="L424" t="inlineStr"/>
-      <c r="M424" t="inlineStr"/>
-      <c r="N424" t="inlineStr"/>
       <c r="O424" t="inlineStr">
         <is>
           <t>Low</t>
@@ -23897,7 +23284,6 @@
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="F425" t="inlineStr"/>
       <c r="G425" t="inlineStr">
         <is>
           <t>SE, growth</t>
@@ -23908,16 +23294,11 @@
           <t>new</t>
         </is>
       </c>
-      <c r="I425" t="inlineStr"/>
-      <c r="J425" t="inlineStr"/>
-      <c r="K425" t="inlineStr"/>
       <c r="L425" t="inlineStr">
         <is>
           <t>Mid-Atlantic/Southeast territory (East-coast customers)</t>
         </is>
       </c>
-      <c r="M425" t="inlineStr"/>
-      <c r="N425" t="inlineStr"/>
       <c r="O425" t="inlineStr">
         <is>
           <t>Low</t>
@@ -23950,7 +23331,6 @@
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="F426" t="inlineStr"/>
       <c r="G426" t="inlineStr">
         <is>
           <t>Partner SE - GTM-eng lane fit</t>
@@ -23961,12 +23341,6 @@
           <t>new</t>
         </is>
       </c>
-      <c r="I426" t="inlineStr"/>
-      <c r="J426" t="inlineStr"/>
-      <c r="K426" t="inlineStr"/>
-      <c r="L426" t="inlineStr"/>
-      <c r="M426" t="inlineStr"/>
-      <c r="N426" t="inlineStr"/>
       <c r="O426" t="inlineStr">
         <is>
           <t>Low</t>
@@ -23999,7 +23373,6 @@
           <t>2026-07-27</t>
         </is>
       </c>
-      <c r="F427" t="inlineStr"/>
       <c r="G427" t="inlineStr">
         <is>
           <t>SE, Central US territory - fit</t>
@@ -24010,16 +23383,11 @@
           <t>new</t>
         </is>
       </c>
-      <c r="I427" t="inlineStr"/>
-      <c r="J427" t="inlineStr"/>
-      <c r="K427" t="inlineStr"/>
       <c r="L427" t="inlineStr">
         <is>
           <t>Jack is MT, one hour off the territory</t>
         </is>
       </c>
-      <c r="M427" t="inlineStr"/>
-      <c r="N427" t="inlineStr"/>
       <c r="O427" t="inlineStr">
         <is>
           <t>Low</t>
@@ -24067,19 +23435,98 @@
           <t>new</t>
         </is>
       </c>
-      <c r="I428" t="inlineStr"/>
-      <c r="J428" t="inlineStr"/>
-      <c r="K428" t="inlineStr"/>
       <c r="L428" t="inlineStr">
         <is>
           <t>Posting explicitly lists Utah among eligible remote-residence states (Lincoln, NE prioritized). Pipeline-style requisition R-102566, live and open. Caveat: requires proven managerial experience - Jack's lead/founder experience is adjacent rather than formal EM title.</t>
         </is>
       </c>
-      <c r="M428" t="inlineStr"/>
-      <c r="N428" t="inlineStr"/>
       <c r="O428" t="inlineStr">
         <is>
           <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>AZX</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>Senior ML Engineer (Client Solutions)</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>Remote (US)</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>https://wellfound.com/jobs/4656847-senior-ml-engineer-client-solutions</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>$140,000–$230,000</t>
+        </is>
+      </c>
+      <c r="G429" t="inlineStr">
+        <is>
+          <t>Client-facing ML delivery, Python/SQL/Postgres/Docker/FastAPI/React, LLM retrieval edges, travel 2x/yr summits only; deadline Nov 12, 2026; AZX cap: max 2 roles at a time — Client Solutions is the one AZX role to use</t>
+        </is>
+      </c>
+      <c r="H429" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>Salesforce</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>Software Engineering SMTS / LMTS - AI Core (REMOTE)</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>https://builtin.com/job/software-engineering-smts-lmts-ai-core-remote/11700721</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>$172,500–$260,100</t>
+        </is>
+      </c>
+      <c r="G430" t="inlineStr">
+        <is>
+          <t>RAG/hybrid search + agent infra, Python/Postgres/pgvector, voice agents nice-to-have; Salesforce cap: max 3 roles in 12 months, this is the first</t>
+        </is>
+      </c>
+      <c r="H430" t="inlineStr">
+        <is>
+          <t>new</t>
         </is>
       </c>
     </row>

--- a/tracker.xlsx
+++ b/tracker.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4335" uniqueCount="2051">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4335" uniqueCount="2049">
   <si>
     <t>Company</t>
   </si>
@@ -5578,13 +5578,7 @@
     <t>Strongest fit: SQL fluency (Snowflake/Databricks/BigQuery), identity resolution, data eng/analytics, agent-native workflow; 2-4 yrs in AE/SE/FDE/implementation role</t>
   </si>
   <si>
-    <t>resume-hightouch-forward-deployed-engineer.pdf</t>
-  </si>
-  <si>
-    <t>cover-letter-hightouch-forward-deployed-engineer.pdf</t>
-  </si>
-  <si>
-    <t>Hightouch caps at 3 applications per candidate - auto-reject above 3; pick max 3. Salary band from mirrors, not the posting. Ready to apply - materials complete, 2026-10-28. Folder applications/hightouch-forward-deployed-engineer/. Hightouch caps candidates at 3 applications; this is one of the 3 picked (391, 393, 394). Hightouch moved to Ashby: https://jobs.ashbyhq.com/hightouch-inc/dace612e-16c3-49a2-b1fe-622d80516f2d</t>
+    <t>Hightouch caps at 3 applications per candidate - auto-reject above 3; pick max 3. Salary band from mirrors, not the posting. Ready to apply - materials complete, 2026-10-28. Folder applications/hightouch-forward-deployed-engineer/. Held back (2026-10-28): Hightouch caps candidates at 2 applications; Jack chose rows 393 (Applied AI Research) and 400 (Full Stack Product Engineer). Materials stay in applications/hightouch-forward-deployed-engineer/ if Jack swaps this one in. Hightouch moved to Ashby: https://jobs.ashbyhq.com/hightouch-inc/dace612e-16c3-49a2-b1fe-622d80516f2d</t>
   </si>
   <si>
     <t>Forward Deployed Architect</t>
@@ -5596,7 +5590,7 @@
     <t>Strong fit: data architecture + identity matching for enterprise customers, SQL, dbt/SQLMesh bonus, directs agents; 5+ yrs customer-facing technical role</t>
   </si>
   <si>
-    <t>Hightouch caps at 3 applications per candidate - auto-reject above 3; pick max 3. Not tailored (2026-10-28): Hightouch auto-rejects candidates who apply to more than 3 roles; tailored rows 391, 393 and 394 instead. Swap with one of those if Jack prefers this role. Hightouch's board moved to Ashby (jobs.ashbyhq.com/hightouch-inc).</t>
+    <t>Hightouch caps at 3 applications per candidate - auto-reject above 3; pick max 3. Not tailored (2026-10-28): Hightouch caps candidates at 2 applications; Jack chose rows 393 (Applied AI Research) and 400 (Full Stack Product Engineer). Hightouch's board moved to Ashby (jobs.ashbyhq.com/hightouch-inc).</t>
   </si>
   <si>
     <t>Software Engineer, Applied AI Research</t>
@@ -5617,7 +5611,7 @@
     <t>cover-letter-hightouch-software-engineer-applied-ai-research.pdf</t>
   </si>
   <si>
-    <t>Hightouch caps at 3 applications per candidate - auto-reject above 3; pick max 3. Senior role, research/experimental leaning. Ready to apply - materials complete, 2026-10-28. Folder applications/hightouch-software-engineer-applied-ai-research/. Hightouch caps candidates at 3 applications; this is one of the 3 picked (391, 393, 394). Hightouch moved to Ashby: https://jobs.ashbyhq.com/hightouch-inc/6cabea6f-4f1b-4e14-9c1e-e2c1a7ac9413</t>
+    <t>Hightouch caps at 3 applications per candidate - auto-reject above 3; pick max 3. Senior role, research/experimental leaning. Ready to apply - materials complete, 2026-10-28. Folder applications/hightouch-software-engineer-applied-ai-research/. Hightouch caps candidates at 2 applications; Jack chose rows 393 (Applied AI Research) and 400 (Full Stack Product Engineer). Hightouch moved to Ashby: https://jobs.ashbyhq.com/hightouch-inc/6cabea6f-4f1b-4e14-9c1e-e2c1a7ac9413</t>
   </si>
   <si>
     <t>Software Engineer, AI Agents</t>
@@ -5632,13 +5626,7 @@
     <t>AI agents SWE - direct LLM-agent fit</t>
   </si>
   <si>
-    <t>resume-hightouch-software-engineer-ai-agents.pdf</t>
-  </si>
-  <si>
-    <t>cover-letter-hightouch-software-engineer-ai-agents.pdf</t>
-  </si>
-  <si>
-    <t>Hightouch caps at 3 applications per candidate - auto-reject above 3; pick max 3. Ready to apply - materials complete, 2026-10-28. Folder applications/hightouch-software-engineer-ai-agents/. Hightouch caps candidates at 3 applications; this is one of the 3 picked (391, 393, 394). Hightouch moved to Ashby: https://jobs.ashbyhq.com/hightouch-inc/83b879e6-628e-41b4-a601-191e2dc69a54</t>
+    <t>Hightouch caps at 3 applications per candidate - auto-reject above 3; pick max 3. Ready to apply - materials complete, 2026-10-28. Folder applications/hightouch-software-engineer-ai-agents/. Held back (2026-10-28): Hightouch caps candidates at 2 applications; Jack chose rows 393 (Applied AI Research) and 400 (Full Stack Product Engineer). Materials stay in applications/hightouch-software-engineer-ai-agents/ if Jack swaps this one in. Hightouch moved to Ashby: https://jobs.ashbyhq.com/hightouch-inc/83b879e6-628e-41b4-a601-191e2dc69a54</t>
   </si>
   <si>
     <t>Software Engineer, Control Plane</t>
@@ -5674,7 +5662,7 @@
     <t>Distributed systems SWE - fit</t>
   </si>
   <si>
-    <t>Hightouch caps at 3 applications per candidate - auto-reject above 3; pick max 3. Evergreen posting (first published 2023). Not tailored (2026-10-28): Hightouch auto-rejects candidates who apply to more than 3 roles; tailored rows 391, 393 and 394 instead. Swap with one of those if Jack prefers this role. Hightouch's board moved to Ashby (jobs.ashbyhq.com/hightouch-inc).</t>
+    <t>Hightouch caps at 3 applications per candidate - auto-reject above 3; pick max 3. Evergreen posting (first published 2023). Not tailored (2026-10-28): Hightouch caps candidates at 2 applications; Jack chose rows 393 (Applied AI Research) and 400 (Full Stack Product Engineer). Hightouch's board moved to Ashby (jobs.ashbyhq.com/hightouch-inc).</t>
   </si>
   <si>
     <t>Software Engineer, Native Delivery</t>
@@ -5710,7 +5698,13 @@
     <t>Full-stack product eng - fit</t>
   </si>
   <si>
-    <t>Hightouch caps at 3 applications per candidate - auto-reject above 3; pick max 3. Evergreen posting (first published 2022). Not tailored (2026-10-28): Hightouch auto-rejects candidates who apply to more than 3 roles; tailored rows 391, 393 and 394 instead. Swap with one of those if Jack prefers this role. Hightouch's board moved to Ashby (jobs.ashbyhq.com/hightouch-inc).</t>
+    <t>resume-hightouch-full-stack-product-engineer.pdf</t>
+  </si>
+  <si>
+    <t>cover-letter-hightouch-full-stack-product-engineer.pdf</t>
+  </si>
+  <si>
+    <t>Hightouch caps at 3 applications per candidate - auto-reject above 3; pick max 3. Evergreen posting (first published 2022). Ready to apply - materials complete, 2026-10-28. Folder applications/hightouch-full-stack-product-engineer/. Form: US work authorization and sponsorship yes/no. Hightouch caps candidates at 2 applications; Jack chose rows 393 (Applied AI Research) and 400 (Full Stack Product Engineer). Ashby: https://jobs.ashbyhq.com/hightouch-inc/a287cb33-e488-4395-acde-afa0eca9655b</t>
   </si>
   <si>
     <t>Developer Productivity Engineer</t>
@@ -5734,7 +5728,7 @@
     <t>AI productivity eng</t>
   </si>
   <si>
-    <t>Hightouch caps at 3 applications per candidate - auto-reject above 3; pick max 3. Staff-level. Not tailored (2026-10-28): Hightouch auto-rejects candidates who apply to more than 3 roles; tailored rows 391, 393 and 394 instead. Swap with one of those if Jack prefers this role. Hightouch's board moved to Ashby (jobs.ashbyhq.com/hightouch-inc).</t>
+    <t>Hightouch caps at 3 applications per candidate - auto-reject above 3; pick max 3. Staff-level. Not tailored (2026-10-28): Hightouch caps candidates at 2 applications; Jack chose rows 393 (Applied AI Research) and 400 (Full Stack Product Engineer). Hightouch's board moved to Ashby (jobs.ashbyhq.com/hightouch-inc).</t>
   </si>
   <si>
     <t>Engineering Manager, Agents</t>
@@ -5770,7 +5764,7 @@
     <t>Hands-on EM leading 300+ destination integrations</t>
   </si>
   <si>
-    <t>Hightouch caps at 3 applications per candidate - auto-reject above 3; pick max 3. Direct job page resolves, but role didn't render on the Oct 28 careers-page list - verify still open at apply time. Not tailored (2026-10-28): Hightouch auto-rejects candidates who apply to more than 3 roles; tailored rows 391, 393 and 394 instead. Swap with one of those if Jack prefers this role. Hightouch's board moved to Ashby (jobs.ashbyhq.com/hightouch-inc).</t>
+    <t>Hightouch caps at 3 applications per candidate - auto-reject above 3; pick max 3. Direct job page resolves, but role didn't render on the Oct 28 careers-page list - verify still open at apply time. Not tailored (2026-10-28): Hightouch caps candidates at 2 applications; Jack chose rows 393 (Applied AI Research) and 400 (Full Stack Product Engineer). Hightouch's board moved to Ashby (jobs.ashbyhq.com/hightouch-inc).</t>
   </si>
   <si>
     <t>Manager, Solutions Engineering</t>
@@ -5788,7 +5782,7 @@
     <t>Leads SE team; SQL/Python/JS, warehousing, ETL/ELT</t>
   </si>
   <si>
-    <t>Hightouch caps at 3 applications per candidate - auto-reject above 3; pick max 3. Requires proven technical-team management + pre/post-sales client experience. Not tailored (2026-10-28): Hightouch auto-rejects candidates who apply to more than 3 roles; tailored rows 391, 393 and 394 instead. Swap with one of those if Jack prefers this role. Hightouch's board moved to Ashby (jobs.ashbyhq.com/hightouch-inc).</t>
+    <t>Hightouch caps at 3 applications per candidate - auto-reject above 3; pick max 3. Requires proven technical-team management + pre/post-sales client experience. Not tailored (2026-10-28): Hightouch caps candidates at 2 applications; Jack chose rows 393 (Applied AI Research) and 400 (Full Stack Product Engineer). Hightouch's board moved to Ashby (jobs.ashbyhq.com/hightouch-inc).</t>
   </si>
   <si>
     <t>Manager, Solutions Engineering, Mid-Market</t>
@@ -5803,7 +5797,7 @@
     <t>Leads mid-market SE team - EM-adjacent fit</t>
   </si>
   <si>
-    <t>Hightouch caps at 3 applications per candidate - auto-reject above 3; pick max 3. Same management caveat as Manager, Solutions Engineering. Not tailored (2026-10-28): Hightouch auto-rejects candidates who apply to more than 3 roles; tailored rows 391, 393 and 394 instead. Swap with one of those if Jack prefers this role. Hightouch's board moved to Ashby (jobs.ashbyhq.com/hightouch-inc).</t>
+    <t>Hightouch caps at 3 applications per candidate - auto-reject above 3; pick max 3. Same management caveat as Manager, Solutions Engineering. Not tailored (2026-10-28): Hightouch caps candidates at 2 applications; Jack chose rows 393 (Applied AI Research) and 400 (Full Stack Product Engineer). Hightouch's board moved to Ashby (jobs.ashbyhq.com/hightouch-inc).</t>
   </si>
   <si>
     <t>Deployment Architect</t>
@@ -5830,7 +5824,7 @@
     <t>Enterprise email/SMS deployment &amp; migration</t>
   </si>
   <si>
-    <t>Hightouch caps at 3 applications per candidate - auto-reject above 3; pick max 3. Weak fit: niche ESP/messaging domain (10DLC, deliverability, Braze/SFMC), 5-10 yrs in that niche required. Not tailored (2026-10-28): Hightouch auto-rejects candidates who apply to more than 3 roles; tailored rows 391, 393 and 394 instead. Swap with one of those if Jack prefers this role. Hightouch's board moved to Ashby (jobs.ashbyhq.com/hightouch-inc).</t>
+    <t>Hightouch caps at 3 applications per candidate - auto-reject above 3; pick max 3. Weak fit: niche ESP/messaging domain (10DLC, deliverability, Braze/SFMC), 5-10 yrs in that niche required. Not tailored (2026-10-28): Hightouch caps candidates at 2 applications; Jack chose rows 393 (Applied AI Research) and 400 (Full Stack Product Engineer). Hightouch's board moved to Ashby (jobs.ashbyhq.com/hightouch-inc).</t>
   </si>
   <si>
     <t>https://job-boards.greenhouse.io/hightouch/jobs/6011820004</t>
@@ -5842,7 +5836,7 @@
     <t>Partner-facing technical (Snowflake/Databricks/BigQuery); careers site now titles it 'Partner Solutions Engineer'</t>
   </si>
   <si>
-    <t>Hightouch caps at 3 applications per candidate - auto-reject above 3; pick max 3. Partner/alliances focus, up to 30% travel. Not tailored (2026-10-28): Hightouch auto-rejects candidates who apply to more than 3 roles; tailored rows 391, 393 and 394 instead. Swap with one of those if Jack prefers this role. Hightouch's board moved to Ashby (jobs.ashbyhq.com/hightouch-inc).</t>
+    <t>Hightouch caps at 3 applications per candidate - auto-reject above 3; pick max 3. Partner/alliances focus, up to 30% travel. Not tailored (2026-10-28): Hightouch caps candidates at 2 applications; Jack chose rows 393 (Applied AI Research) and 400 (Full Stack Product Engineer). Hightouch's board moved to Ashby (jobs.ashbyhq.com/hightouch-inc).</t>
   </si>
   <si>
     <t>Solutions Engineer, Mid-Market (Pre-Sales)</t>
@@ -5857,7 +5851,7 @@
     <t>Pre-sales SE, data ecosystems</t>
   </si>
   <si>
-    <t>Hightouch caps at 3 applications per candidate - auto-reject above 3; pick max 3. Requires 2+ yrs pre-sales/SE experience - founder/CTO customer work is the closest match; stretch. Not tailored (2026-10-28): Hightouch auto-rejects candidates who apply to more than 3 roles; tailored rows 391, 393 and 394 instead. Swap with one of those if Jack prefers this role. Hightouch's board moved to Ashby (jobs.ashbyhq.com/hightouch-inc).</t>
+    <t>Hightouch caps at 3 applications per candidate - auto-reject above 3; pick max 3. Requires 2+ yrs pre-sales/SE experience - founder/CTO customer work is the closest match; stretch. Not tailored (2026-10-28): Hightouch caps candidates at 2 applications; Jack chose rows 393 (Applied AI Research) and 400 (Full Stack Product Engineer). Hightouch's board moved to Ashby (jobs.ashbyhq.com/hightouch-inc).</t>
   </si>
   <si>
     <t>Senior Backend Engineer - Analytics</t>
@@ -20660,16 +20654,12 @@
         <v>1852</v>
       </c>
       <c r="H391" t="s">
-        <v>336</v>
-      </c>
-      <c r="I391" s="1" t="s">
+        <v>1090</v>
+      </c>
+      <c r="I391" s="1"/>
+      <c r="J391" s="1"/>
+      <c r="L391" t="s">
         <v>1853</v>
-      </c>
-      <c r="J391" s="1" t="s">
-        <v>1854</v>
-      </c>
-      <c r="L391" t="s">
-        <v>1855</v>
       </c>
       <c r="M391" s="1" t="s">
         <v>30</v>
@@ -20686,25 +20676,25 @@
         <v>1847</v>
       </c>
       <c r="B392" t="s">
-        <v>1856</v>
+        <v>1854</v>
       </c>
       <c r="C392" t="s">
         <v>1848</v>
       </c>
       <c r="D392" t="s">
-        <v>1857</v>
+        <v>1855</v>
       </c>
       <c r="E392" t="s">
         <v>1850</v>
       </c>
       <c r="G392" t="s">
-        <v>1858</v>
+        <v>1856</v>
       </c>
       <c r="H392" t="s">
         <v>1090</v>
       </c>
       <c r="L392" t="s">
-        <v>1859</v>
+        <v>1857</v>
       </c>
       <c r="O392" t="s">
         <v>43</v>
@@ -20715,34 +20705,34 @@
         <v>1847</v>
       </c>
       <c r="B393" t="s">
-        <v>1860</v>
+        <v>1858</v>
       </c>
       <c r="C393" t="s">
         <v>1848</v>
       </c>
       <c r="D393" t="s">
-        <v>1861</v>
+        <v>1859</v>
       </c>
       <c r="E393" t="s">
         <v>1497</v>
       </c>
       <c r="F393" t="s">
-        <v>1862</v>
+        <v>1860</v>
       </c>
       <c r="G393" t="s">
-        <v>1863</v>
+        <v>1861</v>
       </c>
       <c r="H393" t="s">
         <v>336</v>
       </c>
       <c r="I393" s="1" t="s">
+        <v>1862</v>
+      </c>
+      <c r="J393" s="1" t="s">
+        <v>1863</v>
+      </c>
+      <c r="L393" t="s">
         <v>1864</v>
-      </c>
-      <c r="J393" s="1" t="s">
-        <v>1865</v>
-      </c>
-      <c r="L393" t="s">
-        <v>1866</v>
       </c>
       <c r="M393" s="1" t="s">
         <v>30</v>
@@ -20759,31 +20749,27 @@
         <v>1847</v>
       </c>
       <c r="B394" t="s">
-        <v>1867</v>
+        <v>1865</v>
       </c>
       <c r="C394" t="s">
         <v>1848</v>
       </c>
       <c r="D394" t="s">
+        <v>1866</v>
+      </c>
+      <c r="E394" t="s">
+        <v>1867</v>
+      </c>
+      <c r="G394" t="s">
         <v>1868</v>
       </c>
-      <c r="E394" t="s">
+      <c r="H394" t="s">
+        <v>1090</v>
+      </c>
+      <c r="I394" s="1"/>
+      <c r="J394" s="1"/>
+      <c r="L394" t="s">
         <v>1869</v>
-      </c>
-      <c r="G394" t="s">
-        <v>1870</v>
-      </c>
-      <c r="H394" t="s">
-        <v>336</v>
-      </c>
-      <c r="I394" s="1" t="s">
-        <v>1871</v>
-      </c>
-      <c r="J394" s="1" t="s">
-        <v>1872</v>
-      </c>
-      <c r="L394" t="s">
-        <v>1873</v>
       </c>
       <c r="M394" s="1" t="s">
         <v>30</v>
@@ -20800,25 +20786,25 @@
         <v>1847</v>
       </c>
       <c r="B395" t="s">
-        <v>1874</v>
+        <v>1870</v>
       </c>
       <c r="C395" t="s">
         <v>1848</v>
       </c>
       <c r="D395" t="s">
-        <v>1875</v>
+        <v>1871</v>
       </c>
       <c r="E395" t="s">
-        <v>1876</v>
+        <v>1872</v>
       </c>
       <c r="G395" t="s">
-        <v>1877</v>
+        <v>1873</v>
       </c>
       <c r="H395" t="s">
         <v>1090</v>
       </c>
       <c r="L395" t="s">
-        <v>1859</v>
+        <v>1857</v>
       </c>
       <c r="O395" t="s">
         <v>43</v>
@@ -20829,25 +20815,25 @@
         <v>1847</v>
       </c>
       <c r="B396" t="s">
-        <v>1878</v>
+        <v>1874</v>
       </c>
       <c r="C396" t="s">
         <v>1848</v>
       </c>
       <c r="D396" t="s">
-        <v>1879</v>
+        <v>1875</v>
       </c>
       <c r="E396" t="s">
+        <v>1872</v>
+      </c>
+      <c r="G396" t="s">
         <v>1876</v>
-      </c>
-      <c r="G396" t="s">
-        <v>1880</v>
       </c>
       <c r="H396" t="s">
         <v>1090</v>
       </c>
       <c r="L396" t="s">
-        <v>1859</v>
+        <v>1857</v>
       </c>
       <c r="O396" t="s">
         <v>43</v>
@@ -20858,25 +20844,25 @@
         <v>1847</v>
       </c>
       <c r="B397" t="s">
-        <v>1881</v>
+        <v>1877</v>
       </c>
       <c r="C397" t="s">
         <v>1848</v>
       </c>
       <c r="D397" t="s">
-        <v>1882</v>
+        <v>1878</v>
       </c>
       <c r="E397" t="s">
-        <v>1883</v>
+        <v>1879</v>
       </c>
       <c r="G397" t="s">
-        <v>1884</v>
+        <v>1880</v>
       </c>
       <c r="H397" t="s">
         <v>1090</v>
       </c>
       <c r="L397" t="s">
-        <v>1885</v>
+        <v>1881</v>
       </c>
       <c r="O397" t="s">
         <v>43</v>
@@ -20887,25 +20873,25 @@
         <v>1847</v>
       </c>
       <c r="B398" t="s">
-        <v>1886</v>
+        <v>1882</v>
       </c>
       <c r="C398" t="s">
         <v>1848</v>
       </c>
       <c r="D398" t="s">
-        <v>1887</v>
+        <v>1883</v>
       </c>
       <c r="E398" t="s">
-        <v>1888</v>
+        <v>1884</v>
       </c>
       <c r="G398" t="s">
-        <v>1889</v>
+        <v>1885</v>
       </c>
       <c r="H398" t="s">
         <v>1090</v>
       </c>
       <c r="L398" t="s">
-        <v>1859</v>
+        <v>1857</v>
       </c>
       <c r="O398" t="s">
         <v>43</v>
@@ -20916,25 +20902,25 @@
         <v>1847</v>
       </c>
       <c r="B399" t="s">
-        <v>1890</v>
+        <v>1886</v>
       </c>
       <c r="C399" t="s">
         <v>1848</v>
       </c>
       <c r="D399" t="s">
-        <v>1891</v>
+        <v>1887</v>
       </c>
       <c r="E399" t="s">
-        <v>1876</v>
+        <v>1872</v>
       </c>
       <c r="G399" t="s">
-        <v>1892</v>
+        <v>1888</v>
       </c>
       <c r="H399" t="s">
         <v>1090</v>
       </c>
       <c r="L399" t="s">
-        <v>1859</v>
+        <v>1857</v>
       </c>
       <c r="O399" t="s">
         <v>43</v>
@@ -20945,25 +20931,37 @@
         <v>1847</v>
       </c>
       <c r="B400" t="s">
-        <v>1893</v>
+        <v>1889</v>
       </c>
       <c r="C400" t="s">
         <v>1848</v>
       </c>
       <c r="D400" t="s">
+        <v>1890</v>
+      </c>
+      <c r="E400" t="s">
+        <v>1891</v>
+      </c>
+      <c r="G400" t="s">
+        <v>1892</v>
+      </c>
+      <c r="H400" t="s">
+        <v>336</v>
+      </c>
+      <c r="I400" s="1" t="s">
+        <v>1893</v>
+      </c>
+      <c r="J400" s="1" t="s">
         <v>1894</v>
       </c>
-      <c r="E400" t="s">
+      <c r="L400" t="s">
         <v>1895</v>
       </c>
-      <c r="G400" t="s">
-        <v>1896</v>
-      </c>
-      <c r="H400" t="s">
-        <v>1090</v>
-      </c>
-      <c r="L400" t="s">
-        <v>1897</v>
+      <c r="M400" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="N400" s="1" t="s">
+        <v>38</v>
       </c>
       <c r="O400" t="s">
         <v>43</v>
@@ -20974,25 +20972,25 @@
         <v>1847</v>
       </c>
       <c r="B401" t="s">
-        <v>1898</v>
+        <v>1896</v>
       </c>
       <c r="C401" t="s">
         <v>1848</v>
       </c>
       <c r="D401" t="s">
+        <v>1897</v>
+      </c>
+      <c r="E401" t="s">
+        <v>1898</v>
+      </c>
+      <c r="G401" t="s">
         <v>1899</v>
-      </c>
-      <c r="E401" t="s">
-        <v>1900</v>
-      </c>
-      <c r="G401" t="s">
-        <v>1901</v>
       </c>
       <c r="H401" t="s">
         <v>1090</v>
       </c>
       <c r="L401" t="s">
-        <v>1859</v>
+        <v>1857</v>
       </c>
       <c r="O401" t="s">
         <v>43</v>
@@ -21003,25 +21001,25 @@
         <v>1847</v>
       </c>
       <c r="B402" t="s">
-        <v>1902</v>
+        <v>1900</v>
       </c>
       <c r="C402" t="s">
         <v>1848</v>
       </c>
       <c r="D402" t="s">
-        <v>1903</v>
+        <v>1901</v>
       </c>
       <c r="E402" t="s">
         <v>1705</v>
       </c>
       <c r="G402" t="s">
-        <v>1904</v>
+        <v>1902</v>
       </c>
       <c r="H402" t="s">
         <v>1090</v>
       </c>
       <c r="L402" t="s">
-        <v>1905</v>
+        <v>1903</v>
       </c>
       <c r="O402" t="s">
         <v>43</v>
@@ -21032,25 +21030,25 @@
         <v>1847</v>
       </c>
       <c r="B403" t="s">
-        <v>1906</v>
+        <v>1904</v>
       </c>
       <c r="C403" t="s">
         <v>1848</v>
       </c>
       <c r="D403" t="s">
-        <v>1907</v>
+        <v>1905</v>
       </c>
       <c r="E403" t="s">
         <v>1705</v>
       </c>
       <c r="G403" t="s">
-        <v>1908</v>
+        <v>1906</v>
       </c>
       <c r="H403" t="s">
         <v>1090</v>
       </c>
       <c r="L403" t="s">
-        <v>1859</v>
+        <v>1857</v>
       </c>
       <c r="O403" t="s">
         <v>43</v>
@@ -21061,25 +21059,25 @@
         <v>1847</v>
       </c>
       <c r="B404" t="s">
-        <v>1909</v>
+        <v>1907</v>
       </c>
       <c r="C404" t="s">
         <v>1848</v>
       </c>
       <c r="D404" t="s">
-        <v>1910</v>
+        <v>1908</v>
       </c>
       <c r="E404" t="s">
         <v>1705</v>
       </c>
       <c r="G404" t="s">
-        <v>1911</v>
+        <v>1909</v>
       </c>
       <c r="H404" t="s">
         <v>1090</v>
       </c>
       <c r="L404" t="s">
-        <v>1859</v>
+        <v>1857</v>
       </c>
       <c r="O404" t="s">
         <v>43</v>
@@ -21090,28 +21088,28 @@
         <v>1847</v>
       </c>
       <c r="B405" t="s">
-        <v>1912</v>
+        <v>1910</v>
       </c>
       <c r="C405" t="s">
         <v>1848</v>
       </c>
       <c r="D405" t="s">
+        <v>1911</v>
+      </c>
+      <c r="E405" t="s">
+        <v>1912</v>
+      </c>
+      <c r="F405" t="s">
         <v>1913</v>
       </c>
-      <c r="E405" t="s">
+      <c r="G405" t="s">
         <v>1914</v>
-      </c>
-      <c r="F405" t="s">
-        <v>1915</v>
-      </c>
-      <c r="G405" t="s">
-        <v>1916</v>
       </c>
       <c r="H405" t="s">
         <v>1090</v>
       </c>
       <c r="L405" t="s">
-        <v>1917</v>
+        <v>1915</v>
       </c>
       <c r="O405" t="s">
         <v>43</v>
@@ -21122,28 +21120,28 @@
         <v>1847</v>
       </c>
       <c r="B406" t="s">
-        <v>1918</v>
+        <v>1916</v>
       </c>
       <c r="C406" t="s">
         <v>1848</v>
       </c>
       <c r="D406" t="s">
+        <v>1917</v>
+      </c>
+      <c r="E406" t="s">
+        <v>1918</v>
+      </c>
+      <c r="F406" t="s">
         <v>1919</v>
       </c>
-      <c r="E406" t="s">
+      <c r="G406" t="s">
         <v>1920</v>
-      </c>
-      <c r="F406" t="s">
-        <v>1921</v>
-      </c>
-      <c r="G406" t="s">
-        <v>1922</v>
       </c>
       <c r="H406" t="s">
         <v>1090</v>
       </c>
       <c r="L406" t="s">
-        <v>1923</v>
+        <v>1921</v>
       </c>
       <c r="O406" t="s">
         <v>43</v>
@@ -21154,25 +21152,25 @@
         <v>1847</v>
       </c>
       <c r="B407" t="s">
-        <v>1924</v>
+        <v>1922</v>
       </c>
       <c r="C407" t="s">
         <v>1848</v>
       </c>
       <c r="D407" t="s">
+        <v>1923</v>
+      </c>
+      <c r="E407" t="s">
+        <v>1924</v>
+      </c>
+      <c r="G407" t="s">
         <v>1925</v>
-      </c>
-      <c r="E407" t="s">
-        <v>1926</v>
-      </c>
-      <c r="G407" t="s">
-        <v>1927</v>
       </c>
       <c r="H407" t="s">
         <v>1090</v>
       </c>
       <c r="L407" t="s">
-        <v>1928</v>
+        <v>1926</v>
       </c>
       <c r="O407" t="s">
         <v>43</v>
@@ -21183,25 +21181,25 @@
         <v>1847</v>
       </c>
       <c r="B408" t="s">
-        <v>1929</v>
+        <v>1927</v>
       </c>
       <c r="C408" t="s">
         <v>1848</v>
       </c>
       <c r="D408" t="s">
+        <v>1928</v>
+      </c>
+      <c r="E408" t="s">
+        <v>1929</v>
+      </c>
+      <c r="G408" t="s">
         <v>1930</v>
-      </c>
-      <c r="E408" t="s">
-        <v>1931</v>
-      </c>
-      <c r="G408" t="s">
-        <v>1932</v>
       </c>
       <c r="H408" t="s">
         <v>1090</v>
       </c>
       <c r="L408" t="s">
-        <v>1859</v>
+        <v>1857</v>
       </c>
       <c r="O408" t="s">
         <v>43</v>
@@ -21212,28 +21210,28 @@
         <v>1847</v>
       </c>
       <c r="B409" t="s">
-        <v>1933</v>
+        <v>1931</v>
       </c>
       <c r="C409" t="s">
         <v>1848</v>
       </c>
       <c r="D409" t="s">
-        <v>1934</v>
+        <v>1932</v>
       </c>
       <c r="E409" t="s">
         <v>1791</v>
       </c>
       <c r="F409" t="s">
-        <v>1935</v>
+        <v>1933</v>
       </c>
       <c r="G409" t="s">
-        <v>1936</v>
+        <v>1934</v>
       </c>
       <c r="H409" t="s">
         <v>1090</v>
       </c>
       <c r="L409" t="s">
-        <v>1937</v>
+        <v>1935</v>
       </c>
       <c r="O409" t="s">
         <v>43</v>
@@ -21250,19 +21248,19 @@
         <v>1848</v>
       </c>
       <c r="D410" t="s">
+        <v>1936</v>
+      </c>
+      <c r="E410" t="s">
+        <v>1937</v>
+      </c>
+      <c r="G410" t="s">
         <v>1938</v>
-      </c>
-      <c r="E410" t="s">
-        <v>1939</v>
-      </c>
-      <c r="G410" t="s">
-        <v>1940</v>
       </c>
       <c r="H410" t="s">
         <v>1090</v>
       </c>
       <c r="L410" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="O410" t="s">
         <v>43</v>
@@ -21273,25 +21271,25 @@
         <v>1847</v>
       </c>
       <c r="B411" t="s">
-        <v>1942</v>
+        <v>1940</v>
       </c>
       <c r="C411" t="s">
         <v>1848</v>
       </c>
       <c r="D411" t="s">
+        <v>1941</v>
+      </c>
+      <c r="E411" t="s">
+        <v>1942</v>
+      </c>
+      <c r="G411" t="s">
         <v>1943</v>
-      </c>
-      <c r="E411" t="s">
-        <v>1944</v>
-      </c>
-      <c r="G411" t="s">
-        <v>1945</v>
       </c>
       <c r="H411" t="s">
         <v>1090</v>
       </c>
       <c r="L411" t="s">
-        <v>1946</v>
+        <v>1944</v>
       </c>
       <c r="O411" t="s">
         <v>43</v>
@@ -21302,29 +21300,29 @@
         <v>65</v>
       </c>
       <c r="B412" t="s">
-        <v>1947</v>
+        <v>1945</v>
       </c>
       <c r="C412" t="s">
         <v>126</v>
       </c>
       <c r="D412" t="s">
-        <v>1948</v>
+        <v>1946</v>
       </c>
       <c r="E412" t="s">
         <v>1801</v>
       </c>
       <c r="G412" t="s">
-        <v>1949</v>
+        <v>1947</v>
       </c>
       <c r="H412" t="s">
         <v>336</v>
       </c>
       <c r="I412" s="1" t="s">
-        <v>1950</v>
+        <v>1948</v>
       </c>
       <c r="J412" s="1"/>
       <c r="L412" s="1" t="s">
-        <v>1951</v>
+        <v>1949</v>
       </c>
       <c r="M412" s="1" t="s">
         <v>69</v>
@@ -21341,29 +21339,29 @@
         <v>65</v>
       </c>
       <c r="B413" t="s">
-        <v>1952</v>
+        <v>1950</v>
       </c>
       <c r="C413" t="s">
         <v>126</v>
       </c>
       <c r="D413" t="s">
-        <v>1953</v>
+        <v>1951</v>
       </c>
       <c r="E413" t="s">
         <v>1380</v>
       </c>
       <c r="G413" t="s">
-        <v>1954</v>
+        <v>1952</v>
       </c>
       <c r="H413" t="s">
         <v>336</v>
       </c>
       <c r="I413" s="1" t="s">
-        <v>1955</v>
+        <v>1953</v>
       </c>
       <c r="J413" s="1"/>
       <c r="L413" s="1" t="s">
-        <v>1956</v>
+        <v>1954</v>
       </c>
       <c r="M413" s="1" t="s">
         <v>69</v>
@@ -21380,29 +21378,29 @@
         <v>65</v>
       </c>
       <c r="B414" t="s">
-        <v>1957</v>
+        <v>1955</v>
       </c>
       <c r="C414" t="s">
         <v>126</v>
       </c>
       <c r="D414" t="s">
-        <v>1958</v>
+        <v>1956</v>
       </c>
       <c r="E414" t="s">
         <v>1224</v>
       </c>
       <c r="G414" t="s">
-        <v>1959</v>
+        <v>1957</v>
       </c>
       <c r="H414" t="s">
         <v>336</v>
       </c>
       <c r="I414" s="1" t="s">
-        <v>1960</v>
+        <v>1958</v>
       </c>
       <c r="J414" s="1"/>
       <c r="L414" t="s">
-        <v>1961</v>
+        <v>1959</v>
       </c>
       <c r="M414" s="1" t="s">
         <v>69</v>
@@ -21419,29 +21417,29 @@
         <v>65</v>
       </c>
       <c r="B415" t="s">
-        <v>1962</v>
+        <v>1960</v>
       </c>
       <c r="C415" t="s">
         <v>126</v>
       </c>
       <c r="D415" t="s">
-        <v>1963</v>
+        <v>1961</v>
       </c>
       <c r="E415" t="s">
         <v>1224</v>
       </c>
       <c r="G415" t="s">
-        <v>1964</v>
+        <v>1962</v>
       </c>
       <c r="H415" t="s">
         <v>336</v>
       </c>
       <c r="I415" s="1" t="s">
-        <v>1965</v>
+        <v>1963</v>
       </c>
       <c r="J415" s="1"/>
       <c r="L415" t="s">
-        <v>1966</v>
+        <v>1964</v>
       </c>
       <c r="M415" s="1" t="s">
         <v>69</v>
@@ -21458,29 +21456,29 @@
         <v>65</v>
       </c>
       <c r="B416" t="s">
-        <v>1967</v>
+        <v>1965</v>
       </c>
       <c r="C416" t="s">
         <v>126</v>
       </c>
       <c r="D416" t="s">
+        <v>1966</v>
+      </c>
+      <c r="E416" t="s">
+        <v>1967</v>
+      </c>
+      <c r="G416" t="s">
         <v>1968</v>
-      </c>
-      <c r="E416" t="s">
-        <v>1969</v>
-      </c>
-      <c r="G416" t="s">
-        <v>1970</v>
       </c>
       <c r="H416" t="s">
         <v>336</v>
       </c>
       <c r="I416" s="1" t="s">
-        <v>1971</v>
+        <v>1969</v>
       </c>
       <c r="J416" s="1"/>
       <c r="L416" t="s">
-        <v>1972</v>
+        <v>1970</v>
       </c>
       <c r="M416" s="1" t="s">
         <v>69</v>
@@ -21497,25 +21495,25 @@
         <v>65</v>
       </c>
       <c r="B417" t="s">
-        <v>1973</v>
+        <v>1971</v>
       </c>
       <c r="C417" t="s">
         <v>126</v>
       </c>
       <c r="D417" t="s">
-        <v>1974</v>
+        <v>1972</v>
       </c>
       <c r="E417" t="s">
         <v>1422</v>
       </c>
       <c r="G417" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="H417" t="s">
         <v>1090</v>
       </c>
       <c r="L417" t="s">
-        <v>1976</v>
+        <v>1974</v>
       </c>
       <c r="O417" t="s">
         <v>43</v>
@@ -21526,29 +21524,29 @@
         <v>65</v>
       </c>
       <c r="B418" t="s">
-        <v>1977</v>
+        <v>1975</v>
       </c>
       <c r="C418" t="s">
         <v>126</v>
       </c>
       <c r="D418" t="s">
-        <v>1978</v>
+        <v>1976</v>
       </c>
       <c r="E418" t="s">
         <v>1407</v>
       </c>
       <c r="G418" t="s">
-        <v>1979</v>
+        <v>1977</v>
       </c>
       <c r="H418" t="s">
         <v>336</v>
       </c>
       <c r="I418" s="1" t="s">
-        <v>1980</v>
+        <v>1978</v>
       </c>
       <c r="J418" s="1"/>
       <c r="L418" t="s">
-        <v>1981</v>
+        <v>1979</v>
       </c>
       <c r="M418" s="1" t="s">
         <v>69</v>
@@ -21565,25 +21563,25 @@
         <v>65</v>
       </c>
       <c r="B419" t="s">
-        <v>1982</v>
+        <v>1980</v>
       </c>
       <c r="C419" t="s">
         <v>126</v>
       </c>
       <c r="D419" t="s">
+        <v>1981</v>
+      </c>
+      <c r="E419" t="s">
+        <v>1982</v>
+      </c>
+      <c r="G419" t="s">
         <v>1983</v>
-      </c>
-      <c r="E419" t="s">
-        <v>1984</v>
-      </c>
-      <c r="G419" t="s">
-        <v>1985</v>
       </c>
       <c r="H419" t="s">
         <v>36</v>
       </c>
       <c r="L419" t="s">
-        <v>1986</v>
+        <v>1984</v>
       </c>
       <c r="O419" t="s">
         <v>43</v>
@@ -21594,29 +21592,29 @@
         <v>65</v>
       </c>
       <c r="B420" t="s">
-        <v>1987</v>
+        <v>1985</v>
       </c>
       <c r="C420" t="s">
         <v>126</v>
       </c>
       <c r="D420" t="s">
+        <v>1986</v>
+      </c>
+      <c r="E420" t="s">
+        <v>1987</v>
+      </c>
+      <c r="G420" t="s">
         <v>1988</v>
-      </c>
-      <c r="E420" t="s">
-        <v>1989</v>
-      </c>
-      <c r="G420" t="s">
-        <v>1990</v>
       </c>
       <c r="H420" t="s">
         <v>336</v>
       </c>
       <c r="I420" s="1" t="s">
-        <v>1991</v>
+        <v>1989</v>
       </c>
       <c r="J420" s="1"/>
       <c r="L420" s="1" t="s">
-        <v>1992</v>
+        <v>1990</v>
       </c>
       <c r="M420" s="1" t="s">
         <v>69</v>
@@ -21633,29 +21631,29 @@
         <v>65</v>
       </c>
       <c r="B421" t="s">
-        <v>1993</v>
+        <v>1991</v>
       </c>
       <c r="C421" t="s">
         <v>126</v>
       </c>
       <c r="D421" t="s">
-        <v>1994</v>
+        <v>1992</v>
       </c>
       <c r="E421" t="s">
         <v>1380</v>
       </c>
       <c r="G421" t="s">
-        <v>1995</v>
+        <v>1993</v>
       </c>
       <c r="H421" t="s">
         <v>336</v>
       </c>
       <c r="I421" s="1" t="s">
-        <v>1996</v>
+        <v>1994</v>
       </c>
       <c r="J421" s="1"/>
       <c r="L421" t="s">
-        <v>1997</v>
+        <v>1995</v>
       </c>
       <c r="M421" s="1" t="s">
         <v>69</v>
@@ -21672,29 +21670,29 @@
         <v>65</v>
       </c>
       <c r="B422" t="s">
-        <v>1998</v>
+        <v>1996</v>
       </c>
       <c r="C422" t="s">
         <v>126</v>
       </c>
       <c r="D422" t="s">
-        <v>1999</v>
+        <v>1997</v>
       </c>
       <c r="E422" t="s">
         <v>1224</v>
       </c>
       <c r="G422" t="s">
-        <v>2000</v>
+        <v>1998</v>
       </c>
       <c r="H422" t="s">
         <v>336</v>
       </c>
       <c r="I422" s="1" t="s">
-        <v>2001</v>
+        <v>1999</v>
       </c>
       <c r="J422" s="1"/>
       <c r="L422" s="1" t="s">
-        <v>2002</v>
+        <v>2000</v>
       </c>
       <c r="M422" s="1" t="s">
         <v>69</v>
@@ -21711,25 +21709,25 @@
         <v>65</v>
       </c>
       <c r="B423" t="s">
-        <v>2003</v>
+        <v>2001</v>
       </c>
       <c r="C423" t="s">
         <v>126</v>
       </c>
       <c r="D423" t="s">
-        <v>2004</v>
+        <v>2002</v>
       </c>
       <c r="E423" t="s">
         <v>1850</v>
       </c>
       <c r="G423" t="s">
-        <v>2005</v>
+        <v>2003</v>
       </c>
       <c r="H423" t="s">
         <v>36</v>
       </c>
       <c r="L423" s="1" t="s">
-        <v>2006</v>
+        <v>2004</v>
       </c>
       <c r="O423" t="s">
         <v>43</v>
@@ -21740,25 +21738,25 @@
         <v>65</v>
       </c>
       <c r="B424" t="s">
+        <v>2005</v>
+      </c>
+      <c r="C424" t="s">
+        <v>2006</v>
+      </c>
+      <c r="D424" t="s">
         <v>2007</v>
       </c>
-      <c r="C424" t="s">
+      <c r="E424" t="s">
         <v>2008</v>
       </c>
-      <c r="D424" t="s">
+      <c r="G424" t="s">
         <v>2009</v>
-      </c>
-      <c r="E424" t="s">
-        <v>2010</v>
-      </c>
-      <c r="G424" t="s">
-        <v>2011</v>
       </c>
       <c r="H424" t="s">
         <v>1090</v>
       </c>
       <c r="L424" s="1" t="s">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="O424" t="s">
         <v>43</v>
@@ -21769,25 +21767,25 @@
         <v>65</v>
       </c>
       <c r="B425" t="s">
+        <v>2011</v>
+      </c>
+      <c r="C425" t="s">
+        <v>2012</v>
+      </c>
+      <c r="D425" t="s">
         <v>2013</v>
-      </c>
-      <c r="C425" t="s">
-        <v>2014</v>
-      </c>
-      <c r="D425" t="s">
-        <v>2015</v>
       </c>
       <c r="E425" t="s">
         <v>1224</v>
       </c>
       <c r="G425" t="s">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="H425" t="s">
         <v>1090</v>
       </c>
       <c r="L425" t="s">
-        <v>2017</v>
+        <v>2015</v>
       </c>
       <c r="O425" t="s">
         <v>43</v>
@@ -21798,25 +21796,25 @@
         <v>65</v>
       </c>
       <c r="B426" t="s">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="C426" t="s">
         <v>126</v>
       </c>
       <c r="D426" t="s">
-        <v>2019</v>
+        <v>2017</v>
       </c>
       <c r="E426" t="s">
         <v>1380</v>
       </c>
       <c r="G426" t="s">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="H426" t="s">
         <v>1090</v>
       </c>
       <c r="L426" s="1" t="s">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="O426" t="s">
         <v>43</v>
@@ -21827,25 +21825,25 @@
         <v>65</v>
       </c>
       <c r="B427" t="s">
+        <v>2020</v>
+      </c>
+      <c r="C427" t="s">
+        <v>2021</v>
+      </c>
+      <c r="D427" t="s">
         <v>2022</v>
       </c>
-      <c r="C427" t="s">
+      <c r="E427" t="s">
         <v>2023</v>
       </c>
-      <c r="D427" t="s">
+      <c r="G427" t="s">
         <v>2024</v>
-      </c>
-      <c r="E427" t="s">
-        <v>2025</v>
-      </c>
-      <c r="G427" t="s">
-        <v>2026</v>
       </c>
       <c r="H427" t="s">
         <v>1090</v>
       </c>
       <c r="L427" t="s">
-        <v>2027</v>
+        <v>2025</v>
       </c>
       <c r="O427" t="s">
         <v>43</v>
@@ -21859,31 +21857,31 @@
         <v>1396</v>
       </c>
       <c r="C428" t="s">
+        <v>2026</v>
+      </c>
+      <c r="D428" t="s">
+        <v>2027</v>
+      </c>
+      <c r="E428" t="s">
         <v>2028</v>
       </c>
-      <c r="D428" t="s">
+      <c r="F428" t="s">
         <v>2029</v>
       </c>
-      <c r="E428" t="s">
+      <c r="G428" t="s">
         <v>2030</v>
-      </c>
-      <c r="F428" t="s">
-        <v>2031</v>
-      </c>
-      <c r="G428" t="s">
-        <v>2032</v>
       </c>
       <c r="H428" t="s">
         <v>336</v>
       </c>
       <c r="I428" s="1" t="s">
+        <v>2031</v>
+      </c>
+      <c r="J428" s="1" t="s">
+        <v>2032</v>
+      </c>
+      <c r="L428" t="s">
         <v>2033</v>
-      </c>
-      <c r="J428" s="1" t="s">
-        <v>2034</v>
-      </c>
-      <c r="L428" t="s">
-        <v>2035</v>
       </c>
       <c r="M428" s="1" t="s">
         <v>30</v>
@@ -21897,64 +21895,64 @@
     </row>
     <row r="429" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
-        <v>2036</v>
+        <v>2034</v>
       </c>
       <c r="B429" t="s">
-        <v>2037</v>
+        <v>2035</v>
       </c>
       <c r="C429" t="s">
         <v>824</v>
       </c>
       <c r="D429" t="s">
+        <v>2036</v>
+      </c>
+      <c r="E429" t="s">
+        <v>2037</v>
+      </c>
+      <c r="F429" t="s">
         <v>2038</v>
       </c>
-      <c r="E429" t="s">
+      <c r="G429" t="s">
         <v>2039</v>
-      </c>
-      <c r="F429" t="s">
-        <v>2040</v>
-      </c>
-      <c r="G429" t="s">
-        <v>2041</v>
       </c>
       <c r="H429" t="s">
         <v>1090</v>
       </c>
       <c r="L429" s="1" t="s">
-        <v>2042</v>
+        <v>2040</v>
       </c>
     </row>
     <row r="430" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
-        <v>2043</v>
+        <v>2041</v>
       </c>
       <c r="B430" t="s">
-        <v>2044</v>
+        <v>2042</v>
       </c>
       <c r="C430" t="s">
         <v>830</v>
       </c>
       <c r="D430" t="s">
+        <v>2043</v>
+      </c>
+      <c r="E430" t="s">
+        <v>2044</v>
+      </c>
+      <c r="F430" t="s">
         <v>2045</v>
       </c>
-      <c r="E430" t="s">
+      <c r="G430" t="s">
         <v>2046</v>
-      </c>
-      <c r="F430" t="s">
-        <v>2047</v>
-      </c>
-      <c r="G430" t="s">
-        <v>2048</v>
       </c>
       <c r="H430" t="s">
         <v>336</v>
       </c>
       <c r="I430" s="1" t="s">
-        <v>2049</v>
+        <v>2047</v>
       </c>
       <c r="J430" s="1"/>
       <c r="L430" s="1" t="s">
-        <v>2050</v>
+        <v>2048</v>
       </c>
       <c r="M430" s="1" t="s">
         <v>22</v>
